--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -668,7 +668,7 @@
             <v>3</v>
           </cell>
           <cell r="M16">
-            <v>90000</v>
+            <v>790000</v>
           </cell>
         </row>
         <row r="17">
@@ -1009,7 +1009,7 @@
             <v>3</v>
           </cell>
           <cell r="M47">
-            <v>277000</v>
+            <v>662000</v>
           </cell>
         </row>
         <row r="48">
@@ -1020,7 +1020,7 @@
             <v>0</v>
           </cell>
           <cell r="M48">
-            <v>300000</v>
+            <v>685000</v>
           </cell>
         </row>
         <row r="49">
@@ -1031,7 +1031,7 @@
             <v>0</v>
           </cell>
           <cell r="M49">
-            <v>145000</v>
+            <v>530000</v>
           </cell>
         </row>
         <row r="50">
@@ -1042,7 +1042,7 @@
             <v>0</v>
           </cell>
           <cell r="M50">
-            <v>3200000</v>
+            <v>3368000</v>
           </cell>
         </row>
         <row r="51">
@@ -1053,7 +1053,7 @@
             <v>0</v>
           </cell>
           <cell r="M51">
-            <v>2650000</v>
+            <v>2909000</v>
           </cell>
         </row>
         <row r="52">
@@ -1064,7 +1064,7 @@
             <v>0</v>
           </cell>
           <cell r="M52">
-            <v>2495000</v>
+            <v>2663000</v>
           </cell>
         </row>
         <row r="53">
@@ -1075,7 +1075,7 @@
             <v>0</v>
           </cell>
           <cell r="M53">
-            <v>2650000</v>
+            <v>3035000</v>
           </cell>
         </row>
         <row r="54">
@@ -1086,7 +1086,7 @@
             <v>0</v>
           </cell>
           <cell r="M54">
-            <v>3380000</v>
+            <v>3496000</v>
           </cell>
         </row>
         <row r="55">
@@ -1097,7 +1097,7 @@
             <v>0</v>
           </cell>
           <cell r="M55">
-            <v>3222000</v>
+            <v>3280000</v>
           </cell>
         </row>
         <row r="56">
@@ -1141,7 +1141,7 @@
             <v>0</v>
           </cell>
           <cell r="M59">
-            <v>145000</v>
+            <v>313000</v>
           </cell>
         </row>
         <row r="60">
@@ -1361,7 +1361,7 @@
             <v>0</v>
           </cell>
           <cell r="M79">
-            <v>285000</v>
+            <v>402000</v>
           </cell>
         </row>
         <row r="80">
@@ -1416,7 +1416,7 @@
             <v>0</v>
           </cell>
           <cell r="M84">
-            <v>458400</v>
+            <v>511200</v>
           </cell>
         </row>
         <row r="85">
@@ -1427,7 +1427,7 @@
             <v>0</v>
           </cell>
           <cell r="M85">
-            <v>158400</v>
+            <v>396000</v>
           </cell>
         </row>
         <row r="86">
@@ -1438,7 +1438,7 @@
             <v>0</v>
           </cell>
           <cell r="M86">
-            <v>2000800</v>
+            <v>2700800</v>
           </cell>
         </row>
         <row r="87">
@@ -1471,7 +1471,7 @@
             <v>0</v>
           </cell>
           <cell r="M89">
-            <v>617000</v>
+            <v>734000</v>
           </cell>
         </row>
         <row r="90">
@@ -1482,7 +1482,7 @@
             <v>0</v>
           </cell>
           <cell r="M90">
-            <v>110400</v>
+            <v>227400</v>
           </cell>
         </row>
         <row r="91">
@@ -1493,7 +1493,7 @@
             <v>0</v>
           </cell>
           <cell r="M91">
-            <v>52800</v>
+            <v>105600</v>
           </cell>
         </row>
         <row r="92">
@@ -1504,7 +1504,7 @@
             <v>0</v>
           </cell>
           <cell r="M92">
-            <v>66000</v>
+            <v>118800</v>
           </cell>
         </row>
         <row r="93">
@@ -1512,10 +1512,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I93">
-            <v>0</v>
+            <v>19</v>
           </cell>
           <cell r="M93">
-            <v>52800</v>
+            <v>105600</v>
           </cell>
         </row>
         <row r="94">
@@ -1526,7 +1526,7 @@
             <v>0</v>
           </cell>
           <cell r="M94">
-            <v>518000</v>
+            <v>723600</v>
           </cell>
         </row>
         <row r="95">
@@ -1537,7 +1537,7 @@
             <v>0</v>
           </cell>
           <cell r="M95">
-            <v>220800</v>
+            <v>273600</v>
           </cell>
         </row>
         <row r="96">
@@ -1548,7 +1548,7 @@
             <v>1</v>
           </cell>
           <cell r="M96">
-            <v>271200</v>
+            <v>376800</v>
           </cell>
         </row>
         <row r="97">
@@ -1559,7 +1559,7 @@
             <v>0</v>
           </cell>
           <cell r="M97">
-            <v>273600</v>
+            <v>326400</v>
           </cell>
         </row>
         <row r="98">
@@ -1570,7 +1570,7 @@
             <v>0</v>
           </cell>
           <cell r="M98">
-            <v>132000</v>
+            <v>632000</v>
           </cell>
         </row>
         <row r="99">
@@ -1578,10 +1578,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I99">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="M99">
-            <v>52800</v>
+            <v>105600</v>
           </cell>
         </row>
         <row r="100">
@@ -1592,7 +1592,7 @@
             <v>0</v>
           </cell>
           <cell r="M100">
-            <v>2038400</v>
+            <v>2238400</v>
           </cell>
         </row>
         <row r="101">
@@ -1603,7 +1603,7 @@
             <v>0</v>
           </cell>
           <cell r="M101">
-            <v>1552800</v>
+            <v>1605600</v>
           </cell>
         </row>
         <row r="102">
@@ -1614,7 +1614,7 @@
             <v>0</v>
           </cell>
           <cell r="M102">
-            <v>169200</v>
+            <v>222000</v>
           </cell>
         </row>
         <row r="103">
@@ -1633,7 +1633,7 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I104">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M104">
             <v>2168000</v>
@@ -1647,7 +1647,7 @@
             <v>3</v>
           </cell>
           <cell r="M105">
-            <v>2402500</v>
+            <v>2519500</v>
           </cell>
         </row>
         <row r="106">
@@ -1669,7 +1669,7 @@
             <v>0</v>
           </cell>
           <cell r="M107">
-            <v>223200</v>
+            <v>276000</v>
           </cell>
         </row>
         <row r="108">
@@ -1680,7 +1680,7 @@
             <v>0</v>
           </cell>
           <cell r="M108">
-            <v>1220800</v>
+            <v>1273600</v>
           </cell>
         </row>
         <row r="109">
@@ -1702,7 +1702,7 @@
             <v>0</v>
           </cell>
           <cell r="M110">
-            <v>220800</v>
+            <v>273600</v>
           </cell>
         </row>
         <row r="111">
@@ -1710,7 +1710,7 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I111">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="M111">
             <v>368400</v>
@@ -1735,7 +1735,7 @@
             <v>3</v>
           </cell>
           <cell r="M113">
-            <v>680800</v>
+            <v>1012800</v>
           </cell>
         </row>
         <row r="114">
@@ -1779,7 +1779,7 @@
             <v>1</v>
           </cell>
           <cell r="M117">
-            <v>658400</v>
+            <v>858400</v>
           </cell>
         </row>
         <row r="118">
@@ -1834,7 +1834,7 @@
             <v>3</v>
           </cell>
           <cell r="M122">
-            <v>1088500</v>
+            <v>1205500</v>
           </cell>
         </row>
         <row r="123">
@@ -1856,7 +1856,7 @@
             <v>3</v>
           </cell>
           <cell r="M124">
-            <v>361200</v>
+            <v>414000</v>
           </cell>
         </row>
         <row r="125">
@@ -1878,7 +1878,7 @@
             <v>0</v>
           </cell>
           <cell r="M126">
-            <v>989200</v>
+            <v>1106200</v>
           </cell>
         </row>
         <row r="127">
@@ -1889,7 +1889,7 @@
             <v>0</v>
           </cell>
           <cell r="M127">
-            <v>3368800</v>
+            <v>3485800</v>
           </cell>
         </row>
         <row r="128">
@@ -1900,7 +1900,7 @@
             <v>0</v>
           </cell>
           <cell r="M128">
-            <v>355200</v>
+            <v>408000</v>
           </cell>
         </row>
         <row r="129">
@@ -1933,7 +1933,7 @@
             <v>0</v>
           </cell>
           <cell r="M131">
-            <v>500000</v>
+            <v>1000000</v>
           </cell>
         </row>
         <row r="132">
@@ -1944,7 +1944,7 @@
             <v>2</v>
           </cell>
           <cell r="M132">
-            <v>3770000</v>
+            <v>3887000</v>
           </cell>
         </row>
         <row r="133">
@@ -1955,7 +1955,7 @@
             <v>0</v>
           </cell>
           <cell r="M133">
-            <v>0</v>
+            <v>117000</v>
           </cell>
         </row>
         <row r="134">
@@ -1966,7 +1966,7 @@
             <v>0</v>
           </cell>
           <cell r="M134">
-            <v>224400</v>
+            <v>356400</v>
           </cell>
         </row>
         <row r="135">
@@ -1988,7 +1988,7 @@
             <v>3</v>
           </cell>
           <cell r="M136">
-            <v>361200</v>
+            <v>493200</v>
           </cell>
         </row>
         <row r="137">
@@ -2010,7 +2010,7 @@
             <v>0</v>
           </cell>
           <cell r="M138">
-            <v>1000000</v>
+            <v>1450000</v>
           </cell>
         </row>
         <row r="139">
@@ -2032,7 +2032,7 @@
             <v>0</v>
           </cell>
           <cell r="M140">
-            <v>617000</v>
+            <v>734000</v>
           </cell>
         </row>
         <row r="141">
@@ -2054,7 +2054,7 @@
             <v>0</v>
           </cell>
           <cell r="M142">
-            <v>168000</v>
+            <v>285000</v>
           </cell>
         </row>
         <row r="143">
@@ -2073,10 +2073,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I144">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M144">
-            <v>780000</v>
+            <v>897000</v>
           </cell>
         </row>
         <row r="145">
@@ -2098,7 +2098,7 @@
             <v>0</v>
           </cell>
           <cell r="M146">
-            <v>324900</v>
+            <v>628500</v>
           </cell>
         </row>
         <row r="147">
@@ -2109,7 +2109,7 @@
             <v>0</v>
           </cell>
           <cell r="M147">
-            <v>324900</v>
+            <v>681300</v>
           </cell>
         </row>
         <row r="148">
@@ -2120,7 +2120,7 @@
             <v>0</v>
           </cell>
           <cell r="M148">
-            <v>0</v>
+            <v>303600</v>
           </cell>
         </row>
         <row r="149">
@@ -2131,7 +2131,7 @@
             <v>0</v>
           </cell>
           <cell r="M149">
-            <v>0</v>
+            <v>1316800</v>
           </cell>
         </row>
         <row r="150">
@@ -2142,7 +2142,7 @@
             <v>0</v>
           </cell>
           <cell r="M150">
-            <v>132000</v>
+            <v>411000</v>
           </cell>
         </row>
         <row r="151">
@@ -2153,7 +2153,7 @@
             <v>2</v>
           </cell>
           <cell r="M151">
-            <v>132000</v>
+            <v>300000</v>
           </cell>
         </row>
         <row r="152">
@@ -2164,7 +2164,7 @@
             <v>1</v>
           </cell>
           <cell r="M152">
-            <v>4000000</v>
+            <v>9565000</v>
           </cell>
         </row>
         <row r="153">
@@ -2175,7 +2175,7 @@
             <v>0</v>
           </cell>
           <cell r="M153">
-            <v>0</v>
+            <v>168000</v>
           </cell>
         </row>
         <row r="154">
@@ -2186,7 +2186,7 @@
             <v>0</v>
           </cell>
           <cell r="M154">
-            <v>132000</v>
+            <v>532000</v>
           </cell>
         </row>
         <row r="155">
@@ -2205,7 +2205,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I156">
-            <v>4</v>
+            <v>24</v>
           </cell>
           <cell r="M156">
             <v>234000</v>
@@ -2227,7 +2227,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I158">
-            <v>4</v>
+            <v>24</v>
           </cell>
           <cell r="M158">
             <v>234000</v>
@@ -2241,7 +2241,7 @@
             <v>0</v>
           </cell>
           <cell r="M159">
-            <v>1261500</v>
+            <v>1761500</v>
           </cell>
         </row>
         <row r="160">
@@ -2296,7 +2296,7 @@
             <v>0</v>
           </cell>
           <cell r="M164">
-            <v>132000</v>
+            <v>300000</v>
           </cell>
         </row>
         <row r="165">
@@ -2307,7 +2307,7 @@
             <v>0</v>
           </cell>
           <cell r="M165">
-            <v>217000</v>
+            <v>385000</v>
           </cell>
         </row>
         <row r="166">
@@ -2318,7 +2318,7 @@
             <v>0</v>
           </cell>
           <cell r="M166">
-            <v>132000</v>
+            <v>534000</v>
           </cell>
         </row>
         <row r="167">
@@ -2329,7 +2329,7 @@
             <v>0</v>
           </cell>
           <cell r="M167">
-            <v>2795000</v>
+            <v>2963000</v>
           </cell>
         </row>
         <row r="168">
@@ -2340,7 +2340,7 @@
             <v>0</v>
           </cell>
           <cell r="M168">
-            <v>517000</v>
+            <v>919000</v>
           </cell>
         </row>
         <row r="169">
@@ -2351,7 +2351,7 @@
             <v>0</v>
           </cell>
           <cell r="M169">
-            <v>385000</v>
+            <v>619000</v>
           </cell>
         </row>
         <row r="170">
@@ -2362,7 +2362,7 @@
             <v>0</v>
           </cell>
           <cell r="M170">
-            <v>1100000</v>
+            <v>1300000</v>
           </cell>
         </row>
         <row r="171">
@@ -2373,7 +2373,7 @@
             <v>0</v>
           </cell>
           <cell r="M171">
-            <v>85000</v>
+            <v>253000</v>
           </cell>
         </row>
         <row r="172">
@@ -2384,7 +2384,7 @@
             <v>0</v>
           </cell>
           <cell r="M172">
-            <v>85000</v>
+            <v>487000</v>
           </cell>
         </row>
         <row r="173">
@@ -2395,7 +2395,7 @@
             <v>0</v>
           </cell>
           <cell r="M173">
-            <v>85000</v>
+            <v>253000</v>
           </cell>
         </row>
         <row r="174">
@@ -2406,7 +2406,7 @@
             <v>0</v>
           </cell>
           <cell r="M174">
-            <v>0</v>
+            <v>1234000</v>
           </cell>
         </row>
         <row r="175">
@@ -2417,7 +2417,7 @@
             <v>0</v>
           </cell>
           <cell r="M175">
-            <v>0</v>
+            <v>327600</v>
           </cell>
         </row>
         <row r="176">
@@ -2428,7 +2428,7 @@
             <v>0</v>
           </cell>
           <cell r="M176">
-            <v>0</v>
+            <v>117000</v>
           </cell>
         </row>
         <row r="177">
@@ -2439,7 +2439,7 @@
             <v>0</v>
           </cell>
           <cell r="M177">
-            <v>0</v>
+            <v>327600</v>
           </cell>
         </row>
         <row r="178">
@@ -2447,10 +2447,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I178">
-            <v>4</v>
+            <v>24</v>
           </cell>
           <cell r="M178">
-            <v>0</v>
+            <v>304200</v>
           </cell>
         </row>
         <row r="179">
@@ -2461,7 +2461,7 @@
             <v>3</v>
           </cell>
           <cell r="M179">
-            <v>1160000</v>
+            <v>1328000</v>
           </cell>
         </row>
         <row r="180">
@@ -2480,7 +2480,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I181">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="M181">
             <v>404000</v>
@@ -2502,10 +2502,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I183">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M183">
-            <v>564000</v>
+            <v>654000</v>
           </cell>
         </row>
         <row r="184">
@@ -2513,10 +2513,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I184">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M184">
-            <v>2854000</v>
+            <v>3612000</v>
           </cell>
         </row>
         <row r="185">
@@ -2524,10 +2524,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I185">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M185">
-            <v>300000</v>
+            <v>390000</v>
           </cell>
         </row>
         <row r="186">
@@ -2546,10 +2546,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I187">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M187">
-            <v>5320000</v>
+            <v>8580000</v>
           </cell>
         </row>
         <row r="188">
@@ -2557,10 +2557,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I188">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M188">
-            <v>1320000</v>
+            <v>3420000</v>
           </cell>
         </row>
         <row r="189">
@@ -2579,10 +2579,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I190">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M190">
-            <v>100000</v>
+            <v>190000</v>
           </cell>
         </row>
         <row r="191">
@@ -2593,7 +2593,7 @@
             <v>1</v>
           </cell>
           <cell r="M191">
-            <v>0</v>
+            <v>304200</v>
           </cell>
         </row>
         <row r="192">
@@ -2604,7 +2604,7 @@
             <v>0</v>
           </cell>
           <cell r="M192">
-            <v>1600000</v>
+            <v>1904200</v>
           </cell>
         </row>
         <row r="193">
@@ -2714,7 +2714,7 @@
             <v>2</v>
           </cell>
           <cell r="M202">
-            <v>2000000</v>
+            <v>2304200</v>
           </cell>
         </row>
         <row r="203">
@@ -2725,7 +2725,7 @@
             <v>0</v>
           </cell>
           <cell r="M203">
-            <v>2500000</v>
+            <v>2804200</v>
           </cell>
         </row>
         <row r="204">
@@ -3074,7 +3074,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I235">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="M235">
             <v>6139000</v>
@@ -3121,7 +3121,7 @@
             <v>4</v>
           </cell>
           <cell r="M239">
-            <v>1340000</v>
+            <v>1490000</v>
           </cell>
         </row>
         <row r="240">
@@ -3176,7 +3176,7 @@
             <v>3</v>
           </cell>
           <cell r="M244">
-            <v>381000</v>
+            <v>497000</v>
           </cell>
         </row>
         <row r="245">
@@ -3187,7 +3187,7 @@
             <v>5</v>
           </cell>
           <cell r="M245">
-            <v>3134000</v>
+            <v>3656000</v>
           </cell>
         </row>
         <row r="246">
@@ -3198,7 +3198,7 @@
             <v>9</v>
           </cell>
           <cell r="M246">
-            <v>3475000</v>
+            <v>3591000</v>
           </cell>
         </row>
         <row r="247">
@@ -3209,7 +3209,7 @@
             <v>5</v>
           </cell>
           <cell r="M247">
-            <v>659000</v>
+            <v>744000</v>
           </cell>
         </row>
         <row r="248">
@@ -3220,7 +3220,7 @@
             <v>9</v>
           </cell>
           <cell r="M248">
-            <v>589000</v>
+            <v>647000</v>
           </cell>
         </row>
         <row r="249">
@@ -3231,7 +3231,7 @@
             <v>6</v>
           </cell>
           <cell r="M249">
-            <v>1054000</v>
+            <v>1170000</v>
           </cell>
         </row>
         <row r="250">
@@ -3242,7 +3242,7 @@
             <v>9</v>
           </cell>
           <cell r="M250">
-            <v>3518500</v>
+            <v>3634500</v>
           </cell>
         </row>
         <row r="251">
@@ -3253,7 +3253,7 @@
             <v>3</v>
           </cell>
           <cell r="M251">
-            <v>288000</v>
+            <v>673000</v>
           </cell>
         </row>
         <row r="252">
@@ -3264,7 +3264,7 @@
             <v>9</v>
           </cell>
           <cell r="M252">
-            <v>4023000</v>
+            <v>4124500</v>
           </cell>
         </row>
         <row r="253">
@@ -3396,7 +3396,7 @@
             <v>0</v>
           </cell>
           <cell r="M264">
-            <v>324900</v>
+            <v>456900</v>
           </cell>
         </row>
         <row r="265">
@@ -3407,7 +3407,7 @@
             <v>0</v>
           </cell>
           <cell r="M265">
-            <v>302400</v>
+            <v>658800</v>
           </cell>
         </row>
         <row r="266">
@@ -3418,7 +3418,7 @@
             <v>0</v>
           </cell>
           <cell r="M266">
-            <v>600000</v>
+            <v>652800</v>
           </cell>
         </row>
         <row r="267">
@@ -3429,7 +3429,7 @@
             <v>0</v>
           </cell>
           <cell r="M267">
-            <v>324900</v>
+            <v>681300</v>
           </cell>
         </row>
         <row r="268">
@@ -3440,7 +3440,7 @@
             <v>0</v>
           </cell>
           <cell r="M268">
-            <v>2350000</v>
+            <v>2435000</v>
           </cell>
         </row>
         <row r="269">
@@ -3451,7 +3451,7 @@
             <v>0</v>
           </cell>
           <cell r="M269">
-            <v>2350000</v>
+            <v>3035000</v>
           </cell>
         </row>
         <row r="270">
@@ -3473,7 +3473,7 @@
             <v>0</v>
           </cell>
           <cell r="M271">
-            <v>0</v>
+            <v>300000</v>
           </cell>
         </row>
         <row r="272">
@@ -3484,7 +3484,7 @@
             <v>3</v>
           </cell>
           <cell r="M272">
-            <v>1218000</v>
+            <v>1891000</v>
           </cell>
         </row>
         <row r="273">
@@ -3495,7 +3495,7 @@
             <v>3</v>
           </cell>
           <cell r="M273">
-            <v>403000</v>
+            <v>488000</v>
           </cell>
         </row>
         <row r="274">
@@ -3539,7 +3539,7 @@
             <v>0</v>
           </cell>
           <cell r="M277">
-            <v>0</v>
+            <v>304200</v>
           </cell>
         </row>
         <row r="278">
@@ -3550,7 +3550,7 @@
             <v>1</v>
           </cell>
           <cell r="M278">
-            <v>0</v>
+            <v>304200</v>
           </cell>
         </row>
         <row r="279">
@@ -3561,7 +3561,7 @@
             <v>0</v>
           </cell>
           <cell r="M279">
-            <v>0</v>
+            <v>304200</v>
           </cell>
         </row>
         <row r="280">
@@ -3759,7 +3759,7 @@
             <v>0</v>
           </cell>
           <cell r="M297">
-            <v>2000000</v>
+            <v>2385000</v>
           </cell>
         </row>
         <row r="298">
@@ -3781,7 +3781,7 @@
             <v>0</v>
           </cell>
           <cell r="M299">
-            <v>2350000</v>
+            <v>2735000</v>
           </cell>
         </row>
         <row r="300">
@@ -3792,7 +3792,7 @@
             <v>0</v>
           </cell>
           <cell r="M300">
-            <v>132000</v>
+            <v>300000</v>
           </cell>
         </row>
         <row r="301">
@@ -3803,7 +3803,7 @@
             <v>0</v>
           </cell>
           <cell r="M301">
-            <v>132000</v>
+            <v>300000</v>
           </cell>
         </row>
         <row r="302">
@@ -3814,7 +3814,7 @@
             <v>0</v>
           </cell>
           <cell r="M302">
-            <v>132000</v>
+            <v>300000</v>
           </cell>
         </row>
         <row r="303">
@@ -3825,7 +3825,7 @@
             <v>0</v>
           </cell>
           <cell r="M303">
-            <v>0</v>
+            <v>224400</v>
           </cell>
         </row>
         <row r="304">
@@ -3836,7 +3836,7 @@
             <v>0</v>
           </cell>
           <cell r="M304">
-            <v>0</v>
+            <v>132000</v>
           </cell>
         </row>
         <row r="305">
@@ -3844,7 +3844,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I305">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="M305">
             <v>349000</v>
@@ -3869,7 +3869,7 @@
             <v>3</v>
           </cell>
           <cell r="M307">
-            <v>656000</v>
+            <v>824000</v>
           </cell>
         </row>
         <row r="308">
@@ -3880,7 +3880,7 @@
             <v>3</v>
           </cell>
           <cell r="M308">
-            <v>1156000</v>
+            <v>1201000</v>
           </cell>
         </row>
         <row r="309">
@@ -3891,7 +3891,7 @@
             <v>3</v>
           </cell>
           <cell r="M309">
-            <v>643000</v>
+            <v>811000</v>
           </cell>
         </row>
         <row r="310">
@@ -3910,7 +3910,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I311">
-            <v>0</v>
+            <v>19</v>
           </cell>
           <cell r="M311">
             <v>6754000</v>
@@ -3924,7 +3924,7 @@
             <v>0</v>
           </cell>
           <cell r="M312">
-            <v>0</v>
+            <v>1045000</v>
           </cell>
         </row>
         <row r="313">
@@ -3961,7 +3961,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>104617000</v>
+        <v>110510000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.23507176568468924</v>
+        <v>0.24831318835194097</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-340425813.60751247</v>
+        <v>-334532813.60751247</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-18912545.200417358</v>
+        <v>-18585156.31152847</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>83725000</v>
+        <v>101421000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.18671673932891286</v>
+        <v>0.2261809306596318</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-364681502.2821191</v>
+        <v>-346985502.2821191</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-20260083.460117728</v>
+        <v>-19276972.349006616</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>26669500</v>
+        <v>28167000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.16393923707489191</v>
+        <v>0.17314447180068918</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-136009675.99138665</v>
+        <v>-134512175.99138665</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-7556093.1106325919</v>
+        <v>-7472898.6661881469</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>23999600</v>
+        <v>29818000</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>9.2652898985005838E-2</v>
+        <v>0.11511542450436274</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-235027373.39112824</v>
+        <v>-229208973.39112824</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-13057076.299507124</v>
+        <v>-12733831.85506268</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>47078000</v>
+        <v>55571800</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.12191206083469749</v>
+        <v>0.14390740180750333</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-339085597.57738662</v>
+        <v>-330591797.57738662</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-18838088.754299257</v>
+        <v>-18366210.976521477</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4472,19 +4472,19 @@
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>0.10522053814491651</v>
+        <v>0.32709862945050133</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-391.17700755954917</v>
+        <v>-294.17700755954917</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-21.73205597553051</v>
+        <v>-16.343167086641621</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>9.8784794102154502E-2</v>
+        <v>0.25076140041316142</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-355.79760376551121</v>
+        <v>-295.79760376551121</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-19.7665335425284</v>
+        <v>-16.433200209195068</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.17448372824335667</v>
+        <v>0.32506557590543161</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-345.3771216659535</v>
+        <v>-282.3771216659535</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-19.187617870330751</v>
+        <v>-15.687617870330749</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -1438,7 +1438,7 @@
             <v>0</v>
           </cell>
           <cell r="M86">
-            <v>2700800</v>
+            <v>3000800</v>
           </cell>
         </row>
         <row r="87">
@@ -1592,7 +1592,7 @@
             <v>0</v>
           </cell>
           <cell r="M100">
-            <v>2238400</v>
+            <v>2388400</v>
           </cell>
         </row>
         <row r="101">
@@ -1941,7 +1941,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I132">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="M132">
             <v>3887000</v>
@@ -3088,7 +3088,7 @@
             <v>0</v>
           </cell>
           <cell r="M236">
-            <v>402000</v>
+            <v>1402000</v>
           </cell>
         </row>
         <row r="237">
@@ -3484,7 +3484,7 @@
             <v>3</v>
           </cell>
           <cell r="M272">
-            <v>1891000</v>
+            <v>2027000</v>
           </cell>
         </row>
         <row r="273">
@@ -3961,7 +3961,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>110510000</v>
+        <v>110646000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.24831318835194097</v>
+        <v>0.24861877692868392</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-334532813.60751247</v>
+        <v>-334396813.60751247</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-18585156.31152847</v>
+        <v>-18577600.755972914</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>101421000</v>
+        <v>102421000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.2261809306596318</v>
+        <v>0.22841104997081618</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-346985502.2821191</v>
+        <v>-345985502.2821191</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-19276972.349006616</v>
+        <v>-19221416.79345106</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>29818000</v>
+        <v>29968000</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.11511542450436274</v>
+        <v>0.11569451477452353</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-229208973.39112824</v>
+        <v>-229058973.39112824</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-12733831.85506268</v>
+        <v>-12725498.521729346</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>55571800</v>
+        <v>55871800</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.14390740180750333</v>
+        <v>0.14468427461965358</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-330591797.57738662</v>
+        <v>-330291797.57738662</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-18366210.976521477</v>
+        <v>-18349544.309854813</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.32506557590543161</v>
+        <v>0.3274557639635598</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-282.3771216659535</v>
+        <v>-281.3771216659535</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-15.687617870330749</v>
+        <v>-15.632062314775194</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -1009,7 +1009,7 @@
             <v>3</v>
           </cell>
           <cell r="M47">
-            <v>662000</v>
+            <v>930000</v>
           </cell>
         </row>
         <row r="48">
@@ -1020,7 +1020,7 @@
             <v>0</v>
           </cell>
           <cell r="M48">
-            <v>685000</v>
+            <v>770000</v>
           </cell>
         </row>
         <row r="49">
@@ -1031,7 +1031,7 @@
             <v>0</v>
           </cell>
           <cell r="M49">
-            <v>530000</v>
+            <v>698000</v>
           </cell>
         </row>
         <row r="50">
@@ -1075,7 +1075,7 @@
             <v>0</v>
           </cell>
           <cell r="M53">
-            <v>3035000</v>
+            <v>3203000</v>
           </cell>
         </row>
         <row r="54">
@@ -1119,7 +1119,7 @@
             <v>0</v>
           </cell>
           <cell r="M57">
-            <v>385000</v>
+            <v>770000</v>
           </cell>
         </row>
         <row r="58">
@@ -1141,7 +1141,7 @@
             <v>0</v>
           </cell>
           <cell r="M59">
-            <v>313000</v>
+            <v>698000</v>
           </cell>
         </row>
         <row r="60">
@@ -1358,10 +1358,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I79">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M79">
-            <v>402000</v>
+            <v>492000</v>
           </cell>
         </row>
         <row r="80">
@@ -1457,10 +1457,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I88">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M88">
-            <v>117000</v>
+            <v>277200</v>
           </cell>
         </row>
         <row r="89">
@@ -1490,10 +1490,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I91">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M91">
-            <v>105600</v>
+            <v>327600</v>
           </cell>
         </row>
         <row r="92">
@@ -1501,10 +1501,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I92">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M92">
-            <v>118800</v>
+            <v>540800</v>
           </cell>
         </row>
         <row r="93">
@@ -1512,10 +1512,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I93">
-            <v>19</v>
+            <v>22</v>
           </cell>
           <cell r="M93">
-            <v>105600</v>
+            <v>327600</v>
           </cell>
         </row>
         <row r="94">
@@ -1523,10 +1523,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I94">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M94">
-            <v>723600</v>
+            <v>813600</v>
           </cell>
         </row>
         <row r="95">
@@ -1600,10 +1600,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I101">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M101">
-            <v>1605600</v>
+            <v>2195600</v>
           </cell>
         </row>
         <row r="102">
@@ -1611,10 +1611,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I102">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M102">
-            <v>222000</v>
+            <v>397000</v>
           </cell>
         </row>
         <row r="103">
@@ -1622,10 +1622,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I103">
-            <v>2</v>
+            <v>5</v>
           </cell>
           <cell r="M103">
-            <v>1052800</v>
+            <v>1142800</v>
           </cell>
         </row>
         <row r="104">
@@ -1633,10 +1633,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I104">
-            <v>1</v>
+            <v>4</v>
           </cell>
           <cell r="M104">
-            <v>2168000</v>
+            <v>2343000</v>
           </cell>
         </row>
         <row r="105">
@@ -1644,7 +1644,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I105">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="M105">
             <v>2519500</v>
@@ -1655,10 +1655,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I106">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M106">
-            <v>220800</v>
+            <v>480800</v>
           </cell>
         </row>
         <row r="107">
@@ -1677,10 +1677,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I108">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M108">
-            <v>1273600</v>
+            <v>1863600</v>
           </cell>
         </row>
         <row r="109">
@@ -1688,10 +1688,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I109">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M109">
-            <v>52800</v>
+            <v>397800</v>
           </cell>
         </row>
         <row r="110">
@@ -1699,10 +1699,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I110">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M110">
-            <v>273600</v>
+            <v>448600</v>
           </cell>
         </row>
         <row r="111">
@@ -1710,10 +1710,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I111">
-            <v>20</v>
+            <v>23</v>
           </cell>
           <cell r="M111">
-            <v>368400</v>
+            <v>628400</v>
           </cell>
         </row>
         <row r="112">
@@ -1735,7 +1735,7 @@
             <v>3</v>
           </cell>
           <cell r="M113">
-            <v>1012800</v>
+            <v>1144800</v>
           </cell>
         </row>
         <row r="114">
@@ -1743,10 +1743,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I114">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M114">
-            <v>1511200</v>
+            <v>1601200</v>
           </cell>
         </row>
         <row r="115">
@@ -1754,10 +1754,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I115">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M115">
-            <v>408000</v>
+            <v>583000</v>
           </cell>
         </row>
         <row r="116">
@@ -1787,10 +1787,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I118">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M118">
-            <v>52800</v>
+            <v>312800</v>
           </cell>
         </row>
         <row r="119">
@@ -1809,10 +1809,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I120">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M120">
-            <v>52800</v>
+            <v>312800</v>
           </cell>
         </row>
         <row r="121">
@@ -1820,10 +1820,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I121">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M121">
-            <v>378000</v>
+            <v>468000</v>
           </cell>
         </row>
         <row r="122">
@@ -1864,10 +1864,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I125">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="M125">
-            <v>378000</v>
+            <v>1468000</v>
           </cell>
         </row>
         <row r="126">
@@ -1886,10 +1886,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I127">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M127">
-            <v>3485800</v>
+            <v>4575800</v>
           </cell>
         </row>
         <row r="128">
@@ -1930,10 +1930,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I131">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M131">
-            <v>1000000</v>
+            <v>1090000</v>
           </cell>
         </row>
         <row r="132">
@@ -1941,10 +1941,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I132">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M132">
-            <v>3887000</v>
+            <v>4477000</v>
           </cell>
         </row>
         <row r="133">
@@ -1952,10 +1952,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I133">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M133">
-            <v>117000</v>
+            <v>207000</v>
           </cell>
         </row>
         <row r="134">
@@ -2051,10 +2051,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I142">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M142">
-            <v>285000</v>
+            <v>375000</v>
           </cell>
         </row>
         <row r="143">
@@ -2073,10 +2073,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I144">
-            <v>9</v>
+            <v>12</v>
           </cell>
           <cell r="M144">
-            <v>897000</v>
+            <v>987000</v>
           </cell>
         </row>
         <row r="145">
@@ -2252,7 +2252,7 @@
             <v>0</v>
           </cell>
           <cell r="M160">
-            <v>2313000</v>
+            <v>3313000</v>
           </cell>
         </row>
         <row r="161">
@@ -2260,10 +2260,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I161">
-            <v>2</v>
+            <v>5</v>
           </cell>
           <cell r="M161">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="162">
@@ -2285,7 +2285,7 @@
             <v>0</v>
           </cell>
           <cell r="M163">
-            <v>2670000</v>
+            <v>3670000</v>
           </cell>
         </row>
         <row r="164">
@@ -2615,7 +2615,7 @@
             <v>0</v>
           </cell>
           <cell r="M193">
-            <v>3007000</v>
+            <v>3409000</v>
           </cell>
         </row>
         <row r="194">
@@ -2623,10 +2623,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I194">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M194">
-            <v>132000</v>
+            <v>624000</v>
           </cell>
         </row>
         <row r="195">
@@ -2634,10 +2634,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I195">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M195">
-            <v>132000</v>
+            <v>624000</v>
           </cell>
         </row>
         <row r="196">
@@ -2648,7 +2648,7 @@
             <v>0</v>
           </cell>
           <cell r="M196">
-            <v>1000000</v>
+            <v>2045000</v>
           </cell>
         </row>
         <row r="197">
@@ -2656,10 +2656,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I197">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M197">
-            <v>132000</v>
+            <v>456000</v>
           </cell>
         </row>
         <row r="198">
@@ -2667,10 +2667,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I198">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M198">
-            <v>132000</v>
+            <v>624000</v>
           </cell>
         </row>
         <row r="199">
@@ -2681,7 +2681,7 @@
             <v>4</v>
           </cell>
           <cell r="M199">
-            <v>132000</v>
+            <v>366000</v>
           </cell>
         </row>
         <row r="200">
@@ -2714,7 +2714,7 @@
             <v>2</v>
           </cell>
           <cell r="M202">
-            <v>2304200</v>
+            <v>4304200</v>
           </cell>
         </row>
         <row r="203">
@@ -2780,7 +2780,7 @@
             <v>1</v>
           </cell>
           <cell r="M208">
-            <v>264000</v>
+            <v>666000</v>
           </cell>
         </row>
         <row r="209">
@@ -2788,10 +2788,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I209">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M209">
-            <v>132000</v>
+            <v>390000</v>
           </cell>
         </row>
         <row r="210">
@@ -2810,10 +2810,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I211">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M211">
-            <v>132000</v>
+            <v>456000</v>
           </cell>
         </row>
         <row r="212">
@@ -2835,7 +2835,7 @@
             <v>0</v>
           </cell>
           <cell r="M213">
-            <v>132000</v>
+            <v>534000</v>
           </cell>
         </row>
         <row r="214">
@@ -2865,10 +2865,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I216">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M216">
-            <v>132000</v>
+            <v>456000</v>
           </cell>
         </row>
         <row r="217">
@@ -2876,10 +2876,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I217">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M217">
-            <v>132000</v>
+            <v>456000</v>
           </cell>
         </row>
         <row r="218">
@@ -2887,10 +2887,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I218">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M218">
-            <v>132000</v>
+            <v>456000</v>
           </cell>
         </row>
         <row r="219">
@@ -2898,10 +2898,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I219">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M219">
-            <v>132000</v>
+            <v>456000</v>
           </cell>
         </row>
         <row r="220">
@@ -3121,7 +3121,7 @@
             <v>4</v>
           </cell>
           <cell r="M239">
-            <v>1490000</v>
+            <v>1790000</v>
           </cell>
         </row>
         <row r="240">
@@ -3198,7 +3198,7 @@
             <v>9</v>
           </cell>
           <cell r="M246">
-            <v>3591000</v>
+            <v>3649000</v>
           </cell>
         </row>
         <row r="247">
@@ -3209,7 +3209,7 @@
             <v>5</v>
           </cell>
           <cell r="M247">
-            <v>744000</v>
+            <v>1129000</v>
           </cell>
         </row>
         <row r="248">
@@ -3231,7 +3231,7 @@
             <v>6</v>
           </cell>
           <cell r="M249">
-            <v>1170000</v>
+            <v>1428000</v>
           </cell>
         </row>
         <row r="250">
@@ -3242,7 +3242,7 @@
             <v>9</v>
           </cell>
           <cell r="M250">
-            <v>3634500</v>
+            <v>3692500</v>
           </cell>
         </row>
         <row r="251">
@@ -3253,7 +3253,7 @@
             <v>3</v>
           </cell>
           <cell r="M251">
-            <v>673000</v>
+            <v>1058000</v>
           </cell>
         </row>
         <row r="252">
@@ -3264,7 +3264,7 @@
             <v>9</v>
           </cell>
           <cell r="M252">
-            <v>4124500</v>
+            <v>4182500</v>
           </cell>
         </row>
         <row r="253">
@@ -3294,10 +3294,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I255">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M255">
-            <v>658000</v>
+            <v>748000</v>
           </cell>
         </row>
         <row r="256">
@@ -3305,10 +3305,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I256">
-            <v>8</v>
+            <v>11</v>
           </cell>
           <cell r="M256">
-            <v>3396200</v>
+            <v>3486200</v>
           </cell>
         </row>
         <row r="257">
@@ -3327,10 +3327,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I258">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M258">
-            <v>566000</v>
+            <v>656000</v>
           </cell>
         </row>
         <row r="259">
@@ -3338,10 +3338,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I259">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M259">
-            <v>570000</v>
+            <v>660000</v>
           </cell>
         </row>
         <row r="260">
@@ -3484,7 +3484,7 @@
             <v>3</v>
           </cell>
           <cell r="M272">
-            <v>2027000</v>
+            <v>2412000</v>
           </cell>
         </row>
         <row r="273">
@@ -3495,7 +3495,7 @@
             <v>3</v>
           </cell>
           <cell r="M273">
-            <v>488000</v>
+            <v>873000</v>
           </cell>
         </row>
         <row r="274">
@@ -3506,7 +3506,7 @@
             <v>3</v>
           </cell>
           <cell r="M274">
-            <v>2608000</v>
+            <v>2993000</v>
           </cell>
         </row>
         <row r="275">
@@ -3671,7 +3671,7 @@
             <v>0</v>
           </cell>
           <cell r="M289">
-            <v>302000</v>
+            <v>802000</v>
           </cell>
         </row>
         <row r="290">
@@ -3961,7 +3961,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>110646000</v>
+        <v>114030000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.24861877692868392</v>
+        <v>0.25622253974999393</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-334396813.60751247</v>
+        <v>-331012813.60751247</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-18577600.755972914</v>
+        <v>-18389600.755972914</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>102421000</v>
+        <v>109384000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.22841104997081618</v>
+        <v>0.24393937073459307</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-345985502.2821191</v>
+        <v>-339022502.2821191</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-19221416.79345106</v>
+        <v>-18834583.460117728</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>28167000</v>
+        <v>28599000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.17314447180068918</v>
+        <v>0.17580000529086912</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-134512175.99138665</v>
+        <v>-134080175.99138665</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-7472898.6661881469</v>
+        <v>-7448898.6661881469</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>29968000</v>
+        <v>35591000</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.11569451477452353</v>
+        <v>0.13740267870195097</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-229058973.39112824</v>
+        <v>-223435973.39112824</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-12725498.521729346</v>
+        <v>-12413109.632840458</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>55871800</v>
+        <v>62702000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.14468427461965358</v>
+        <v>0.16237159689148228</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-330291797.57738662</v>
+        <v>-323461597.57738662</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-18349544.309854813</v>
+        <v>-17970088.754299257</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4472,19 +4472,19 @@
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>0.32709862945050133</v>
+        <v>0.39572071954501215</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-294.17700755954917</v>
+        <v>-264.17700755954917</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-16.343167086641621</v>
+        <v>-14.676500419974953</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.25076140041316142</v>
+        <v>0.38754034609306764</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-295.79760376551121</v>
+        <v>-241.79760376551121</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-16.433200209195068</v>
+        <v>-13.433200209195068</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.3274557639635598</v>
+        <v>0.43262403852119941</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-281.3771216659535</v>
+        <v>-237.3771216659535</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-15.632062314775194</v>
+        <v>-13.187617870330749</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -973,10 +973,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I44">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M44">
-            <v>3616000</v>
+            <v>4216000</v>
           </cell>
         </row>
         <row r="45">
@@ -987,7 +987,7 @@
             <v>3</v>
           </cell>
           <cell r="M45">
-            <v>3326000</v>
+            <v>3711000</v>
           </cell>
         </row>
         <row r="46">
@@ -998,7 +998,7 @@
             <v>3</v>
           </cell>
           <cell r="M46">
-            <v>3326000</v>
+            <v>3711000</v>
           </cell>
         </row>
         <row r="47">
@@ -1086,7 +1086,7 @@
             <v>0</v>
           </cell>
           <cell r="M54">
-            <v>3496000</v>
+            <v>3554000</v>
           </cell>
         </row>
         <row r="55">
@@ -1119,7 +1119,7 @@
             <v>0</v>
           </cell>
           <cell r="M57">
-            <v>770000</v>
+            <v>1155000</v>
           </cell>
         </row>
         <row r="58">
@@ -1130,7 +1130,7 @@
             <v>0</v>
           </cell>
           <cell r="M58">
-            <v>1008000</v>
+            <v>1140000</v>
           </cell>
         </row>
         <row r="59">
@@ -1402,10 +1402,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I83">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M83">
-            <v>408000</v>
+            <v>630000</v>
           </cell>
         </row>
         <row r="84">
@@ -1413,10 +1413,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I84">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M84">
-            <v>511200</v>
+            <v>733200</v>
           </cell>
         </row>
         <row r="85">
@@ -1424,10 +1424,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I85">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M85">
-            <v>396000</v>
+            <v>486000</v>
           </cell>
         </row>
         <row r="86">
@@ -1435,10 +1435,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I86">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M86">
-            <v>3000800</v>
+            <v>3740800</v>
           </cell>
         </row>
         <row r="87">
@@ -1446,10 +1446,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I87">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M87">
-            <v>300000</v>
+            <v>390000</v>
           </cell>
         </row>
         <row r="88">
@@ -1460,7 +1460,7 @@
             <v>3</v>
           </cell>
           <cell r="M88">
-            <v>277200</v>
+            <v>604800</v>
           </cell>
         </row>
         <row r="89">
@@ -1471,7 +1471,7 @@
             <v>0</v>
           </cell>
           <cell r="M89">
-            <v>734000</v>
+            <v>851000</v>
           </cell>
         </row>
         <row r="90">
@@ -1482,7 +1482,7 @@
             <v>0</v>
           </cell>
           <cell r="M90">
-            <v>227400</v>
+            <v>344400</v>
           </cell>
         </row>
         <row r="91">
@@ -1537,7 +1537,7 @@
             <v>0</v>
           </cell>
           <cell r="M95">
-            <v>273600</v>
+            <v>405600</v>
           </cell>
         </row>
         <row r="96">
@@ -1548,7 +1548,7 @@
             <v>1</v>
           </cell>
           <cell r="M96">
-            <v>376800</v>
+            <v>508800</v>
           </cell>
         </row>
         <row r="97">
@@ -1589,10 +1589,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I100">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M100">
-            <v>2388400</v>
+            <v>2678400</v>
           </cell>
         </row>
         <row r="101">
@@ -1666,10 +1666,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I107">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M107">
-            <v>276000</v>
+            <v>498000</v>
           </cell>
         </row>
         <row r="108">
@@ -1713,7 +1713,7 @@
             <v>23</v>
           </cell>
           <cell r="M111">
-            <v>628400</v>
+            <v>681200</v>
           </cell>
         </row>
         <row r="112">
@@ -1724,7 +1724,7 @@
             <v>3</v>
           </cell>
           <cell r="M112">
-            <v>430800</v>
+            <v>694800</v>
           </cell>
         </row>
         <row r="113">
@@ -1735,7 +1735,7 @@
             <v>3</v>
           </cell>
           <cell r="M113">
-            <v>1144800</v>
+            <v>1376800</v>
           </cell>
         </row>
         <row r="114">
@@ -1831,10 +1831,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I122">
-            <v>3</v>
+            <v>9</v>
           </cell>
           <cell r="M122">
-            <v>1205500</v>
+            <v>1885500</v>
           </cell>
         </row>
         <row r="123">
@@ -1867,7 +1867,7 @@
             <v>8</v>
           </cell>
           <cell r="M125">
-            <v>1468000</v>
+            <v>1520800</v>
           </cell>
         </row>
         <row r="126">
@@ -1889,7 +1889,7 @@
             <v>3</v>
           </cell>
           <cell r="M127">
-            <v>4575800</v>
+            <v>5692800</v>
           </cell>
         </row>
         <row r="128">
@@ -1908,10 +1908,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I129">
-            <v>9</v>
+            <v>12</v>
           </cell>
           <cell r="M129">
-            <v>1546900</v>
+            <v>1636900</v>
           </cell>
         </row>
         <row r="130">
@@ -1955,7 +1955,7 @@
             <v>3</v>
           </cell>
           <cell r="M133">
-            <v>207000</v>
+            <v>511200</v>
           </cell>
         </row>
         <row r="134">
@@ -1977,7 +1977,7 @@
             <v>3</v>
           </cell>
           <cell r="M135">
-            <v>361200</v>
+            <v>493200</v>
           </cell>
         </row>
         <row r="136">
@@ -1988,7 +1988,7 @@
             <v>3</v>
           </cell>
           <cell r="M136">
-            <v>493200</v>
+            <v>625200</v>
           </cell>
         </row>
         <row r="137">
@@ -1999,7 +1999,7 @@
             <v>3</v>
           </cell>
           <cell r="M137">
-            <v>361200</v>
+            <v>493200</v>
           </cell>
         </row>
         <row r="138">
@@ -2095,10 +2095,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I146">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M146">
-            <v>628500</v>
+            <v>850500</v>
           </cell>
         </row>
         <row r="147">
@@ -2362,7 +2362,7 @@
             <v>0</v>
           </cell>
           <cell r="M170">
-            <v>1300000</v>
+            <v>1600000</v>
           </cell>
         </row>
         <row r="171">
@@ -2725,7 +2725,7 @@
             <v>0</v>
           </cell>
           <cell r="M203">
-            <v>2804200</v>
+            <v>3804200</v>
           </cell>
         </row>
         <row r="204">
@@ -2733,10 +2733,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I204">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M204">
-            <v>6122000</v>
+            <v>6446000</v>
           </cell>
         </row>
         <row r="205">
@@ -2766,10 +2766,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I207">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M207">
-            <v>302000</v>
+            <v>626000</v>
           </cell>
         </row>
         <row r="208">
@@ -2821,10 +2821,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I212">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M212">
-            <v>302000</v>
+            <v>560000</v>
           </cell>
         </row>
         <row r="213">
@@ -2843,10 +2843,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I214">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M214">
-            <v>302000</v>
+            <v>626000</v>
           </cell>
         </row>
         <row r="215">
@@ -2854,10 +2854,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I215">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M215">
-            <v>302000</v>
+            <v>626000</v>
           </cell>
         </row>
         <row r="216">
@@ -2920,10 +2920,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I221">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M221">
-            <v>794000</v>
+            <v>1594000</v>
           </cell>
         </row>
         <row r="222">
@@ -2942,10 +2942,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I223">
-            <v>1</v>
+            <v>4</v>
           </cell>
           <cell r="M223">
-            <v>1002000</v>
+            <v>1392000</v>
           </cell>
         </row>
         <row r="224">
@@ -2986,10 +2986,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I227">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M227">
-            <v>1132000</v>
+            <v>2222000</v>
           </cell>
         </row>
         <row r="228">
@@ -2997,10 +2997,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I228">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M228">
-            <v>1000000</v>
+            <v>2090000</v>
           </cell>
         </row>
         <row r="229">
@@ -3008,10 +3008,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I229">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M229">
-            <v>302000</v>
+            <v>560000</v>
           </cell>
         </row>
         <row r="230">
@@ -3162,7 +3162,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I243">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M243">
             <v>487000</v>
@@ -3187,7 +3187,7 @@
             <v>5</v>
           </cell>
           <cell r="M245">
-            <v>3656000</v>
+            <v>3741000</v>
           </cell>
         </row>
         <row r="246">
@@ -3198,7 +3198,7 @@
             <v>9</v>
           </cell>
           <cell r="M246">
-            <v>3649000</v>
+            <v>3707000</v>
           </cell>
         </row>
         <row r="247">
@@ -3220,7 +3220,7 @@
             <v>9</v>
           </cell>
           <cell r="M248">
-            <v>647000</v>
+            <v>705000</v>
           </cell>
         </row>
         <row r="249">
@@ -3231,7 +3231,7 @@
             <v>6</v>
           </cell>
           <cell r="M249">
-            <v>1428000</v>
+            <v>1786000</v>
           </cell>
         </row>
         <row r="250">
@@ -3242,7 +3242,7 @@
             <v>9</v>
           </cell>
           <cell r="M250">
-            <v>3692500</v>
+            <v>3750500</v>
           </cell>
         </row>
         <row r="251">
@@ -3264,7 +3264,7 @@
             <v>9</v>
           </cell>
           <cell r="M252">
-            <v>4182500</v>
+            <v>4240500</v>
           </cell>
         </row>
         <row r="253">
@@ -3308,7 +3308,7 @@
             <v>11</v>
           </cell>
           <cell r="M256">
-            <v>3486200</v>
+            <v>3603200</v>
           </cell>
         </row>
         <row r="257">
@@ -3330,7 +3330,7 @@
             <v>3</v>
           </cell>
           <cell r="M258">
-            <v>656000</v>
+            <v>1007000</v>
           </cell>
         </row>
         <row r="259">
@@ -3352,7 +3352,7 @@
             <v>4</v>
           </cell>
           <cell r="M260">
-            <v>522000</v>
+            <v>826200</v>
           </cell>
         </row>
         <row r="261">
@@ -3360,10 +3360,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I261">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M261">
-            <v>355200</v>
+            <v>616800</v>
           </cell>
         </row>
         <row r="262">
@@ -3382,10 +3382,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I263">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M263">
-            <v>355200</v>
+            <v>577200</v>
           </cell>
         </row>
         <row r="264">
@@ -3404,10 +3404,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I265">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M265">
-            <v>658800</v>
+            <v>880800</v>
           </cell>
         </row>
         <row r="266">
@@ -3492,7 +3492,7 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I273">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="M273">
             <v>873000</v>
@@ -3569,10 +3569,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I280">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M280">
-            <v>1266000</v>
+            <v>1801000</v>
           </cell>
         </row>
         <row r="281">
@@ -3580,10 +3580,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I281">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M281">
-            <v>1266000</v>
+            <v>1951000</v>
           </cell>
         </row>
         <row r="282">
@@ -3594,7 +3594,7 @@
             <v>3</v>
           </cell>
           <cell r="M282">
-            <v>4166000</v>
+            <v>4551000</v>
           </cell>
         </row>
         <row r="283">
@@ -3605,7 +3605,7 @@
             <v>3</v>
           </cell>
           <cell r="M283">
-            <v>4166000</v>
+            <v>4551000</v>
           </cell>
         </row>
         <row r="284">
@@ -3616,7 +3616,7 @@
             <v>3</v>
           </cell>
           <cell r="M284">
-            <v>2776000</v>
+            <v>3161000</v>
           </cell>
         </row>
         <row r="285">
@@ -3627,7 +3627,7 @@
             <v>3</v>
           </cell>
           <cell r="M285">
-            <v>1266000</v>
+            <v>1566000</v>
           </cell>
         </row>
         <row r="286">
@@ -3638,7 +3638,7 @@
             <v>3</v>
           </cell>
           <cell r="M286">
-            <v>3616000</v>
+            <v>3869000</v>
           </cell>
         </row>
         <row r="287">
@@ -3657,10 +3657,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I288">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M288">
-            <v>302000</v>
+            <v>502000</v>
           </cell>
         </row>
         <row r="289">
@@ -3668,10 +3668,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I289">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M289">
-            <v>802000</v>
+            <v>1126000</v>
           </cell>
         </row>
         <row r="290">
@@ -3679,10 +3679,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I290">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M290">
-            <v>302000</v>
+            <v>560000</v>
           </cell>
         </row>
         <row r="291">
@@ -3690,10 +3690,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I291">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M291">
-            <v>302000</v>
+            <v>626000</v>
           </cell>
         </row>
         <row r="292">
@@ -3961,7 +3961,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>114030000</v>
+        <v>118930000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.25622253974999393</v>
+        <v>0.26723271641205626</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-331012813.60751247</v>
+        <v>-326112813.60751247</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-18389600.755972914</v>
+        <v>-18117378.533750694</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>109384000</v>
+        <v>115972000</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.24393937073459307</v>
+        <v>0.25863139675667579</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-339022502.2821191</v>
+        <v>-332434502.2821191</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-18834583.460117728</v>
+        <v>-18468583.460117728</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>28599000</v>
+        <v>29247000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.17580000529086912</v>
+        <v>0.17978330552613897</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-134080175.99138665</v>
+        <v>-133432175.99138665</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-7448898.6661881469</v>
+        <v>-7412898.6661881469</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>35591000</v>
+        <v>38826200</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.13740267870195097</v>
+        <v>0.14989249764877888</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-223435973.39112824</v>
+        <v>-220200773.39112824</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-12413109.632840458</v>
+        <v>-12233376.299507124</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>62702000</v>
+        <v>68057000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.16237159689148228</v>
+        <v>0.17623877658836415</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-323461597.57738662</v>
+        <v>-318106597.57738662</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-17970088.754299257</v>
+        <v>-17672588.754299257</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4445,19 +4445,19 @@
       </c>
       <c r="D11" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A11,[1]Sheet1!$I:$I)</f>
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>0.13739632065397531</v>
+        <v>0.17174540081746914</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-652.93438881757243</v>
+        <v>-626.93438881757243</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-36.274132712087358</v>
+        <v>-34.829688267642915</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -4472,19 +4472,19 @@
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>0.39572071954501215</v>
+        <v>0.53067749673088327</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-264.17700755954917</v>
+        <v>-205.17700755954917</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-14.676500419974953</v>
+        <v>-11.398722642197177</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.38754034609306764</v>
+        <v>0.45592981893302076</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-241.79760376551121</v>
+        <v>-214.79760376551121</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-13.433200209195068</v>
+        <v>-11.933200209195068</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.43262403852119941</v>
+        <v>0.468476859393122</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-237.3771216659535</v>
+        <v>-222.3771216659535</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-13.187617870330749</v>
+        <v>-12.354284536997417</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -566,10 +566,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I7">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M7">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="8">
@@ -577,10 +577,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I8">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M8">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="9">
@@ -588,10 +588,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I9">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M9">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="10">
@@ -599,10 +599,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I10">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M10">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="11">
@@ -621,10 +621,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I12">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M12">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="13">
@@ -632,10 +632,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I13">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M13">
-            <v>58000</v>
+            <v>208000</v>
           </cell>
         </row>
         <row r="14">
@@ -676,10 +676,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I17">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M17">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="18">
@@ -687,10 +687,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I18">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M18">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="19">
@@ -709,10 +709,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I20">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M20">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="21">
@@ -720,10 +720,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I21">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M21">
-            <v>1000000</v>
+            <v>1090000</v>
           </cell>
         </row>
         <row r="22">
@@ -731,10 +731,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I22">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M22">
-            <v>1000000</v>
+            <v>1150000</v>
           </cell>
         </row>
         <row r="23">
@@ -742,10 +742,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I23">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M23">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="24">
@@ -756,7 +756,7 @@
             <v>0</v>
           </cell>
           <cell r="M24">
-            <v>0</v>
+            <v>2000000</v>
           </cell>
         </row>
         <row r="25">
@@ -786,10 +786,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I27">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M27">
-            <v>0</v>
+            <v>120000</v>
           </cell>
         </row>
         <row r="28">
@@ -811,7 +811,7 @@
             <v>0</v>
           </cell>
           <cell r="M29">
-            <v>0</v>
+            <v>58000</v>
           </cell>
         </row>
         <row r="30">
@@ -830,10 +830,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I31">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M31">
-            <v>0</v>
+            <v>150000</v>
           </cell>
         </row>
         <row r="32">
@@ -852,10 +852,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I33">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M33">
-            <v>0</v>
+            <v>150000</v>
           </cell>
         </row>
         <row r="34">
@@ -910,7 +910,7 @@
             <v>3</v>
           </cell>
           <cell r="M38">
-            <v>90000</v>
+            <v>235000</v>
           </cell>
         </row>
         <row r="39">
@@ -921,7 +921,7 @@
             <v>0</v>
           </cell>
           <cell r="M39">
-            <v>0</v>
+            <v>58000</v>
           </cell>
         </row>
         <row r="40">
@@ -954,7 +954,7 @@
             <v>3</v>
           </cell>
           <cell r="M42">
-            <v>133500</v>
+            <v>206000</v>
           </cell>
         </row>
         <row r="43">
@@ -1006,10 +1006,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I47">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M47">
-            <v>930000</v>
+            <v>1675000</v>
           </cell>
         </row>
         <row r="48">
@@ -1017,10 +1017,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I48">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M48">
-            <v>770000</v>
+            <v>1515000</v>
           </cell>
         </row>
         <row r="49">
@@ -1028,10 +1028,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I49">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M49">
-            <v>698000</v>
+            <v>1443000</v>
           </cell>
         </row>
         <row r="50">
@@ -1050,10 +1050,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I51">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M51">
-            <v>2909000</v>
+            <v>5549000</v>
           </cell>
         </row>
         <row r="52">
@@ -1061,10 +1061,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I52">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M52">
-            <v>2663000</v>
+            <v>6858000</v>
           </cell>
         </row>
         <row r="53">
@@ -1072,10 +1072,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I53">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M53">
-            <v>3203000</v>
+            <v>4033000</v>
           </cell>
         </row>
         <row r="54">
@@ -1086,7 +1086,7 @@
             <v>0</v>
           </cell>
           <cell r="M54">
-            <v>3554000</v>
+            <v>3612000</v>
           </cell>
         </row>
         <row r="55">
@@ -1097,7 +1097,7 @@
             <v>0</v>
           </cell>
           <cell r="M55">
-            <v>3280000</v>
+            <v>3338000</v>
           </cell>
         </row>
         <row r="56">
@@ -1138,10 +1138,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I59">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M59">
-            <v>698000</v>
+            <v>1443000</v>
           </cell>
         </row>
         <row r="60">
@@ -1152,7 +1152,7 @@
             <v>0</v>
           </cell>
           <cell r="M60">
-            <v>1045000</v>
+            <v>1575000</v>
           </cell>
         </row>
         <row r="61">
@@ -1160,10 +1160,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I61">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M61">
-            <v>1045000</v>
+            <v>1875000</v>
           </cell>
         </row>
         <row r="62">
@@ -1174,7 +1174,7 @@
             <v>0</v>
           </cell>
           <cell r="M62">
-            <v>3911000</v>
+            <v>4056000</v>
           </cell>
         </row>
         <row r="63">
@@ -1185,7 +1185,7 @@
             <v>0</v>
           </cell>
           <cell r="M63">
-            <v>3575000</v>
+            <v>4105000</v>
           </cell>
         </row>
         <row r="64">
@@ -1193,10 +1193,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I64">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M64">
-            <v>996000</v>
+            <v>1826000</v>
           </cell>
         </row>
         <row r="65">
@@ -1204,10 +1204,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I65">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M65">
-            <v>5475000</v>
+            <v>7305000</v>
           </cell>
         </row>
         <row r="66">
@@ -1215,10 +1215,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I66">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M66">
-            <v>3180000</v>
+            <v>4010000</v>
           </cell>
         </row>
         <row r="67">
@@ -1229,7 +1229,7 @@
             <v>0</v>
           </cell>
           <cell r="M67">
-            <v>1045000</v>
+            <v>1575000</v>
           </cell>
         </row>
         <row r="68">
@@ -1237,10 +1237,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I68">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M68">
-            <v>1266000</v>
+            <v>1951000</v>
           </cell>
         </row>
         <row r="69">
@@ -1251,7 +1251,7 @@
             <v>3</v>
           </cell>
           <cell r="M69">
-            <v>779000</v>
+            <v>1164000</v>
           </cell>
         </row>
         <row r="70">
@@ -1259,10 +1259,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I70">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M70">
-            <v>6266000</v>
+            <v>6951000</v>
           </cell>
         </row>
         <row r="71">
@@ -1270,10 +1270,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I71">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M71">
-            <v>1770000</v>
+            <v>2455000</v>
           </cell>
         </row>
         <row r="72">
@@ -1281,10 +1281,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I72">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M72">
-            <v>1128000</v>
+            <v>1813000</v>
           </cell>
         </row>
         <row r="73">
@@ -1303,10 +1303,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I74">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M74">
-            <v>1266000</v>
+            <v>1951000</v>
           </cell>
         </row>
         <row r="75">
@@ -1314,10 +1314,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I75">
-            <v>4</v>
+            <v>14</v>
           </cell>
           <cell r="M75">
-            <v>1798000</v>
+            <v>2883000</v>
           </cell>
         </row>
         <row r="76">
@@ -1325,10 +1325,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I76">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M76">
-            <v>1173000</v>
+            <v>1690000</v>
           </cell>
         </row>
         <row r="77">
@@ -1336,10 +1336,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I77">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M77">
-            <v>1018000</v>
+            <v>1703000</v>
           </cell>
         </row>
         <row r="78">
@@ -1350,7 +1350,7 @@
             <v>0</v>
           </cell>
           <cell r="M78">
-            <v>0</v>
+            <v>336000</v>
           </cell>
         </row>
         <row r="79">
@@ -1358,10 +1358,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I79">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M79">
-            <v>492000</v>
+            <v>642000</v>
           </cell>
         </row>
         <row r="80">
@@ -1391,10 +1391,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I82">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M82">
-            <v>355200</v>
+            <v>445200</v>
           </cell>
         </row>
         <row r="83">
@@ -1405,7 +1405,7 @@
             <v>3</v>
           </cell>
           <cell r="M83">
-            <v>630000</v>
+            <v>798000</v>
           </cell>
         </row>
         <row r="84">
@@ -1416,7 +1416,7 @@
             <v>3</v>
           </cell>
           <cell r="M84">
-            <v>733200</v>
+            <v>901200</v>
           </cell>
         </row>
         <row r="85">
@@ -1424,10 +1424,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I85">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M85">
-            <v>486000</v>
+            <v>810000</v>
           </cell>
         </row>
         <row r="86">
@@ -1438,7 +1438,7 @@
             <v>3</v>
           </cell>
           <cell r="M86">
-            <v>3740800</v>
+            <v>4140800</v>
           </cell>
         </row>
         <row r="87">
@@ -1471,7 +1471,7 @@
             <v>0</v>
           </cell>
           <cell r="M89">
-            <v>851000</v>
+            <v>1351000</v>
           </cell>
         </row>
         <row r="90">
@@ -1493,7 +1493,7 @@
             <v>3</v>
           </cell>
           <cell r="M91">
-            <v>327600</v>
+            <v>631800</v>
           </cell>
         </row>
         <row r="92">
@@ -1504,7 +1504,7 @@
             <v>3</v>
           </cell>
           <cell r="M92">
-            <v>540800</v>
+            <v>845000</v>
           </cell>
         </row>
         <row r="93">
@@ -1515,7 +1515,7 @@
             <v>22</v>
           </cell>
           <cell r="M93">
-            <v>327600</v>
+            <v>631800</v>
           </cell>
         </row>
         <row r="94">
@@ -1559,7 +1559,7 @@
             <v>0</v>
           </cell>
           <cell r="M97">
-            <v>326400</v>
+            <v>396600</v>
           </cell>
         </row>
         <row r="98">
@@ -1567,10 +1567,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I98">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M98">
-            <v>632000</v>
+            <v>722000</v>
           </cell>
         </row>
         <row r="99">
@@ -1578,10 +1578,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I99">
-            <v>20</v>
+            <v>23</v>
           </cell>
           <cell r="M99">
-            <v>105600</v>
+            <v>327600</v>
           </cell>
         </row>
         <row r="100">
@@ -1589,10 +1589,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I100">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M100">
-            <v>2678400</v>
+            <v>3368800</v>
           </cell>
         </row>
         <row r="101">
@@ -1625,7 +1625,7 @@
             <v>5</v>
           </cell>
           <cell r="M103">
-            <v>1142800</v>
+            <v>1195600</v>
           </cell>
         </row>
         <row r="104">
@@ -1636,7 +1636,7 @@
             <v>4</v>
           </cell>
           <cell r="M104">
-            <v>2343000</v>
+            <v>2475000</v>
           </cell>
         </row>
         <row r="105">
@@ -1644,10 +1644,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I105">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="M105">
-            <v>2519500</v>
+            <v>4609500</v>
           </cell>
         </row>
         <row r="106">
@@ -1658,7 +1658,7 @@
             <v>3</v>
           </cell>
           <cell r="M106">
-            <v>480800</v>
+            <v>612800</v>
           </cell>
         </row>
         <row r="107">
@@ -1680,7 +1680,7 @@
             <v>3</v>
           </cell>
           <cell r="M108">
-            <v>1863600</v>
+            <v>1929600</v>
           </cell>
         </row>
         <row r="109">
@@ -1724,7 +1724,7 @@
             <v>3</v>
           </cell>
           <cell r="M112">
-            <v>694800</v>
+            <v>862800</v>
           </cell>
         </row>
         <row r="113">
@@ -1735,7 +1735,7 @@
             <v>3</v>
           </cell>
           <cell r="M113">
-            <v>1376800</v>
+            <v>2344800</v>
           </cell>
         </row>
         <row r="114">
@@ -1746,7 +1746,7 @@
             <v>6</v>
           </cell>
           <cell r="M114">
-            <v>1601200</v>
+            <v>1718200</v>
           </cell>
         </row>
         <row r="115">
@@ -1754,10 +1754,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I115">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M115">
-            <v>583000</v>
+            <v>897400</v>
           </cell>
         </row>
         <row r="116">
@@ -1765,10 +1765,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I116">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M116">
-            <v>394800</v>
+            <v>484800</v>
           </cell>
         </row>
         <row r="117">
@@ -1779,7 +1779,7 @@
             <v>1</v>
           </cell>
           <cell r="M117">
-            <v>858400</v>
+            <v>928600</v>
           </cell>
         </row>
         <row r="118">
@@ -1801,7 +1801,7 @@
             <v>0</v>
           </cell>
           <cell r="M119">
-            <v>855200</v>
+            <v>987200</v>
           </cell>
         </row>
         <row r="120">
@@ -1823,7 +1823,7 @@
             <v>6</v>
           </cell>
           <cell r="M121">
-            <v>468000</v>
+            <v>507600</v>
           </cell>
         </row>
         <row r="122">
@@ -1831,10 +1831,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I122">
-            <v>9</v>
+            <v>12</v>
           </cell>
           <cell r="M122">
-            <v>1885500</v>
+            <v>1975500</v>
           </cell>
         </row>
         <row r="123">
@@ -1845,7 +1845,7 @@
             <v>3</v>
           </cell>
           <cell r="M123">
-            <v>361200</v>
+            <v>529200</v>
           </cell>
         </row>
         <row r="124">
@@ -1856,7 +1856,7 @@
             <v>3</v>
           </cell>
           <cell r="M124">
-            <v>414000</v>
+            <v>684200</v>
           </cell>
         </row>
         <row r="125">
@@ -1867,7 +1867,7 @@
             <v>8</v>
           </cell>
           <cell r="M125">
-            <v>1520800</v>
+            <v>1591000</v>
           </cell>
         </row>
         <row r="126">
@@ -1875,10 +1875,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I126">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M126">
-            <v>1106200</v>
+            <v>1196200</v>
           </cell>
         </row>
         <row r="127">
@@ -1889,7 +1889,7 @@
             <v>3</v>
           </cell>
           <cell r="M127">
-            <v>5692800</v>
+            <v>5809800</v>
           </cell>
         </row>
         <row r="128">
@@ -1900,7 +1900,7 @@
             <v>0</v>
           </cell>
           <cell r="M128">
-            <v>408000</v>
+            <v>478200</v>
           </cell>
         </row>
         <row r="129">
@@ -1908,10 +1908,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I129">
-            <v>12</v>
+            <v>22</v>
           </cell>
           <cell r="M129">
-            <v>1636900</v>
+            <v>2053900</v>
           </cell>
         </row>
         <row r="130">
@@ -1919,10 +1919,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I130">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M130">
-            <v>1052800</v>
+            <v>1274800</v>
           </cell>
         </row>
         <row r="131">
@@ -1944,7 +1944,7 @@
             <v>6</v>
           </cell>
           <cell r="M132">
-            <v>4477000</v>
+            <v>5477000</v>
           </cell>
         </row>
         <row r="133">
@@ -1966,7 +1966,7 @@
             <v>0</v>
           </cell>
           <cell r="M134">
-            <v>356400</v>
+            <v>1132200</v>
           </cell>
         </row>
         <row r="135">
@@ -1977,7 +1977,7 @@
             <v>3</v>
           </cell>
           <cell r="M135">
-            <v>493200</v>
+            <v>965400</v>
           </cell>
         </row>
         <row r="136">
@@ -1988,7 +1988,7 @@
             <v>3</v>
           </cell>
           <cell r="M136">
-            <v>625200</v>
+            <v>1097400</v>
           </cell>
         </row>
         <row r="137">
@@ -1999,7 +1999,7 @@
             <v>3</v>
           </cell>
           <cell r="M137">
-            <v>493200</v>
+            <v>797400</v>
           </cell>
         </row>
         <row r="138">
@@ -2007,10 +2007,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I138">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M138">
-            <v>1450000</v>
+            <v>1600000</v>
           </cell>
         </row>
         <row r="139">
@@ -2021,7 +2021,7 @@
             <v>0</v>
           </cell>
           <cell r="M139">
-            <v>617000</v>
+            <v>917000</v>
           </cell>
         </row>
         <row r="140">
@@ -2043,7 +2043,7 @@
             <v>3</v>
           </cell>
           <cell r="M141">
-            <v>361200</v>
+            <v>529200</v>
           </cell>
         </row>
         <row r="142">
@@ -2065,7 +2065,7 @@
             <v>3</v>
           </cell>
           <cell r="M143">
-            <v>361200</v>
+            <v>833400</v>
           </cell>
         </row>
         <row r="144">
@@ -2076,7 +2076,7 @@
             <v>12</v>
           </cell>
           <cell r="M144">
-            <v>987000</v>
+            <v>1487000</v>
           </cell>
         </row>
         <row r="145">
@@ -2084,10 +2084,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I145">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M145">
-            <v>0</v>
+            <v>792000</v>
           </cell>
         </row>
         <row r="146">
@@ -2098,7 +2098,7 @@
             <v>3</v>
           </cell>
           <cell r="M146">
-            <v>850500</v>
+            <v>1154700</v>
           </cell>
         </row>
         <row r="147">
@@ -2109,7 +2109,7 @@
             <v>0</v>
           </cell>
           <cell r="M147">
-            <v>681300</v>
+            <v>849300</v>
           </cell>
         </row>
         <row r="148">
@@ -2120,7 +2120,7 @@
             <v>0</v>
           </cell>
           <cell r="M148">
-            <v>303600</v>
+            <v>607800</v>
           </cell>
         </row>
         <row r="149">
@@ -2131,7 +2131,7 @@
             <v>0</v>
           </cell>
           <cell r="M149">
-            <v>1316800</v>
+            <v>1621000</v>
           </cell>
         </row>
         <row r="150">
@@ -2164,7 +2164,7 @@
             <v>1</v>
           </cell>
           <cell r="M152">
-            <v>9565000</v>
+            <v>12565000</v>
           </cell>
         </row>
         <row r="153">
@@ -2194,10 +2194,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I155">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M155">
-            <v>300000</v>
+            <v>390000</v>
           </cell>
         </row>
         <row r="156">
@@ -2205,10 +2205,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I156">
-            <v>24</v>
+            <v>27</v>
           </cell>
           <cell r="M156">
-            <v>234000</v>
+            <v>324000</v>
           </cell>
         </row>
         <row r="157">
@@ -2216,10 +2216,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I157">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M157">
-            <v>168000</v>
+            <v>258000</v>
           </cell>
         </row>
         <row r="158">
@@ -2227,10 +2227,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I158">
-            <v>24</v>
+            <v>27</v>
           </cell>
           <cell r="M158">
-            <v>234000</v>
+            <v>324000</v>
           </cell>
         </row>
         <row r="159">
@@ -2238,10 +2238,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I159">
-            <v>0</v>
+            <v>8</v>
           </cell>
           <cell r="M159">
-            <v>1761500</v>
+            <v>2001500</v>
           </cell>
         </row>
         <row r="160">
@@ -2249,10 +2249,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I160">
-            <v>0</v>
+            <v>8</v>
           </cell>
           <cell r="M160">
-            <v>3313000</v>
+            <v>4753000</v>
           </cell>
         </row>
         <row r="161">
@@ -2260,10 +2260,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I161">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="M161">
-            <v>90000</v>
+            <v>180000</v>
           </cell>
         </row>
         <row r="162">
@@ -2271,10 +2271,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I162">
-            <v>0</v>
+            <v>13</v>
           </cell>
           <cell r="M162">
-            <v>5813000</v>
+            <v>6437000</v>
           </cell>
         </row>
         <row r="163">
@@ -2282,10 +2282,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I163">
-            <v>0</v>
+            <v>8</v>
           </cell>
           <cell r="M163">
-            <v>3670000</v>
+            <v>5910000</v>
           </cell>
         </row>
         <row r="164">
@@ -2293,10 +2293,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I164">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M164">
-            <v>300000</v>
+            <v>654000</v>
           </cell>
         </row>
         <row r="165">
@@ -2304,10 +2304,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I165">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M165">
-            <v>385000</v>
+            <v>607000</v>
           </cell>
         </row>
         <row r="166">
@@ -2315,10 +2315,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I166">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M166">
-            <v>534000</v>
+            <v>1158000</v>
           </cell>
         </row>
         <row r="167">
@@ -2326,10 +2326,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I167">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M167">
-            <v>2963000</v>
+            <v>3185000</v>
           </cell>
         </row>
         <row r="168">
@@ -2337,10 +2337,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I168">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M168">
-            <v>919000</v>
+            <v>1273000</v>
           </cell>
         </row>
         <row r="169">
@@ -2351,7 +2351,7 @@
             <v>0</v>
           </cell>
           <cell r="M169">
-            <v>619000</v>
+            <v>1119000</v>
           </cell>
         </row>
         <row r="170">
@@ -2359,10 +2359,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I170">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M170">
-            <v>1600000</v>
+            <v>2212500</v>
           </cell>
         </row>
         <row r="171">
@@ -2370,10 +2370,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I171">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M171">
-            <v>253000</v>
+            <v>511000</v>
           </cell>
         </row>
         <row r="172">
@@ -2381,10 +2381,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I172">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M172">
-            <v>487000</v>
+            <v>877000</v>
           </cell>
         </row>
         <row r="173">
@@ -2392,10 +2392,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I173">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M173">
-            <v>253000</v>
+            <v>343000</v>
           </cell>
         </row>
         <row r="174">
@@ -2458,10 +2458,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I179">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M179">
-            <v>1328000</v>
+            <v>1820000</v>
           </cell>
         </row>
         <row r="180">
@@ -2469,10 +2469,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I180">
-            <v>2</v>
+            <v>5</v>
           </cell>
           <cell r="M180">
-            <v>2000000</v>
+            <v>3090000</v>
           </cell>
         </row>
         <row r="181">
@@ -2483,7 +2483,7 @@
             <v>20</v>
           </cell>
           <cell r="M181">
-            <v>404000</v>
+            <v>572000</v>
           </cell>
         </row>
         <row r="182">
@@ -2502,10 +2502,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I183">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M183">
-            <v>654000</v>
+            <v>894000</v>
           </cell>
         </row>
         <row r="184">
@@ -2516,7 +2516,7 @@
             <v>6</v>
           </cell>
           <cell r="M184">
-            <v>3612000</v>
+            <v>4612000</v>
           </cell>
         </row>
         <row r="185">
@@ -2527,7 +2527,7 @@
             <v>3</v>
           </cell>
           <cell r="M185">
-            <v>390000</v>
+            <v>690000</v>
           </cell>
         </row>
         <row r="186">
@@ -2535,10 +2535,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I186">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M186">
-            <v>536000</v>
+            <v>794000</v>
           </cell>
         </row>
         <row r="187">
@@ -2568,10 +2568,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I189">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M189">
-            <v>536000</v>
+            <v>1028000</v>
           </cell>
         </row>
         <row r="190">
@@ -2689,10 +2689,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I200">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M200">
-            <v>0</v>
+            <v>768000</v>
           </cell>
         </row>
         <row r="201">
@@ -2700,10 +2700,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I201">
-            <v>4</v>
+            <v>14</v>
           </cell>
           <cell r="M201">
-            <v>0</v>
+            <v>768000</v>
           </cell>
         </row>
         <row r="202">
@@ -2835,7 +2835,7 @@
             <v>0</v>
           </cell>
           <cell r="M213">
-            <v>534000</v>
+            <v>684000</v>
           </cell>
         </row>
         <row r="214">
@@ -2923,7 +2923,7 @@
             <v>13</v>
           </cell>
           <cell r="M221">
-            <v>1594000</v>
+            <v>1828000</v>
           </cell>
         </row>
         <row r="222">
@@ -2931,10 +2931,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I222">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M222">
-            <v>1324000</v>
+            <v>2648000</v>
           </cell>
         </row>
         <row r="223">
@@ -2953,10 +2953,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I224">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M224">
-            <v>319000</v>
+            <v>577000</v>
           </cell>
         </row>
         <row r="225">
@@ -2964,10 +2964,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I225">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M225">
-            <v>2695000</v>
+            <v>2885000</v>
           </cell>
         </row>
         <row r="226">
@@ -2975,10 +2975,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I226">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M226">
-            <v>487000</v>
+            <v>745000</v>
           </cell>
         </row>
         <row r="227">
@@ -3019,10 +3019,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I230">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M230">
-            <v>6090000</v>
+            <v>10180000</v>
           </cell>
         </row>
         <row r="231">
@@ -3030,10 +3030,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I231">
-            <v>1</v>
+            <v>4</v>
           </cell>
           <cell r="M231">
-            <v>253000</v>
+            <v>511000</v>
           </cell>
         </row>
         <row r="232">
@@ -3041,10 +3041,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I232">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M232">
-            <v>319000</v>
+            <v>643000</v>
           </cell>
         </row>
         <row r="233">
@@ -3052,10 +3052,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I233">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M233">
-            <v>3135000</v>
+            <v>6395000</v>
           </cell>
         </row>
         <row r="234">
@@ -3063,10 +3063,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I234">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M234">
-            <v>524000</v>
+            <v>782000</v>
           </cell>
         </row>
         <row r="235">
@@ -3077,7 +3077,7 @@
             <v>20</v>
           </cell>
           <cell r="M235">
-            <v>6139000</v>
+            <v>6307000</v>
           </cell>
         </row>
         <row r="236">
@@ -3085,10 +3085,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I236">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M236">
-            <v>1402000</v>
+            <v>1492000</v>
           </cell>
         </row>
         <row r="237">
@@ -3096,10 +3096,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I237">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M237">
-            <v>319000</v>
+            <v>643000</v>
           </cell>
         </row>
         <row r="238">
@@ -3107,10 +3107,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I238">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M238">
-            <v>253000</v>
+            <v>577000</v>
           </cell>
         </row>
         <row r="239">
@@ -3121,7 +3121,7 @@
             <v>4</v>
           </cell>
           <cell r="M239">
-            <v>1790000</v>
+            <v>2458000</v>
           </cell>
         </row>
         <row r="240">
@@ -3129,10 +3129,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I240">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M240">
-            <v>253000</v>
+            <v>877000</v>
           </cell>
         </row>
         <row r="241">
@@ -3143,7 +3143,7 @@
             <v>0</v>
           </cell>
           <cell r="M241">
-            <v>3657000</v>
+            <v>3891000</v>
           </cell>
         </row>
         <row r="242">
@@ -3151,10 +3151,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I242">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M242">
-            <v>253000</v>
+            <v>511000</v>
           </cell>
         </row>
         <row r="243">
@@ -3162,10 +3162,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I243">
-            <v>10</v>
+            <v>15</v>
           </cell>
           <cell r="M243">
-            <v>487000</v>
+            <v>655000</v>
           </cell>
         </row>
         <row r="244">
@@ -3187,7 +3187,7 @@
             <v>5</v>
           </cell>
           <cell r="M245">
-            <v>3741000</v>
+            <v>3886000</v>
           </cell>
         </row>
         <row r="246">
@@ -3195,10 +3195,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I246">
-            <v>9</v>
+            <v>14</v>
           </cell>
           <cell r="M246">
-            <v>3707000</v>
+            <v>3915000</v>
           </cell>
         </row>
         <row r="247">
@@ -3217,10 +3217,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I248">
-            <v>9</v>
+            <v>14</v>
           </cell>
           <cell r="M248">
-            <v>705000</v>
+            <v>913000</v>
           </cell>
         </row>
         <row r="249">
@@ -3228,10 +3228,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I249">
-            <v>6</v>
+            <v>11</v>
           </cell>
           <cell r="M249">
-            <v>1786000</v>
+            <v>2194000</v>
           </cell>
         </row>
         <row r="250">
@@ -3239,10 +3239,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I250">
-            <v>9</v>
+            <v>14</v>
           </cell>
           <cell r="M250">
-            <v>3750500</v>
+            <v>4016500</v>
           </cell>
         </row>
         <row r="251">
@@ -3250,10 +3250,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I251">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M251">
-            <v>1058000</v>
+            <v>1888000</v>
           </cell>
         </row>
         <row r="252">
@@ -3261,10 +3261,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I252">
-            <v>9</v>
+            <v>14</v>
           </cell>
           <cell r="M252">
-            <v>4240500</v>
+            <v>4448500</v>
           </cell>
         </row>
         <row r="253">
@@ -3272,10 +3272,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I253">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M253">
-            <v>0</v>
+            <v>150000</v>
           </cell>
         </row>
         <row r="254">
@@ -3283,10 +3283,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I254">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M254">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="255">
@@ -3297,7 +3297,7 @@
             <v>6</v>
           </cell>
           <cell r="M255">
-            <v>748000</v>
+            <v>982000</v>
           </cell>
         </row>
         <row r="256">
@@ -3308,7 +3308,7 @@
             <v>11</v>
           </cell>
           <cell r="M256">
-            <v>3603200</v>
+            <v>3720200</v>
           </cell>
         </row>
         <row r="257">
@@ -3327,10 +3327,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I258">
-            <v>3</v>
+            <v>23</v>
           </cell>
           <cell r="M258">
-            <v>1007000</v>
+            <v>1841000</v>
           </cell>
         </row>
         <row r="259">
@@ -3338,10 +3338,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I259">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M259">
-            <v>660000</v>
+            <v>960000</v>
           </cell>
         </row>
         <row r="260">
@@ -3363,7 +3363,7 @@
             <v>3</v>
           </cell>
           <cell r="M261">
-            <v>616800</v>
+            <v>784800</v>
           </cell>
         </row>
         <row r="262">
@@ -3371,10 +3371,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I262">
-            <v>0</v>
+            <v>6</v>
           </cell>
           <cell r="M262">
-            <v>355200</v>
+            <v>1103400</v>
           </cell>
         </row>
         <row r="263">
@@ -3385,7 +3385,7 @@
             <v>3</v>
           </cell>
           <cell r="M263">
-            <v>577200</v>
+            <v>745200</v>
           </cell>
         </row>
         <row r="264">
@@ -3396,7 +3396,7 @@
             <v>0</v>
           </cell>
           <cell r="M264">
-            <v>456900</v>
+            <v>761100</v>
           </cell>
         </row>
         <row r="265">
@@ -3407,7 +3407,7 @@
             <v>3</v>
           </cell>
           <cell r="M265">
-            <v>880800</v>
+            <v>1392600</v>
           </cell>
         </row>
         <row r="266">
@@ -3418,7 +3418,7 @@
             <v>0</v>
           </cell>
           <cell r="M266">
-            <v>652800</v>
+            <v>1023000</v>
           </cell>
         </row>
         <row r="267">
@@ -3426,10 +3426,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I267">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M267">
-            <v>681300</v>
+            <v>1293900</v>
           </cell>
         </row>
         <row r="268">
@@ -3481,10 +3481,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I272">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M272">
-            <v>2412000</v>
+            <v>3666000</v>
           </cell>
         </row>
         <row r="273">
@@ -3525,10 +3525,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I276">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M276">
-            <v>0</v>
+            <v>119000</v>
           </cell>
         </row>
         <row r="277">
@@ -3649,7 +3649,7 @@
             <v>3</v>
           </cell>
           <cell r="M287">
-            <v>90000</v>
+            <v>148000</v>
           </cell>
         </row>
         <row r="288">
@@ -3734,10 +3734,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I295">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M295">
-            <v>1266000</v>
+            <v>1951000</v>
           </cell>
         </row>
         <row r="296">
@@ -3825,7 +3825,7 @@
             <v>0</v>
           </cell>
           <cell r="M303">
-            <v>224400</v>
+            <v>528600</v>
           </cell>
         </row>
         <row r="304">
@@ -3836,7 +3836,7 @@
             <v>0</v>
           </cell>
           <cell r="M304">
-            <v>132000</v>
+            <v>436200</v>
           </cell>
         </row>
         <row r="305">
@@ -3844,10 +3844,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I305">
-            <v>20</v>
+            <v>23</v>
           </cell>
           <cell r="M305">
-            <v>349000</v>
+            <v>673000</v>
           </cell>
         </row>
         <row r="306">
@@ -3855,10 +3855,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I306">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M306">
-            <v>302000</v>
+            <v>560000</v>
           </cell>
         </row>
         <row r="307">
@@ -3866,10 +3866,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I307">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M307">
-            <v>824000</v>
+            <v>1616000</v>
           </cell>
         </row>
         <row r="308">
@@ -3877,10 +3877,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I308">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M308">
-            <v>1201000</v>
+            <v>1536000</v>
           </cell>
         </row>
         <row r="309">
@@ -3888,10 +3888,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I309">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M309">
-            <v>811000</v>
+            <v>1635000</v>
           </cell>
         </row>
         <row r="310">
@@ -3899,10 +3899,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I310">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M310">
-            <v>319000</v>
+            <v>577000</v>
           </cell>
         </row>
         <row r="311">
@@ -3913,7 +3913,7 @@
             <v>19</v>
           </cell>
           <cell r="M311">
-            <v>6754000</v>
+            <v>6988000</v>
           </cell>
         </row>
         <row r="312">
@@ -3921,10 +3921,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I312">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M312">
-            <v>1045000</v>
+            <v>2135000</v>
           </cell>
         </row>
         <row r="313">
@@ -3932,10 +3932,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I313">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M313">
-            <v>0</v>
+            <v>90000</v>
           </cell>
         </row>
         <row r="314">
@@ -3961,7 +3961,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>118930000</v>
+        <v>144977000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.26723271641205626</v>
+        <v>0.32575966978281917</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-326112813.60751247</v>
+        <v>-300065813.60751247</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-18117378.533750694</v>
+        <v>-16670322.978195138</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>115972000</v>
+        <v>144305500</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.25863139675667579</v>
+        <v>0.32181848226011867</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-332434502.2821191</v>
+        <v>-304101002.2821191</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-18468583.460117728</v>
+        <v>-16894500.126784395</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>29247000</v>
+        <v>35031500</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.17978330552613897</v>
+        <v>0.21534102190101337</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-133432175.99138665</v>
+        <v>-127647675.99138665</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-7412898.6661881469</v>
+        <v>-7091537.5550770359</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>38826200</v>
+        <v>51673600</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.14989249764877888</v>
+        <v>0.19949119322787037</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-220200773.39112824</v>
+        <v>-207353373.39112824</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-12233376.299507124</v>
+        <v>-11519631.85506268</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>68057000</v>
+        <v>82875000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.17623877658836415</v>
+        <v>0.21461111435650526</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-318106597.57738662</v>
+        <v>-303288597.57738662</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-17672588.754299257</v>
+        <v>-16849366.532077033</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4445,19 +4445,19 @@
       </c>
       <c r="D11" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A11,[1]Sheet1!$I:$I)</f>
-        <v>130</v>
+        <v>350</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>0.17174540081746914</v>
+        <v>0.46239146373933998</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-626.93438881757243</v>
+        <v>-406.93438881757243</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-34.829688267642915</v>
+        <v>-22.60746604542069</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -4472,19 +4472,19 @@
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
-        <v>232</v>
+        <v>345</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>0.53067749673088327</v>
+        <v>0.78915403608687384</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-205.17700755954917</v>
+        <v>-92.177007559549168</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-11.398722642197177</v>
+        <v>-5.120944864419398</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -4499,19 +4499,19 @@
       </c>
       <c r="D13" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A13,[1]Sheet1!$I:$I)</f>
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="3"/>
-        <v>0.44108459878036421</v>
+        <v>0.83806073768269196</v>
       </c>
       <c r="F13" s="10">
         <f t="shared" si="4"/>
-        <v>-126.71387819141353</v>
+        <v>-36.713878191413528</v>
       </c>
       <c r="G13" s="19">
         <f t="shared" si="5"/>
-        <v>-7.0396598995229738</v>
+        <v>-2.0396598995229738</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.45592981893302076</v>
+        <v>0.53191812208852418</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-214.79760376551121</v>
+        <v>-184.79760376551121</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-11.933200209195068</v>
+        <v>-10.2665335425284</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>196</v>
+        <v>333</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.468476859393122</v>
+        <v>0.7959326233566818</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-222.3771216659535</v>
+        <v>-85.377121665953496</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-12.354284536997417</v>
+        <v>-4.7431734258863054</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -701,7 +701,7 @@
             <v>3</v>
           </cell>
           <cell r="M19">
-            <v>590000</v>
+            <v>1090000</v>
           </cell>
         </row>
         <row r="20">
@@ -731,7 +731,7 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I22">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="M22">
             <v>1150000</v>
@@ -1050,10 +1050,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I51">
-            <v>10</v>
+            <v>20</v>
           </cell>
           <cell r="M51">
-            <v>5549000</v>
+            <v>8074000</v>
           </cell>
         </row>
         <row r="52">
@@ -1083,10 +1083,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I54">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="M54">
-            <v>3612000</v>
+            <v>4512000</v>
           </cell>
         </row>
         <row r="55">
@@ -1094,10 +1094,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I55">
-            <v>0</v>
+            <v>30</v>
           </cell>
           <cell r="M55">
-            <v>3338000</v>
+            <v>4238000</v>
           </cell>
         </row>
         <row r="56">
@@ -1361,7 +1361,7 @@
             <v>8</v>
           </cell>
           <cell r="M79">
-            <v>642000</v>
+            <v>876000</v>
           </cell>
         </row>
         <row r="80">
@@ -1413,10 +1413,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I84">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M84">
-            <v>901200</v>
+            <v>991200</v>
           </cell>
         </row>
         <row r="85">
@@ -1424,10 +1424,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I85">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M85">
-            <v>810000</v>
+            <v>1170000</v>
           </cell>
         </row>
         <row r="86">
@@ -1435,10 +1435,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I86">
-            <v>3</v>
+            <v>16</v>
           </cell>
           <cell r="M86">
-            <v>4140800</v>
+            <v>5030800</v>
           </cell>
         </row>
         <row r="87">
@@ -1446,10 +1446,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I87">
-            <v>3</v>
+            <v>26</v>
           </cell>
           <cell r="M87">
-            <v>390000</v>
+            <v>1380000</v>
           </cell>
         </row>
         <row r="88">
@@ -1460,7 +1460,7 @@
             <v>3</v>
           </cell>
           <cell r="M88">
-            <v>604800</v>
+            <v>721800</v>
           </cell>
         </row>
         <row r="89">
@@ -1468,10 +1468,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I89">
-            <v>0</v>
+            <v>15</v>
           </cell>
           <cell r="M89">
-            <v>1351000</v>
+            <v>1801000</v>
           </cell>
         </row>
         <row r="90">
@@ -1479,10 +1479,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I90">
-            <v>0</v>
+            <v>14</v>
           </cell>
           <cell r="M90">
-            <v>344400</v>
+            <v>764400</v>
           </cell>
         </row>
         <row r="91">
@@ -1523,10 +1523,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I94">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M94">
-            <v>813600</v>
+            <v>906600</v>
           </cell>
         </row>
         <row r="95">
@@ -1534,10 +1534,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I95">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M95">
-            <v>405600</v>
+            <v>501600</v>
           </cell>
         </row>
         <row r="96">
@@ -1545,10 +1545,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I96">
-            <v>1</v>
+            <v>4</v>
           </cell>
           <cell r="M96">
-            <v>508800</v>
+            <v>601800</v>
           </cell>
         </row>
         <row r="97">
@@ -1556,10 +1556,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I97">
-            <v>0</v>
+            <v>6</v>
           </cell>
           <cell r="M97">
-            <v>396600</v>
+            <v>579600</v>
           </cell>
         </row>
         <row r="98">
@@ -1570,7 +1570,7 @@
             <v>3</v>
           </cell>
           <cell r="M98">
-            <v>722000</v>
+            <v>956000</v>
           </cell>
         </row>
         <row r="99">
@@ -1578,10 +1578,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I99">
-            <v>23</v>
+            <v>26</v>
           </cell>
           <cell r="M99">
-            <v>327600</v>
+            <v>420600</v>
           </cell>
         </row>
         <row r="100">
@@ -1589,10 +1589,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I100">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M100">
-            <v>3368800</v>
+            <v>3661800</v>
           </cell>
         </row>
         <row r="101">
@@ -1600,10 +1600,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I101">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M101">
-            <v>2195600</v>
+            <v>2385600</v>
           </cell>
         </row>
         <row r="102">
@@ -1611,10 +1611,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I102">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M102">
-            <v>397000</v>
+            <v>490000</v>
           </cell>
         </row>
         <row r="103">
@@ -1666,10 +1666,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I107">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M107">
-            <v>498000</v>
+            <v>588000</v>
           </cell>
         </row>
         <row r="108">
@@ -1677,10 +1677,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I108">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M108">
-            <v>1929600</v>
+            <v>2022600</v>
           </cell>
         </row>
         <row r="109">
@@ -1699,10 +1699,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I110">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M110">
-            <v>448600</v>
+            <v>541600</v>
           </cell>
         </row>
         <row r="111">
@@ -1732,10 +1732,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I113">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M113">
-            <v>2344800</v>
+            <v>2734800</v>
           </cell>
         </row>
         <row r="114">
@@ -1746,7 +1746,7 @@
             <v>6</v>
           </cell>
           <cell r="M114">
-            <v>1718200</v>
+            <v>1952200</v>
           </cell>
         </row>
         <row r="115">
@@ -1776,10 +1776,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I117">
-            <v>1</v>
+            <v>4</v>
           </cell>
           <cell r="M117">
-            <v>928600</v>
+            <v>1103600</v>
           </cell>
         </row>
         <row r="118">
@@ -1853,10 +1853,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I124">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M124">
-            <v>684200</v>
+            <v>774200</v>
           </cell>
         </row>
         <row r="125">
@@ -1897,10 +1897,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I128">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M128">
-            <v>478200</v>
+            <v>653200</v>
           </cell>
         </row>
         <row r="129">
@@ -1930,10 +1930,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I131">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M131">
-            <v>1090000</v>
+            <v>1890000</v>
           </cell>
         </row>
         <row r="132">
@@ -1941,10 +1941,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I132">
-            <v>6</v>
+            <v>21</v>
           </cell>
           <cell r="M132">
-            <v>5477000</v>
+            <v>7161000</v>
           </cell>
         </row>
         <row r="133">
@@ -2021,7 +2021,7 @@
             <v>0</v>
           </cell>
           <cell r="M139">
-            <v>917000</v>
+            <v>1151000</v>
           </cell>
         </row>
         <row r="140">
@@ -2029,10 +2029,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I140">
-            <v>0</v>
+            <v>7</v>
           </cell>
           <cell r="M140">
-            <v>734000</v>
+            <v>944000</v>
           </cell>
         </row>
         <row r="141">
@@ -2106,10 +2106,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I147">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M147">
-            <v>849300</v>
+            <v>939300</v>
           </cell>
         </row>
         <row r="148">
@@ -2150,10 +2150,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I151">
-            <v>2</v>
+            <v>8</v>
           </cell>
           <cell r="M151">
-            <v>300000</v>
+            <v>744000</v>
           </cell>
         </row>
         <row r="152">
@@ -2161,10 +2161,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I152">
-            <v>1</v>
+            <v>21</v>
           </cell>
           <cell r="M152">
-            <v>12565000</v>
+            <v>15210000</v>
           </cell>
         </row>
         <row r="153">
@@ -2172,10 +2172,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I153">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M153">
-            <v>168000</v>
+            <v>450000</v>
           </cell>
         </row>
         <row r="154">
@@ -2183,10 +2183,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I154">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M154">
-            <v>532000</v>
+            <v>682000</v>
           </cell>
         </row>
         <row r="155">
@@ -2274,7 +2274,7 @@
             <v>13</v>
           </cell>
           <cell r="M162">
-            <v>6437000</v>
+            <v>16437000</v>
           </cell>
         </row>
         <row r="163">
@@ -2502,10 +2502,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I183">
-            <v>6</v>
+            <v>11</v>
           </cell>
           <cell r="M183">
-            <v>894000</v>
+            <v>1044000</v>
           </cell>
         </row>
         <row r="184">
@@ -2513,10 +2513,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I184">
-            <v>6</v>
+            <v>16</v>
           </cell>
           <cell r="M184">
-            <v>4612000</v>
+            <v>5412000</v>
           </cell>
         </row>
         <row r="185">
@@ -2524,10 +2524,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I185">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M185">
-            <v>690000</v>
+            <v>990000</v>
           </cell>
         </row>
         <row r="186">
@@ -2546,10 +2546,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I187">
-            <v>3</v>
+            <v>23</v>
           </cell>
           <cell r="M187">
-            <v>8580000</v>
+            <v>11160000</v>
           </cell>
         </row>
         <row r="188">
@@ -2557,10 +2557,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I188">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M188">
-            <v>3420000</v>
+            <v>5040000</v>
           </cell>
         </row>
         <row r="189">
@@ -2579,10 +2579,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I190">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M190">
-            <v>190000</v>
+            <v>490000</v>
           </cell>
         </row>
         <row r="191">
@@ -3121,7 +3121,7 @@
             <v>4</v>
           </cell>
           <cell r="M239">
-            <v>2458000</v>
+            <v>2758000</v>
           </cell>
         </row>
         <row r="240">
@@ -3162,7 +3162,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I243">
-            <v>15</v>
+            <v>16</v>
           </cell>
           <cell r="M243">
             <v>655000</v>
@@ -3173,10 +3173,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I244">
-            <v>3</v>
+            <v>33</v>
           </cell>
           <cell r="M244">
-            <v>497000</v>
+            <v>1397000</v>
           </cell>
         </row>
         <row r="245">
@@ -3187,7 +3187,7 @@
             <v>5</v>
           </cell>
           <cell r="M245">
-            <v>3886000</v>
+            <v>4031000</v>
           </cell>
         </row>
         <row r="246">
@@ -3195,10 +3195,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I246">
-            <v>14</v>
+            <v>19</v>
           </cell>
           <cell r="M246">
-            <v>3915000</v>
+            <v>4065000</v>
           </cell>
         </row>
         <row r="247">
@@ -3206,10 +3206,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I247">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="M247">
-            <v>1129000</v>
+            <v>3654000</v>
           </cell>
         </row>
         <row r="248">
@@ -3228,10 +3228,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I249">
-            <v>11</v>
+            <v>16</v>
           </cell>
           <cell r="M249">
-            <v>2194000</v>
+            <v>2344000</v>
           </cell>
         </row>
         <row r="250">
@@ -3239,10 +3239,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I250">
-            <v>14</v>
+            <v>19</v>
           </cell>
           <cell r="M250">
-            <v>4016500</v>
+            <v>4166500</v>
           </cell>
         </row>
         <row r="251">
@@ -3250,10 +3250,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I251">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M251">
-            <v>1888000</v>
+            <v>4413000</v>
           </cell>
         </row>
         <row r="252">
@@ -3261,10 +3261,10 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I252">
-            <v>14</v>
+            <v>19</v>
           </cell>
           <cell r="M252">
-            <v>4448500</v>
+            <v>4598500</v>
           </cell>
         </row>
         <row r="253">
@@ -3404,10 +3404,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I265">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M265">
-            <v>1392600</v>
+            <v>1695100</v>
           </cell>
         </row>
         <row r="266">
@@ -3426,10 +3426,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I267">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M267">
-            <v>1293900</v>
+            <v>1596400</v>
           </cell>
         </row>
         <row r="268">
@@ -3481,10 +3481,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I272">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M272">
-            <v>3666000</v>
+            <v>4411000</v>
           </cell>
         </row>
         <row r="273">
@@ -3789,10 +3789,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I300">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M300">
-            <v>300000</v>
+            <v>522000</v>
           </cell>
         </row>
         <row r="301">
@@ -3800,10 +3800,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I301">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M301">
-            <v>300000</v>
+            <v>654000</v>
           </cell>
         </row>
         <row r="302">
@@ -3811,10 +3811,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I302">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M302">
-            <v>300000</v>
+            <v>522000</v>
           </cell>
         </row>
         <row r="303">
@@ -3961,7 +3961,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>144977000</v>
+        <v>153442000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.32575966978281917</v>
+        <v>0.3447803117102391</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-300065813.60751247</v>
+        <v>-291600813.60751247</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-16670322.978195138</v>
+        <v>-16200045.20041736</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>144305500</v>
+        <v>154674500</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.32181848226011867</v>
+        <v>0.34494258939778955</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-304101002.2821191</v>
+        <v>-293732002.2821191</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-16894500.126784395</v>
+        <v>-16318444.571228839</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>35031500</v>
+        <v>38831500</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.21534102190101337</v>
+        <v>0.23869988130537376</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-127647675.99138665</v>
+        <v>-123847675.99138665</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-7091537.5550770359</v>
+        <v>-6880426.4439659249</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>51673600</v>
+        <v>55058600</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.19949119322787037</v>
+        <v>0.21255933032449884</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-207353373.39112824</v>
+        <v>-203968373.39112824</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-11519631.85506268</v>
+        <v>-11331576.299507124</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>82875000</v>
+        <v>99372000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.21461111435650526</v>
+        <v>0.25733135029664728</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-303288597.57738662</v>
+        <v>-286791597.57738662</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-16849366.532077033</v>
+        <v>-15932866.532077035</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4445,19 +4445,19 @@
       </c>
       <c r="D11" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A11,[1]Sheet1!$I:$I)</f>
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>0.46239146373933998</v>
+        <v>0.51523620245240742</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-406.93438881757243</v>
+        <v>-366.93438881757243</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-22.60746604542069</v>
+        <v>-20.385243823198469</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -4472,19 +4472,19 @@
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
-        <v>345</v>
+        <v>456</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>0.78915403608687384</v>
+        <v>1.0430557694365636</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>-92.177007559549168</v>
+        <v>18.822992440450832</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>-5.120944864419398</v>
+        <v>1.0457218022472685</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -4499,19 +4499,19 @@
       </c>
       <c r="D13" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A13,[1]Sheet1!$I:$I)</f>
-        <v>190</v>
+        <v>301</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="3"/>
-        <v>0.83806073768269196</v>
+        <v>1.3276646423288962</v>
       </c>
       <c r="F13" s="10">
         <f t="shared" si="4"/>
-        <v>-36.713878191413528</v>
+        <v>74.286121808586472</v>
       </c>
       <c r="G13" s="19">
         <f t="shared" si="5"/>
-        <v>-2.0396598995229738</v>
+        <v>4.1270067671436932</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
-        <v>210</v>
+        <v>273</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.53191812208852418</v>
+        <v>0.69149355871508145</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-184.79760376551121</v>
+        <v>-121.79760376551121</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-10.2665335425284</v>
+        <v>-6.7665335425284008</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>333</v>
+        <v>430</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.7959326233566818</v>
+        <v>1.0277808649951146</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-85.377121665953496</v>
+        <v>11.622878334046504</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-4.7431734258863054</v>
+        <v>0.64571546300258353</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -1592,7 +1592,7 @@
             <v>9</v>
           </cell>
           <cell r="M100">
-            <v>3661800</v>
+            <v>3811800</v>
           </cell>
         </row>
         <row r="101">
@@ -2241,7 +2241,7 @@
             <v>8</v>
           </cell>
           <cell r="M159">
-            <v>2001500</v>
+            <v>2301500</v>
           </cell>
         </row>
         <row r="160">
@@ -3162,7 +3162,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I243">
-            <v>16</v>
+            <v>17</v>
           </cell>
           <cell r="M243">
             <v>655000</v>
@@ -3484,7 +3484,7 @@
             <v>23</v>
           </cell>
           <cell r="M272">
-            <v>4411000</v>
+            <v>4479000</v>
           </cell>
         </row>
         <row r="273">
@@ -3961,7 +3961,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>153442000</v>
+        <v>153510000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.3447803117102391</v>
+        <v>0.3449331059986106</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-291600813.60751247</v>
+        <v>-291532813.60751247</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-16200045.20041736</v>
+        <v>-16196267.422639582</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>55058600</v>
+        <v>55208600</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.21255933032449884</v>
+        <v>0.21313842059465962</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-203968373.39112824</v>
+        <v>-203818373.39112824</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-11331576.299507124</v>
+        <v>-11323242.96617379</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>99372000</v>
+        <v>99672000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.25733135029664728</v>
+        <v>0.2581082231087975</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-286791597.57738662</v>
+        <v>-286491597.57738662</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-15932866.532077035</v>
+        <v>-15916199.865410367</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4472,19 +4472,19 @@
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>1.0430557694365636</v>
+        <v>1.0453431724397142</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>18.822992440450832</v>
+        <v>19.822992440450832</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>1.0457218022472685</v>
+        <v>1.1012773578028241</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -731,7 +731,7 @@
             <v>DSE-BENGKAYANG01</v>
           </cell>
           <cell r="I22">
-            <v>6</v>
+            <v>5</v>
           </cell>
           <cell r="M22">
             <v>1150000</v>
@@ -1006,7 +1006,7 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I47">
-            <v>13</v>
+            <v>10</v>
           </cell>
           <cell r="M47">
             <v>1675000</v>
@@ -1105,10 +1105,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I56">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M56">
-            <v>426000</v>
+            <v>3376000</v>
           </cell>
         </row>
         <row r="57">
@@ -1116,10 +1116,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I57">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M57">
-            <v>1155000</v>
+            <v>3680000</v>
           </cell>
         </row>
         <row r="58">
@@ -1138,10 +1138,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I59">
-            <v>10</v>
+            <v>20</v>
           </cell>
           <cell r="M59">
-            <v>1443000</v>
+            <v>3968000</v>
           </cell>
         </row>
         <row r="60">
@@ -1314,7 +1314,7 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I75">
-            <v>14</v>
+            <v>13</v>
           </cell>
           <cell r="M75">
             <v>2883000</v>
@@ -1361,7 +1361,7 @@
             <v>8</v>
           </cell>
           <cell r="M79">
-            <v>876000</v>
+            <v>961000</v>
           </cell>
         </row>
         <row r="80">
@@ -1438,7 +1438,7 @@
             <v>16</v>
           </cell>
           <cell r="M86">
-            <v>5030800</v>
+            <v>5530800</v>
           </cell>
         </row>
         <row r="87">
@@ -1490,10 +1490,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I91">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M91">
-            <v>631800</v>
+            <v>721800</v>
           </cell>
         </row>
         <row r="92">
@@ -1501,10 +1501,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I92">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M92">
-            <v>845000</v>
+            <v>1250000</v>
           </cell>
         </row>
         <row r="93">
@@ -1512,10 +1512,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I93">
-            <v>22</v>
+            <v>25</v>
           </cell>
           <cell r="M93">
-            <v>631800</v>
+            <v>1061800</v>
           </cell>
         </row>
         <row r="94">
@@ -1526,7 +1526,7 @@
             <v>6</v>
           </cell>
           <cell r="M94">
-            <v>906600</v>
+            <v>1006600</v>
           </cell>
         </row>
         <row r="95">
@@ -1545,7 +1545,7 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I96">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="M96">
             <v>601800</v>
@@ -1578,10 +1578,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I99">
-            <v>26</v>
+            <v>29</v>
           </cell>
           <cell r="M99">
-            <v>420600</v>
+            <v>510600</v>
           </cell>
         </row>
         <row r="100">
@@ -1592,7 +1592,7 @@
             <v>9</v>
           </cell>
           <cell r="M100">
-            <v>3811800</v>
+            <v>4011800</v>
           </cell>
         </row>
         <row r="101">
@@ -1611,10 +1611,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I102">
-            <v>6</v>
+            <v>11</v>
           </cell>
           <cell r="M102">
-            <v>490000</v>
+            <v>810000</v>
           </cell>
         </row>
         <row r="103">
@@ -1622,10 +1622,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I103">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="M103">
-            <v>1195600</v>
+            <v>1845600</v>
           </cell>
         </row>
         <row r="104">
@@ -1633,10 +1633,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I104">
-            <v>4</v>
+            <v>8</v>
           </cell>
           <cell r="M104">
-            <v>2475000</v>
+            <v>2795000</v>
           </cell>
         </row>
         <row r="105">
@@ -1644,7 +1644,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I105">
-            <v>8</v>
+            <v>6</v>
           </cell>
           <cell r="M105">
             <v>4609500</v>
@@ -1655,10 +1655,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I106">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M106">
-            <v>612800</v>
+            <v>932800</v>
           </cell>
         </row>
         <row r="107">
@@ -1677,10 +1677,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I108">
-            <v>6</v>
+            <v>11</v>
           </cell>
           <cell r="M108">
-            <v>2022600</v>
+            <v>2512600</v>
           </cell>
         </row>
         <row r="109">
@@ -1688,10 +1688,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I109">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M109">
-            <v>397800</v>
+            <v>547800</v>
           </cell>
         </row>
         <row r="110">
@@ -1699,10 +1699,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I110">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M110">
-            <v>541600</v>
+            <v>631600</v>
           </cell>
         </row>
         <row r="111">
@@ -1710,10 +1710,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I111">
-            <v>23</v>
+            <v>28</v>
           </cell>
           <cell r="M111">
-            <v>681200</v>
+            <v>1001200</v>
           </cell>
         </row>
         <row r="112">
@@ -1746,7 +1746,7 @@
             <v>6</v>
           </cell>
           <cell r="M114">
-            <v>1952200</v>
+            <v>2037200</v>
           </cell>
         </row>
         <row r="115">
@@ -1754,10 +1754,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I115">
-            <v>6</v>
+            <v>11</v>
           </cell>
           <cell r="M115">
-            <v>897400</v>
+            <v>1547400</v>
           </cell>
         </row>
         <row r="116">
@@ -1776,7 +1776,7 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I117">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="M117">
             <v>1103600</v>
@@ -1787,10 +1787,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I118">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M118">
-            <v>312800</v>
+            <v>717800</v>
           </cell>
         </row>
         <row r="119">
@@ -1809,10 +1809,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I120">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M120">
-            <v>312800</v>
+            <v>632800</v>
           </cell>
         </row>
         <row r="121">
@@ -1820,10 +1820,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I121">
-            <v>6</v>
+            <v>11</v>
           </cell>
           <cell r="M121">
-            <v>507600</v>
+            <v>827600</v>
           </cell>
         </row>
         <row r="122">
@@ -1864,7 +1864,7 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I125">
-            <v>8</v>
+            <v>6</v>
           </cell>
           <cell r="M125">
             <v>1591000</v>
@@ -1911,7 +1911,7 @@
             <v>22</v>
           </cell>
           <cell r="M129">
-            <v>2053900</v>
+            <v>3053900</v>
           </cell>
         </row>
         <row r="130">
@@ -1941,7 +1941,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I132">
-            <v>21</v>
+            <v>18</v>
           </cell>
           <cell r="M132">
             <v>7161000</v>
@@ -2073,10 +2073,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I144">
-            <v>12</v>
+            <v>6</v>
           </cell>
           <cell r="M144">
-            <v>1487000</v>
+            <v>1572000</v>
           </cell>
         </row>
         <row r="145">
@@ -2150,7 +2150,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I151">
-            <v>8</v>
+            <v>6</v>
           </cell>
           <cell r="M151">
             <v>744000</v>
@@ -2205,7 +2205,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I156">
-            <v>27</v>
+            <v>23</v>
           </cell>
           <cell r="M156">
             <v>324000</v>
@@ -2227,7 +2227,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I158">
-            <v>27</v>
+            <v>23</v>
           </cell>
           <cell r="M158">
             <v>324000</v>
@@ -2260,7 +2260,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I161">
-            <v>8</v>
+            <v>6</v>
           </cell>
           <cell r="M161">
             <v>180000</v>
@@ -2362,7 +2362,7 @@
             <v>3</v>
           </cell>
           <cell r="M170">
-            <v>2212500</v>
+            <v>2362500</v>
           </cell>
         </row>
         <row r="171">
@@ -2447,7 +2447,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I178">
-            <v>24</v>
+            <v>20</v>
           </cell>
           <cell r="M178">
             <v>304200</v>
@@ -2469,7 +2469,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I180">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="M180">
             <v>3090000</v>
@@ -2590,7 +2590,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I191">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M191">
             <v>304200</v>
@@ -2612,10 +2612,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I193">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M193">
-            <v>3409000</v>
+            <v>4093000</v>
           </cell>
         </row>
         <row r="194">
@@ -2623,10 +2623,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I194">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M194">
-            <v>624000</v>
+            <v>942000</v>
           </cell>
         </row>
         <row r="195">
@@ -2634,10 +2634,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I195">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M195">
-            <v>624000</v>
+            <v>942000</v>
           </cell>
         </row>
         <row r="196">
@@ -2645,10 +2645,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I196">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M196">
-            <v>2045000</v>
+            <v>2390000</v>
           </cell>
         </row>
         <row r="197">
@@ -2656,10 +2656,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I197">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M197">
-            <v>456000</v>
+            <v>883000</v>
           </cell>
         </row>
         <row r="198">
@@ -2667,10 +2667,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I198">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M198">
-            <v>624000</v>
+            <v>1051000</v>
           </cell>
         </row>
         <row r="199">
@@ -2678,10 +2678,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I199">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="M199">
-            <v>366000</v>
+            <v>684000</v>
           </cell>
         </row>
         <row r="200">
@@ -2689,7 +2689,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I200">
-            <v>13</v>
+            <v>10</v>
           </cell>
           <cell r="M200">
             <v>768000</v>
@@ -2700,7 +2700,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I201">
-            <v>14</v>
+            <v>10</v>
           </cell>
           <cell r="M201">
             <v>768000</v>
@@ -2725,7 +2725,7 @@
             <v>0</v>
           </cell>
           <cell r="M203">
-            <v>3804200</v>
+            <v>5824200</v>
           </cell>
         </row>
         <row r="204">
@@ -2777,7 +2777,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I208">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M208">
             <v>666000</v>
@@ -2788,10 +2788,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I209">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M209">
-            <v>390000</v>
+            <v>672000</v>
           </cell>
         </row>
         <row r="210">
@@ -2799,10 +2799,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I210">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M210">
-            <v>132000</v>
+            <v>582000</v>
           </cell>
         </row>
         <row r="211">
@@ -2810,10 +2810,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I211">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M211">
-            <v>456000</v>
+            <v>942000</v>
           </cell>
         </row>
         <row r="212">
@@ -2832,10 +2832,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I213">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M213">
-            <v>684000</v>
+            <v>5184000</v>
           </cell>
         </row>
         <row r="214">
@@ -2865,10 +2865,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I216">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M216">
-            <v>456000</v>
+            <v>2178000</v>
           </cell>
         </row>
         <row r="217">
@@ -2876,10 +2876,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I217">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M217">
-            <v>456000</v>
+            <v>924000</v>
           </cell>
         </row>
         <row r="218">
@@ -2887,10 +2887,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I218">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M218">
-            <v>456000</v>
+            <v>1410000</v>
           </cell>
         </row>
         <row r="219">
@@ -2898,10 +2898,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I219">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M219">
-            <v>456000</v>
+            <v>1970000</v>
           </cell>
         </row>
         <row r="220">
@@ -2942,7 +2942,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I223">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="M223">
             <v>1392000</v>
@@ -3030,7 +3030,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I231">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="M231">
             <v>511000</v>
@@ -3118,10 +3118,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I239">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="M239">
-            <v>2758000</v>
+            <v>3058000</v>
           </cell>
         </row>
         <row r="240">
@@ -3162,7 +3162,7 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I243">
-            <v>17</v>
+            <v>0</v>
           </cell>
           <cell r="M243">
             <v>655000</v>
@@ -3187,7 +3187,7 @@
             <v>5</v>
           </cell>
           <cell r="M245">
-            <v>4031000</v>
+            <v>4199000</v>
           </cell>
         </row>
         <row r="246">
@@ -3198,7 +3198,7 @@
             <v>19</v>
           </cell>
           <cell r="M246">
-            <v>4065000</v>
+            <v>4137500</v>
           </cell>
         </row>
         <row r="247">
@@ -3206,10 +3206,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I247">
-            <v>15</v>
+            <v>25</v>
           </cell>
           <cell r="M247">
-            <v>3654000</v>
+            <v>6604000</v>
           </cell>
         </row>
         <row r="248">
@@ -3231,7 +3231,7 @@
             <v>16</v>
           </cell>
           <cell r="M249">
-            <v>2344000</v>
+            <v>2416500</v>
           </cell>
         </row>
         <row r="250">
@@ -3242,7 +3242,7 @@
             <v>19</v>
           </cell>
           <cell r="M250">
-            <v>4166500</v>
+            <v>4239000</v>
           </cell>
         </row>
         <row r="251">
@@ -3250,10 +3250,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I251">
-            <v>23</v>
+            <v>33</v>
           </cell>
           <cell r="M251">
-            <v>4413000</v>
+            <v>6938000</v>
           </cell>
         </row>
         <row r="252">
@@ -3264,7 +3264,7 @@
             <v>19</v>
           </cell>
           <cell r="M252">
-            <v>4598500</v>
+            <v>4671000</v>
           </cell>
         </row>
         <row r="253">
@@ -3297,7 +3297,7 @@
             <v>6</v>
           </cell>
           <cell r="M255">
-            <v>982000</v>
+            <v>1067000</v>
           </cell>
         </row>
         <row r="256">
@@ -3305,10 +3305,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I256">
-            <v>11</v>
+            <v>9</v>
           </cell>
           <cell r="M256">
-            <v>3720200</v>
+            <v>3805200</v>
           </cell>
         </row>
         <row r="257">
@@ -3316,10 +3316,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I257">
-            <v>0</v>
+            <v>9</v>
           </cell>
           <cell r="M257">
-            <v>351000</v>
+            <v>2621000</v>
           </cell>
         </row>
         <row r="258">
@@ -3330,7 +3330,7 @@
             <v>23</v>
           </cell>
           <cell r="M258">
-            <v>1841000</v>
+            <v>1926000</v>
           </cell>
         </row>
         <row r="259">
@@ -3341,7 +3341,7 @@
             <v>13</v>
           </cell>
           <cell r="M259">
-            <v>960000</v>
+            <v>1045000</v>
           </cell>
         </row>
         <row r="260">
@@ -3481,10 +3481,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I272">
-            <v>23</v>
+            <v>33</v>
           </cell>
           <cell r="M272">
-            <v>4479000</v>
+            <v>7429000</v>
           </cell>
         </row>
         <row r="273">
@@ -3492,10 +3492,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I273">
-            <v>4</v>
+            <v>13</v>
           </cell>
           <cell r="M273">
-            <v>873000</v>
+            <v>3398000</v>
           </cell>
         </row>
         <row r="274">
@@ -3547,7 +3547,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I278">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M278">
             <v>304200</v>
@@ -3701,7 +3701,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I292">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="M292">
             <v>0</v>
@@ -3712,7 +3712,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I293">
-            <v>4</v>
+            <v>0</v>
           </cell>
           <cell r="M293">
             <v>0</v>
@@ -3961,7 +3961,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>153510000</v>
+        <v>172628000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.3449331059986106</v>
+        <v>0.38789077077928574</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-291532813.60751247</v>
+        <v>-272414813.60751247</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-16196267.422639582</v>
+        <v>-15134156.31152847</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>154674500</v>
+        <v>168337500</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.34494258939778955</v>
+        <v>0.37541270954650185</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-293732002.2821191</v>
+        <v>-280069002.2821191</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-16318444.571228839</v>
+        <v>-15559389.015673283</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>38831500</v>
+        <v>39121500</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.23869988130537376</v>
+        <v>0.24048253110202231</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-123847675.99138665</v>
+        <v>-123557675.99138665</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-6880426.4439659249</v>
+        <v>-6864315.3328548139</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>55208600</v>
+        <v>60878600</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.21313842059465962</v>
+        <v>0.23502803280673745</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-203818373.39112824</v>
+        <v>-198148373.39112824</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-11323242.96617379</v>
+        <v>-11008242.96617379</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>99672000</v>
+        <v>106057000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.2581082231087975</v>
+        <v>0.27464266612739524</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-286491597.57738662</v>
+        <v>-280106597.57738662</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-15916199.865410367</v>
+        <v>-15561477.643188145</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4445,19 +4445,19 @@
       </c>
       <c r="D11" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A11,[1]Sheet1!$I:$I)</f>
-        <v>390</v>
+        <v>455</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>0.51523620245240742</v>
+        <v>0.60110890286114194</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-366.93438881757243</v>
+        <v>-301.93438881757243</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-20.385243823198469</v>
+        <v>-16.774132712087358</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -4472,19 +4472,19 @@
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
-        <v>457</v>
+        <v>513</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>1.0453431724397142</v>
+        <v>1.1734377406161343</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>19.822992440450832</v>
+        <v>75.822992440450832</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>1.1012773578028241</v>
+        <v>4.212388468913935</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -4499,19 +4499,19 @@
       </c>
       <c r="D13" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A13,[1]Sheet1!$I:$I)</f>
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="3"/>
-        <v>1.3276646423288962</v>
+        <v>1.3232537963410926</v>
       </c>
       <c r="F13" s="10">
         <f t="shared" si="4"/>
-        <v>74.286121808586472</v>
+        <v>73.286121808586472</v>
       </c>
       <c r="G13" s="19">
         <f t="shared" si="5"/>
-        <v>4.1270067671436932</v>
+        <v>4.0714512115881369</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
-        <v>273</v>
+        <v>338</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.69149355871508145</v>
+        <v>0.85613488221867229</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-121.79760376551121</v>
+        <v>-56.797603765511212</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-6.7665335425284008</v>
+        <v>-3.1554224314172896</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>430</v>
+        <v>396</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>1.0277808649951146</v>
+        <v>0.94651447101875674</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>11.622878334046504</v>
+        <v>-22.377121665953496</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>0.64571546300258353</v>
+        <v>-1.2431734258863054</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -657,7 +657,7 @@
             <v>3</v>
           </cell>
           <cell r="M15">
-            <v>590000</v>
+            <v>1090000</v>
           </cell>
         </row>
         <row r="16">
@@ -973,10 +973,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I44">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M44">
-            <v>4216000</v>
+            <v>6016000</v>
           </cell>
         </row>
         <row r="45">
@@ -987,7 +987,7 @@
             <v>3</v>
           </cell>
           <cell r="M45">
-            <v>3711000</v>
+            <v>5211000</v>
           </cell>
         </row>
         <row r="46">
@@ -998,7 +998,7 @@
             <v>3</v>
           </cell>
           <cell r="M46">
-            <v>3711000</v>
+            <v>5211000</v>
           </cell>
         </row>
         <row r="47">
@@ -1086,7 +1086,7 @@
             <v>30</v>
           </cell>
           <cell r="M54">
-            <v>4512000</v>
+            <v>4584500</v>
           </cell>
         </row>
         <row r="55">
@@ -1097,7 +1097,7 @@
             <v>30</v>
           </cell>
           <cell r="M55">
-            <v>4238000</v>
+            <v>4310500</v>
           </cell>
         </row>
         <row r="56">
@@ -1119,7 +1119,7 @@
             <v>10</v>
           </cell>
           <cell r="M57">
-            <v>3680000</v>
+            <v>4340000</v>
           </cell>
         </row>
         <row r="58">
@@ -1405,7 +1405,7 @@
             <v>3</v>
           </cell>
           <cell r="M83">
-            <v>798000</v>
+            <v>883000</v>
           </cell>
         </row>
         <row r="84">
@@ -1416,7 +1416,7 @@
             <v>6</v>
           </cell>
           <cell r="M84">
-            <v>991200</v>
+            <v>1076200</v>
           </cell>
         </row>
         <row r="85">
@@ -1427,7 +1427,7 @@
             <v>9</v>
           </cell>
           <cell r="M85">
-            <v>1170000</v>
+            <v>1255000</v>
           </cell>
         </row>
         <row r="86">
@@ -1438,7 +1438,7 @@
             <v>16</v>
           </cell>
           <cell r="M86">
-            <v>5530800</v>
+            <v>5780800</v>
           </cell>
         </row>
         <row r="87">
@@ -1471,7 +1471,7 @@
             <v>15</v>
           </cell>
           <cell r="M89">
-            <v>1801000</v>
+            <v>1886000</v>
           </cell>
         </row>
         <row r="90">
@@ -1482,7 +1482,7 @@
             <v>14</v>
           </cell>
           <cell r="M90">
-            <v>764400</v>
+            <v>849400</v>
           </cell>
         </row>
         <row r="91">
@@ -1534,10 +1534,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I95">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M95">
-            <v>501600</v>
+            <v>676600</v>
           </cell>
         </row>
         <row r="96">
@@ -1548,7 +1548,7 @@
             <v>3</v>
           </cell>
           <cell r="M96">
-            <v>601800</v>
+            <v>771800</v>
           </cell>
         </row>
         <row r="97">
@@ -1570,7 +1570,7 @@
             <v>3</v>
           </cell>
           <cell r="M98">
-            <v>956000</v>
+            <v>1456000</v>
           </cell>
         </row>
         <row r="99">
@@ -1592,7 +1592,7 @@
             <v>9</v>
           </cell>
           <cell r="M100">
-            <v>4011800</v>
+            <v>4211800</v>
           </cell>
         </row>
         <row r="101">
@@ -1647,7 +1647,7 @@
             <v>6</v>
           </cell>
           <cell r="M105">
-            <v>4609500</v>
+            <v>4694500</v>
           </cell>
         </row>
         <row r="106">
@@ -1669,7 +1669,7 @@
             <v>6</v>
           </cell>
           <cell r="M107">
-            <v>588000</v>
+            <v>758000</v>
           </cell>
         </row>
         <row r="108">
@@ -1680,7 +1680,7 @@
             <v>11</v>
           </cell>
           <cell r="M108">
-            <v>2512600</v>
+            <v>3512600</v>
           </cell>
         </row>
         <row r="109">
@@ -1721,10 +1721,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I112">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M112">
-            <v>862800</v>
+            <v>1182800</v>
           </cell>
         </row>
         <row r="113">
@@ -1732,10 +1732,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I113">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M113">
-            <v>2734800</v>
+            <v>2909800</v>
           </cell>
         </row>
         <row r="114">
@@ -1834,7 +1834,7 @@
             <v>12</v>
           </cell>
           <cell r="M122">
-            <v>1975500</v>
+            <v>2060500</v>
           </cell>
         </row>
         <row r="123">
@@ -1878,7 +1878,7 @@
             <v>3</v>
           </cell>
           <cell r="M126">
-            <v>1196200</v>
+            <v>1281200</v>
           </cell>
         </row>
         <row r="127">
@@ -1889,7 +1889,7 @@
             <v>3</v>
           </cell>
           <cell r="M127">
-            <v>5809800</v>
+            <v>5894800</v>
           </cell>
         </row>
         <row r="128">
@@ -1911,7 +1911,7 @@
             <v>22</v>
           </cell>
           <cell r="M129">
-            <v>3053900</v>
+            <v>3138900</v>
           </cell>
         </row>
         <row r="130">
@@ -1944,7 +1944,7 @@
             <v>18</v>
           </cell>
           <cell r="M132">
-            <v>7161000</v>
+            <v>8161000</v>
           </cell>
         </row>
         <row r="133">
@@ -1977,7 +1977,7 @@
             <v>3</v>
           </cell>
           <cell r="M135">
-            <v>965400</v>
+            <v>1050400</v>
           </cell>
         </row>
         <row r="136">
@@ -1988,7 +1988,7 @@
             <v>3</v>
           </cell>
           <cell r="M136">
-            <v>1097400</v>
+            <v>1352400</v>
           </cell>
         </row>
         <row r="137">
@@ -1999,7 +1999,7 @@
             <v>3</v>
           </cell>
           <cell r="M137">
-            <v>797400</v>
+            <v>882400</v>
           </cell>
         </row>
         <row r="138">
@@ -2010,7 +2010,7 @@
             <v>5</v>
           </cell>
           <cell r="M138">
-            <v>1600000</v>
+            <v>2100000</v>
           </cell>
         </row>
         <row r="139">
@@ -2021,7 +2021,7 @@
             <v>0</v>
           </cell>
           <cell r="M139">
-            <v>1151000</v>
+            <v>2151000</v>
           </cell>
         </row>
         <row r="140">
@@ -2032,7 +2032,7 @@
             <v>7</v>
           </cell>
           <cell r="M140">
-            <v>944000</v>
+            <v>1029000</v>
           </cell>
         </row>
         <row r="141">
@@ -2065,7 +2065,7 @@
             <v>3</v>
           </cell>
           <cell r="M143">
-            <v>833400</v>
+            <v>1130900</v>
           </cell>
         </row>
         <row r="144">
@@ -2087,7 +2087,7 @@
             <v>3</v>
           </cell>
           <cell r="M145">
-            <v>792000</v>
+            <v>1111000</v>
           </cell>
         </row>
         <row r="146">
@@ -2095,10 +2095,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I146">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M146">
-            <v>1154700</v>
+            <v>1361700</v>
           </cell>
         </row>
         <row r="147">
@@ -2219,7 +2219,7 @@
             <v>3</v>
           </cell>
           <cell r="M157">
-            <v>258000</v>
+            <v>358000</v>
           </cell>
         </row>
         <row r="158">
@@ -2241,7 +2241,7 @@
             <v>8</v>
           </cell>
           <cell r="M159">
-            <v>2301500</v>
+            <v>2801500</v>
           </cell>
         </row>
         <row r="160">
@@ -2714,7 +2714,7 @@
             <v>2</v>
           </cell>
           <cell r="M202">
-            <v>4304200</v>
+            <v>6324200</v>
           </cell>
         </row>
         <row r="203">
@@ -2824,7 +2824,7 @@
             <v>3</v>
           </cell>
           <cell r="M212">
-            <v>560000</v>
+            <v>939000</v>
           </cell>
         </row>
         <row r="213">
@@ -2846,7 +2846,7 @@
             <v>3</v>
           </cell>
           <cell r="M214">
-            <v>626000</v>
+            <v>1160000</v>
           </cell>
         </row>
         <row r="215">
@@ -2857,7 +2857,7 @@
             <v>3</v>
           </cell>
           <cell r="M215">
-            <v>626000</v>
+            <v>926000</v>
           </cell>
         </row>
         <row r="216">
@@ -2912,7 +2912,7 @@
             <v>0</v>
           </cell>
           <cell r="M220">
-            <v>302000</v>
+            <v>470000</v>
           </cell>
         </row>
         <row r="221">
@@ -2923,7 +2923,7 @@
             <v>13</v>
           </cell>
           <cell r="M221">
-            <v>1828000</v>
+            <v>2362000</v>
           </cell>
         </row>
         <row r="222">
@@ -2934,7 +2934,7 @@
             <v>6</v>
           </cell>
           <cell r="M222">
-            <v>2648000</v>
+            <v>4484000</v>
           </cell>
         </row>
         <row r="223">
@@ -2945,7 +2945,7 @@
             <v>3</v>
           </cell>
           <cell r="M223">
-            <v>1392000</v>
+            <v>1869000</v>
           </cell>
         </row>
         <row r="224">
@@ -2989,7 +2989,7 @@
             <v>3</v>
           </cell>
           <cell r="M227">
-            <v>2222000</v>
+            <v>2267000</v>
           </cell>
         </row>
         <row r="228">
@@ -3000,7 +3000,7 @@
             <v>3</v>
           </cell>
           <cell r="M228">
-            <v>2090000</v>
+            <v>2735000</v>
           </cell>
         </row>
         <row r="229">
@@ -3011,7 +3011,7 @@
             <v>3</v>
           </cell>
           <cell r="M229">
-            <v>560000</v>
+            <v>939000</v>
           </cell>
         </row>
         <row r="230">
@@ -3121,7 +3121,7 @@
             <v>3</v>
           </cell>
           <cell r="M239">
-            <v>3058000</v>
+            <v>3358000</v>
           </cell>
         </row>
         <row r="240">
@@ -3198,7 +3198,7 @@
             <v>19</v>
           </cell>
           <cell r="M246">
-            <v>4137500</v>
+            <v>4210000</v>
           </cell>
         </row>
         <row r="247">
@@ -3206,10 +3206,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I247">
-            <v>25</v>
+            <v>35</v>
           </cell>
           <cell r="M247">
-            <v>6604000</v>
+            <v>6904000</v>
           </cell>
         </row>
         <row r="248">
@@ -3220,7 +3220,7 @@
             <v>14</v>
           </cell>
           <cell r="M248">
-            <v>913000</v>
+            <v>985500</v>
           </cell>
         </row>
         <row r="249">
@@ -3231,7 +3231,7 @@
             <v>16</v>
           </cell>
           <cell r="M249">
-            <v>2416500</v>
+            <v>2789000</v>
           </cell>
         </row>
         <row r="250">
@@ -3242,7 +3242,7 @@
             <v>19</v>
           </cell>
           <cell r="M250">
-            <v>4239000</v>
+            <v>4311500</v>
           </cell>
         </row>
         <row r="251">
@@ -3264,7 +3264,7 @@
             <v>19</v>
           </cell>
           <cell r="M252">
-            <v>4671000</v>
+            <v>4743500</v>
           </cell>
         </row>
         <row r="253">
@@ -3297,7 +3297,7 @@
             <v>6</v>
           </cell>
           <cell r="M255">
-            <v>1067000</v>
+            <v>6117000</v>
           </cell>
         </row>
         <row r="256">
@@ -3330,7 +3330,7 @@
             <v>23</v>
           </cell>
           <cell r="M258">
-            <v>1926000</v>
+            <v>2245000</v>
           </cell>
         </row>
         <row r="259">
@@ -3363,7 +3363,7 @@
             <v>3</v>
           </cell>
           <cell r="M261">
-            <v>784800</v>
+            <v>855000</v>
           </cell>
         </row>
         <row r="262">
@@ -3385,7 +3385,7 @@
             <v>3</v>
           </cell>
           <cell r="M263">
-            <v>745200</v>
+            <v>862200</v>
           </cell>
         </row>
         <row r="264">
@@ -3418,7 +3418,7 @@
             <v>0</v>
           </cell>
           <cell r="M266">
-            <v>1023000</v>
+            <v>1623000</v>
           </cell>
         </row>
         <row r="267">
@@ -3481,10 +3481,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I272">
-            <v>33</v>
+            <v>43</v>
           </cell>
           <cell r="M272">
-            <v>7429000</v>
+            <v>8442000</v>
           </cell>
         </row>
         <row r="273">
@@ -3569,10 +3569,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I280">
-            <v>8</v>
+            <v>18</v>
           </cell>
           <cell r="M280">
-            <v>1801000</v>
+            <v>3601000</v>
           </cell>
         </row>
         <row r="281">
@@ -3580,10 +3580,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I281">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M281">
-            <v>1951000</v>
+            <v>3751000</v>
           </cell>
         </row>
         <row r="282">
@@ -3591,10 +3591,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I282">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M282">
-            <v>4551000</v>
+            <v>5511000</v>
           </cell>
         </row>
         <row r="283">
@@ -3613,10 +3613,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I284">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M284">
-            <v>3161000</v>
+            <v>4121000</v>
           </cell>
         </row>
         <row r="285">
@@ -3624,10 +3624,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I285">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M285">
-            <v>1566000</v>
+            <v>2856000</v>
           </cell>
         </row>
         <row r="286">
@@ -3635,10 +3635,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I286">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M286">
-            <v>3869000</v>
+            <v>6394000</v>
           </cell>
         </row>
         <row r="287">
@@ -3660,7 +3660,7 @@
             <v>3</v>
           </cell>
           <cell r="M288">
-            <v>502000</v>
+            <v>670000</v>
           </cell>
         </row>
         <row r="289">
@@ -3671,7 +3671,7 @@
             <v>3</v>
           </cell>
           <cell r="M289">
-            <v>1126000</v>
+            <v>1637000</v>
           </cell>
         </row>
         <row r="290">
@@ -3682,7 +3682,7 @@
             <v>3</v>
           </cell>
           <cell r="M290">
-            <v>560000</v>
+            <v>962000</v>
           </cell>
         </row>
         <row r="291">
@@ -3693,7 +3693,7 @@
             <v>3</v>
           </cell>
           <cell r="M291">
-            <v>626000</v>
+            <v>3296000</v>
           </cell>
         </row>
         <row r="292">
@@ -4280,23 +4280,23 @@
         <v>3</v>
       </c>
       <c r="C4" s="10">
-        <v>445042813.60751247</v>
+        <v>437430636.51666558</v>
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>172628000</v>
+        <v>188736000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.38789077077928574</v>
+        <v>0.43146497808872469</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-272414813.60751247</v>
+        <v>-248694636.51666558</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-15134156.31152847</v>
+        <v>-13816368.695370309</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4307,23 +4307,23 @@
         <v>3</v>
       </c>
       <c r="C5" s="10">
-        <v>448406502.2821191</v>
+        <v>440736791.41455084</v>
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>168337500</v>
+        <v>177685500</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.37541270954650185</v>
+        <v>0.40315558732847312</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-280069002.2821191</v>
+        <v>-263051291.41455084</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-15559389.015673283</v>
+        <v>-14613960.634141713</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4334,23 +4334,23 @@
         <v>3</v>
       </c>
       <c r="C6" s="10">
-        <v>162679175.99138665</v>
+        <v>159896651.12237126</v>
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>39121500</v>
+        <v>40429000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.24048253110202231</v>
+        <v>0.25284457001578531</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-123557675.99138665</v>
+        <v>-119467651.12237126</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-6864315.3328548139</v>
+        <v>-6637091.7290206254</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4361,23 +4361,23 @@
         <v>3</v>
       </c>
       <c r="C7" s="10">
-        <v>259026973.39112824</v>
+        <v>254596480.11616376</v>
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>60878600</v>
+        <v>65060300</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.23502803280673745</v>
+        <v>0.25554281021605318</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-198148373.39112824</v>
+        <v>-189536180.11616376</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-11008242.96617379</v>
+        <v>-10529787.78423132</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4388,23 +4388,23 @@
         <v>3</v>
       </c>
       <c r="C8" s="10">
-        <v>386163597.57738662</v>
+        <v>379558512.40149158</v>
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>106057000</v>
+        <v>118295000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.27464266612739524</v>
+        <v>0.31166472660971239</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-280106597.57738662</v>
+        <v>-261263512.40149158</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-15561477.643188145</v>
+        <v>-14514639.577860644</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4441,23 +4441,23 @@
         <v>3</v>
       </c>
       <c r="C11" s="10">
-        <v>756.93438881757243</v>
+        <v>820</v>
       </c>
       <c r="D11" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A11,[1]Sheet1!$I:$I)</f>
-        <v>455</v>
+        <v>545</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>0.60110890286114194</v>
+        <v>0.66463414634146345</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-301.93438881757243</v>
+        <v>-275</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-16.774132712087358</v>
+        <v>-15.277777777777779</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -4468,7 +4468,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="10">
-        <v>437.17700755954917</v>
+        <v>474</v>
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
@@ -4476,15 +4476,15 @@
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>1.1734377406161343</v>
+        <v>1.0822784810126582</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>75.822992440450832</v>
+        <v>39</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>4.212388468913935</v>
+        <v>2.1666666666666665</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -4495,7 +4495,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="10">
-        <v>226.71387819141353</v>
+        <v>246</v>
       </c>
       <c r="D13" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A13,[1]Sheet1!$I:$I)</f>
@@ -4503,15 +4503,15 @@
       </c>
       <c r="E13" s="9">
         <f t="shared" si="3"/>
-        <v>1.3232537963410926</v>
+        <v>1.2195121951219512</v>
       </c>
       <c r="F13" s="10">
         <f t="shared" si="4"/>
-        <v>73.286121808586472</v>
+        <v>54</v>
       </c>
       <c r="G13" s="19">
         <f t="shared" si="5"/>
-        <v>4.0714512115881369</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5">
@@ -4522,23 +4522,23 @@
         <v>3</v>
       </c>
       <c r="C14" s="10">
-        <v>394.79760376551121</v>
+        <v>428</v>
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.85613488221867229</v>
+        <v>0.82242990654205606</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-56.797603765511212</v>
+        <v>-76</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-3.1554224314172896</v>
+        <v>-4.2222222222222223</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -4549,7 +4549,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="10">
-        <v>418.3771216659535</v>
+        <v>453</v>
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
@@ -4557,15 +4557,15 @@
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.94651447101875674</v>
+        <v>0.8741721854304636</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-22.377121665953496</v>
+        <v>-57</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-1.2431734258863054</v>
+        <v>-3.1666666666666665</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -701,7 +701,7 @@
             <v>3</v>
           </cell>
           <cell r="M19">
-            <v>1090000</v>
+            <v>2090000</v>
           </cell>
         </row>
         <row r="20">
@@ -800,7 +800,7 @@
             <v>4</v>
           </cell>
           <cell r="M28">
-            <v>1120000</v>
+            <v>3120000</v>
           </cell>
         </row>
         <row r="29">
@@ -1237,10 +1237,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I68">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M68">
-            <v>1951000</v>
+            <v>4476000</v>
           </cell>
         </row>
         <row r="69">
@@ -1248,10 +1248,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I69">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M69">
-            <v>1164000</v>
+            <v>3689000</v>
           </cell>
         </row>
         <row r="70">
@@ -1259,10 +1259,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I70">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M70">
-            <v>6951000</v>
+            <v>7911000</v>
           </cell>
         </row>
         <row r="71">
@@ -1270,10 +1270,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I71">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M71">
-            <v>2455000</v>
+            <v>8415000</v>
           </cell>
         </row>
         <row r="72">
@@ -1281,10 +1281,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I72">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M72">
-            <v>1813000</v>
+            <v>3103000</v>
           </cell>
         </row>
         <row r="73">
@@ -1292,10 +1292,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I73">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M73">
-            <v>425000</v>
+            <v>1385000</v>
           </cell>
         </row>
         <row r="74">
@@ -1303,10 +1303,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I74">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M74">
-            <v>1951000</v>
+            <v>3241000</v>
           </cell>
         </row>
         <row r="75">
@@ -1314,10 +1314,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I75">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M75">
-            <v>2883000</v>
+            <v>4243000</v>
           </cell>
         </row>
         <row r="76">
@@ -1325,10 +1325,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I76">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M76">
-            <v>1690000</v>
+            <v>2650000</v>
           </cell>
         </row>
         <row r="77">
@@ -1336,10 +1336,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I77">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M77">
-            <v>1703000</v>
+            <v>2663000</v>
           </cell>
         </row>
         <row r="78">
@@ -1347,10 +1347,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I78">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M78">
-            <v>336000</v>
+            <v>1296000</v>
           </cell>
         </row>
         <row r="79">
@@ -1369,10 +1369,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I80">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M80">
-            <v>52800</v>
+            <v>406800</v>
           </cell>
         </row>
         <row r="81">
@@ -1380,10 +1380,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I81">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M81">
-            <v>52800</v>
+            <v>406800</v>
           </cell>
         </row>
         <row r="82">
@@ -1394,7 +1394,7 @@
             <v>3</v>
           </cell>
           <cell r="M82">
-            <v>445200</v>
+            <v>515400</v>
           </cell>
         </row>
         <row r="83">
@@ -1438,7 +1438,7 @@
             <v>16</v>
           </cell>
           <cell r="M86">
-            <v>5780800</v>
+            <v>5980800</v>
           </cell>
         </row>
         <row r="87">
@@ -1449,7 +1449,7 @@
             <v>26</v>
           </cell>
           <cell r="M87">
-            <v>1380000</v>
+            <v>1680000</v>
           </cell>
         </row>
         <row r="88">
@@ -1581,7 +1581,7 @@
             <v>29</v>
           </cell>
           <cell r="M99">
-            <v>510600</v>
+            <v>651000</v>
           </cell>
         </row>
         <row r="100">
@@ -1592,7 +1592,7 @@
             <v>9</v>
           </cell>
           <cell r="M100">
-            <v>4211800</v>
+            <v>4482000</v>
           </cell>
         </row>
         <row r="101">
@@ -1625,7 +1625,7 @@
             <v>8</v>
           </cell>
           <cell r="M103">
-            <v>1845600</v>
+            <v>1915800</v>
           </cell>
         </row>
         <row r="104">
@@ -1636,7 +1636,7 @@
             <v>8</v>
           </cell>
           <cell r="M104">
-            <v>2795000</v>
+            <v>2865200</v>
           </cell>
         </row>
         <row r="105">
@@ -1658,7 +1658,7 @@
             <v>8</v>
           </cell>
           <cell r="M106">
-            <v>932800</v>
+            <v>1003000</v>
           </cell>
         </row>
         <row r="107">
@@ -1680,7 +1680,7 @@
             <v>11</v>
           </cell>
           <cell r="M108">
-            <v>3512600</v>
+            <v>3582800</v>
           </cell>
         </row>
         <row r="109">
@@ -1713,7 +1713,7 @@
             <v>28</v>
           </cell>
           <cell r="M111">
-            <v>1001200</v>
+            <v>1071400</v>
           </cell>
         </row>
         <row r="112">
@@ -1757,7 +1757,7 @@
             <v>11</v>
           </cell>
           <cell r="M115">
-            <v>1547400</v>
+            <v>1617600</v>
           </cell>
         </row>
         <row r="116">
@@ -1768,7 +1768,7 @@
             <v>3</v>
           </cell>
           <cell r="M116">
-            <v>484800</v>
+            <v>555000</v>
           </cell>
         </row>
         <row r="117">
@@ -1779,7 +1779,7 @@
             <v>3</v>
           </cell>
           <cell r="M117">
-            <v>1103600</v>
+            <v>1603600</v>
           </cell>
         </row>
         <row r="118">
@@ -1798,10 +1798,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I119">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M119">
-            <v>987200</v>
+            <v>1077200</v>
           </cell>
         </row>
         <row r="120">
@@ -1823,7 +1823,7 @@
             <v>11</v>
           </cell>
           <cell r="M121">
-            <v>827600</v>
+            <v>897800</v>
           </cell>
         </row>
         <row r="122">
@@ -1867,7 +1867,7 @@
             <v>6</v>
           </cell>
           <cell r="M125">
-            <v>1591000</v>
+            <v>1661200</v>
           </cell>
         </row>
         <row r="126">
@@ -1922,7 +1922,7 @@
             <v>3</v>
           </cell>
           <cell r="M130">
-            <v>1274800</v>
+            <v>3345000</v>
           </cell>
         </row>
         <row r="131">
@@ -1963,10 +1963,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I134">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="M134">
-            <v>1132200</v>
+            <v>1252200</v>
           </cell>
         </row>
         <row r="135">
@@ -2197,7 +2197,7 @@
             <v>3</v>
           </cell>
           <cell r="M155">
-            <v>390000</v>
+            <v>475000</v>
           </cell>
         </row>
         <row r="156">
@@ -2241,7 +2241,7 @@
             <v>8</v>
           </cell>
           <cell r="M159">
-            <v>2801500</v>
+            <v>2971500</v>
           </cell>
         </row>
         <row r="160">
@@ -2252,7 +2252,7 @@
             <v>8</v>
           </cell>
           <cell r="M160">
-            <v>4753000</v>
+            <v>4923000</v>
           </cell>
         </row>
         <row r="161">
@@ -2263,7 +2263,7 @@
             <v>6</v>
           </cell>
           <cell r="M161">
-            <v>180000</v>
+            <v>265000</v>
           </cell>
         </row>
         <row r="162">
@@ -2274,7 +2274,7 @@
             <v>13</v>
           </cell>
           <cell r="M162">
-            <v>16437000</v>
+            <v>16607000</v>
           </cell>
         </row>
         <row r="163">
@@ -2285,7 +2285,7 @@
             <v>8</v>
           </cell>
           <cell r="M163">
-            <v>5910000</v>
+            <v>6080000</v>
           </cell>
         </row>
         <row r="164">
@@ -2362,7 +2362,7 @@
             <v>3</v>
           </cell>
           <cell r="M170">
-            <v>2362500</v>
+            <v>2512500</v>
           </cell>
         </row>
         <row r="171">
@@ -2461,7 +2461,7 @@
             <v>6</v>
           </cell>
           <cell r="M179">
-            <v>1820000</v>
+            <v>4490000</v>
           </cell>
         </row>
         <row r="180">
@@ -2472,7 +2472,7 @@
             <v>3</v>
           </cell>
           <cell r="M180">
-            <v>3090000</v>
+            <v>4090000</v>
           </cell>
         </row>
         <row r="181">
@@ -2483,7 +2483,7 @@
             <v>20</v>
           </cell>
           <cell r="M181">
-            <v>572000</v>
+            <v>704000</v>
           </cell>
         </row>
         <row r="182">
@@ -2494,7 +2494,7 @@
             <v>0</v>
           </cell>
           <cell r="M182">
-            <v>217000</v>
+            <v>385000</v>
           </cell>
         </row>
         <row r="183">
@@ -2516,7 +2516,7 @@
             <v>16</v>
           </cell>
           <cell r="M184">
-            <v>5412000</v>
+            <v>6216000</v>
           </cell>
         </row>
         <row r="185">
@@ -2538,7 +2538,7 @@
             <v>3</v>
           </cell>
           <cell r="M186">
-            <v>794000</v>
+            <v>1028000</v>
           </cell>
         </row>
         <row r="187">
@@ -2571,7 +2571,7 @@
             <v>3</v>
           </cell>
           <cell r="M189">
-            <v>1028000</v>
+            <v>3038000</v>
           </cell>
         </row>
         <row r="190">
@@ -3231,7 +3231,7 @@
             <v>16</v>
           </cell>
           <cell r="M249">
-            <v>2789000</v>
+            <v>2934000</v>
           </cell>
         </row>
         <row r="250">
@@ -3242,7 +3242,7 @@
             <v>19</v>
           </cell>
           <cell r="M250">
-            <v>4311500</v>
+            <v>4456500</v>
           </cell>
         </row>
         <row r="251">
@@ -3264,7 +3264,7 @@
             <v>19</v>
           </cell>
           <cell r="M252">
-            <v>4743500</v>
+            <v>4888500</v>
           </cell>
         </row>
         <row r="253">
@@ -3374,7 +3374,7 @@
             <v>6</v>
           </cell>
           <cell r="M262">
-            <v>1103400</v>
+            <v>1173600</v>
           </cell>
         </row>
         <row r="263">
@@ -3393,10 +3393,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I264">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M264">
-            <v>761100</v>
+            <v>851100</v>
           </cell>
         </row>
         <row r="265">
@@ -3407,7 +3407,7 @@
             <v>6</v>
           </cell>
           <cell r="M265">
-            <v>1695100</v>
+            <v>1765300</v>
           </cell>
         </row>
         <row r="266">
@@ -3415,10 +3415,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I266">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M266">
-            <v>1623000</v>
+            <v>1713000</v>
           </cell>
         </row>
         <row r="267">
@@ -3484,7 +3484,7 @@
             <v>43</v>
           </cell>
           <cell r="M272">
-            <v>8442000</v>
+            <v>8466000</v>
           </cell>
         </row>
         <row r="273">
@@ -3734,10 +3734,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I295">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M295">
-            <v>1951000</v>
+            <v>4476000</v>
           </cell>
         </row>
         <row r="296">
@@ -3847,7 +3847,7 @@
             <v>23</v>
           </cell>
           <cell r="M305">
-            <v>673000</v>
+            <v>841000</v>
           </cell>
         </row>
         <row r="306">
@@ -3858,7 +3858,7 @@
             <v>3</v>
           </cell>
           <cell r="M306">
-            <v>560000</v>
+            <v>860000</v>
           </cell>
         </row>
         <row r="307">
@@ -3869,7 +3869,7 @@
             <v>6</v>
           </cell>
           <cell r="M307">
-            <v>1616000</v>
+            <v>1952000</v>
           </cell>
         </row>
         <row r="308">
@@ -3880,7 +3880,7 @@
             <v>6</v>
           </cell>
           <cell r="M308">
-            <v>1536000</v>
+            <v>1781000</v>
           </cell>
         </row>
         <row r="309">
@@ -3891,7 +3891,7 @@
             <v>6</v>
           </cell>
           <cell r="M309">
-            <v>1635000</v>
+            <v>1935000</v>
           </cell>
         </row>
         <row r="310">
@@ -3902,7 +3902,7 @@
             <v>3</v>
           </cell>
           <cell r="M310">
-            <v>577000</v>
+            <v>745000</v>
           </cell>
         </row>
         <row r="311">
@@ -3913,7 +3913,7 @@
             <v>19</v>
           </cell>
           <cell r="M311">
-            <v>6988000</v>
+            <v>8056000</v>
           </cell>
         </row>
         <row r="312">
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>188736000</v>
+        <v>211035000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.43146497808872469</v>
+        <v>0.48244220313535313</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-248694636.51666558</v>
+        <v>-226395636.51666558</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-13816368.695370309</v>
+        <v>-12577535.362036977</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>177685500</v>
+        <v>187438500</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.40315558732847312</v>
+        <v>0.42528444107970548</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-263051291.41455084</v>
+        <v>-253298291.41455084</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-14613960.634141713</v>
+        <v>-14072127.300808379</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>40429000</v>
+        <v>43864000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.25284457001578531</v>
+        <v>0.27432719629900337</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-119467651.12237126</v>
+        <v>-116032651.12237126</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-6637091.7290206254</v>
+        <v>-6446258.3956872923</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>65060300</v>
+        <v>69981500</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.25554281021605318</v>
+        <v>0.27487222120301824</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-189536180.11616376</v>
+        <v>-184614980.11616376</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-10529787.78423132</v>
+        <v>-10256387.78423132</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>118295000</v>
+        <v>119645000</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.31166472660971239</v>
+        <v>0.315221490470595</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-261263512.40149158</v>
+        <v>-259913512.40149158</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-14514639.577860644</v>
+        <v>-14439639.577860644</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4445,19 +4445,19 @@
       </c>
       <c r="D11" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A11,[1]Sheet1!$I:$I)</f>
-        <v>545</v>
+        <v>665</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>0.66463414634146345</v>
+        <v>0.81097560975609762</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-275</v>
+        <v>-155</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-15.277777777777779</v>
+        <v>-8.6111111111111107</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.82242990654205606</v>
+        <v>0.87149532710280375</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-76</v>
+        <v>-55</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-4.2222222222222223</v>
+        <v>-3.0555555555555554</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -734,7 +734,7 @@
             <v>5</v>
           </cell>
           <cell r="M22">
-            <v>1150000</v>
+            <v>2150000</v>
           </cell>
         </row>
         <row r="23">
@@ -1086,7 +1086,7 @@
             <v>30</v>
           </cell>
           <cell r="M54">
-            <v>4584500</v>
+            <v>4729500</v>
           </cell>
         </row>
         <row r="55">
@@ -1097,7 +1097,7 @@
             <v>30</v>
           </cell>
           <cell r="M55">
-            <v>4310500</v>
+            <v>4455500</v>
           </cell>
         </row>
         <row r="56">
@@ -1108,7 +1108,7 @@
             <v>13</v>
           </cell>
           <cell r="M56">
-            <v>3376000</v>
+            <v>4426000</v>
           </cell>
         </row>
         <row r="57">
@@ -1152,7 +1152,7 @@
             <v>0</v>
           </cell>
           <cell r="M60">
-            <v>1575000</v>
+            <v>2535000</v>
           </cell>
         </row>
         <row r="61">
@@ -1163,7 +1163,7 @@
             <v>10</v>
           </cell>
           <cell r="M61">
-            <v>1875000</v>
+            <v>2835000</v>
           </cell>
         </row>
         <row r="62">
@@ -1185,7 +1185,7 @@
             <v>0</v>
           </cell>
           <cell r="M63">
-            <v>4105000</v>
+            <v>4237000</v>
           </cell>
         </row>
         <row r="64">
@@ -1207,7 +1207,7 @@
             <v>13</v>
           </cell>
           <cell r="M65">
-            <v>7305000</v>
+            <v>14105000</v>
           </cell>
         </row>
         <row r="66">
@@ -1229,7 +1229,7 @@
             <v>0</v>
           </cell>
           <cell r="M67">
-            <v>1575000</v>
+            <v>2535000</v>
           </cell>
         </row>
         <row r="68">
@@ -1405,7 +1405,7 @@
             <v>3</v>
           </cell>
           <cell r="M83">
-            <v>883000</v>
+            <v>953200</v>
           </cell>
         </row>
         <row r="84">
@@ -1416,7 +1416,7 @@
             <v>6</v>
           </cell>
           <cell r="M84">
-            <v>1076200</v>
+            <v>1146400</v>
           </cell>
         </row>
         <row r="85">
@@ -1559,7 +1559,7 @@
             <v>6</v>
           </cell>
           <cell r="M97">
-            <v>579600</v>
+            <v>649800</v>
           </cell>
         </row>
         <row r="98">
@@ -1570,7 +1570,7 @@
             <v>3</v>
           </cell>
           <cell r="M98">
-            <v>1456000</v>
+            <v>1541000</v>
           </cell>
         </row>
         <row r="99">
@@ -1592,7 +1592,7 @@
             <v>9</v>
           </cell>
           <cell r="M100">
-            <v>4482000</v>
+            <v>4582000</v>
           </cell>
         </row>
         <row r="101">
@@ -1647,7 +1647,7 @@
             <v>6</v>
           </cell>
           <cell r="M105">
-            <v>4694500</v>
+            <v>4779500</v>
           </cell>
         </row>
         <row r="106">
@@ -1713,7 +1713,7 @@
             <v>28</v>
           </cell>
           <cell r="M111">
-            <v>1071400</v>
+            <v>1141600</v>
           </cell>
         </row>
         <row r="112">
@@ -1724,7 +1724,7 @@
             <v>8</v>
           </cell>
           <cell r="M112">
-            <v>1182800</v>
+            <v>1272800</v>
           </cell>
         </row>
         <row r="113">
@@ -1735,7 +1735,7 @@
             <v>9</v>
           </cell>
           <cell r="M113">
-            <v>2909800</v>
+            <v>3180000</v>
           </cell>
         </row>
         <row r="114">
@@ -1746,7 +1746,7 @@
             <v>6</v>
           </cell>
           <cell r="M114">
-            <v>2037200</v>
+            <v>2505200</v>
           </cell>
         </row>
         <row r="115">
@@ -1779,7 +1779,7 @@
             <v>3</v>
           </cell>
           <cell r="M117">
-            <v>1603600</v>
+            <v>1673800</v>
           </cell>
         </row>
         <row r="118">
@@ -1823,7 +1823,7 @@
             <v>11</v>
           </cell>
           <cell r="M121">
-            <v>897800</v>
+            <v>968000</v>
           </cell>
         </row>
         <row r="122">
@@ -1834,7 +1834,7 @@
             <v>12</v>
           </cell>
           <cell r="M122">
-            <v>2060500</v>
+            <v>2560500</v>
           </cell>
         </row>
         <row r="123">
@@ -1845,7 +1845,7 @@
             <v>3</v>
           </cell>
           <cell r="M123">
-            <v>529200</v>
+            <v>599400</v>
           </cell>
         </row>
         <row r="124">
@@ -1856,7 +1856,7 @@
             <v>6</v>
           </cell>
           <cell r="M124">
-            <v>774200</v>
+            <v>844400</v>
           </cell>
         </row>
         <row r="125">
@@ -1867,7 +1867,7 @@
             <v>6</v>
           </cell>
           <cell r="M125">
-            <v>1661200</v>
+            <v>1731400</v>
           </cell>
         </row>
         <row r="126">
@@ -1878,7 +1878,7 @@
             <v>3</v>
           </cell>
           <cell r="M126">
-            <v>1281200</v>
+            <v>1366200</v>
           </cell>
         </row>
         <row r="127">
@@ -1889,7 +1889,7 @@
             <v>3</v>
           </cell>
           <cell r="M127">
-            <v>5894800</v>
+            <v>5979800</v>
           </cell>
         </row>
         <row r="128">
@@ -1900,7 +1900,7 @@
             <v>3</v>
           </cell>
           <cell r="M128">
-            <v>653200</v>
+            <v>723400</v>
           </cell>
         </row>
         <row r="129">
@@ -1911,7 +1911,7 @@
             <v>22</v>
           </cell>
           <cell r="M129">
-            <v>3138900</v>
+            <v>3223900</v>
           </cell>
         </row>
         <row r="130">
@@ -1944,7 +1944,7 @@
             <v>18</v>
           </cell>
           <cell r="M132">
-            <v>8161000</v>
+            <v>9161000</v>
           </cell>
         </row>
         <row r="133">
@@ -1966,7 +1966,7 @@
             <v>4</v>
           </cell>
           <cell r="M134">
-            <v>1252200</v>
+            <v>1322400</v>
           </cell>
         </row>
         <row r="135">
@@ -1977,7 +1977,7 @@
             <v>3</v>
           </cell>
           <cell r="M135">
-            <v>1050400</v>
+            <v>1120600</v>
           </cell>
         </row>
         <row r="136">
@@ -1988,7 +1988,7 @@
             <v>3</v>
           </cell>
           <cell r="M136">
-            <v>1352400</v>
+            <v>1422600</v>
           </cell>
         </row>
         <row r="137">
@@ -2032,7 +2032,7 @@
             <v>7</v>
           </cell>
           <cell r="M140">
-            <v>1029000</v>
+            <v>1229000</v>
           </cell>
         </row>
         <row r="141">
@@ -2043,7 +2043,7 @@
             <v>3</v>
           </cell>
           <cell r="M141">
-            <v>529200</v>
+            <v>599400</v>
           </cell>
         </row>
         <row r="142">
@@ -2065,7 +2065,7 @@
             <v>3</v>
           </cell>
           <cell r="M143">
-            <v>1130900</v>
+            <v>1201100</v>
           </cell>
         </row>
         <row r="144">
@@ -2109,7 +2109,7 @@
             <v>3</v>
           </cell>
           <cell r="M147">
-            <v>939300</v>
+            <v>1009500</v>
           </cell>
         </row>
         <row r="148">
@@ -2252,7 +2252,7 @@
             <v>8</v>
           </cell>
           <cell r="M160">
-            <v>4923000</v>
+            <v>5823000</v>
           </cell>
         </row>
         <row r="161">
@@ -2362,7 +2362,7 @@
             <v>3</v>
           </cell>
           <cell r="M170">
-            <v>2512500</v>
+            <v>2662500</v>
           </cell>
         </row>
         <row r="171">
@@ -2428,7 +2428,7 @@
             <v>0</v>
           </cell>
           <cell r="M176">
-            <v>117000</v>
+            <v>3147000</v>
           </cell>
         </row>
         <row r="177">
@@ -2923,7 +2923,7 @@
             <v>13</v>
           </cell>
           <cell r="M221">
-            <v>2362000</v>
+            <v>3120000</v>
           </cell>
         </row>
         <row r="222">
@@ -2934,7 +2934,7 @@
             <v>6</v>
           </cell>
           <cell r="M222">
-            <v>4484000</v>
+            <v>5654000</v>
           </cell>
         </row>
         <row r="223">
@@ -2956,7 +2956,7 @@
             <v>3</v>
           </cell>
           <cell r="M224">
-            <v>577000</v>
+            <v>811000</v>
           </cell>
         </row>
         <row r="225">
@@ -2967,7 +2967,7 @@
             <v>3</v>
           </cell>
           <cell r="M225">
-            <v>2885000</v>
+            <v>3030000</v>
           </cell>
         </row>
         <row r="226">
@@ -3022,7 +3022,7 @@
             <v>6</v>
           </cell>
           <cell r="M230">
-            <v>10180000</v>
+            <v>15225000</v>
           </cell>
         </row>
         <row r="231">
@@ -3033,7 +3033,7 @@
             <v>3</v>
           </cell>
           <cell r="M231">
-            <v>511000</v>
+            <v>656000</v>
           </cell>
         </row>
         <row r="232">
@@ -3044,7 +3044,7 @@
             <v>3</v>
           </cell>
           <cell r="M232">
-            <v>643000</v>
+            <v>1737000</v>
           </cell>
         </row>
         <row r="233">
@@ -3055,7 +3055,7 @@
             <v>6</v>
           </cell>
           <cell r="M233">
-            <v>6395000</v>
+            <v>9326000</v>
           </cell>
         </row>
         <row r="234">
@@ -3066,7 +3066,7 @@
             <v>6</v>
           </cell>
           <cell r="M234">
-            <v>782000</v>
+            <v>1850000</v>
           </cell>
         </row>
         <row r="235">
@@ -3077,7 +3077,7 @@
             <v>20</v>
           </cell>
           <cell r="M235">
-            <v>6307000</v>
+            <v>6541000</v>
           </cell>
         </row>
         <row r="236">
@@ -3088,7 +3088,7 @@
             <v>3</v>
           </cell>
           <cell r="M236">
-            <v>1492000</v>
+            <v>2250000</v>
           </cell>
         </row>
         <row r="237">
@@ -3099,7 +3099,7 @@
             <v>3</v>
           </cell>
           <cell r="M237">
-            <v>643000</v>
+            <v>788000</v>
           </cell>
         </row>
         <row r="238">
@@ -3110,7 +3110,7 @@
             <v>3</v>
           </cell>
           <cell r="M238">
-            <v>577000</v>
+            <v>722000</v>
           </cell>
         </row>
         <row r="239">
@@ -3121,7 +3121,7 @@
             <v>3</v>
           </cell>
           <cell r="M239">
-            <v>3358000</v>
+            <v>3826000</v>
           </cell>
         </row>
         <row r="240">
@@ -3132,7 +3132,7 @@
             <v>3</v>
           </cell>
           <cell r="M240">
-            <v>877000</v>
+            <v>1022000</v>
           </cell>
         </row>
         <row r="241">
@@ -3143,7 +3143,7 @@
             <v>0</v>
           </cell>
           <cell r="M241">
-            <v>3891000</v>
+            <v>4036000</v>
           </cell>
         </row>
         <row r="242">
@@ -3154,7 +3154,7 @@
             <v>3</v>
           </cell>
           <cell r="M242">
-            <v>511000</v>
+            <v>656000</v>
           </cell>
         </row>
         <row r="243">
@@ -3165,7 +3165,7 @@
             <v>0</v>
           </cell>
           <cell r="M243">
-            <v>655000</v>
+            <v>800000</v>
           </cell>
         </row>
         <row r="244">
@@ -3187,7 +3187,7 @@
             <v>5</v>
           </cell>
           <cell r="M245">
-            <v>4199000</v>
+            <v>4367000</v>
           </cell>
         </row>
         <row r="246">
@@ -3198,7 +3198,7 @@
             <v>19</v>
           </cell>
           <cell r="M246">
-            <v>4210000</v>
+            <v>4355000</v>
           </cell>
         </row>
         <row r="247">
@@ -3220,7 +3220,7 @@
             <v>14</v>
           </cell>
           <cell r="M248">
-            <v>985500</v>
+            <v>1130500</v>
           </cell>
         </row>
         <row r="249">
@@ -3231,7 +3231,7 @@
             <v>16</v>
           </cell>
           <cell r="M249">
-            <v>2934000</v>
+            <v>3234000</v>
           </cell>
         </row>
         <row r="250">
@@ -3242,7 +3242,7 @@
             <v>19</v>
           </cell>
           <cell r="M250">
-            <v>4456500</v>
+            <v>4601500</v>
           </cell>
         </row>
         <row r="251">
@@ -3253,7 +3253,7 @@
             <v>33</v>
           </cell>
           <cell r="M251">
-            <v>6938000</v>
+            <v>8738000</v>
           </cell>
         </row>
         <row r="252">
@@ -3330,7 +3330,7 @@
             <v>23</v>
           </cell>
           <cell r="M258">
-            <v>2245000</v>
+            <v>2755500</v>
           </cell>
         </row>
         <row r="259">
@@ -3341,7 +3341,7 @@
             <v>13</v>
           </cell>
           <cell r="M259">
-            <v>1045000</v>
+            <v>3470000</v>
           </cell>
         </row>
         <row r="260">
@@ -3363,7 +3363,7 @@
             <v>3</v>
           </cell>
           <cell r="M261">
-            <v>855000</v>
+            <v>925200</v>
           </cell>
         </row>
         <row r="262">
@@ -3385,7 +3385,7 @@
             <v>3</v>
           </cell>
           <cell r="M263">
-            <v>862200</v>
+            <v>932400</v>
           </cell>
         </row>
         <row r="264">
@@ -3440,7 +3440,7 @@
             <v>0</v>
           </cell>
           <cell r="M268">
-            <v>2435000</v>
+            <v>3395000</v>
           </cell>
         </row>
         <row r="269">
@@ -3451,7 +3451,7 @@
             <v>0</v>
           </cell>
           <cell r="M269">
-            <v>3035000</v>
+            <v>3995000</v>
           </cell>
         </row>
         <row r="270">
@@ -3473,7 +3473,7 @@
             <v>0</v>
           </cell>
           <cell r="M271">
-            <v>300000</v>
+            <v>1440000</v>
           </cell>
         </row>
         <row r="272">
@@ -3484,7 +3484,7 @@
             <v>43</v>
           </cell>
           <cell r="M272">
-            <v>8466000</v>
+            <v>8598000</v>
           </cell>
         </row>
         <row r="273">
@@ -3495,7 +3495,7 @@
             <v>13</v>
           </cell>
           <cell r="M273">
-            <v>3398000</v>
+            <v>4358000</v>
           </cell>
         </row>
         <row r="274">
@@ -3506,7 +3506,7 @@
             <v>3</v>
           </cell>
           <cell r="M274">
-            <v>2993000</v>
+            <v>3953000</v>
           </cell>
         </row>
         <row r="275">
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>211035000</v>
+        <v>228977000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.48244220313535313</v>
+        <v>0.52345899186070444</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-226395636.51666558</v>
+        <v>-208453636.51666558</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-12577535.362036977</v>
+        <v>-11580757.584259199</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>187438500</v>
+        <v>202508500</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.42528444107970548</v>
+        <v>0.4594771844439085</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-253298291.41455084</v>
+        <v>-238228291.41455084</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-14072127.300808379</v>
+        <v>-13234905.078586157</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>43864000</v>
+        <v>45889000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.27432719629900337</v>
+        <v>0.28699162664063849</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-116032651.12237126</v>
+        <v>-114007651.12237126</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-6446258.3956872923</v>
+        <v>-6333758.3956872923</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>69981500</v>
+        <v>71705300</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.27487222120301824</v>
+        <v>0.28164293539047869</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-184614980.11616376</v>
+        <v>-182891180.11616376</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-10256387.78423132</v>
+        <v>-10160621.117564654</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>119645000</v>
+        <v>129103500</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.315221490470595</v>
+        <v>0.34014123193589757</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-259913512.40149158</v>
+        <v>-250455012.40149158</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-14439639.577860644</v>
+        <v>-13914167.355638422</v>
       </c>
     </row>
     <row r="9" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -1009,7 +1009,7 @@
             <v>10</v>
           </cell>
           <cell r="M47">
-            <v>1675000</v>
+            <v>2515000</v>
           </cell>
         </row>
         <row r="48">
@@ -1020,7 +1020,7 @@
             <v>10</v>
           </cell>
           <cell r="M48">
-            <v>1515000</v>
+            <v>2355000</v>
           </cell>
         </row>
         <row r="49">
@@ -1031,7 +1031,7 @@
             <v>10</v>
           </cell>
           <cell r="M49">
-            <v>1443000</v>
+            <v>2103000</v>
           </cell>
         </row>
         <row r="50">
@@ -1053,7 +1053,7 @@
             <v>20</v>
           </cell>
           <cell r="M51">
-            <v>8074000</v>
+            <v>8866000</v>
           </cell>
         </row>
         <row r="52">
@@ -1064,7 +1064,7 @@
             <v>10</v>
           </cell>
           <cell r="M52">
-            <v>6858000</v>
+            <v>7194000</v>
           </cell>
         </row>
         <row r="53">
@@ -1075,7 +1075,7 @@
             <v>10</v>
           </cell>
           <cell r="M53">
-            <v>4033000</v>
+            <v>4873000</v>
           </cell>
         </row>
         <row r="54">
@@ -1086,7 +1086,7 @@
             <v>30</v>
           </cell>
           <cell r="M54">
-            <v>4729500</v>
+            <v>4831000</v>
           </cell>
         </row>
         <row r="55">
@@ -1097,7 +1097,7 @@
             <v>30</v>
           </cell>
           <cell r="M55">
-            <v>4455500</v>
+            <v>4557000</v>
           </cell>
         </row>
         <row r="56">
@@ -1105,7 +1105,7 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I56">
-            <v>13</v>
+            <v>48</v>
           </cell>
           <cell r="M56">
             <v>4426000</v>
@@ -1141,7 +1141,7 @@
             <v>20</v>
           </cell>
           <cell r="M59">
-            <v>3968000</v>
+            <v>4808000</v>
           </cell>
         </row>
         <row r="60">
@@ -1149,7 +1149,7 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I60">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M60">
             <v>2535000</v>
@@ -1160,7 +1160,7 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I61">
-            <v>10</v>
+            <v>20</v>
           </cell>
           <cell r="M61">
             <v>2835000</v>
@@ -1204,7 +1204,7 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I65">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M65">
             <v>14105000</v>
@@ -1226,7 +1226,7 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I67">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M67">
             <v>2535000</v>
@@ -1413,10 +1413,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I84">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M84">
-            <v>1146400</v>
+            <v>1704400</v>
           </cell>
         </row>
         <row r="85">
@@ -1424,10 +1424,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I85">
-            <v>9</v>
+            <v>14</v>
           </cell>
           <cell r="M85">
-            <v>1255000</v>
+            <v>2575000</v>
           </cell>
         </row>
         <row r="86">
@@ -1438,7 +1438,7 @@
             <v>16</v>
           </cell>
           <cell r="M86">
-            <v>5980800</v>
+            <v>6830800</v>
           </cell>
         </row>
         <row r="87">
@@ -1490,10 +1490,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I91">
-            <v>6</v>
+            <v>11</v>
           </cell>
           <cell r="M91">
-            <v>721800</v>
+            <v>1105800</v>
           </cell>
         </row>
         <row r="92">
@@ -1501,10 +1501,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I92">
-            <v>8</v>
+            <v>13</v>
           </cell>
           <cell r="M92">
-            <v>1250000</v>
+            <v>1634000</v>
           </cell>
         </row>
         <row r="93">
@@ -1512,10 +1512,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I93">
-            <v>25</v>
+            <v>30</v>
           </cell>
           <cell r="M93">
-            <v>1061800</v>
+            <v>1445800</v>
           </cell>
         </row>
         <row r="94">
@@ -1526,7 +1526,7 @@
             <v>6</v>
           </cell>
           <cell r="M94">
-            <v>1006600</v>
+            <v>1774600</v>
           </cell>
         </row>
         <row r="95">
@@ -1537,7 +1537,7 @@
             <v>6</v>
           </cell>
           <cell r="M95">
-            <v>676600</v>
+            <v>1144600</v>
           </cell>
         </row>
         <row r="96">
@@ -1545,10 +1545,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I96">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M96">
-            <v>771800</v>
+            <v>1329800</v>
           </cell>
         </row>
         <row r="97">
@@ -1559,7 +1559,7 @@
             <v>6</v>
           </cell>
           <cell r="M97">
-            <v>649800</v>
+            <v>1117800</v>
           </cell>
         </row>
         <row r="98">
@@ -1581,7 +1581,7 @@
             <v>29</v>
           </cell>
           <cell r="M99">
-            <v>651000</v>
+            <v>885000</v>
           </cell>
         </row>
         <row r="100">
@@ -1589,10 +1589,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I100">
-            <v>9</v>
+            <v>14</v>
           </cell>
           <cell r="M100">
-            <v>4582000</v>
+            <v>5300000</v>
           </cell>
         </row>
         <row r="101">
@@ -1603,7 +1603,7 @@
             <v>6</v>
           </cell>
           <cell r="M101">
-            <v>2385600</v>
+            <v>3119600</v>
           </cell>
         </row>
         <row r="102">
@@ -1614,7 +1614,7 @@
             <v>11</v>
           </cell>
           <cell r="M102">
-            <v>810000</v>
+            <v>2278000</v>
           </cell>
         </row>
         <row r="103">
@@ -1625,7 +1625,7 @@
             <v>8</v>
           </cell>
           <cell r="M103">
-            <v>1915800</v>
+            <v>2083800</v>
           </cell>
         </row>
         <row r="104">
@@ -1669,7 +1669,7 @@
             <v>6</v>
           </cell>
           <cell r="M107">
-            <v>758000</v>
+            <v>992000</v>
           </cell>
         </row>
         <row r="108">
@@ -1680,7 +1680,7 @@
             <v>11</v>
           </cell>
           <cell r="M108">
-            <v>3582800</v>
+            <v>3816800</v>
           </cell>
         </row>
         <row r="109">
@@ -1702,7 +1702,7 @@
             <v>9</v>
           </cell>
           <cell r="M110">
-            <v>631600</v>
+            <v>1099600</v>
           </cell>
         </row>
         <row r="111">
@@ -1721,7 +1721,7 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I112">
-            <v>8</v>
+            <v>11</v>
           </cell>
           <cell r="M112">
             <v>1272800</v>
@@ -1735,7 +1735,7 @@
             <v>9</v>
           </cell>
           <cell r="M113">
-            <v>3180000</v>
+            <v>3280000</v>
           </cell>
         </row>
         <row r="114">
@@ -1779,7 +1779,7 @@
             <v>3</v>
           </cell>
           <cell r="M117">
-            <v>1673800</v>
+            <v>1907800</v>
           </cell>
         </row>
         <row r="118">
@@ -1856,7 +1856,7 @@
             <v>6</v>
           </cell>
           <cell r="M124">
-            <v>844400</v>
+            <v>1078400</v>
           </cell>
         </row>
         <row r="125">
@@ -1900,7 +1900,7 @@
             <v>3</v>
           </cell>
           <cell r="M128">
-            <v>723400</v>
+            <v>957400</v>
           </cell>
         </row>
         <row r="129">
@@ -1963,10 +1963,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I134">
-            <v>4</v>
+            <v>9</v>
           </cell>
           <cell r="M134">
-            <v>1322400</v>
+            <v>1940400</v>
           </cell>
         </row>
         <row r="135">
@@ -1974,10 +1974,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I135">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M135">
-            <v>1120600</v>
+            <v>1678600</v>
           </cell>
         </row>
         <row r="136">
@@ -1985,10 +1985,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I136">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M136">
-            <v>1422600</v>
+            <v>2040600</v>
           </cell>
         </row>
         <row r="137">
@@ -1996,10 +1996,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I137">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M137">
-            <v>882400</v>
+            <v>1266400</v>
           </cell>
         </row>
         <row r="138">
@@ -2018,10 +2018,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I139">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="M139">
-            <v>2151000</v>
+            <v>2301000</v>
           </cell>
         </row>
         <row r="140">
@@ -2062,10 +2062,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I143">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M143">
-            <v>1201100</v>
+            <v>1819100</v>
           </cell>
         </row>
         <row r="144">
@@ -2095,10 +2095,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I146">
-            <v>6</v>
+            <v>11</v>
           </cell>
           <cell r="M146">
-            <v>1361700</v>
+            <v>1745700</v>
           </cell>
         </row>
         <row r="147">
@@ -2109,7 +2109,7 @@
             <v>3</v>
           </cell>
           <cell r="M147">
-            <v>1009500</v>
+            <v>1243500</v>
           </cell>
         </row>
         <row r="148">
@@ -2117,10 +2117,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I148">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M148">
-            <v>607800</v>
+            <v>978000</v>
           </cell>
         </row>
         <row r="149">
@@ -2128,10 +2128,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I149">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M149">
-            <v>1621000</v>
+            <v>1991200</v>
           </cell>
         </row>
         <row r="150">
@@ -2164,7 +2164,7 @@
             <v>21</v>
           </cell>
           <cell r="M152">
-            <v>15210000</v>
+            <v>17210000</v>
           </cell>
         </row>
         <row r="153">
@@ -2194,10 +2194,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I155">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M155">
-            <v>475000</v>
+            <v>625000</v>
           </cell>
         </row>
         <row r="156">
@@ -2238,10 +2238,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I159">
-            <v>8</v>
+            <v>13</v>
           </cell>
           <cell r="M159">
-            <v>2971500</v>
+            <v>3621500</v>
           </cell>
         </row>
         <row r="160">
@@ -2249,10 +2249,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I160">
-            <v>8</v>
+            <v>13</v>
           </cell>
           <cell r="M160">
-            <v>5823000</v>
+            <v>6973000</v>
           </cell>
         </row>
         <row r="161">
@@ -2260,10 +2260,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I161">
-            <v>6</v>
+            <v>11</v>
           </cell>
           <cell r="M161">
-            <v>265000</v>
+            <v>415000</v>
           </cell>
         </row>
         <row r="162">
@@ -2271,10 +2271,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I162">
-            <v>13</v>
+            <v>18</v>
           </cell>
           <cell r="M162">
-            <v>16607000</v>
+            <v>16757000</v>
           </cell>
         </row>
         <row r="163">
@@ -2282,10 +2282,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I163">
-            <v>8</v>
+            <v>13</v>
           </cell>
           <cell r="M163">
-            <v>6080000</v>
+            <v>6230000</v>
           </cell>
         </row>
         <row r="164">
@@ -2293,10 +2293,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I164">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M164">
-            <v>654000</v>
+            <v>1584000</v>
           </cell>
         </row>
         <row r="165">
@@ -2304,10 +2304,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I165">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M165">
-            <v>607000</v>
+            <v>1501000</v>
           </cell>
         </row>
         <row r="166">
@@ -2315,10 +2315,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I166">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M166">
-            <v>1158000</v>
+            <v>2308000</v>
           </cell>
         </row>
         <row r="167">
@@ -2337,10 +2337,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I168">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M168">
-            <v>1273000</v>
+            <v>1831000</v>
           </cell>
         </row>
         <row r="169">
@@ -2359,10 +2359,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I170">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M170">
-            <v>2662500</v>
+            <v>2997500</v>
           </cell>
         </row>
         <row r="171">
@@ -2370,10 +2370,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I171">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M171">
-            <v>511000</v>
+            <v>769000</v>
           </cell>
         </row>
         <row r="172">
@@ -2381,10 +2381,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I172">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M172">
-            <v>877000</v>
+            <v>1567000</v>
           </cell>
         </row>
         <row r="173">
@@ -2392,10 +2392,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I173">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M173">
-            <v>343000</v>
+            <v>601000</v>
           </cell>
         </row>
         <row r="174">
@@ -2403,10 +2403,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I174">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="M174">
-            <v>1234000</v>
+            <v>1834000</v>
           </cell>
         </row>
         <row r="175">
@@ -2414,10 +2414,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I175">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M175">
-            <v>327600</v>
+            <v>861600</v>
           </cell>
         </row>
         <row r="176">
@@ -2425,10 +2425,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I176">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="M176">
-            <v>3147000</v>
+            <v>3747000</v>
           </cell>
         </row>
         <row r="177">
@@ -2436,10 +2436,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I177">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="M177">
-            <v>327600</v>
+            <v>927600</v>
           </cell>
         </row>
         <row r="178">
@@ -2447,10 +2447,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I178">
-            <v>20</v>
+            <v>40</v>
           </cell>
           <cell r="M178">
-            <v>304200</v>
+            <v>904200</v>
           </cell>
         </row>
         <row r="179">
@@ -2458,10 +2458,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I179">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M179">
-            <v>4490000</v>
+            <v>4916000</v>
           </cell>
         </row>
         <row r="180">
@@ -2513,10 +2513,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I184">
-            <v>16</v>
+            <v>19</v>
           </cell>
           <cell r="M184">
-            <v>6216000</v>
+            <v>6642000</v>
           </cell>
         </row>
         <row r="185">
@@ -2590,10 +2590,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I191">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M191">
-            <v>304200</v>
+            <v>604200</v>
           </cell>
         </row>
         <row r="192">
@@ -2604,7 +2604,7 @@
             <v>0</v>
           </cell>
           <cell r="M192">
-            <v>1904200</v>
+            <v>2354200</v>
           </cell>
         </row>
         <row r="193">
@@ -3176,7 +3176,7 @@
             <v>33</v>
           </cell>
           <cell r="M244">
-            <v>1397000</v>
+            <v>1542000</v>
           </cell>
         </row>
         <row r="245">
@@ -3187,7 +3187,7 @@
             <v>5</v>
           </cell>
           <cell r="M245">
-            <v>4367000</v>
+            <v>4499000</v>
           </cell>
         </row>
         <row r="246">
@@ -3198,7 +3198,7 @@
             <v>19</v>
           </cell>
           <cell r="M246">
-            <v>4355000</v>
+            <v>4645000</v>
           </cell>
         </row>
         <row r="247">
@@ -3209,7 +3209,7 @@
             <v>35</v>
           </cell>
           <cell r="M247">
-            <v>6904000</v>
+            <v>7744000</v>
           </cell>
         </row>
         <row r="248">
@@ -3220,7 +3220,7 @@
             <v>14</v>
           </cell>
           <cell r="M248">
-            <v>1130500</v>
+            <v>1275500</v>
           </cell>
         </row>
         <row r="249">
@@ -3231,7 +3231,7 @@
             <v>16</v>
           </cell>
           <cell r="M249">
-            <v>3234000</v>
+            <v>3524000</v>
           </cell>
         </row>
         <row r="250">
@@ -3242,7 +3242,7 @@
             <v>19</v>
           </cell>
           <cell r="M250">
-            <v>4601500</v>
+            <v>4891500</v>
           </cell>
         </row>
         <row r="251">
@@ -3250,10 +3250,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I251">
-            <v>33</v>
+            <v>43</v>
           </cell>
           <cell r="M251">
-            <v>8738000</v>
+            <v>9398000</v>
           </cell>
         </row>
         <row r="252">
@@ -3264,7 +3264,7 @@
             <v>19</v>
           </cell>
           <cell r="M252">
-            <v>4888500</v>
+            <v>5178500</v>
           </cell>
         </row>
         <row r="253">
@@ -3371,10 +3371,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I262">
-            <v>6</v>
+            <v>11</v>
           </cell>
           <cell r="M262">
-            <v>1173600</v>
+            <v>1557600</v>
           </cell>
         </row>
         <row r="263">
@@ -3393,10 +3393,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I264">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M264">
-            <v>851100</v>
+            <v>1235100</v>
           </cell>
         </row>
         <row r="265">
@@ -3404,10 +3404,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I265">
-            <v>6</v>
+            <v>14</v>
           </cell>
           <cell r="M265">
-            <v>1765300</v>
+            <v>2730700</v>
           </cell>
         </row>
         <row r="266">
@@ -3415,10 +3415,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I266">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="M266">
-            <v>1713000</v>
+            <v>2097000</v>
           </cell>
         </row>
         <row r="267">
@@ -3426,10 +3426,10 @@
             <v>DSE-JAGOIBABNG01</v>
           </cell>
           <cell r="I267">
-            <v>6</v>
+            <v>11</v>
           </cell>
           <cell r="M267">
-            <v>1596400</v>
+            <v>2718400</v>
           </cell>
         </row>
         <row r="268">
@@ -3437,7 +3437,7 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I268">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M268">
             <v>3395000</v>
@@ -3448,7 +3448,7 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I269">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M269">
             <v>3995000</v>
@@ -3470,7 +3470,7 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I271">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M271">
             <v>1440000</v>
@@ -3484,7 +3484,7 @@
             <v>43</v>
           </cell>
           <cell r="M272">
-            <v>8598000</v>
+            <v>8921000</v>
           </cell>
         </row>
         <row r="273">
@@ -3492,10 +3492,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I273">
-            <v>13</v>
+            <v>23</v>
           </cell>
           <cell r="M273">
-            <v>4358000</v>
+            <v>5018000</v>
           </cell>
         </row>
         <row r="274">
@@ -3503,10 +3503,10 @@
             <v>DSE1082</v>
           </cell>
           <cell r="I274">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M274">
-            <v>3953000</v>
+            <v>4793000</v>
           </cell>
         </row>
         <row r="275">
@@ -3536,10 +3536,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I277">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="M277">
-            <v>304200</v>
+            <v>904200</v>
           </cell>
         </row>
         <row r="278">
@@ -3547,10 +3547,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I278">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="M278">
-            <v>304200</v>
+            <v>904200</v>
           </cell>
         </row>
         <row r="279">
@@ -3558,10 +3558,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I279">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="M279">
-            <v>304200</v>
+            <v>904200</v>
           </cell>
         </row>
         <row r="280">
@@ -3866,10 +3866,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I307">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M307">
-            <v>1952000</v>
+            <v>2548000</v>
           </cell>
         </row>
         <row r="308">
@@ -3877,10 +3877,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I308">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="M308">
-            <v>1781000</v>
+            <v>1871000</v>
           </cell>
         </row>
         <row r="309">
@@ -3921,10 +3921,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I312">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M312">
-            <v>2135000</v>
+            <v>3225000</v>
           </cell>
         </row>
         <row r="313">
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>228977000</v>
+        <v>237580000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.52345899186070444</v>
+        <v>0.54312610998600797</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-208453636.51666558</v>
+        <v>-199850636.51666558</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-11580757.584259199</v>
+        <v>-11102813.139814755</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>202508500</v>
+        <v>212209500</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.4594771844439085</v>
+        <v>0.48148805394464728</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-238228291.41455084</v>
+        <v>-228527291.41455084</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-13234905.078586157</v>
+        <v>-12695960.634141713</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>45889000</v>
+        <v>47542000</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.28699162664063849</v>
+        <v>0.29732955422321766</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-114007651.12237126</v>
+        <v>-112354651.12237126</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-6333758.3956872923</v>
+        <v>-6241925.0623539584</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>71705300</v>
+        <v>89451100</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.28164293539047869</v>
+        <v>0.35134460601806627</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-182891180.11616376</v>
+        <v>-165145380.11616376</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-10160621.117564654</v>
+        <v>-9174743.339786876</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>129103500</v>
+        <v>137987500</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.34014123193589757</v>
+        <v>0.36354737278040228</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-250455012.40149158</v>
+        <v>-241571012.40149158</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-13914167.355638422</v>
+        <v>-13420611.800082866</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4445,19 +4445,19 @@
       </c>
       <c r="D11" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A11,[1]Sheet1!$I:$I)</f>
-        <v>665</v>
+        <v>800</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:E15" si="3">D11/C11</f>
-        <v>0.81097560975609762</v>
+        <v>0.97560975609756095</v>
       </c>
       <c r="F11" s="10">
         <f>D11-C11</f>
-        <v>-155</v>
+        <v>-20</v>
       </c>
       <c r="G11" s="19">
         <f>F11/18</f>
-        <v>-8.6111111111111107</v>
+        <v>-1.1111111111111112</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5">
@@ -4472,19 +4472,19 @@
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>1.0822784810126582</v>
+        <v>1.1645569620253164</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>2.1666666666666665</v>
+        <v>4.333333333333333</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D14" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A14,[1]Sheet1!$I:$I)</f>
-        <v>373</v>
+        <v>483</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="3"/>
-        <v>0.87149532710280375</v>
+        <v>1.1285046728971964</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="4"/>
-        <v>-55</v>
+        <v>55</v>
       </c>
       <c r="G14" s="19">
         <f t="shared" si="5"/>
-        <v>-3.0555555555555554</v>
+        <v>3.0555555555555554</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>396</v>
+        <v>591</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>0.8741721854304636</v>
+        <v>1.304635761589404</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>-57</v>
+        <v>138</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>-3.1666666666666665</v>
+        <v>7.666666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -1438,7 +1438,7 @@
             <v>16</v>
           </cell>
           <cell r="M86">
-            <v>6830800</v>
+            <v>6980800</v>
           </cell>
         </row>
         <row r="87">
@@ -3121,7 +3121,7 @@
             <v>3</v>
           </cell>
           <cell r="M239">
-            <v>3826000</v>
+            <v>4126000</v>
           </cell>
         </row>
         <row r="240">
@@ -3484,7 +3484,7 @@
             <v>43</v>
           </cell>
           <cell r="M272">
-            <v>8921000</v>
+            <v>9057000</v>
           </cell>
         </row>
         <row r="273">
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>237580000</v>
+        <v>237716000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.54312610998600797</v>
+        <v>0.54343701642155851</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-199850636.51666558</v>
+        <v>-199714636.51666558</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-11102813.139814755</v>
+        <v>-11095257.584259199</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>212209500</v>
+        <v>212509500</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.48148805394464728</v>
+        <v>0.48216873231287954</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-228527291.41455084</v>
+        <v>-228227291.41455084</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-12695960.634141713</v>
+        <v>-12679293.967475047</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>137987500</v>
+        <v>138137500</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.36354737278040228</v>
+        <v>0.3639425687649448</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-241571012.40149158</v>
+        <v>-241421012.40149158</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-13420611.800082866</v>
+        <v>-13412278.466749532</v>
       </c>
     </row>
     <row r="9" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -668,7 +668,7 @@
             <v>3</v>
           </cell>
           <cell r="M16">
-            <v>790000</v>
+            <v>1490000</v>
           </cell>
         </row>
         <row r="17">
@@ -1141,7 +1141,7 @@
             <v>20</v>
           </cell>
           <cell r="M59">
-            <v>4808000</v>
+            <v>5468000</v>
           </cell>
         </row>
         <row r="60">
@@ -1361,7 +1361,7 @@
             <v>8</v>
           </cell>
           <cell r="M79">
-            <v>961000</v>
+            <v>1195000</v>
           </cell>
         </row>
         <row r="80">
@@ -1449,7 +1449,7 @@
             <v>26</v>
           </cell>
           <cell r="M87">
-            <v>1680000</v>
+            <v>1980000</v>
           </cell>
         </row>
         <row r="88">
@@ -1493,7 +1493,7 @@
             <v>11</v>
           </cell>
           <cell r="M91">
-            <v>1105800</v>
+            <v>1156200</v>
           </cell>
         </row>
         <row r="92">
@@ -1504,7 +1504,7 @@
             <v>13</v>
           </cell>
           <cell r="M92">
-            <v>1634000</v>
+            <v>1918000</v>
           </cell>
         </row>
         <row r="93">
@@ -1515,7 +1515,7 @@
             <v>30</v>
           </cell>
           <cell r="M93">
-            <v>1445800</v>
+            <v>1496200</v>
           </cell>
         </row>
         <row r="94">
@@ -1526,7 +1526,7 @@
             <v>6</v>
           </cell>
           <cell r="M94">
-            <v>1774600</v>
+            <v>1858600</v>
           </cell>
         </row>
         <row r="95">
@@ -1559,7 +1559,7 @@
             <v>6</v>
           </cell>
           <cell r="M97">
-            <v>1117800</v>
+            <v>1168200</v>
           </cell>
         </row>
         <row r="98">
@@ -1592,7 +1592,7 @@
             <v>14</v>
           </cell>
           <cell r="M100">
-            <v>5300000</v>
+            <v>5500000</v>
           </cell>
         </row>
         <row r="101">
@@ -1603,7 +1603,7 @@
             <v>6</v>
           </cell>
           <cell r="M101">
-            <v>3119600</v>
+            <v>3203600</v>
           </cell>
         </row>
         <row r="102">
@@ -1614,7 +1614,7 @@
             <v>11</v>
           </cell>
           <cell r="M102">
-            <v>2278000</v>
+            <v>2362000</v>
           </cell>
         </row>
         <row r="103">
@@ -1625,7 +1625,7 @@
             <v>8</v>
           </cell>
           <cell r="M103">
-            <v>2083800</v>
+            <v>2434200</v>
           </cell>
         </row>
         <row r="104">
@@ -1636,7 +1636,7 @@
             <v>8</v>
           </cell>
           <cell r="M104">
-            <v>2865200</v>
+            <v>2949200</v>
           </cell>
         </row>
         <row r="105">
@@ -1658,7 +1658,7 @@
             <v>8</v>
           </cell>
           <cell r="M106">
-            <v>1003000</v>
+            <v>1087000</v>
           </cell>
         </row>
         <row r="107">
@@ -1680,7 +1680,7 @@
             <v>11</v>
           </cell>
           <cell r="M108">
-            <v>3816800</v>
+            <v>3984800</v>
           </cell>
         </row>
         <row r="109">
@@ -1691,7 +1691,7 @@
             <v>8</v>
           </cell>
           <cell r="M109">
-            <v>547800</v>
+            <v>715800</v>
           </cell>
         </row>
         <row r="110">
@@ -1702,7 +1702,7 @@
             <v>9</v>
           </cell>
           <cell r="M110">
-            <v>1099600</v>
+            <v>1183600</v>
           </cell>
         </row>
         <row r="111">
@@ -1713,7 +1713,7 @@
             <v>28</v>
           </cell>
           <cell r="M111">
-            <v>1141600</v>
+            <v>1192000</v>
           </cell>
         </row>
         <row r="112">
@@ -1743,10 +1743,10 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I114">
-            <v>6</v>
+            <v>11</v>
           </cell>
           <cell r="M114">
-            <v>2505200</v>
+            <v>3655200</v>
           </cell>
         </row>
         <row r="115">
@@ -1757,7 +1757,7 @@
             <v>11</v>
           </cell>
           <cell r="M115">
-            <v>1617600</v>
+            <v>1701600</v>
           </cell>
         </row>
         <row r="116">
@@ -1790,7 +1790,7 @@
             <v>8</v>
           </cell>
           <cell r="M118">
-            <v>717800</v>
+            <v>885800</v>
           </cell>
         </row>
         <row r="119">
@@ -1812,7 +1812,7 @@
             <v>8</v>
           </cell>
           <cell r="M120">
-            <v>632800</v>
+            <v>716800</v>
           </cell>
         </row>
         <row r="121">
@@ -1823,7 +1823,7 @@
             <v>11</v>
           </cell>
           <cell r="M121">
-            <v>968000</v>
+            <v>1052000</v>
           </cell>
         </row>
         <row r="122">
@@ -1878,7 +1878,7 @@
             <v>3</v>
           </cell>
           <cell r="M126">
-            <v>1366200</v>
+            <v>1834200</v>
           </cell>
         </row>
         <row r="127">
@@ -1889,7 +1889,7 @@
             <v>3</v>
           </cell>
           <cell r="M127">
-            <v>5979800</v>
+            <v>6479800</v>
           </cell>
         </row>
         <row r="128">
@@ -1933,7 +1933,7 @@
             <v>13</v>
           </cell>
           <cell r="M131">
-            <v>1890000</v>
+            <v>2390000</v>
           </cell>
         </row>
         <row r="132">
@@ -1944,7 +1944,7 @@
             <v>18</v>
           </cell>
           <cell r="M132">
-            <v>9161000</v>
+            <v>10161000</v>
           </cell>
         </row>
         <row r="133">
@@ -2010,7 +2010,7 @@
             <v>5</v>
           </cell>
           <cell r="M138">
-            <v>2100000</v>
+            <v>2600000</v>
           </cell>
         </row>
         <row r="139">
@@ -2032,7 +2032,7 @@
             <v>7</v>
           </cell>
           <cell r="M140">
-            <v>1229000</v>
+            <v>1429000</v>
           </cell>
         </row>
         <row r="141">
@@ -2054,7 +2054,7 @@
             <v>3</v>
           </cell>
           <cell r="M142">
-            <v>375000</v>
+            <v>609000</v>
           </cell>
         </row>
         <row r="143">
@@ -2362,7 +2362,7 @@
             <v>6</v>
           </cell>
           <cell r="M170">
-            <v>2997500</v>
+            <v>3147500</v>
           </cell>
         </row>
         <row r="171">
@@ -2612,10 +2612,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I193">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="M193">
-            <v>4093000</v>
+            <v>4483000</v>
           </cell>
         </row>
         <row r="194">
@@ -2623,10 +2623,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I194">
-            <v>8</v>
+            <v>11</v>
           </cell>
           <cell r="M194">
-            <v>942000</v>
+            <v>1332000</v>
           </cell>
         </row>
         <row r="195">
@@ -2634,10 +2634,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I195">
-            <v>8</v>
+            <v>11</v>
           </cell>
           <cell r="M195">
-            <v>942000</v>
+            <v>1200000</v>
           </cell>
         </row>
         <row r="196">
@@ -2645,10 +2645,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I196">
-            <v>10</v>
+            <v>13</v>
           </cell>
           <cell r="M196">
-            <v>2390000</v>
+            <v>3480000</v>
           </cell>
         </row>
         <row r="197">
@@ -2656,10 +2656,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I197">
-            <v>8</v>
+            <v>11</v>
           </cell>
           <cell r="M197">
-            <v>883000</v>
+            <v>1352000</v>
           </cell>
         </row>
         <row r="198">
@@ -2667,10 +2667,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I198">
-            <v>8</v>
+            <v>11</v>
           </cell>
           <cell r="M198">
-            <v>1051000</v>
+            <v>1431000</v>
           </cell>
         </row>
         <row r="199">
@@ -2678,10 +2678,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I199">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="M199">
-            <v>684000</v>
+            <v>1087000</v>
           </cell>
         </row>
         <row r="200">
@@ -2725,7 +2725,7 @@
             <v>0</v>
           </cell>
           <cell r="M203">
-            <v>5824200</v>
+            <v>7844200</v>
           </cell>
         </row>
         <row r="204">
@@ -2777,10 +2777,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I208">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="M208">
-            <v>666000</v>
+            <v>1230000</v>
           </cell>
         </row>
         <row r="209">
@@ -2788,10 +2788,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I209">
-            <v>8</v>
+            <v>11</v>
           </cell>
           <cell r="M209">
-            <v>672000</v>
+            <v>894000</v>
           </cell>
         </row>
         <row r="210">
@@ -2799,10 +2799,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I210">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="M210">
-            <v>582000</v>
+            <v>840000</v>
           </cell>
         </row>
         <row r="211">
@@ -2810,10 +2810,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I211">
-            <v>8</v>
+            <v>11</v>
           </cell>
           <cell r="M211">
-            <v>942000</v>
+            <v>1632000</v>
           </cell>
         </row>
         <row r="212">
@@ -2832,10 +2832,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I213">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="M213">
-            <v>5184000</v>
+            <v>7221000</v>
           </cell>
         </row>
         <row r="214">
@@ -2865,10 +2865,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I216">
-            <v>8</v>
+            <v>11</v>
           </cell>
           <cell r="M216">
-            <v>2178000</v>
+            <v>3108000</v>
           </cell>
         </row>
         <row r="217">
@@ -2876,10 +2876,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I217">
-            <v>13</v>
+            <v>16</v>
           </cell>
           <cell r="M217">
-            <v>924000</v>
+            <v>1182000</v>
           </cell>
         </row>
         <row r="218">
@@ -2887,10 +2887,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I218">
-            <v>8</v>
+            <v>11</v>
           </cell>
           <cell r="M218">
-            <v>1410000</v>
+            <v>2160000</v>
           </cell>
         </row>
         <row r="219">
@@ -2898,10 +2898,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I219">
-            <v>8</v>
+            <v>11</v>
           </cell>
           <cell r="M219">
-            <v>1970000</v>
+            <v>3588000</v>
           </cell>
         </row>
         <row r="220">
@@ -3187,7 +3187,7 @@
             <v>5</v>
           </cell>
           <cell r="M245">
-            <v>4499000</v>
+            <v>4584000</v>
           </cell>
         </row>
         <row r="246">
@@ -3198,7 +3198,7 @@
             <v>19</v>
           </cell>
           <cell r="M246">
-            <v>4645000</v>
+            <v>4813000</v>
           </cell>
         </row>
         <row r="247">
@@ -3209,7 +3209,7 @@
             <v>35</v>
           </cell>
           <cell r="M247">
-            <v>7744000</v>
+            <v>8584000</v>
           </cell>
         </row>
         <row r="248">
@@ -3231,7 +3231,7 @@
             <v>16</v>
           </cell>
           <cell r="M249">
-            <v>3524000</v>
+            <v>3706500</v>
           </cell>
         </row>
         <row r="250">
@@ -3242,7 +3242,7 @@
             <v>19</v>
           </cell>
           <cell r="M250">
-            <v>4891500</v>
+            <v>5059500</v>
           </cell>
         </row>
         <row r="251">
@@ -3253,7 +3253,7 @@
             <v>43</v>
           </cell>
           <cell r="M251">
-            <v>9398000</v>
+            <v>10238000</v>
           </cell>
         </row>
         <row r="252">
@@ -3264,7 +3264,7 @@
             <v>19</v>
           </cell>
           <cell r="M252">
-            <v>5178500</v>
+            <v>5346500</v>
           </cell>
         </row>
         <row r="253">
@@ -3297,7 +3297,7 @@
             <v>6</v>
           </cell>
           <cell r="M255">
-            <v>6117000</v>
+            <v>6351000</v>
           </cell>
         </row>
         <row r="256">
@@ -3308,7 +3308,7 @@
             <v>9</v>
           </cell>
           <cell r="M256">
-            <v>3805200</v>
+            <v>4039200</v>
           </cell>
         </row>
         <row r="257">
@@ -3330,7 +3330,7 @@
             <v>23</v>
           </cell>
           <cell r="M258">
-            <v>2755500</v>
+            <v>2989500</v>
           </cell>
         </row>
         <row r="259">
@@ -3341,7 +3341,7 @@
             <v>13</v>
           </cell>
           <cell r="M259">
-            <v>3470000</v>
+            <v>3704000</v>
           </cell>
         </row>
         <row r="260">
@@ -3484,7 +3484,7 @@
             <v>43</v>
           </cell>
           <cell r="M272">
-            <v>9057000</v>
+            <v>9222000</v>
           </cell>
         </row>
         <row r="273">
@@ -3495,7 +3495,7 @@
             <v>23</v>
           </cell>
           <cell r="M273">
-            <v>5018000</v>
+            <v>5858000</v>
           </cell>
         </row>
         <row r="274">
@@ -3506,7 +3506,7 @@
             <v>13</v>
           </cell>
           <cell r="M274">
-            <v>4793000</v>
+            <v>5633000</v>
           </cell>
         </row>
         <row r="275">
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>237716000</v>
+        <v>241986000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.54343701642155851</v>
+        <v>0.55319856406715273</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-199714636.51666558</v>
+        <v>-195444636.51666558</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-11095257.584259199</v>
+        <v>-10858035.362036977</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>212509500</v>
+        <v>223366500</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.48216873231287954</v>
+        <v>0.50680248245920678</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-228227291.41455084</v>
+        <v>-217370291.41455084</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-12679293.967475047</v>
+        <v>-12076127.300808379</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>47542000</v>
+        <v>48928500</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.29732955422321766</v>
+        <v>0.30600078023244087</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-112354651.12237126</v>
+        <v>-110968151.12237126</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-6241925.0623539584</v>
+        <v>-6164897.2845761813</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>89451100</v>
+        <v>91747100</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.35134460601806627</v>
+        <v>0.36036279825290163</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-165145380.11616376</v>
+        <v>-162849380.11616376</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-9174743.339786876</v>
+        <v>-9047187.78423132</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>138137500</v>
+        <v>146179500</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.3639425687649448</v>
+        <v>0.3851303428162175</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-241421012.40149158</v>
+        <v>-233379012.40149158</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-13412278.466749532</v>
+        <v>-12965500.688971754</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4472,19 +4472,19 @@
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
-        <v>552</v>
+        <v>607</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>1.1645569620253164</v>
+        <v>1.2805907172995781</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>4.333333333333333</v>
+        <v>7.3888888888888893</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>1.304635761589404</v>
+        <v>1.315673289183223</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>7.666666666666667</v>
+        <v>7.9444444444444446</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -976,7 +976,7 @@
             <v>23</v>
           </cell>
           <cell r="M44">
-            <v>6016000</v>
+            <v>6856000</v>
           </cell>
         </row>
         <row r="45">
@@ -987,7 +987,7 @@
             <v>3</v>
           </cell>
           <cell r="M45">
-            <v>5211000</v>
+            <v>5596000</v>
           </cell>
         </row>
         <row r="46">
@@ -998,7 +998,7 @@
             <v>3</v>
           </cell>
           <cell r="M46">
-            <v>5211000</v>
+            <v>6051000</v>
           </cell>
         </row>
         <row r="47">
@@ -1086,7 +1086,7 @@
             <v>30</v>
           </cell>
           <cell r="M54">
-            <v>4831000</v>
+            <v>4999000</v>
           </cell>
         </row>
         <row r="55">
@@ -1097,7 +1097,7 @@
             <v>30</v>
           </cell>
           <cell r="M55">
-            <v>4557000</v>
+            <v>4725000</v>
           </cell>
         </row>
         <row r="56">
@@ -1405,7 +1405,7 @@
             <v>3</v>
           </cell>
           <cell r="M83">
-            <v>953200</v>
+            <v>1037200</v>
           </cell>
         </row>
         <row r="84">
@@ -1416,7 +1416,7 @@
             <v>9</v>
           </cell>
           <cell r="M84">
-            <v>1704400</v>
+            <v>1754800</v>
           </cell>
         </row>
         <row r="85">
@@ -1427,7 +1427,7 @@
             <v>14</v>
           </cell>
           <cell r="M85">
-            <v>2575000</v>
+            <v>2625400</v>
           </cell>
         </row>
         <row r="86">
@@ -1438,7 +1438,7 @@
             <v>16</v>
           </cell>
           <cell r="M86">
-            <v>6980800</v>
+            <v>7480800</v>
           </cell>
         </row>
         <row r="87">
@@ -1460,7 +1460,7 @@
             <v>3</v>
           </cell>
           <cell r="M88">
-            <v>721800</v>
+            <v>2102400</v>
           </cell>
         </row>
         <row r="89">
@@ -1537,7 +1537,7 @@
             <v>6</v>
           </cell>
           <cell r="M95">
-            <v>1144600</v>
+            <v>1228600</v>
           </cell>
         </row>
         <row r="96">
@@ -1548,7 +1548,7 @@
             <v>6</v>
           </cell>
           <cell r="M96">
-            <v>1329800</v>
+            <v>1380200</v>
           </cell>
         </row>
         <row r="97">
@@ -1570,7 +1570,7 @@
             <v>3</v>
           </cell>
           <cell r="M98">
-            <v>1541000</v>
+            <v>1775000</v>
           </cell>
         </row>
         <row r="99">
@@ -1592,7 +1592,7 @@
             <v>14</v>
           </cell>
           <cell r="M100">
-            <v>5500000</v>
+            <v>5750400</v>
           </cell>
         </row>
         <row r="101">
@@ -1647,7 +1647,7 @@
             <v>6</v>
           </cell>
           <cell r="M105">
-            <v>4779500</v>
+            <v>5013500</v>
           </cell>
         </row>
         <row r="106">
@@ -1669,7 +1669,7 @@
             <v>6</v>
           </cell>
           <cell r="M107">
-            <v>992000</v>
+            <v>1042400</v>
           </cell>
         </row>
         <row r="108">
@@ -1724,7 +1724,7 @@
             <v>11</v>
           </cell>
           <cell r="M112">
-            <v>1272800</v>
+            <v>1323200</v>
           </cell>
         </row>
         <row r="113">
@@ -1735,7 +1735,7 @@
             <v>9</v>
           </cell>
           <cell r="M113">
-            <v>3280000</v>
+            <v>3530400</v>
           </cell>
         </row>
         <row r="114">
@@ -1834,7 +1834,7 @@
             <v>12</v>
           </cell>
           <cell r="M122">
-            <v>2560500</v>
+            <v>3060500</v>
           </cell>
         </row>
         <row r="123">
@@ -1878,7 +1878,7 @@
             <v>3</v>
           </cell>
           <cell r="M126">
-            <v>1834200</v>
+            <v>2068200</v>
           </cell>
         </row>
         <row r="127">
@@ -1889,7 +1889,7 @@
             <v>3</v>
           </cell>
           <cell r="M127">
-            <v>6479800</v>
+            <v>6979800</v>
           </cell>
         </row>
         <row r="128">
@@ -1911,7 +1911,7 @@
             <v>22</v>
           </cell>
           <cell r="M129">
-            <v>3223900</v>
+            <v>3457900</v>
           </cell>
         </row>
         <row r="130">
@@ -1977,7 +1977,7 @@
             <v>6</v>
           </cell>
           <cell r="M135">
-            <v>1678600</v>
+            <v>1729000</v>
           </cell>
         </row>
         <row r="136">
@@ -1988,7 +1988,7 @@
             <v>8</v>
           </cell>
           <cell r="M136">
-            <v>2040600</v>
+            <v>2091000</v>
           </cell>
         </row>
         <row r="137">
@@ -1999,7 +1999,7 @@
             <v>8</v>
           </cell>
           <cell r="M137">
-            <v>1266400</v>
+            <v>1316800</v>
           </cell>
         </row>
         <row r="138">
@@ -2073,7 +2073,7 @@
             <v>DSE-JAGOIBABNG02</v>
           </cell>
           <cell r="I144">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="M144">
             <v>1572000</v>
@@ -2098,7 +2098,7 @@
             <v>11</v>
           </cell>
           <cell r="M146">
-            <v>1745700</v>
+            <v>1796100</v>
           </cell>
         </row>
         <row r="147">
@@ -2362,7 +2362,7 @@
             <v>6</v>
           </cell>
           <cell r="M170">
-            <v>3147500</v>
+            <v>3297500</v>
           </cell>
         </row>
         <row r="171">
@@ -2733,10 +2733,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I204">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M204">
-            <v>6446000</v>
+            <v>6981000</v>
           </cell>
         </row>
         <row r="205">
@@ -2744,10 +2744,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I205">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M205">
-            <v>302000</v>
+            <v>392000</v>
           </cell>
         </row>
         <row r="206">
@@ -2755,10 +2755,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I206">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M206">
-            <v>302000</v>
+            <v>537000</v>
           </cell>
         </row>
         <row r="207">
@@ -2766,10 +2766,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I207">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M207">
-            <v>626000</v>
+            <v>1161000</v>
           </cell>
         </row>
         <row r="208">
@@ -2821,10 +2821,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I212">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M212">
-            <v>939000</v>
+            <v>1342000</v>
           </cell>
         </row>
         <row r="213">
@@ -2854,10 +2854,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I215">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M215">
-            <v>926000</v>
+            <v>1616000</v>
           </cell>
         </row>
         <row r="216">
@@ -2909,10 +2909,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I220">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="M220">
-            <v>470000</v>
+            <v>692000</v>
           </cell>
         </row>
         <row r="221">
@@ -2920,10 +2920,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I221">
-            <v>13</v>
+            <v>16</v>
           </cell>
           <cell r="M221">
-            <v>3120000</v>
+            <v>3836000</v>
           </cell>
         </row>
         <row r="222">
@@ -2942,10 +2942,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I223">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M223">
-            <v>1869000</v>
+            <v>2259000</v>
           </cell>
         </row>
         <row r="224">
@@ -2986,10 +2986,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I227">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M227">
-            <v>2267000</v>
+            <v>2567000</v>
           </cell>
         </row>
         <row r="228">
@@ -2997,10 +2997,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I228">
-            <v>3</v>
+            <v>13</v>
           </cell>
           <cell r="M228">
-            <v>2735000</v>
+            <v>4060000</v>
           </cell>
         </row>
         <row r="229">
@@ -3008,10 +3008,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I229">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M229">
-            <v>939000</v>
+            <v>1174000</v>
           </cell>
         </row>
         <row r="230">
@@ -3187,7 +3187,7 @@
             <v>5</v>
           </cell>
           <cell r="M245">
-            <v>4584000</v>
+            <v>4716000</v>
           </cell>
         </row>
         <row r="246">
@@ -3198,7 +3198,7 @@
             <v>19</v>
           </cell>
           <cell r="M246">
-            <v>4813000</v>
+            <v>4981000</v>
           </cell>
         </row>
         <row r="247">
@@ -3220,7 +3220,7 @@
             <v>14</v>
           </cell>
           <cell r="M248">
-            <v>1275500</v>
+            <v>1443500</v>
           </cell>
         </row>
         <row r="249">
@@ -3231,7 +3231,7 @@
             <v>16</v>
           </cell>
           <cell r="M249">
-            <v>3706500</v>
+            <v>3874500</v>
           </cell>
         </row>
         <row r="250">
@@ -3242,7 +3242,7 @@
             <v>19</v>
           </cell>
           <cell r="M250">
-            <v>5059500</v>
+            <v>5227500</v>
           </cell>
         </row>
         <row r="251">
@@ -3264,7 +3264,7 @@
             <v>19</v>
           </cell>
           <cell r="M252">
-            <v>5346500</v>
+            <v>5514500</v>
           </cell>
         </row>
         <row r="253">
@@ -3308,7 +3308,7 @@
             <v>9</v>
           </cell>
           <cell r="M256">
-            <v>4039200</v>
+            <v>5539200</v>
           </cell>
         </row>
         <row r="257">
@@ -3330,7 +3330,7 @@
             <v>23</v>
           </cell>
           <cell r="M258">
-            <v>2989500</v>
+            <v>5337000</v>
           </cell>
         </row>
         <row r="259">
@@ -3407,7 +3407,7 @@
             <v>14</v>
           </cell>
           <cell r="M265">
-            <v>2730700</v>
+            <v>2781100</v>
           </cell>
         </row>
         <row r="266">
@@ -3484,7 +3484,7 @@
             <v>43</v>
           </cell>
           <cell r="M272">
-            <v>9222000</v>
+            <v>9354000</v>
           </cell>
         </row>
         <row r="273">
@@ -3572,7 +3572,7 @@
             <v>18</v>
           </cell>
           <cell r="M280">
-            <v>3601000</v>
+            <v>4022000</v>
           </cell>
         </row>
         <row r="281">
@@ -3616,7 +3616,7 @@
             <v>13</v>
           </cell>
           <cell r="M284">
-            <v>4121000</v>
+            <v>4338000</v>
           </cell>
         </row>
         <row r="285">
@@ -3627,7 +3627,7 @@
             <v>13</v>
           </cell>
           <cell r="M285">
-            <v>2856000</v>
+            <v>3241000</v>
           </cell>
         </row>
         <row r="286">
@@ -3638,7 +3638,7 @@
             <v>13</v>
           </cell>
           <cell r="M286">
-            <v>6394000</v>
+            <v>6779000</v>
           </cell>
         </row>
         <row r="287">
@@ -3657,10 +3657,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I288">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M288">
-            <v>670000</v>
+            <v>1028000</v>
           </cell>
         </row>
         <row r="289">
@@ -3668,10 +3668,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I289">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M289">
-            <v>1637000</v>
+            <v>2172000</v>
           </cell>
         </row>
         <row r="290">
@@ -3679,10 +3679,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I290">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M290">
-            <v>962000</v>
+            <v>1497000</v>
           </cell>
         </row>
         <row r="291">
@@ -3690,10 +3690,10 @@
             <v>DSE1147</v>
           </cell>
           <cell r="I291">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="M291">
-            <v>3296000</v>
+            <v>4226000</v>
           </cell>
         </row>
         <row r="292">
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D4" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A4,[1]Sheet1!$M:$M)</f>
-        <v>241986000</v>
+        <v>245723000</v>
       </c>
       <c r="E4" s="9">
         <f>D4/C4</f>
-        <v>0.55319856406715273</v>
+        <v>0.56174163281459655</v>
       </c>
       <c r="F4" s="10">
         <f>D4-C4</f>
-        <v>-195444636.51666558</v>
+        <v>-191707636.51666558</v>
       </c>
       <c r="G4" s="19">
         <f>F4/18</f>
-        <v>-10858035.362036977</v>
+        <v>-10650424.250925865</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D5" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A5,[1]Sheet1!$M:$M)</f>
-        <v>223366500</v>
+        <v>231550500</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.50680248245920678</v>
+        <v>0.52537138834458419</v>
       </c>
       <c r="F5" s="10">
         <f t="shared" ref="F5:F8" si="1">D5-C5</f>
-        <v>-217370291.41455084</v>
+        <v>-209186291.41455084</v>
       </c>
       <c r="G5" s="19">
         <f t="shared" ref="G5:G8" si="2">F5/18</f>
-        <v>-12076127.300808379</v>
+        <v>-11621460.634141713</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5">
@@ -4338,19 +4338,19 @@
       </c>
       <c r="D6" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A6,[1]Sheet1!$M:$M)</f>
-        <v>48928500</v>
+        <v>50104500</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>0.30600078023244087</v>
+        <v>0.3133555308901016</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>-110968151.12237126</v>
+        <v>-109792151.12237126</v>
       </c>
       <c r="G6" s="19">
         <f t="shared" si="2"/>
-        <v>-6164897.2845761813</v>
+        <v>-6099563.9512428474</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5">
@@ -4365,19 +4365,19 @@
       </c>
       <c r="D7" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A7,[1]Sheet1!$M:$M)</f>
-        <v>91747100</v>
+        <v>92919900</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.36036279825290163</v>
+        <v>0.36496930341536454</v>
       </c>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>-162849380.11616376</v>
+        <v>-161676580.11616376</v>
       </c>
       <c r="G7" s="19">
         <f t="shared" si="2"/>
-        <v>-9047187.78423132</v>
+        <v>-8982032.2286757641</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="D8" s="20">
         <f>SUMIF([1]Sheet1!$C:$C,A8,[1]Sheet1!$M:$M)</f>
-        <v>146179500</v>
+        <v>153843600</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.3851303428162175</v>
+        <v>0.40532248645043278</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>-233379012.40149158</v>
+        <v>-225714912.40149158</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="2"/>
-        <v>-12965500.688971754</v>
+        <v>-12539717.355638422</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4472,19 +4472,19 @@
       </c>
       <c r="D12" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A12,[1]Sheet1!$I:$I)</f>
-        <v>607</v>
+        <v>669</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="3"/>
-        <v>1.2805907172995781</v>
+        <v>1.4113924050632911</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" ref="F12:F15" si="4">D12-C12</f>
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="G12" s="19">
         <f t="shared" ref="G12:G15" si="5">F12/18</f>
-        <v>7.3888888888888893</v>
+        <v>10.833333333333334</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D15" s="10">
         <f>SUMIF([1]Sheet1!$C:$C,A15,[1]Sheet1!$I:$I)</f>
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="3"/>
-        <v>1.315673289183223</v>
+        <v>1.3178807947019868</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="4"/>
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="5"/>
-        <v>7.9444444444444446</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -561,7 +561,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T7">
-            <v>2965700</v>
+            <v>3018500</v>
           </cell>
           <cell r="U7">
             <v>31</v>
@@ -578,7 +578,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T8">
-            <v>210500</v>
+            <v>260900</v>
           </cell>
           <cell r="U8">
             <v>22</v>
@@ -799,7 +799,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T21">
-            <v>492000</v>
+            <v>726000</v>
           </cell>
           <cell r="U21">
             <v>13</v>
@@ -850,7 +850,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T24">
-            <v>203000</v>
+            <v>572000</v>
           </cell>
           <cell r="U24">
             <v>9</v>
@@ -952,7 +952,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T30">
-            <v>463500</v>
+            <v>513900</v>
           </cell>
           <cell r="U30">
             <v>9</v>
@@ -969,7 +969,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T31">
-            <v>324000</v>
+            <v>469000</v>
           </cell>
           <cell r="U31">
             <v>13</v>
@@ -986,7 +986,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T32">
-            <v>361400</v>
+            <v>414200</v>
           </cell>
           <cell r="U32">
             <v>14</v>
@@ -1020,7 +1020,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T34">
-            <v>255600</v>
+            <v>308400</v>
           </cell>
           <cell r="U34">
             <v>5</v>
@@ -1037,7 +1037,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T35">
-            <v>967500</v>
+            <v>1085100</v>
           </cell>
           <cell r="U35">
             <v>0</v>
@@ -1105,10 +1105,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T39">
-            <v>1426000</v>
+            <v>1486000</v>
           </cell>
           <cell r="U39">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y39" t="str">
             <v/>
@@ -1122,10 +1122,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T40">
-            <v>993000</v>
+            <v>2053000</v>
           </cell>
           <cell r="U40">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y40">
             <v>0</v>
@@ -1207,7 +1207,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T45">
-            <v>1843200</v>
+            <v>1944000</v>
           </cell>
           <cell r="U45">
             <v>5</v>
@@ -1292,7 +1292,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T50">
-            <v>0</v>
+            <v>100000</v>
           </cell>
           <cell r="U50">
             <v>0</v>
@@ -1309,7 +1309,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T51">
-            <v>2328000</v>
+            <v>2828000</v>
           </cell>
           <cell r="U51">
             <v>5</v>
@@ -1326,7 +1326,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T52">
-            <v>909600</v>
+            <v>962400</v>
           </cell>
           <cell r="U52">
             <v>3</v>
@@ -1394,7 +1394,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T56">
-            <v>594000</v>
+            <v>828000</v>
           </cell>
           <cell r="U56">
             <v>3</v>
@@ -1411,7 +1411,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T57">
-            <v>357200</v>
+            <v>502200</v>
           </cell>
           <cell r="U57">
             <v>0</v>
@@ -1445,10 +1445,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T59">
-            <v>2110000</v>
+            <v>2549000</v>
           </cell>
           <cell r="U59">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y59" t="str">
             <v/>
@@ -1479,7 +1479,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T61">
-            <v>2261500</v>
+            <v>2311900</v>
           </cell>
           <cell r="U61">
             <v>0</v>
@@ -1496,7 +1496,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T62">
-            <v>5252000</v>
+            <v>5420000</v>
           </cell>
           <cell r="U62">
             <v>0</v>
@@ -1564,7 +1564,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T66">
-            <v>1850000</v>
+            <v>2150000</v>
           </cell>
           <cell r="U66">
             <v>5</v>
@@ -1638,7 +1638,7 @@
             <v>5</v>
           </cell>
           <cell r="Y70">
-            <v>2620000</v>
+            <v>2820000</v>
           </cell>
           <cell r="Z70">
             <v>0</v>
@@ -1649,7 +1649,7 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T71">
-            <v>2050000</v>
+            <v>2200000</v>
           </cell>
           <cell r="U71">
             <v>0</v>
@@ -1768,7 +1768,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T78">
-            <v>318000</v>
+            <v>385200</v>
           </cell>
           <cell r="U78">
             <v>5</v>
@@ -1785,7 +1785,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T79">
-            <v>556400</v>
+            <v>606800</v>
           </cell>
           <cell r="U79">
             <v>0</v>
@@ -1802,10 +1802,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T80">
-            <v>0</v>
+            <v>150000</v>
           </cell>
           <cell r="U80">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y80" t="str">
             <v/>
@@ -1853,10 +1853,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T83">
-            <v>1558000</v>
+            <v>1618000</v>
           </cell>
           <cell r="U83">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y83" t="str">
             <v/>
@@ -1904,7 +1904,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T86">
-            <v>84000</v>
+            <v>168000</v>
           </cell>
           <cell r="U86">
             <v>0</v>
@@ -1955,7 +1955,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T89">
-            <v>385600</v>
+            <v>438400</v>
           </cell>
           <cell r="U89">
             <v>5</v>
@@ -2006,10 +2006,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T92">
-            <v>7145000</v>
+            <v>7295000</v>
           </cell>
           <cell r="U92">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y92" t="str">
             <v/>
@@ -2023,10 +2023,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T93">
-            <v>290000</v>
+            <v>629500</v>
           </cell>
           <cell r="U93">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y93" t="str">
             <v/>
@@ -2159,7 +2159,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T101">
-            <v>198500</v>
+            <v>466700</v>
           </cell>
           <cell r="U101">
             <v>0</v>
@@ -2193,7 +2193,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T103">
-            <v>143000</v>
+            <v>596000</v>
           </cell>
           <cell r="U103">
             <v>0</v>
@@ -2329,10 +2329,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T111">
-            <v>1500000</v>
+            <v>1560000</v>
           </cell>
           <cell r="U111">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y111" t="str">
             <v/>
@@ -2346,10 +2346,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T112">
-            <v>698000</v>
+            <v>758000</v>
           </cell>
           <cell r="U112">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y112" t="str">
             <v/>
@@ -2675,7 +2675,7 @@
             <v>5</v>
           </cell>
           <cell r="Y131">
-            <v>0</v>
+            <v>2000000</v>
           </cell>
           <cell r="Z131">
             <v>0</v>
@@ -2822,7 +2822,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T140">
-            <v>1544000</v>
+            <v>1594400</v>
           </cell>
           <cell r="U140">
             <v>5</v>
@@ -2845,7 +2845,7 @@
             <v/>
           </cell>
           <cell r="Y141">
-            <v>0</v>
+            <v>100000</v>
           </cell>
           <cell r="Z141">
             <v>0</v>
@@ -2941,7 +2941,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T147">
-            <v>562800</v>
+            <v>1162800</v>
           </cell>
           <cell r="U147">
             <v>5</v>
@@ -3145,7 +3145,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T159">
-            <v>2356400</v>
+            <v>3356400</v>
           </cell>
           <cell r="U159">
             <v>5</v>
@@ -3179,13 +3179,13 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T161">
-            <v>2764200</v>
+            <v>2964200</v>
           </cell>
           <cell r="U161">
             <v>0</v>
           </cell>
           <cell r="Y161">
-            <v>1400000</v>
+            <v>1500000</v>
           </cell>
           <cell r="Z161">
             <v>0</v>
@@ -3196,7 +3196,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T162">
-            <v>217900</v>
+            <v>1217900</v>
           </cell>
           <cell r="U162">
             <v>0</v>
@@ -3247,7 +3247,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T165">
-            <v>255600</v>
+            <v>308400</v>
           </cell>
           <cell r="U165">
             <v>5</v>
@@ -3434,13 +3434,13 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T176">
-            <v>1858200</v>
+            <v>2358200</v>
           </cell>
           <cell r="U176">
             <v>0</v>
           </cell>
           <cell r="Y176">
-            <v>700000</v>
+            <v>1000000</v>
           </cell>
           <cell r="Z176">
             <v>0</v>
@@ -3604,7 +3604,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T186">
-            <v>0</v>
+            <v>2020000</v>
           </cell>
           <cell r="U186">
             <v>0</v>
@@ -3757,7 +3757,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T195">
-            <v>16100000</v>
+            <v>16167200</v>
           </cell>
           <cell r="U195">
             <v>8</v>
@@ -3774,7 +3774,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T196">
-            <v>8204000</v>
+            <v>8271200</v>
           </cell>
           <cell r="U196">
             <v>5</v>
@@ -3842,7 +3842,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T200">
-            <v>5210500</v>
+            <v>5260900</v>
           </cell>
           <cell r="U200">
             <v>0</v>
@@ -3859,7 +3859,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T201">
-            <v>210500</v>
+            <v>260900</v>
           </cell>
           <cell r="U201">
             <v>0</v>
@@ -3876,7 +3876,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T202">
-            <v>168000</v>
+            <v>218400</v>
           </cell>
           <cell r="U202">
             <v>0</v>
@@ -4046,10 +4046,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T212">
-            <v>2155000</v>
+            <v>2792000</v>
           </cell>
           <cell r="U212">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y212" t="str">
             <v/>
@@ -4131,7 +4131,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T217">
-            <v>324000</v>
+            <v>558000</v>
           </cell>
           <cell r="U217">
             <v>3</v>
@@ -4148,7 +4148,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T218">
-            <v>324000</v>
+            <v>573000</v>
           </cell>
           <cell r="U218">
             <v>3</v>
@@ -4165,7 +4165,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T219">
-            <v>324000</v>
+            <v>703000</v>
           </cell>
           <cell r="U219">
             <v>3</v>
@@ -4233,10 +4233,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T223">
-            <v>828000</v>
+            <v>888000</v>
           </cell>
           <cell r="U223">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y223" t="str">
             <v/>
@@ -4352,7 +4352,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T230">
-            <v>600000</v>
+            <v>684000</v>
           </cell>
           <cell r="U230">
             <v>0</v>
@@ -4369,7 +4369,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T231">
-            <v>0</v>
+            <v>84000</v>
           </cell>
           <cell r="U231">
             <v>0</v>
@@ -4386,7 +4386,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T232">
-            <v>50600</v>
+            <v>134600</v>
           </cell>
           <cell r="U232">
             <v>0</v>
@@ -4403,7 +4403,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T233">
-            <v>1095000</v>
+            <v>1563000</v>
           </cell>
           <cell r="U233">
             <v>5</v>
@@ -4420,7 +4420,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T234">
-            <v>318000</v>
+            <v>486000</v>
           </cell>
           <cell r="U234">
             <v>5</v>
@@ -4437,7 +4437,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T235">
-            <v>1318000</v>
+            <v>1486000</v>
           </cell>
           <cell r="U235">
             <v>5</v>
@@ -4488,10 +4488,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T238">
-            <v>1252000</v>
+            <v>1402000</v>
           </cell>
           <cell r="U238">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y238" t="str">
             <v/>
@@ -4505,10 +4505,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T239">
-            <v>168000</v>
+            <v>318000</v>
           </cell>
           <cell r="U239">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y239" t="str">
             <v/>
@@ -4518,7 +4518,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4979,53 +4979,53 @@
         <f>F6+D6</f>
         <v>255</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$T:$T)</f>
-        <v>52992100</v>
-      </c>
-      <c r="J6" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J6" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$U:$U)</f>
-        <v>112</v>
-      </c>
-      <c r="K6" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K6" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$Y:$Y)</f>
-        <v>5000000</v>
-      </c>
-      <c r="L6" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L6" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$Z:$Z)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M6" s="17" t="e">
         <f>K6+I6</f>
-        <v>57992100</v>
-      </c>
-      <c r="N6" s="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N6" s="17" t="e">
         <f>L6+J6</f>
-        <v>112</v>
-      </c>
-      <c r="O6" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O6" s="19" t="e">
         <f t="shared" ref="O6:T11" si="0">I6/C6</f>
-        <v>0.36209046032026138</v>
-      </c>
-      <c r="P6" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P6" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.5258215962441315</v>
-      </c>
-      <c r="Q6" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q6" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.26065943298595295</v>
-      </c>
-      <c r="R6" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R6" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S6" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="S6" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.35033650750638062</v>
-      </c>
-      <c r="T6" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T6" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.4392156862745098</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="14.5">
@@ -5055,53 +5055,53 @@
         <f t="shared" si="1"/>
         <v>225</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$T:$T)</f>
-        <v>25230100</v>
-      </c>
-      <c r="J7" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J7" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$U:$U)</f>
-        <v>63</v>
-      </c>
-      <c r="K7" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K7" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Y:$Y)</f>
-        <v>12400000</v>
-      </c>
-      <c r="L7" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L7" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Z:$Z)</f>
-        <v>1</v>
-      </c>
-      <c r="M7" s="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M7" s="17" t="e">
         <f t="shared" ref="M7:N11" si="2">K7+I7</f>
-        <v>37630100</v>
-      </c>
-      <c r="N7" s="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N7" s="17" t="e">
         <f t="shared" si="2"/>
-        <v>64</v>
-      </c>
-      <c r="O7" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O7" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.36763090712581986</v>
-      </c>
-      <c r="P7" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P7" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.31188118811881188</v>
-      </c>
-      <c r="Q7" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q7" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.8755763033222731</v>
-      </c>
-      <c r="R7" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R7" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>4.3478260869565216E-2</v>
-      </c>
-      <c r="S7" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="S7" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.45451927690487276</v>
-      </c>
-      <c r="T7" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T7" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.28444444444444444</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="14.5">
@@ -5131,53 +5131,53 @@
         <f t="shared" si="1"/>
         <v>230</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$T:$T)</f>
-        <v>14072800</v>
-      </c>
-      <c r="J8" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J8" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$U:$U)</f>
-        <v>22</v>
-      </c>
-      <c r="K8" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K8" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Y:$Y)</f>
-        <v>1500000</v>
-      </c>
-      <c r="L8" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L8" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Z:$Z)</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M8" s="17" t="e">
         <f t="shared" si="2"/>
-        <v>15572800</v>
-      </c>
-      <c r="N8" s="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N8" s="17" t="e">
         <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="O8" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O8" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.1511365254762147</v>
-      </c>
-      <c r="P8" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P8" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>9.7777777777777783E-2</v>
-      </c>
-      <c r="Q8" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q8" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.35851449522781542</v>
-      </c>
-      <c r="R8" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R8" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S8" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="S8" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.16005411105045059</v>
-      </c>
-      <c r="T8" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T8" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>9.5652173913043481E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="14.5">
@@ -5207,53 +5207,53 @@
         <f t="shared" si="1"/>
         <v>445</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$T:$T)</f>
-        <v>75853000</v>
-      </c>
-      <c r="J9" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J9" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$U:$U)</f>
-        <v>117</v>
-      </c>
-      <c r="K9" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K9" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Y:$Y)</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L9" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Z:$Z)</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M9" s="17" t="e">
         <f t="shared" si="2"/>
-        <v>75853000</v>
-      </c>
-      <c r="N9" s="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N9" s="17" t="e">
         <f t="shared" si="2"/>
-        <v>117</v>
-      </c>
-      <c r="O9" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O9" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.24741080540753846</v>
-      </c>
-      <c r="P9" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P9" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="Q9" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q9" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R9" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="S9" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.23381527264296287</v>
-      </c>
-      <c r="T9" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T9" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.26292134831460673</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="14.5">
@@ -5283,53 +5283,53 @@
         <f t="shared" si="1"/>
         <v>427</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$T:$T)</f>
-        <v>24876200</v>
-      </c>
-      <c r="J10" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J10" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$U:$U)</f>
-        <v>123</v>
-      </c>
-      <c r="K10" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K10" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Y:$Y)</f>
-        <v>5100000</v>
-      </c>
-      <c r="L10" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L10" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Z:$Z)</f>
-        <v>1</v>
-      </c>
-      <c r="M10" s="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M10" s="17" t="e">
         <f t="shared" si="2"/>
-        <v>29976200</v>
-      </c>
-      <c r="N10" s="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N10" s="17" t="e">
         <f t="shared" si="2"/>
-        <v>124</v>
-      </c>
-      <c r="O10" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O10" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.20047035536061519</v>
-      </c>
-      <c r="P10" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P10" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.50617283950617287</v>
-      </c>
-      <c r="Q10" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q10" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.15688731466995104</v>
-      </c>
-      <c r="R10" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R10" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>5.434782608695652E-3</v>
-      </c>
-      <c r="S10" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="S10" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.19142308424244794</v>
-      </c>
-      <c r="T10" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T10" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.29039812646370022</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="14.5">
@@ -5359,53 +5359,53 @@
         <f t="shared" si="1"/>
         <v>430</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$T:$T)</f>
-        <v>35541900</v>
-      </c>
-      <c r="J11" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J11" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$U:$U)</f>
-        <v>143</v>
-      </c>
-      <c r="K11" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K11" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Y:$Y)</f>
-        <v>4720000</v>
-      </c>
-      <c r="L11" s="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L11" s="18" t="e">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Z:$Z)</f>
-        <v>3</v>
-      </c>
-      <c r="M11" s="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M11" s="17" t="e">
         <f t="shared" si="2"/>
-        <v>40261900</v>
-      </c>
-      <c r="N11" s="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N11" s="17" t="e">
         <f t="shared" si="2"/>
-        <v>146</v>
-      </c>
-      <c r="O11" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O11" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.13702020947526081</v>
-      </c>
-      <c r="P11" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P11" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.40056022408963587</v>
-      </c>
-      <c r="Q11" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q11" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.12554013843079501</v>
-      </c>
-      <c r="R11" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R11" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>4.1095890410958902E-2</v>
-      </c>
-      <c r="S11" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="S11" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.13556688256677346</v>
-      </c>
-      <c r="T11" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T11" s="19" t="e">
         <f t="shared" si="0"/>
-        <v>0.33953488372093021</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="14.5">
@@ -5437,53 +5437,53 @@
         <f t="shared" si="3"/>
         <v>2012</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="23" t="e">
         <f t="shared" si="3"/>
-        <v>228566100</v>
-      </c>
-      <c r="J12" s="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J12" s="23" t="e">
         <f t="shared" si="3"/>
-        <v>580</v>
-      </c>
-      <c r="K12" s="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K12" s="23" t="e">
         <f t="shared" si="3"/>
-        <v>28720000</v>
-      </c>
-      <c r="L12" s="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L12" s="23" t="e">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="M12" s="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M12" s="23" t="e">
         <f t="shared" si="3"/>
-        <v>257286100</v>
-      </c>
-      <c r="N12" s="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N12" s="23" t="e">
         <f t="shared" si="3"/>
-        <v>585</v>
-      </c>
-      <c r="O12" s="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O12" s="24" t="e">
         <f>AVERAGE(O6:O11)</f>
-        <v>0.2442932105276184</v>
-      </c>
-      <c r="P12" s="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P12" s="24" t="e">
         <f t="shared" ref="P12:T12" si="4">AVERAGE(P6:P11)</f>
-        <v>0.36120227095608831</v>
-      </c>
-      <c r="Q12" s="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q12" s="24" t="e">
         <f t="shared" si="4"/>
-        <v>0.29619628077279792</v>
-      </c>
-      <c r="R12" s="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R12" s="24" t="e">
         <f t="shared" si="4"/>
-        <v>1.5001488981536628E-2</v>
-      </c>
-      <c r="S12" s="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="S12" s="24" t="e">
         <f t="shared" si="4"/>
-        <v>0.25428585581898139</v>
-      </c>
-      <c r="T12" s="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T12" s="24" t="e">
         <f t="shared" si="4"/>
-        <v>0.28536111052187252</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:20">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -4518,7 +4518,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4979,53 +4979,53 @@
         <f>F6+D6</f>
         <v>255</v>
       </c>
-      <c r="I6" s="18" t="e">
+      <c r="I6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$T:$T)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J6" s="18" t="e">
+        <v>55684100</v>
+      </c>
+      <c r="J6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$U:$U)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K6" s="18" t="e">
+        <v>112</v>
+      </c>
+      <c r="K6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$Y:$Y)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L6" s="18" t="e">
+        <v>5000000</v>
+      </c>
+      <c r="L6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$Z:$Z)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M6" s="17" t="e">
+        <v>0</v>
+      </c>
+      <c r="M6" s="17">
         <f>K6+I6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N6" s="17" t="e">
+        <v>60684100</v>
+      </c>
+      <c r="N6" s="17">
         <f>L6+J6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O6" s="19" t="e">
+        <v>112</v>
+      </c>
+      <c r="O6" s="19">
         <f t="shared" ref="O6:T11" si="0">I6/C6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P6" s="19" t="e">
+        <v>0.38048466472397707</v>
+      </c>
+      <c r="P6" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q6" s="19" t="e">
+        <v>0.5258215962441315</v>
+      </c>
+      <c r="Q6" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R6" s="19" t="e">
+        <v>0.26065943298595295</v>
+      </c>
+      <c r="R6" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S6" s="19" t="e">
+        <v>0</v>
+      </c>
+      <c r="S6" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T6" s="19" t="e">
+        <v>0.36659916876898668</v>
+      </c>
+      <c r="T6" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>0.4392156862745098</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="14.5">
@@ -5055,53 +5055,53 @@
         <f t="shared" si="1"/>
         <v>225</v>
       </c>
-      <c r="I7" s="18" t="e">
+      <c r="I7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$T:$T)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J7" s="18" t="e">
+        <v>26717300</v>
+      </c>
+      <c r="J7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$U:$U)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K7" s="18" t="e">
+        <v>63</v>
+      </c>
+      <c r="K7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Y:$Y)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L7" s="18" t="e">
+        <v>12800000</v>
+      </c>
+      <c r="L7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Z:$Z)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M7" s="17" t="e">
+        <v>1</v>
+      </c>
+      <c r="M7" s="17">
         <f t="shared" ref="M7:N11" si="2">K7+I7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N7" s="17" t="e">
+        <v>39517300</v>
+      </c>
+      <c r="N7" s="17">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O7" s="19" t="e">
+        <v>64</v>
+      </c>
+      <c r="O7" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P7" s="19" t="e">
+        <v>0.38930108223719556</v>
+      </c>
+      <c r="P7" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q7" s="19" t="e">
+        <v>0.31188118811881188</v>
+      </c>
+      <c r="Q7" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R7" s="19" t="e">
+        <v>0.90382070020363681</v>
+      </c>
+      <c r="R7" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S7" s="19" t="e">
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="S7" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T7" s="19" t="e">
+        <v>0.47731402843024412</v>
+      </c>
+      <c r="T7" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>0.28444444444444444</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="14.5">
@@ -5131,53 +5131,53 @@
         <f t="shared" si="1"/>
         <v>230</v>
       </c>
-      <c r="I8" s="18" t="e">
+      <c r="I8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$T:$T)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J8" s="18" t="e">
+        <v>14372800</v>
+      </c>
+      <c r="J8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$U:$U)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K8" s="18" t="e">
+        <v>27</v>
+      </c>
+      <c r="K8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Y:$Y)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L8" s="18" t="e">
+        <v>1500000</v>
+      </c>
+      <c r="L8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Z:$Z)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M8" s="17" t="e">
+        <v>0</v>
+      </c>
+      <c r="M8" s="17">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N8" s="17" t="e">
+        <v>15872800</v>
+      </c>
+      <c r="N8" s="17">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O8" s="19" t="e">
+        <v>27</v>
+      </c>
+      <c r="O8" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P8" s="19" t="e">
+        <v>0.15435841150052149</v>
+      </c>
+      <c r="P8" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q8" s="19" t="e">
+        <v>0.12</v>
+      </c>
+      <c r="Q8" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R8" s="19" t="e">
+        <v>0.35851449522781542</v>
+      </c>
+      <c r="R8" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S8" s="19" t="e">
+        <v>0</v>
+      </c>
+      <c r="S8" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T8" s="19" t="e">
+        <v>0.16313745080406811</v>
+      </c>
+      <c r="T8" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>0.11739130434782609</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="14.5">
@@ -5207,53 +5207,53 @@
         <f t="shared" si="1"/>
         <v>445</v>
       </c>
-      <c r="I9" s="18" t="e">
+      <c r="I9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$T:$T)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J9" s="18" t="e">
+        <v>80553500</v>
+      </c>
+      <c r="J9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$U:$U)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K9" s="18" t="e">
+        <v>143</v>
+      </c>
+      <c r="K9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Y:$Y)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L9" s="18" t="e">
+        <v>0</v>
+      </c>
+      <c r="L9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Z:$Z)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M9" s="17" t="e">
+        <v>0</v>
+      </c>
+      <c r="M9" s="17">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N9" s="17" t="e">
+        <v>80553500</v>
+      </c>
+      <c r="N9" s="17">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O9" s="19" t="e">
+        <v>143</v>
+      </c>
+      <c r="O9" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P9" s="19" t="e">
+        <v>0.26274249289278145</v>
+      </c>
+      <c r="P9" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q9" s="19" t="e">
+        <v>0.3972222222222222</v>
+      </c>
+      <c r="Q9" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R9" s="19" t="e">
+        <v>0</v>
+      </c>
+      <c r="R9" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S9" s="19" t="e">
+        <v>0</v>
+      </c>
+      <c r="S9" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T9" s="19" t="e">
+        <v>0.24830446475215101</v>
+      </c>
+      <c r="T9" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>0.32134831460674157</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="14.5">
@@ -5283,53 +5283,53 @@
         <f t="shared" si="1"/>
         <v>427</v>
       </c>
-      <c r="I10" s="18" t="e">
+      <c r="I10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$T:$T)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J10" s="18" t="e">
+        <v>28362000</v>
+      </c>
+      <c r="J10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$U:$U)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K10" s="18" t="e">
+        <v>123</v>
+      </c>
+      <c r="K10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Y:$Y)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L10" s="18" t="e">
+        <v>5200000</v>
+      </c>
+      <c r="L10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Z:$Z)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M10" s="17" t="e">
+        <v>1</v>
+      </c>
+      <c r="M10" s="17">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N10" s="17" t="e">
+        <v>33562000</v>
+      </c>
+      <c r="N10" s="17">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O10" s="19" t="e">
+        <v>124</v>
+      </c>
+      <c r="O10" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P10" s="19" t="e">
+        <v>0.22856144502527589</v>
+      </c>
+      <c r="P10" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q10" s="19" t="e">
+        <v>0.50617283950617287</v>
+      </c>
+      <c r="Q10" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R10" s="19" t="e">
+        <v>0.15996353652622458</v>
+      </c>
+      <c r="R10" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S10" s="19" t="e">
+        <v>5.434782608695652E-3</v>
+      </c>
+      <c r="S10" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T10" s="19" t="e">
+        <v>0.21432141343282465</v>
+      </c>
+      <c r="T10" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>0.29039812646370022</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="14.5">
@@ -5359,53 +5359,53 @@
         <f t="shared" si="1"/>
         <v>430</v>
       </c>
-      <c r="I11" s="18" t="e">
+      <c r="I11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$T:$T)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J11" s="18" t="e">
+        <v>37780100</v>
+      </c>
+      <c r="J11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$U:$U)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K11" s="18" t="e">
+        <v>153</v>
+      </c>
+      <c r="K11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Y:$Y)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L11" s="18" t="e">
+        <v>6920000</v>
+      </c>
+      <c r="L11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Z:$Z)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M11" s="17" t="e">
+        <v>3</v>
+      </c>
+      <c r="M11" s="17">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N11" s="17" t="e">
+        <v>44700100</v>
+      </c>
+      <c r="N11" s="17">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O11" s="19" t="e">
+        <v>156</v>
+      </c>
+      <c r="O11" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P11" s="19" t="e">
+        <v>0.14564885996517635</v>
+      </c>
+      <c r="P11" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q11" s="19" t="e">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="Q11" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R11" s="19" t="e">
+        <v>0.18405460973328422</v>
+      </c>
+      <c r="R11" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S11" s="19" t="e">
+        <v>4.1095890410958902E-2</v>
+      </c>
+      <c r="S11" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T11" s="19" t="e">
+        <v>0.15051086032758093</v>
+      </c>
+      <c r="T11" s="19">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>0.36279069767441863</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="14.5">
@@ -5437,53 +5437,53 @@
         <f t="shared" si="3"/>
         <v>2012</v>
       </c>
-      <c r="I12" s="23" t="e">
+      <c r="I12" s="23">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J12" s="23" t="e">
+        <v>243469800</v>
+      </c>
+      <c r="J12" s="23">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K12" s="23" t="e">
+        <v>621</v>
+      </c>
+      <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L12" s="23" t="e">
+        <v>31420000</v>
+      </c>
+      <c r="L12" s="23">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M12" s="23" t="e">
+        <v>5</v>
+      </c>
+      <c r="M12" s="23">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N12" s="23" t="e">
+        <v>274889800</v>
+      </c>
+      <c r="N12" s="23">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O12" s="24" t="e">
+        <v>626</v>
+      </c>
+      <c r="O12" s="24">
         <f>AVERAGE(O6:O11)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P12" s="24" t="e">
+        <v>0.26018282605748799</v>
+      </c>
+      <c r="P12" s="24">
         <f t="shared" ref="P12:T12" si="4">AVERAGE(P6:P11)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q12" s="24" t="e">
+        <v>0.38161154577712786</v>
+      </c>
+      <c r="Q12" s="24">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R12" s="24" t="e">
+        <v>0.3111687957794857</v>
+      </c>
+      <c r="R12" s="24">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S12" s="24" t="e">
+        <v>1.5001488981536628E-2</v>
+      </c>
+      <c r="S12" s="24">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T12" s="24" t="e">
+        <v>0.27003123108597593</v>
+      </c>
+      <c r="T12" s="24">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v>0.30259809563527346</v>
       </c>
     </row>
     <row r="13" spans="1:20">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -612,10 +612,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T10">
-            <v>0</v>
+            <v>486000</v>
           </cell>
           <cell r="U10">
-            <v>46</v>
+            <v>51</v>
           </cell>
           <cell r="Y10" t="str">
             <v/>
@@ -629,7 +629,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T11">
-            <v>898000</v>
+            <v>983000</v>
           </cell>
           <cell r="U11">
             <v>5</v>
@@ -646,10 +646,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T12">
-            <v>690000</v>
+            <v>750000</v>
           </cell>
           <cell r="U12">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y12" t="str">
             <v/>
@@ -680,10 +680,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T14">
-            <v>0</v>
+            <v>403000</v>
           </cell>
           <cell r="U14">
-            <v>22</v>
+            <v>27</v>
           </cell>
           <cell r="Y14" t="str">
             <v/>
@@ -731,10 +731,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T17">
-            <v>253000</v>
+            <v>403000</v>
           </cell>
           <cell r="U17">
-            <v>9</v>
+            <v>14</v>
           </cell>
           <cell r="Y17" t="str">
             <v/>
@@ -748,10 +748,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T18">
-            <v>636000</v>
+            <v>786000</v>
           </cell>
           <cell r="U18">
-            <v>10</v>
+            <v>15</v>
           </cell>
           <cell r="Y18" t="str">
             <v/>
@@ -782,7 +782,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T20">
-            <v>151200</v>
+            <v>309600</v>
           </cell>
           <cell r="U20">
             <v>7</v>
@@ -850,7 +850,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T24">
-            <v>572000</v>
+            <v>704000</v>
           </cell>
           <cell r="U24">
             <v>9</v>
@@ -952,7 +952,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T30">
-            <v>513900</v>
+            <v>597900</v>
           </cell>
           <cell r="U30">
             <v>9</v>
@@ -1020,7 +1020,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T34">
-            <v>308400</v>
+            <v>361200</v>
           </cell>
           <cell r="U34">
             <v>5</v>
@@ -1037,10 +1037,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T35">
-            <v>1085100</v>
+            <v>1235100</v>
           </cell>
           <cell r="U35">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y35" t="str">
             <v/>
@@ -1054,10 +1054,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T36">
-            <v>8165000</v>
+            <v>10225000</v>
           </cell>
           <cell r="U36">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y36" t="str">
             <v/>
@@ -1071,10 +1071,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T37">
-            <v>132000</v>
+            <v>414000</v>
           </cell>
           <cell r="U37">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y37" t="str">
             <v/>
@@ -1088,10 +1088,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T38">
-            <v>10000000</v>
+            <v>10407400</v>
           </cell>
           <cell r="U38">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y38">
             <v>300000</v>
@@ -1139,7 +1139,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T41">
-            <v>1807400</v>
+            <v>1860200</v>
           </cell>
           <cell r="U41">
             <v>6</v>
@@ -1224,10 +1224,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T46">
-            <v>461600</v>
+            <v>611600</v>
           </cell>
           <cell r="U46">
-            <v>2</v>
+            <v>7</v>
           </cell>
           <cell r="Y46">
             <v>200000</v>
@@ -1258,10 +1258,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T48">
-            <v>1140000</v>
+            <v>1290000</v>
           </cell>
           <cell r="U48">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y48">
             <v>0</v>
@@ -1292,10 +1292,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T50">
-            <v>100000</v>
+            <v>586000</v>
           </cell>
           <cell r="U50">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y50" t="str">
             <v/>
@@ -1326,10 +1326,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T52">
-            <v>962400</v>
+            <v>1522400</v>
           </cell>
           <cell r="U52">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y52">
             <v>500000</v>
@@ -1343,10 +1343,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T53">
-            <v>323400</v>
+            <v>473400</v>
           </cell>
           <cell r="U53">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y53">
             <v>0</v>
@@ -1360,10 +1360,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T54">
-            <v>628000</v>
+            <v>778000</v>
           </cell>
           <cell r="U54">
-            <v>2</v>
+            <v>7</v>
           </cell>
           <cell r="Y54">
             <v>200000</v>
@@ -1428,10 +1428,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T58">
-            <v>295000</v>
+            <v>445000</v>
           </cell>
           <cell r="U58">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y58">
             <v>0</v>
@@ -1479,10 +1479,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T61">
-            <v>2311900</v>
+            <v>2512300</v>
           </cell>
           <cell r="U61">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y61" t="str">
             <v/>
@@ -1496,10 +1496,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T62">
-            <v>5420000</v>
+            <v>6570000</v>
           </cell>
           <cell r="U62">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y62" t="str">
             <v/>
@@ -1513,10 +1513,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T63">
-            <v>934900</v>
+            <v>1108900</v>
           </cell>
           <cell r="U63">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="Y63" t="str">
             <v/>
@@ -1564,7 +1564,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T66">
-            <v>2150000</v>
+            <v>2486000</v>
           </cell>
           <cell r="U66">
             <v>5</v>
@@ -1581,10 +1581,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T67">
-            <v>17700000</v>
+            <v>17850000</v>
           </cell>
           <cell r="U67">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y67">
             <v>0</v>
@@ -1598,10 +1598,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T68">
-            <v>1842000</v>
+            <v>2652000</v>
           </cell>
           <cell r="U68">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y68">
             <v>0</v>
@@ -1615,13 +1615,13 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T69">
-            <v>2295000</v>
+            <v>2945000</v>
           </cell>
           <cell r="U69">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y69">
-            <v>0</v>
+            <v>500000</v>
           </cell>
           <cell r="Z69">
             <v>1</v>
@@ -1632,10 +1632,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T70">
-            <v>4602000</v>
+            <v>4752000</v>
           </cell>
           <cell r="U70">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y70">
             <v>2820000</v>
@@ -1649,10 +1649,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T71">
-            <v>2200000</v>
+            <v>3052800</v>
           </cell>
           <cell r="U71">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y71">
             <v>1200000</v>
@@ -1666,10 +1666,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T72">
-            <v>999000</v>
+            <v>1149000</v>
           </cell>
           <cell r="U72">
-            <v>2</v>
+            <v>7</v>
           </cell>
           <cell r="Y72">
             <v>300000</v>
@@ -1683,10 +1683,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T73">
-            <v>1653600</v>
+            <v>1803600</v>
           </cell>
           <cell r="U73">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y73">
             <v>2000000</v>
@@ -1700,10 +1700,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T74">
-            <v>204600</v>
+            <v>354600</v>
           </cell>
           <cell r="U74">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y74">
             <v>0</v>
@@ -1734,10 +1734,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T76">
-            <v>0</v>
+            <v>234000</v>
           </cell>
           <cell r="U76">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y76" t="str">
             <v/>
@@ -1768,10 +1768,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T78">
-            <v>385200</v>
+            <v>535200</v>
           </cell>
           <cell r="U78">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y78" t="str">
             <v/>
@@ -1785,7 +1785,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T79">
-            <v>606800</v>
+            <v>690800</v>
           </cell>
           <cell r="U79">
             <v>0</v>
@@ -1819,10 +1819,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T81">
-            <v>468000</v>
+            <v>618000</v>
           </cell>
           <cell r="U81">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y81" t="str">
             <v/>
@@ -1836,10 +1836,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T82">
-            <v>768000</v>
+            <v>918000</v>
           </cell>
           <cell r="U82">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y82" t="str">
             <v/>
@@ -1938,10 +1938,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T88">
-            <v>1721000</v>
+            <v>1871000</v>
           </cell>
           <cell r="U88">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y88">
             <v>0</v>
@@ -1955,7 +1955,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T89">
-            <v>438400</v>
+            <v>2938400</v>
           </cell>
           <cell r="U89">
             <v>5</v>
@@ -1972,10 +1972,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T90">
-            <v>253000</v>
+            <v>403000</v>
           </cell>
           <cell r="U90">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y90" t="str">
             <v/>
@@ -2108,10 +2108,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T98">
-            <v>0</v>
+            <v>435000</v>
           </cell>
           <cell r="U98">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y98" t="str">
             <v/>
@@ -2125,10 +2125,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T99">
-            <v>0</v>
+            <v>430800</v>
           </cell>
           <cell r="U99">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y99" t="str">
             <v/>
@@ -2142,10 +2142,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T100">
-            <v>217500</v>
+            <v>367500</v>
           </cell>
           <cell r="U100">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y100" t="str">
             <v/>
@@ -2397,10 +2397,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T115">
-            <v>934000</v>
+            <v>1084000</v>
           </cell>
           <cell r="U115">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y115" t="str">
             <v/>
@@ -2414,10 +2414,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T116">
-            <v>359200</v>
+            <v>575200</v>
           </cell>
           <cell r="U116">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y116" t="str">
             <v/>
@@ -2448,10 +2448,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T118">
-            <v>376000</v>
+            <v>727600</v>
           </cell>
           <cell r="U118">
-            <v>0</v>
+            <v>6</v>
           </cell>
           <cell r="Y118" t="str">
             <v/>
@@ -2465,10 +2465,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T119">
-            <v>322200</v>
+            <v>664200</v>
           </cell>
           <cell r="U119">
-            <v>0</v>
+            <v>7</v>
           </cell>
           <cell r="Y119" t="str">
             <v/>
@@ -2499,10 +2499,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T121">
-            <v>250400</v>
+            <v>718400</v>
           </cell>
           <cell r="U121">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y121" t="str">
             <v/>
@@ -2584,10 +2584,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T126">
-            <v>936000</v>
+            <v>1320000</v>
           </cell>
           <cell r="U126">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y126" t="str">
             <v/>
@@ -2618,10 +2618,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T128">
-            <v>500000</v>
+            <v>650000</v>
           </cell>
           <cell r="U128">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y128" t="str">
             <v/>
@@ -2635,10 +2635,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T129">
-            <v>792000</v>
+            <v>852000</v>
           </cell>
           <cell r="U129">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y129" t="str">
             <v/>
@@ -2652,10 +2652,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T130">
-            <v>234000</v>
+            <v>618000</v>
           </cell>
           <cell r="U130">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y130" t="str">
             <v/>
@@ -2669,13 +2669,13 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T131">
-            <v>8473000</v>
+            <v>8618000</v>
           </cell>
           <cell r="U131">
             <v>5</v>
           </cell>
           <cell r="Y131">
-            <v>2000000</v>
+            <v>7000000</v>
           </cell>
           <cell r="Z131">
             <v>0</v>
@@ -2686,10 +2686,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T132">
-            <v>2690000</v>
+            <v>2840000</v>
           </cell>
           <cell r="U132">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y132">
             <v>0</v>
@@ -2703,10 +2703,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T133">
-            <v>300000</v>
+            <v>450000</v>
           </cell>
           <cell r="U133">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y133">
             <v>100000</v>
@@ -2771,10 +2771,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T137">
-            <v>50400</v>
+            <v>461400</v>
           </cell>
           <cell r="U137">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y137" t="str">
             <v/>
@@ -2788,10 +2788,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T138">
-            <v>0</v>
+            <v>405000</v>
           </cell>
           <cell r="U138">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y138" t="str">
             <v/>
@@ -2941,7 +2941,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T147">
-            <v>1162800</v>
+            <v>1215600</v>
           </cell>
           <cell r="U147">
             <v>5</v>
@@ -2958,10 +2958,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T148">
-            <v>313400</v>
+            <v>463400</v>
           </cell>
           <cell r="U148">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y148">
             <v>0</v>
@@ -2975,10 +2975,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T149">
-            <v>219600</v>
+            <v>369600</v>
           </cell>
           <cell r="U149">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y149" t="str">
             <v/>
@@ -3009,10 +3009,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T151">
-            <v>2944000</v>
+            <v>3094000</v>
           </cell>
           <cell r="U151">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y151">
             <v>2000000</v>
@@ -3026,10 +3026,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T152">
-            <v>1790000</v>
+            <v>1940000</v>
           </cell>
           <cell r="U152">
-            <v>10</v>
+            <v>15</v>
           </cell>
           <cell r="Y152" t="str">
             <v/>
@@ -3077,10 +3077,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T155">
-            <v>6115300</v>
+            <v>6265300</v>
           </cell>
           <cell r="U155">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y155">
             <v>0</v>
@@ -3128,10 +3128,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T158">
-            <v>52800</v>
+            <v>308400</v>
           </cell>
           <cell r="U158">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y158" t="str">
             <v/>
@@ -3162,10 +3162,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T160">
-            <v>251000</v>
+            <v>401000</v>
           </cell>
           <cell r="U160">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y160">
             <v>0</v>
@@ -3179,13 +3179,13 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T161">
-            <v>2964200</v>
+            <v>3314200</v>
           </cell>
           <cell r="U161">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y161">
-            <v>1500000</v>
+            <v>1600000</v>
           </cell>
           <cell r="Z161">
             <v>0</v>
@@ -3196,10 +3196,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T162">
-            <v>1217900</v>
+            <v>1367900</v>
           </cell>
           <cell r="U162">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y162">
             <v>0</v>
@@ -3213,10 +3213,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T163">
-            <v>603200</v>
+            <v>753200</v>
           </cell>
           <cell r="U163">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y163">
             <v>300000</v>
@@ -3230,10 +3230,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T164">
-            <v>206400</v>
+            <v>664800</v>
           </cell>
           <cell r="U164">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="Y164" t="str">
             <v/>
@@ -3247,7 +3247,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T165">
-            <v>308400</v>
+            <v>361200</v>
           </cell>
           <cell r="U165">
             <v>5</v>
@@ -3264,10 +3264,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T166">
-            <v>0</v>
+            <v>308400</v>
           </cell>
           <cell r="U166">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y166" t="str">
             <v/>
@@ -3281,10 +3281,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T167">
-            <v>267400</v>
+            <v>417400</v>
           </cell>
           <cell r="U167">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y167" t="str">
             <v/>
@@ -3400,10 +3400,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T174">
-            <v>352000</v>
+            <v>602000</v>
           </cell>
           <cell r="U174">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y174" t="str">
             <v/>
@@ -3417,10 +3417,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T175">
-            <v>235200</v>
+            <v>385200</v>
           </cell>
           <cell r="U175">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y175">
             <v>0</v>
@@ -3434,10 +3434,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T176">
-            <v>2358200</v>
+            <v>2708200</v>
           </cell>
           <cell r="U176">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y176">
             <v>1000000</v>
@@ -3604,10 +3604,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T186">
-            <v>2020000</v>
+            <v>2419000</v>
           </cell>
           <cell r="U186">
-            <v>0</v>
+            <v>8</v>
           </cell>
           <cell r="Y186" t="str">
             <v/>
@@ -3621,10 +3621,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T187">
-            <v>3000000</v>
+            <v>4402000</v>
           </cell>
           <cell r="U187">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y187" t="str">
             <v/>
@@ -3638,10 +3638,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T188">
-            <v>253000</v>
+            <v>403000</v>
           </cell>
           <cell r="U188">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y188" t="str">
             <v/>
@@ -3672,10 +3672,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T190">
-            <v>1900000</v>
+            <v>2134000</v>
           </cell>
           <cell r="U190">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y190" t="str">
             <v/>
@@ -3757,10 +3757,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T195">
-            <v>16167200</v>
+            <v>16317200</v>
           </cell>
           <cell r="U195">
-            <v>8</v>
+            <v>13</v>
           </cell>
           <cell r="Y195">
             <v>0</v>
@@ -3774,10 +3774,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T196">
-            <v>8271200</v>
+            <v>8505200</v>
           </cell>
           <cell r="U196">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y196" t="str">
             <v/>
@@ -3995,10 +3995,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T209">
-            <v>613000</v>
+            <v>763000</v>
           </cell>
           <cell r="U209">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y209" t="str">
             <v/>
@@ -4012,10 +4012,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T210">
-            <v>547000</v>
+            <v>697000</v>
           </cell>
           <cell r="U210">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y210" t="str">
             <v/>
@@ -4063,10 +4063,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T213">
-            <v>468000</v>
+            <v>618000</v>
           </cell>
           <cell r="U213">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y213" t="str">
             <v/>
@@ -4488,10 +4488,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T238">
-            <v>1402000</v>
+            <v>1552000</v>
           </cell>
           <cell r="U238">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y238" t="str">
             <v/>
@@ -4505,10 +4505,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T239">
-            <v>318000</v>
+            <v>468000</v>
           </cell>
           <cell r="U239">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y239" t="str">
             <v/>
@@ -4981,11 +4981,11 @@
       </c>
       <c r="I6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$T:$T)</f>
-        <v>55684100</v>
+        <v>59629500</v>
       </c>
       <c r="J6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$U:$U)</f>
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="K6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$Y:$Y)</f>
@@ -4997,19 +4997,19 @@
       </c>
       <c r="M6" s="17">
         <f>K6+I6</f>
-        <v>60684100</v>
+        <v>64629500</v>
       </c>
       <c r="N6" s="17">
         <f>L6+J6</f>
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="O6" s="19">
         <f t="shared" ref="O6:T11" si="0">I6/C6</f>
-        <v>0.38048466472397707</v>
+        <v>0.40744324349604988</v>
       </c>
       <c r="P6" s="19">
         <f t="shared" si="0"/>
-        <v>0.5258215962441315</v>
+        <v>0.83568075117370888</v>
       </c>
       <c r="Q6" s="19">
         <f t="shared" si="0"/>
@@ -5021,11 +5021,11 @@
       </c>
       <c r="S6" s="19">
         <f t="shared" si="0"/>
-        <v>0.36659916876898668</v>
+        <v>0.39043375411277792</v>
       </c>
       <c r="T6" s="19">
         <f t="shared" si="0"/>
-        <v>0.4392156862745098</v>
+        <v>0.69803921568627447</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="14.5">
@@ -5057,11 +5057,11 @@
       </c>
       <c r="I7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$T:$T)</f>
-        <v>26717300</v>
+        <v>28517300</v>
       </c>
       <c r="J7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$U:$U)</f>
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="K7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Y:$Y)</f>
@@ -5073,19 +5073,19 @@
       </c>
       <c r="M7" s="17">
         <f t="shared" ref="M7:N11" si="2">K7+I7</f>
-        <v>39517300</v>
+        <v>41317300</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="O7" s="19">
         <f t="shared" si="0"/>
-        <v>0.38930108223719556</v>
+        <v>0.41552910483030758</v>
       </c>
       <c r="P7" s="19">
         <f t="shared" si="0"/>
-        <v>0.31188118811881188</v>
+        <v>0.55940594059405946</v>
       </c>
       <c r="Q7" s="19">
         <f t="shared" si="0"/>
@@ -5097,11 +5097,11 @@
       </c>
       <c r="S7" s="19">
         <f t="shared" si="0"/>
-        <v>0.47731402843024412</v>
+        <v>0.49905552522214131</v>
       </c>
       <c r="T7" s="19">
         <f t="shared" si="0"/>
-        <v>0.28444444444444444</v>
+        <v>0.50666666666666671</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="14.5">
@@ -5133,11 +5133,11 @@
       </c>
       <c r="I8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$T:$T)</f>
-        <v>14372800</v>
+        <v>17782800</v>
       </c>
       <c r="J8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$U:$U)</f>
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="K8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Y:$Y)</f>
@@ -5149,19 +5149,19 @@
       </c>
       <c r="M8" s="17">
         <f t="shared" si="2"/>
-        <v>15872800</v>
+        <v>19282800</v>
       </c>
       <c r="N8" s="17">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="O8" s="19">
         <f t="shared" si="0"/>
-        <v>0.15435841150052149</v>
+        <v>0.19098051597680851</v>
       </c>
       <c r="P8" s="19">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.27555555555555555</v>
       </c>
       <c r="Q8" s="19">
         <f t="shared" si="0"/>
@@ -5173,11 +5173,11 @@
       </c>
       <c r="S8" s="19">
         <f t="shared" si="0"/>
-        <v>0.16313745080406811</v>
+        <v>0.19818474600352079</v>
       </c>
       <c r="T8" s="19">
         <f t="shared" si="0"/>
-        <v>0.11739130434782609</v>
+        <v>0.26956521739130435</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="14.5">
@@ -5209,11 +5209,11 @@
       </c>
       <c r="I9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$T:$T)</f>
-        <v>80553500</v>
+        <v>86279500</v>
       </c>
       <c r="J9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$U:$U)</f>
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="K9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Y:$Y)</f>
@@ -5225,19 +5225,19 @@
       </c>
       <c r="M9" s="17">
         <f t="shared" si="2"/>
-        <v>80553500</v>
+        <v>86279500</v>
       </c>
       <c r="N9" s="17">
         <f t="shared" si="2"/>
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="O9" s="19">
         <f t="shared" si="0"/>
-        <v>0.26274249289278145</v>
+        <v>0.28141906826572072</v>
       </c>
       <c r="P9" s="19">
         <f t="shared" si="0"/>
-        <v>0.3972222222222222</v>
+        <v>0.59444444444444444</v>
       </c>
       <c r="Q9" s="19">
         <f t="shared" si="0"/>
@@ -5249,11 +5249,11 @@
       </c>
       <c r="S9" s="19">
         <f t="shared" si="0"/>
-        <v>0.24830446475215101</v>
+        <v>0.2659547389819587</v>
       </c>
       <c r="T9" s="19">
         <f t="shared" si="0"/>
-        <v>0.32134831460674157</v>
+        <v>0.48089887640449436</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="14.5">
@@ -5285,15 +5285,15 @@
       </c>
       <c r="I10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$T:$T)</f>
-        <v>28362000</v>
+        <v>35705600</v>
       </c>
       <c r="J10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$U:$U)</f>
-        <v>123</v>
+        <v>218</v>
       </c>
       <c r="K10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Y:$Y)</f>
-        <v>5200000</v>
+        <v>5300000</v>
       </c>
       <c r="L10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Z:$Z)</f>
@@ -5301,23 +5301,23 @@
       </c>
       <c r="M10" s="17">
         <f t="shared" si="2"/>
-        <v>33562000</v>
+        <v>41005600</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>219</v>
       </c>
       <c r="O10" s="19">
         <f t="shared" si="0"/>
-        <v>0.22856144502527589</v>
+        <v>0.28774146856690258</v>
       </c>
       <c r="P10" s="19">
         <f t="shared" si="0"/>
-        <v>0.50617283950617287</v>
+        <v>0.89711934156378603</v>
       </c>
       <c r="Q10" s="19">
         <f t="shared" si="0"/>
-        <v>0.15996353652622458</v>
+        <v>0.16303975838249815</v>
       </c>
       <c r="R10" s="19">
         <f t="shared" si="0"/>
@@ -5325,11 +5325,11 @@
       </c>
       <c r="S10" s="19">
         <f t="shared" si="0"/>
-        <v>0.21432141343282465</v>
+        <v>0.26185501908888131</v>
       </c>
       <c r="T10" s="19">
         <f t="shared" si="0"/>
-        <v>0.29039812646370022</v>
+        <v>0.51288056206088994</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="14.5">
@@ -5361,15 +5361,15 @@
       </c>
       <c r="I11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$T:$T)</f>
-        <v>37780100</v>
+        <v>42235100</v>
       </c>
       <c r="J11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$U:$U)</f>
-        <v>153</v>
+        <v>213</v>
       </c>
       <c r="K11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Y:$Y)</f>
-        <v>6920000</v>
+        <v>12420000</v>
       </c>
       <c r="L11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Z:$Z)</f>
@@ -5377,23 +5377,23 @@
       </c>
       <c r="M11" s="17">
         <f t="shared" si="2"/>
-        <v>44700100</v>
+        <v>54655100</v>
       </c>
       <c r="N11" s="17">
         <f t="shared" si="2"/>
-        <v>156</v>
+        <v>216</v>
       </c>
       <c r="O11" s="19">
         <f t="shared" si="0"/>
-        <v>0.14564885996517635</v>
+        <v>0.16282366022099518</v>
       </c>
       <c r="P11" s="19">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.59663865546218486</v>
       </c>
       <c r="Q11" s="19">
         <f t="shared" si="0"/>
-        <v>0.18405460973328422</v>
+        <v>0.33034078798950722</v>
       </c>
       <c r="R11" s="19">
         <f t="shared" si="0"/>
@@ -5401,11 +5401,11 @@
       </c>
       <c r="S11" s="19">
         <f t="shared" si="0"/>
-        <v>0.15051086032758093</v>
+        <v>0.18403059774564193</v>
       </c>
       <c r="T11" s="19">
         <f t="shared" si="0"/>
-        <v>0.36279069767441863</v>
+        <v>0.50232558139534889</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="14.5">
@@ -5439,15 +5439,15 @@
       </c>
       <c r="I12" s="23">
         <f t="shared" si="3"/>
-        <v>243469800</v>
+        <v>270149800</v>
       </c>
       <c r="J12" s="23">
         <f t="shared" si="3"/>
-        <v>621</v>
+        <v>998</v>
       </c>
       <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>31420000</v>
+        <v>37020000</v>
       </c>
       <c r="L12" s="23">
         <f t="shared" si="3"/>
@@ -5455,23 +5455,23 @@
       </c>
       <c r="M12" s="23">
         <f t="shared" si="3"/>
-        <v>274889800</v>
+        <v>307169800</v>
       </c>
       <c r="N12" s="23">
         <f t="shared" si="3"/>
-        <v>626</v>
+        <v>1003</v>
       </c>
       <c r="O12" s="24">
         <f>AVERAGE(O6:O11)</f>
-        <v>0.26018282605748799</v>
+        <v>0.29098951022613073</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ref="P12:T12" si="4">AVERAGE(P6:P11)</f>
-        <v>0.38161154577712786</v>
+        <v>0.62647411479895665</v>
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="4"/>
-        <v>0.3111687957794857</v>
+        <v>0.33606252913156842</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="4"/>
@@ -5479,11 +5479,11 @@
       </c>
       <c r="S12" s="24">
         <f t="shared" si="4"/>
-        <v>0.27003123108597593</v>
+        <v>0.29991906352582037</v>
       </c>
       <c r="T12" s="24">
         <f t="shared" si="4"/>
-        <v>0.30259809563527346</v>
+        <v>0.49506268660082969</v>
       </c>
     </row>
     <row r="13" spans="1:20">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -561,7 +561,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T7">
-            <v>3018500</v>
+            <v>3252500</v>
           </cell>
           <cell r="U7">
             <v>31</v>
@@ -663,10 +663,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T13">
-            <v>168000</v>
+            <v>342000</v>
           </cell>
           <cell r="U13">
-            <v>22</v>
+            <v>25</v>
           </cell>
           <cell r="Y13" t="str">
             <v/>
@@ -850,7 +850,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T24">
-            <v>704000</v>
+            <v>938000</v>
           </cell>
           <cell r="U24">
             <v>9</v>
@@ -901,10 +901,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T27">
-            <v>726000</v>
+            <v>876000</v>
           </cell>
           <cell r="U27">
-            <v>13</v>
+            <v>18</v>
           </cell>
           <cell r="Y27" t="str">
             <v/>
@@ -1179,7 +1179,7 @@
             <v>0</v>
           </cell>
           <cell r="Y43">
-            <v>0</v>
+            <v>200000</v>
           </cell>
           <cell r="Z43">
             <v>0</v>
@@ -1207,13 +1207,13 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T45">
-            <v>1944000</v>
+            <v>2094000</v>
           </cell>
           <cell r="U45">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y45">
-            <v>7000000</v>
+            <v>9020000</v>
           </cell>
           <cell r="Z45">
             <v>0</v>
@@ -1275,7 +1275,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T49">
-            <v>2000000</v>
+            <v>2085000</v>
           </cell>
           <cell r="U49">
             <v>0</v>
@@ -1309,10 +1309,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T51">
-            <v>2828000</v>
+            <v>2978000</v>
           </cell>
           <cell r="U51">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y51" t="str">
             <v/>
@@ -1394,10 +1394,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T56">
-            <v>828000</v>
+            <v>1152000</v>
           </cell>
           <cell r="U56">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y56" t="str">
             <v/>
@@ -1411,7 +1411,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T57">
-            <v>502200</v>
+            <v>670200</v>
           </cell>
           <cell r="U57">
             <v>0</v>
@@ -1479,10 +1479,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T61">
-            <v>2512300</v>
+            <v>2860300</v>
           </cell>
           <cell r="U61">
-            <v>5</v>
+            <v>11</v>
           </cell>
           <cell r="Y61" t="str">
             <v/>
@@ -1530,7 +1530,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T64">
-            <v>313000</v>
+            <v>481000</v>
           </cell>
           <cell r="U64">
             <v>0</v>
@@ -1655,7 +1655,7 @@
             <v>5</v>
           </cell>
           <cell r="Y71">
-            <v>1200000</v>
+            <v>1350000</v>
           </cell>
           <cell r="Z71">
             <v>0</v>
@@ -1717,10 +1717,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T75">
-            <v>535000</v>
+            <v>595000</v>
           </cell>
           <cell r="U75">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y75" t="str">
             <v/>
@@ -1768,7 +1768,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T78">
-            <v>535200</v>
+            <v>619200</v>
           </cell>
           <cell r="U78">
             <v>10</v>
@@ -1870,10 +1870,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T84">
-            <v>426000</v>
+            <v>486000</v>
           </cell>
           <cell r="U84">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y84" t="str">
             <v/>
@@ -1989,10 +1989,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T91">
-            <v>342500</v>
+            <v>492500</v>
           </cell>
           <cell r="U91">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y91" t="str">
             <v/>
@@ -2159,10 +2159,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T101">
-            <v>466700</v>
+            <v>952700</v>
           </cell>
           <cell r="U101">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y101" t="str">
             <v/>
@@ -2176,10 +2176,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T102">
-            <v>235200</v>
+            <v>721200</v>
           </cell>
           <cell r="U102">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y102" t="str">
             <v/>
@@ -2193,10 +2193,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T103">
-            <v>596000</v>
+            <v>1246000</v>
           </cell>
           <cell r="U103">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y103" t="str">
             <v/>
@@ -2397,7 +2397,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T115">
-            <v>1084000</v>
+            <v>1184000</v>
           </cell>
           <cell r="U115">
             <v>5</v>
@@ -2465,7 +2465,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T119">
-            <v>664200</v>
+            <v>898200</v>
           </cell>
           <cell r="U119">
             <v>7</v>
@@ -2856,10 +2856,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T142">
-            <v>363400</v>
+            <v>513400</v>
           </cell>
           <cell r="U142">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y142" t="str">
             <v/>
@@ -2873,10 +2873,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T143">
-            <v>240500</v>
+            <v>420500</v>
           </cell>
           <cell r="U143">
-            <v>0</v>
+            <v>6</v>
           </cell>
           <cell r="Y143" t="str">
             <v/>
@@ -3094,10 +3094,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T156">
-            <v>255000</v>
+            <v>405000</v>
           </cell>
           <cell r="U156">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y156" t="str">
             <v/>
@@ -3128,7 +3128,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T158">
-            <v>308400</v>
+            <v>542400</v>
           </cell>
           <cell r="U158">
             <v>5</v>
@@ -3145,7 +3145,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T159">
-            <v>3356400</v>
+            <v>3528000</v>
           </cell>
           <cell r="U159">
             <v>5</v>
@@ -3162,7 +3162,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T160">
-            <v>401000</v>
+            <v>635000</v>
           </cell>
           <cell r="U160">
             <v>5</v>
@@ -3179,7 +3179,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T161">
-            <v>3314200</v>
+            <v>3514200</v>
           </cell>
           <cell r="U161">
             <v>5</v>
@@ -3230,7 +3230,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T164">
-            <v>664800</v>
+            <v>796800</v>
           </cell>
           <cell r="U164">
             <v>10</v>
@@ -3468,10 +3468,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T178">
-            <v>361700</v>
+            <v>511700</v>
           </cell>
           <cell r="U178">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y178" t="str">
             <v/>
@@ -3485,10 +3485,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T179">
-            <v>558000</v>
+            <v>1076000</v>
           </cell>
           <cell r="U179">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y179" t="str">
             <v/>
@@ -3502,10 +3502,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T180">
-            <v>1650000</v>
+            <v>2500000</v>
           </cell>
           <cell r="U180">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y180" t="str">
             <v/>
@@ -3519,10 +3519,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T181">
-            <v>870000</v>
+            <v>1320000</v>
           </cell>
           <cell r="U181">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y181" t="str">
             <v/>
@@ -3536,10 +3536,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T182">
-            <v>458000</v>
+            <v>921000</v>
           </cell>
           <cell r="U182">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y182" t="str">
             <v/>
@@ -3553,10 +3553,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T183">
-            <v>626000</v>
+            <v>776000</v>
           </cell>
           <cell r="U183">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y183" t="str">
             <v/>
@@ -3689,10 +3689,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T191">
-            <v>518400</v>
+            <v>608400</v>
           </cell>
           <cell r="U191">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="Y191">
             <v>1000000</v>
@@ -3774,7 +3774,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T196">
-            <v>8505200</v>
+            <v>8589200</v>
           </cell>
           <cell r="U196">
             <v>10</v>
@@ -4182,10 +4182,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T220">
-            <v>792000</v>
+            <v>1116000</v>
           </cell>
           <cell r="U220">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y220" t="str">
             <v/>
@@ -4199,10 +4199,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T221">
-            <v>588000</v>
+            <v>648000</v>
           </cell>
           <cell r="U221">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y221" t="str">
             <v/>
@@ -4216,10 +4216,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T222">
-            <v>858000</v>
+            <v>918000</v>
           </cell>
           <cell r="U222">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y222" t="str">
             <v/>
@@ -4250,10 +4250,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T224">
-            <v>870000</v>
+            <v>1745000</v>
           </cell>
           <cell r="U224">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y224" t="str">
             <v/>
@@ -4267,10 +4267,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T225">
-            <v>4656000</v>
+            <v>5976000</v>
           </cell>
           <cell r="U225">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y225" t="str">
             <v/>
@@ -4284,10 +4284,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T226">
-            <v>1812000</v>
+            <v>2802000</v>
           </cell>
           <cell r="U226">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y226" t="str">
             <v/>
@@ -4981,11 +4981,11 @@
       </c>
       <c r="I6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$T:$T)</f>
-        <v>59629500</v>
+        <v>60559500</v>
       </c>
       <c r="J6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$U:$U)</f>
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="K6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$Y:$Y)</f>
@@ -4997,19 +4997,19 @@
       </c>
       <c r="M6" s="17">
         <f>K6+I6</f>
-        <v>64629500</v>
+        <v>65559500</v>
       </c>
       <c r="N6" s="17">
         <f>L6+J6</f>
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="O6" s="19">
         <f t="shared" ref="O6:T11" si="0">I6/C6</f>
-        <v>0.40744324349604988</v>
+        <v>0.41379785348693238</v>
       </c>
       <c r="P6" s="19">
         <f t="shared" si="0"/>
-        <v>0.83568075117370888</v>
+        <v>0.91549295774647887</v>
       </c>
       <c r="Q6" s="19">
         <f t="shared" si="0"/>
@@ -5021,11 +5021,11 @@
       </c>
       <c r="S6" s="19">
         <f t="shared" si="0"/>
-        <v>0.39043375411277792</v>
+        <v>0.39605198404376735</v>
       </c>
       <c r="T6" s="19">
         <f t="shared" si="0"/>
-        <v>0.69803921568627447</v>
+        <v>0.76470588235294112</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="14.5">
@@ -5057,15 +5057,15 @@
       </c>
       <c r="I7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$T:$T)</f>
-        <v>28517300</v>
+        <v>29447300</v>
       </c>
       <c r="J7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$U:$U)</f>
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="K7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Y:$Y)</f>
-        <v>12800000</v>
+        <v>14820000</v>
       </c>
       <c r="L7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Z:$Z)</f>
@@ -5073,23 +5073,23 @@
       </c>
       <c r="M7" s="17">
         <f t="shared" ref="M7:N11" si="2">K7+I7</f>
-        <v>41317300</v>
+        <v>44267300</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" si="2"/>
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="O7" s="19">
         <f t="shared" si="0"/>
-        <v>0.41552910483030758</v>
+        <v>0.42908024983674881</v>
       </c>
       <c r="P7" s="19">
         <f t="shared" si="0"/>
-        <v>0.55940594059405946</v>
+        <v>0.71287128712871284</v>
       </c>
       <c r="Q7" s="19">
         <f t="shared" si="0"/>
-        <v>0.90382070020363681</v>
+        <v>1.0464549044545233</v>
       </c>
       <c r="R7" s="19">
         <f t="shared" si="0"/>
@@ -5097,11 +5097,11 @@
       </c>
       <c r="S7" s="19">
         <f t="shared" si="0"/>
-        <v>0.49905552522214131</v>
+        <v>0.53468742274219505</v>
       </c>
       <c r="T7" s="19">
         <f t="shared" si="0"/>
-        <v>0.50666666666666671</v>
+        <v>0.64444444444444449</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="14.5">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="K8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Y:$Y)</f>
-        <v>1500000</v>
+        <v>1650000</v>
       </c>
       <c r="L8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Z:$Z)</f>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="M8" s="17">
         <f t="shared" si="2"/>
-        <v>19282800</v>
+        <v>19432800</v>
       </c>
       <c r="N8" s="17">
         <f t="shared" si="2"/>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="Q8" s="19">
         <f t="shared" si="0"/>
-        <v>0.35851449522781542</v>
+        <v>0.39436594475059694</v>
       </c>
       <c r="R8" s="19">
         <f t="shared" si="0"/>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="S8" s="19">
         <f t="shared" si="0"/>
-        <v>0.19818474600352079</v>
+        <v>0.19972641588032955</v>
       </c>
       <c r="T8" s="19">
         <f t="shared" si="0"/>
@@ -5209,11 +5209,11 @@
       </c>
       <c r="I9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$T:$T)</f>
-        <v>86279500</v>
+        <v>92933500</v>
       </c>
       <c r="J9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$U:$U)</f>
-        <v>214</v>
+        <v>268</v>
       </c>
       <c r="K9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Y:$Y)</f>
@@ -5225,19 +5225,19 @@
       </c>
       <c r="M9" s="17">
         <f t="shared" si="2"/>
-        <v>86279500</v>
+        <v>92933500</v>
       </c>
       <c r="N9" s="17">
         <f t="shared" si="2"/>
-        <v>214</v>
+        <v>268</v>
       </c>
       <c r="O9" s="19">
         <f t="shared" si="0"/>
-        <v>0.28141906826572072</v>
+        <v>0.30312251439417659</v>
       </c>
       <c r="P9" s="19">
         <f t="shared" si="0"/>
-        <v>0.59444444444444444</v>
+        <v>0.74444444444444446</v>
       </c>
       <c r="Q9" s="19">
         <f t="shared" si="0"/>
@@ -5249,11 +5249,11 @@
       </c>
       <c r="S9" s="19">
         <f t="shared" si="0"/>
-        <v>0.2659547389819587</v>
+        <v>0.28646555363881177</v>
       </c>
       <c r="T9" s="19">
         <f t="shared" si="0"/>
-        <v>0.48089887640449436</v>
+        <v>0.60224719101123592</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="14.5">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="I10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$T:$T)</f>
-        <v>35705600</v>
+        <v>37479200</v>
       </c>
       <c r="J10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$U:$U)</f>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="M10" s="17">
         <f t="shared" si="2"/>
-        <v>41005600</v>
+        <v>42779200</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="2"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="O10" s="19">
         <f t="shared" si="0"/>
-        <v>0.28774146856690258</v>
+        <v>0.30203441613395809</v>
       </c>
       <c r="P10" s="19">
         <f t="shared" si="0"/>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="S10" s="19">
         <f t="shared" si="0"/>
-        <v>0.26185501908888131</v>
+        <v>0.27318093705754998</v>
       </c>
       <c r="T10" s="19">
         <f t="shared" si="0"/>
@@ -5361,15 +5361,15 @@
       </c>
       <c r="I11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$T:$T)</f>
-        <v>42235100</v>
+        <v>44278100</v>
       </c>
       <c r="J11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$U:$U)</f>
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="K11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Y:$Y)</f>
-        <v>12420000</v>
+        <v>12620000</v>
       </c>
       <c r="L11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Z:$Z)</f>
@@ -5377,23 +5377,23 @@
       </c>
       <c r="M11" s="17">
         <f t="shared" si="2"/>
-        <v>54655100</v>
+        <v>56898100</v>
       </c>
       <c r="N11" s="17">
         <f t="shared" si="2"/>
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="O11" s="19">
         <f t="shared" si="0"/>
-        <v>0.16282366022099518</v>
+        <v>0.17069978074235045</v>
       </c>
       <c r="P11" s="19">
         <f t="shared" si="0"/>
-        <v>0.59663865546218486</v>
+        <v>0.6386554621848739</v>
       </c>
       <c r="Q11" s="19">
         <f t="shared" si="0"/>
-        <v>0.33034078798950722</v>
+        <v>0.33566028538064263</v>
       </c>
       <c r="R11" s="19">
         <f t="shared" si="0"/>
@@ -5401,11 +5401,11 @@
       </c>
       <c r="S11" s="19">
         <f t="shared" si="0"/>
-        <v>0.18403059774564193</v>
+        <v>0.19158306093285546</v>
       </c>
       <c r="T11" s="19">
         <f t="shared" si="0"/>
-        <v>0.50232558139534889</v>
+        <v>0.53720930232558139</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="14.5">
@@ -5439,15 +5439,15 @@
       </c>
       <c r="I12" s="23">
         <f t="shared" si="3"/>
-        <v>270149800</v>
+        <v>282480400</v>
       </c>
       <c r="J12" s="23">
         <f t="shared" si="3"/>
-        <v>998</v>
+        <v>1115</v>
       </c>
       <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>37020000</v>
+        <v>39390000</v>
       </c>
       <c r="L12" s="23">
         <f t="shared" si="3"/>
@@ -5455,23 +5455,23 @@
       </c>
       <c r="M12" s="23">
         <f t="shared" si="3"/>
-        <v>307169800</v>
+        <v>321870400</v>
       </c>
       <c r="N12" s="23">
         <f t="shared" si="3"/>
-        <v>1003</v>
+        <v>1120</v>
       </c>
       <c r="O12" s="24">
         <f>AVERAGE(O6:O11)</f>
-        <v>0.29098951022613073</v>
+        <v>0.30161922176182915</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ref="P12:T12" si="4">AVERAGE(P6:P11)</f>
-        <v>0.62647411479895665</v>
+        <v>0.69735650810397531</v>
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="4"/>
-        <v>0.33606252913156842</v>
+        <v>0.366696720992369</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="4"/>
@@ -5479,11 +5479,11 @@
       </c>
       <c r="S12" s="24">
         <f t="shared" si="4"/>
-        <v>0.29991906352582037</v>
+        <v>0.31361589571591825</v>
       </c>
       <c r="T12" s="24">
         <f t="shared" si="4"/>
-        <v>0.49506268660082969</v>
+        <v>0.55517543326439944</v>
       </c>
     </row>
     <row r="13" spans="1:20">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -578,7 +578,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T8">
-            <v>260900</v>
+            <v>428900</v>
           </cell>
           <cell r="U8">
             <v>22</v>
@@ -663,7 +663,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T13">
-            <v>342000</v>
+            <v>510000</v>
           </cell>
           <cell r="U13">
             <v>25</v>
@@ -799,10 +799,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T21">
-            <v>726000</v>
+            <v>786000</v>
           </cell>
           <cell r="U21">
-            <v>13</v>
+            <v>15</v>
           </cell>
           <cell r="Y21" t="str">
             <v/>
@@ -986,7 +986,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T32">
-            <v>414200</v>
+            <v>648200</v>
           </cell>
           <cell r="U32">
             <v>14</v>
@@ -1054,10 +1054,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T36">
-            <v>10225000</v>
+            <v>11315000</v>
           </cell>
           <cell r="U36">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="Y36" t="str">
             <v/>
@@ -1105,10 +1105,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T39">
-            <v>1486000</v>
+            <v>1576000</v>
           </cell>
           <cell r="U39">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="Y39" t="str">
             <v/>
@@ -1122,10 +1122,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T40">
-            <v>2053000</v>
+            <v>2377000</v>
           </cell>
           <cell r="U40">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="Y40">
             <v>0</v>
@@ -1179,7 +1179,7 @@
             <v>0</v>
           </cell>
           <cell r="Y43">
-            <v>200000</v>
+            <v>510000</v>
           </cell>
           <cell r="Z43">
             <v>0</v>
@@ -1377,7 +1377,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T55">
-            <v>0</v>
+            <v>168000</v>
           </cell>
           <cell r="U55">
             <v>0</v>
@@ -1428,7 +1428,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T58">
-            <v>445000</v>
+            <v>530000</v>
           </cell>
           <cell r="U58">
             <v>10</v>
@@ -1445,10 +1445,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T59">
-            <v>2549000</v>
+            <v>2777000</v>
           </cell>
           <cell r="U59">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="Y59" t="str">
             <v/>
@@ -1479,7 +1479,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T61">
-            <v>2860300</v>
+            <v>3028300</v>
           </cell>
           <cell r="U61">
             <v>11</v>
@@ -1496,7 +1496,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T62">
-            <v>6570000</v>
+            <v>6655000</v>
           </cell>
           <cell r="U62">
             <v>5</v>
@@ -1632,13 +1632,13 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T70">
-            <v>4752000</v>
+            <v>5752000</v>
           </cell>
           <cell r="U70">
             <v>10</v>
           </cell>
           <cell r="Y70">
-            <v>2820000</v>
+            <v>3520000</v>
           </cell>
           <cell r="Z70">
             <v>0</v>
@@ -1649,7 +1649,7 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T71">
-            <v>3052800</v>
+            <v>3202800</v>
           </cell>
           <cell r="U71">
             <v>5</v>
@@ -1666,7 +1666,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T72">
-            <v>1149000</v>
+            <v>1275500</v>
           </cell>
           <cell r="U72">
             <v>7</v>
@@ -1683,7 +1683,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T73">
-            <v>1803600</v>
+            <v>2037600</v>
           </cell>
           <cell r="U73">
             <v>5</v>
@@ -1700,7 +1700,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T74">
-            <v>354600</v>
+            <v>1354600</v>
           </cell>
           <cell r="U74">
             <v>5</v>
@@ -1819,10 +1819,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T81">
-            <v>618000</v>
+            <v>810000</v>
           </cell>
           <cell r="U81">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="Y81" t="str">
             <v/>
@@ -1853,10 +1853,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T83">
-            <v>1618000</v>
+            <v>2008000</v>
           </cell>
           <cell r="U83">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="Y83" t="str">
             <v/>
@@ -1955,7 +1955,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T89">
-            <v>2938400</v>
+            <v>3172400</v>
           </cell>
           <cell r="U89">
             <v>5</v>
@@ -1989,7 +1989,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T91">
-            <v>492500</v>
+            <v>660500</v>
           </cell>
           <cell r="U91">
             <v>5</v>
@@ -2006,10 +2006,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T92">
-            <v>7295000</v>
+            <v>8225000</v>
           </cell>
           <cell r="U92">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="Y92" t="str">
             <v/>
@@ -2023,10 +2023,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T93">
-            <v>629500</v>
+            <v>719500</v>
           </cell>
           <cell r="U93">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="Y93" t="str">
             <v/>
@@ -2091,7 +2091,7 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T97">
-            <v>200000</v>
+            <v>350000</v>
           </cell>
           <cell r="U97">
             <v>0</v>
@@ -2295,7 +2295,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T109">
-            <v>1695000</v>
+            <v>2195000</v>
           </cell>
           <cell r="U109">
             <v>5</v>
@@ -2312,7 +2312,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T110">
-            <v>495000</v>
+            <v>663000</v>
           </cell>
           <cell r="U110">
             <v>5</v>
@@ -2329,10 +2329,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T111">
-            <v>1560000</v>
+            <v>1956000</v>
           </cell>
           <cell r="U111">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="Y111" t="str">
             <v/>
@@ -2346,10 +2346,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T112">
-            <v>758000</v>
+            <v>871000</v>
           </cell>
           <cell r="U112">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="Y112" t="str">
             <v/>
@@ -2975,7 +2975,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T149">
-            <v>369600</v>
+            <v>603600</v>
           </cell>
           <cell r="U149">
             <v>5</v>
@@ -2992,7 +2992,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T150">
-            <v>5158200</v>
+            <v>5358200</v>
           </cell>
           <cell r="U150">
             <v>5</v>
@@ -3009,7 +3009,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T151">
-            <v>3094000</v>
+            <v>4104000</v>
           </cell>
           <cell r="U151">
             <v>10</v>
@@ -3026,7 +3026,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T152">
-            <v>1940000</v>
+            <v>2950000</v>
           </cell>
           <cell r="U152">
             <v>15</v>
@@ -3077,7 +3077,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T155">
-            <v>6265300</v>
+            <v>6391800</v>
           </cell>
           <cell r="U155">
             <v>5</v>
@@ -3094,7 +3094,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T156">
-            <v>405000</v>
+            <v>531500</v>
           </cell>
           <cell r="U156">
             <v>5</v>
@@ -3111,10 +3111,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T157">
-            <v>0</v>
+            <v>162500</v>
           </cell>
           <cell r="U157">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="Y157" t="str">
             <v/>
@@ -3179,13 +3179,13 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T161">
-            <v>3514200</v>
+            <v>3614200</v>
           </cell>
           <cell r="U161">
             <v>5</v>
           </cell>
           <cell r="Y161">
-            <v>1600000</v>
+            <v>1700000</v>
           </cell>
           <cell r="Z161">
             <v>0</v>
@@ -3196,7 +3196,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T162">
-            <v>1367900</v>
+            <v>1601900</v>
           </cell>
           <cell r="U162">
             <v>5</v>
@@ -3213,7 +3213,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T163">
-            <v>753200</v>
+            <v>987200</v>
           </cell>
           <cell r="U163">
             <v>5</v>
@@ -3247,7 +3247,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T165">
-            <v>361200</v>
+            <v>595200</v>
           </cell>
           <cell r="U165">
             <v>5</v>
@@ -3264,7 +3264,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T166">
-            <v>308400</v>
+            <v>542400</v>
           </cell>
           <cell r="U166">
             <v>5</v>
@@ -3281,7 +3281,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T167">
-            <v>417400</v>
+            <v>651400</v>
           </cell>
           <cell r="U167">
             <v>5</v>
@@ -3349,10 +3349,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T171">
-            <v>186000</v>
+            <v>462500</v>
           </cell>
           <cell r="U171">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y171" t="str">
             <v/>
@@ -3366,10 +3366,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T172">
-            <v>218400</v>
+            <v>452400</v>
           </cell>
           <cell r="U172">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y172" t="str">
             <v/>
@@ -3417,7 +3417,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T175">
-            <v>385200</v>
+            <v>511700</v>
           </cell>
           <cell r="U175">
             <v>5</v>
@@ -3434,7 +3434,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T176">
-            <v>2708200</v>
+            <v>2834700</v>
           </cell>
           <cell r="U176">
             <v>5</v>
@@ -3451,7 +3451,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T177">
-            <v>51000</v>
+            <v>177500</v>
           </cell>
           <cell r="U177">
             <v>0</v>
@@ -3695,7 +3695,7 @@
             <v>3</v>
           </cell>
           <cell r="Y191">
-            <v>1000000</v>
+            <v>2000000</v>
           </cell>
           <cell r="Z191">
             <v>0</v>
@@ -3842,13 +3842,13 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T200">
-            <v>5260900</v>
+            <v>7428900</v>
           </cell>
           <cell r="U200">
             <v>0</v>
           </cell>
           <cell r="Y200">
-            <v>1000000</v>
+            <v>1500000</v>
           </cell>
           <cell r="Z200">
             <v>0</v>
@@ -3859,7 +3859,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T201">
-            <v>260900</v>
+            <v>428900</v>
           </cell>
           <cell r="U201">
             <v>0</v>
@@ -3876,7 +3876,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T202">
-            <v>218400</v>
+            <v>386400</v>
           </cell>
           <cell r="U202">
             <v>0</v>
@@ -3893,7 +3893,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T203">
-            <v>694500</v>
+            <v>862500</v>
           </cell>
           <cell r="U203">
             <v>0</v>
@@ -4046,10 +4046,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T212">
-            <v>2792000</v>
+            <v>3365000</v>
           </cell>
           <cell r="U212">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="Y212" t="str">
             <v/>
@@ -4233,10 +4233,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T223">
-            <v>888000</v>
+            <v>1182000</v>
           </cell>
           <cell r="U223">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="Y223" t="str">
             <v/>
@@ -4403,7 +4403,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T233">
-            <v>1563000</v>
+            <v>1648000</v>
           </cell>
           <cell r="U233">
             <v>5</v>
@@ -4420,7 +4420,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T234">
-            <v>486000</v>
+            <v>822000</v>
           </cell>
           <cell r="U234">
             <v>5</v>
@@ -4437,7 +4437,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T235">
-            <v>1486000</v>
+            <v>1571000</v>
           </cell>
           <cell r="U235">
             <v>5</v>
@@ -4488,7 +4488,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T238">
-            <v>1552000</v>
+            <v>2052000</v>
           </cell>
           <cell r="U238">
             <v>10</v>
@@ -4505,7 +4505,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T239">
-            <v>468000</v>
+            <v>636000</v>
           </cell>
           <cell r="U239">
             <v>10</v>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="I6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$T:$T)</f>
-        <v>60559500</v>
+        <v>64071500</v>
       </c>
       <c r="J6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$U:$U)</f>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="K6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$Y:$Y)</f>
-        <v>5000000</v>
+        <v>6500000</v>
       </c>
       <c r="L6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$Z:$Z)</f>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="M6" s="17">
         <f>K6+I6</f>
-        <v>65559500</v>
+        <v>70571500</v>
       </c>
       <c r="N6" s="17">
         <f>L6+J6</f>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="O6" s="19">
         <f t="shared" ref="O6:T11" si="0">I6/C6</f>
-        <v>0.41379785348693238</v>
+        <v>0.43779504734497454</v>
       </c>
       <c r="P6" s="19">
         <f t="shared" si="0"/>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="Q6" s="19">
         <f t="shared" si="0"/>
-        <v>0.26065943298595295</v>
+        <v>0.33885726288173884</v>
       </c>
       <c r="R6" s="19">
         <f t="shared" si="0"/>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="S6" s="19">
         <f t="shared" si="0"/>
-        <v>0.39605198404376735</v>
+        <v>0.42633001459658371</v>
       </c>
       <c r="T6" s="19">
         <f t="shared" si="0"/>
@@ -5057,11 +5057,11 @@
       </c>
       <c r="I7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$T:$T)</f>
-        <v>29447300</v>
+        <v>32899300</v>
       </c>
       <c r="J7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$U:$U)</f>
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="K7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Y:$Y)</f>
@@ -5073,19 +5073,19 @@
       </c>
       <c r="M7" s="17">
         <f t="shared" ref="M7:N11" si="2">K7+I7</f>
-        <v>44267300</v>
+        <v>47719300</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" si="2"/>
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="O7" s="19">
         <f t="shared" si="0"/>
-        <v>0.42908024983674881</v>
+        <v>0.47937976872087251</v>
       </c>
       <c r="P7" s="19">
         <f t="shared" si="0"/>
-        <v>0.71287128712871284</v>
+        <v>0.78217821782178221</v>
       </c>
       <c r="Q7" s="19">
         <f t="shared" si="0"/>
@@ -5097,11 +5097,11 @@
       </c>
       <c r="S7" s="19">
         <f t="shared" si="0"/>
-        <v>0.53468742274219505</v>
+        <v>0.57638278214532235</v>
       </c>
       <c r="T7" s="19">
         <f t="shared" si="0"/>
-        <v>0.64444444444444449</v>
+        <v>0.70666666666666667</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="14.5">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="I8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$T:$T)</f>
-        <v>17782800</v>
+        <v>18082800</v>
       </c>
       <c r="J8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$U:$U)</f>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="M8" s="17">
         <f t="shared" si="2"/>
-        <v>19432800</v>
+        <v>19732800</v>
       </c>
       <c r="N8" s="17">
         <f t="shared" si="2"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="O8" s="19">
         <f t="shared" si="0"/>
-        <v>0.19098051597680851</v>
+        <v>0.1942024020011153</v>
       </c>
       <c r="P8" s="19">
         <f t="shared" si="0"/>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="S8" s="19">
         <f t="shared" si="0"/>
-        <v>0.19972641588032955</v>
+        <v>0.2028097556339471</v>
       </c>
       <c r="T8" s="19">
         <f t="shared" si="0"/>
@@ -5209,11 +5209,11 @@
       </c>
       <c r="I9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$T:$T)</f>
-        <v>92933500</v>
+        <v>97703500</v>
       </c>
       <c r="J9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$U:$U)</f>
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="K9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Y:$Y)</f>
@@ -5225,19 +5225,19 @@
       </c>
       <c r="M9" s="17">
         <f t="shared" si="2"/>
-        <v>92933500</v>
+        <v>97703500</v>
       </c>
       <c r="N9" s="17">
         <f t="shared" si="2"/>
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="O9" s="19">
         <f t="shared" si="0"/>
-        <v>0.30312251439417659</v>
+        <v>0.31868089101466568</v>
       </c>
       <c r="P9" s="19">
         <f t="shared" si="0"/>
-        <v>0.74444444444444446</v>
+        <v>0.8305555555555556</v>
       </c>
       <c r="Q9" s="19">
         <f t="shared" si="0"/>
@@ -5249,11 +5249,11 @@
       </c>
       <c r="S9" s="19">
         <f t="shared" si="0"/>
-        <v>0.28646555363881177</v>
+        <v>0.30116897803213749</v>
       </c>
       <c r="T9" s="19">
         <f t="shared" si="0"/>
-        <v>0.60224719101123592</v>
+        <v>0.67191011235955056</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="14.5">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="I10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$T:$T)</f>
-        <v>37479200</v>
+        <v>40885200</v>
       </c>
       <c r="J10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$U:$U)</f>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="K10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Y:$Y)</f>
-        <v>5300000</v>
+        <v>5400000</v>
       </c>
       <c r="L10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Z:$Z)</f>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="M10" s="17">
         <f t="shared" si="2"/>
-        <v>42779200</v>
+        <v>46285200</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="2"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="O10" s="19">
         <f t="shared" si="0"/>
-        <v>0.30203441613395809</v>
+        <v>0.32948241986275334</v>
       </c>
       <c r="P10" s="19">
         <f t="shared" si="0"/>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="Q10" s="19">
         <f t="shared" si="0"/>
-        <v>0.16303975838249815</v>
+        <v>0.16611598023877169</v>
       </c>
       <c r="R10" s="19">
         <f t="shared" si="0"/>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="S10" s="19">
         <f t="shared" si="0"/>
-        <v>0.27318093705754998</v>
+        <v>0.29556967656936345</v>
       </c>
       <c r="T10" s="19">
         <f t="shared" si="0"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="I11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$T:$T)</f>
-        <v>44278100</v>
+        <v>47290100</v>
       </c>
       <c r="J11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$U:$U)</f>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="K11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Y:$Y)</f>
-        <v>12620000</v>
+        <v>13630000</v>
       </c>
       <c r="L11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Z:$Z)</f>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="M11" s="17">
         <f t="shared" si="2"/>
-        <v>56898100</v>
+        <v>60920100</v>
       </c>
       <c r="N11" s="17">
         <f t="shared" si="2"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="O11" s="19">
         <f t="shared" si="0"/>
-        <v>0.17069978074235045</v>
+        <v>0.18231156488837208</v>
       </c>
       <c r="P11" s="19">
         <f t="shared" si="0"/>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="Q11" s="19">
         <f t="shared" si="0"/>
-        <v>0.33566028538064263</v>
+        <v>0.36252374720587627</v>
       </c>
       <c r="R11" s="19">
         <f t="shared" si="0"/>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="S11" s="19">
         <f t="shared" si="0"/>
-        <v>0.19158306093285546</v>
+        <v>0.20512564093239755</v>
       </c>
       <c r="T11" s="19">
         <f t="shared" si="0"/>
@@ -5439,15 +5439,15 @@
       </c>
       <c r="I12" s="23">
         <f t="shared" si="3"/>
-        <v>282480400</v>
+        <v>300932400</v>
       </c>
       <c r="J12" s="23">
         <f t="shared" si="3"/>
-        <v>1115</v>
+        <v>1160</v>
       </c>
       <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>39390000</v>
+        <v>42000000</v>
       </c>
       <c r="L12" s="23">
         <f t="shared" si="3"/>
@@ -5455,23 +5455,23 @@
       </c>
       <c r="M12" s="23">
         <f t="shared" si="3"/>
-        <v>321870400</v>
+        <v>342932400</v>
       </c>
       <c r="N12" s="23">
         <f t="shared" si="3"/>
-        <v>1120</v>
+        <v>1165</v>
       </c>
       <c r="O12" s="24">
         <f>AVERAGE(O6:O11)</f>
-        <v>0.30161922176182915</v>
+        <v>0.32364201563879225</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ref="P12:T12" si="4">AVERAGE(P6:P11)</f>
-        <v>0.69735650810397531</v>
+        <v>0.72325951507133868</v>
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="4"/>
-        <v>0.366696720992369</v>
+        <v>0.38471963992191788</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="4"/>
@@ -5479,11 +5479,11 @@
       </c>
       <c r="S12" s="24">
         <f t="shared" si="4"/>
-        <v>0.31361589571591825</v>
+        <v>0.33456447465162525</v>
       </c>
       <c r="T12" s="24">
         <f t="shared" si="4"/>
-        <v>0.55517543326439944</v>
+        <v>0.57715629052615569</v>
       </c>
     </row>
     <row r="13" spans="1:20">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -531,6 +531,20 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="4">
+          <cell r="T4">
+            <v>315549600</v>
+          </cell>
+          <cell r="U4">
+            <v>1170</v>
+          </cell>
+          <cell r="Y4">
+            <v>42250000</v>
+          </cell>
+          <cell r="Z4">
+            <v>5</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="T5" t="str">
             <v>IM3</v>
@@ -646,7 +660,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T12">
-            <v>750000</v>
+            <v>2108000</v>
           </cell>
           <cell r="U12">
             <v>5</v>
@@ -748,7 +762,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T18">
-            <v>786000</v>
+            <v>954000</v>
           </cell>
           <cell r="U18">
             <v>15</v>
@@ -782,7 +796,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T20">
-            <v>309600</v>
+            <v>543600</v>
           </cell>
           <cell r="U20">
             <v>7</v>
@@ -1020,7 +1034,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T34">
-            <v>361200</v>
+            <v>595200</v>
           </cell>
           <cell r="U34">
             <v>5</v>
@@ -1037,7 +1051,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T35">
-            <v>1235100</v>
+            <v>1319100</v>
           </cell>
           <cell r="U35">
             <v>5</v>
@@ -1139,7 +1153,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T41">
-            <v>1860200</v>
+            <v>2094200</v>
           </cell>
           <cell r="U41">
             <v>6</v>
@@ -1224,7 +1238,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T46">
-            <v>611600</v>
+            <v>695600</v>
           </cell>
           <cell r="U46">
             <v>7</v>
@@ -1258,7 +1272,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T48">
-            <v>1290000</v>
+            <v>2048000</v>
           </cell>
           <cell r="U48">
             <v>5</v>
@@ -1275,7 +1289,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T49">
-            <v>2085000</v>
+            <v>2253000</v>
           </cell>
           <cell r="U49">
             <v>0</v>
@@ -1326,7 +1340,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T52">
-            <v>1522400</v>
+            <v>1756400</v>
           </cell>
           <cell r="U52">
             <v>5</v>
@@ -1360,7 +1374,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T54">
-            <v>778000</v>
+            <v>904500</v>
           </cell>
           <cell r="U54">
             <v>7</v>
@@ -1411,7 +1425,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T57">
-            <v>670200</v>
+            <v>755200</v>
           </cell>
           <cell r="U57">
             <v>0</v>
@@ -1479,7 +1493,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T61">
-            <v>3028300</v>
+            <v>3112300</v>
           </cell>
           <cell r="U61">
             <v>11</v>
@@ -1496,7 +1510,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T62">
-            <v>6655000</v>
+            <v>7655000</v>
           </cell>
           <cell r="U62">
             <v>5</v>
@@ -1513,7 +1527,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T63">
-            <v>1108900</v>
+            <v>1243300</v>
           </cell>
           <cell r="U63">
             <v>3</v>
@@ -1530,7 +1544,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T64">
-            <v>481000</v>
+            <v>649000</v>
           </cell>
           <cell r="U64">
             <v>0</v>
@@ -1564,7 +1578,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T66">
-            <v>2486000</v>
+            <v>2822000</v>
           </cell>
           <cell r="U66">
             <v>5</v>
@@ -1581,7 +1595,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T67">
-            <v>17850000</v>
+            <v>20034000</v>
           </cell>
           <cell r="U67">
             <v>5</v>
@@ -1598,7 +1612,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T68">
-            <v>2652000</v>
+            <v>2988000</v>
           </cell>
           <cell r="U68">
             <v>5</v>
@@ -1768,7 +1782,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T78">
-            <v>619200</v>
+            <v>753600</v>
           </cell>
           <cell r="U78">
             <v>10</v>
@@ -1836,10 +1850,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T82">
-            <v>918000</v>
+            <v>2004000</v>
           </cell>
           <cell r="U82">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="Y82" t="str">
             <v/>
@@ -2142,7 +2156,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T100">
-            <v>367500</v>
+            <v>452500</v>
           </cell>
           <cell r="U100">
             <v>5</v>
@@ -2176,7 +2190,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T102">
-            <v>721200</v>
+            <v>889200</v>
           </cell>
           <cell r="U102">
             <v>5</v>
@@ -2193,7 +2207,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T103">
-            <v>1246000</v>
+            <v>1331000</v>
           </cell>
           <cell r="U103">
             <v>5</v>
@@ -2244,7 +2258,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T106">
-            <v>226000</v>
+            <v>562000</v>
           </cell>
           <cell r="U106">
             <v>0</v>
@@ -2397,7 +2411,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T115">
-            <v>1184000</v>
+            <v>1418000</v>
           </cell>
           <cell r="U115">
             <v>5</v>
@@ -2414,7 +2428,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T116">
-            <v>575200</v>
+            <v>809200</v>
           </cell>
           <cell r="U116">
             <v>5</v>
@@ -2584,7 +2598,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T126">
-            <v>1320000</v>
+            <v>1488000</v>
           </cell>
           <cell r="U126">
             <v>5</v>
@@ -2618,7 +2632,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T128">
-            <v>650000</v>
+            <v>848000</v>
           </cell>
           <cell r="U128">
             <v>5</v>
@@ -2635,7 +2649,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T129">
-            <v>852000</v>
+            <v>1188000</v>
           </cell>
           <cell r="U129">
             <v>5</v>
@@ -2686,7 +2700,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T132">
-            <v>2840000</v>
+            <v>3340000</v>
           </cell>
           <cell r="U132">
             <v>5</v>
@@ -2856,7 +2870,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T142">
-            <v>513400</v>
+            <v>597400</v>
           </cell>
           <cell r="U142">
             <v>5</v>
@@ -2941,7 +2955,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T147">
-            <v>1215600</v>
+            <v>1449600</v>
           </cell>
           <cell r="U147">
             <v>5</v>
@@ -2958,7 +2972,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T148">
-            <v>463400</v>
+            <v>697400</v>
           </cell>
           <cell r="U148">
             <v>5</v>
@@ -3009,7 +3023,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T151">
-            <v>4104000</v>
+            <v>4247300</v>
           </cell>
           <cell r="U151">
             <v>10</v>
@@ -3026,7 +3040,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T152">
-            <v>2950000</v>
+            <v>3076500</v>
           </cell>
           <cell r="U152">
             <v>15</v>
@@ -3077,7 +3091,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T155">
-            <v>6391800</v>
+            <v>6518300</v>
           </cell>
           <cell r="U155">
             <v>5</v>
@@ -3111,7 +3125,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T157">
-            <v>162500</v>
+            <v>246500</v>
           </cell>
           <cell r="U157">
             <v>4</v>
@@ -3179,13 +3193,13 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T161">
-            <v>3614200</v>
+            <v>3714200</v>
           </cell>
           <cell r="U161">
             <v>5</v>
           </cell>
           <cell r="Y161">
-            <v>1700000</v>
+            <v>1950000</v>
           </cell>
           <cell r="Z161">
             <v>0</v>
@@ -3400,7 +3414,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T174">
-            <v>602000</v>
+            <v>653000</v>
           </cell>
           <cell r="U174">
             <v>5</v>
@@ -3757,7 +3771,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T195">
-            <v>16317200</v>
+            <v>16451600</v>
           </cell>
           <cell r="U195">
             <v>13</v>
@@ -3774,7 +3788,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T196">
-            <v>8589200</v>
+            <v>8656400</v>
           </cell>
           <cell r="U196">
             <v>10</v>
@@ -3893,7 +3907,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T203">
-            <v>862500</v>
+            <v>1446500</v>
           </cell>
           <cell r="U203">
             <v>0</v>
@@ -3995,10 +4009,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T209">
-            <v>763000</v>
+            <v>883000</v>
           </cell>
           <cell r="U209">
-            <v>5</v>
+            <v>9</v>
           </cell>
           <cell r="Y209" t="str">
             <v/>
@@ -4012,7 +4026,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T210">
-            <v>697000</v>
+            <v>865000</v>
           </cell>
           <cell r="U210">
             <v>5</v>
@@ -4063,10 +4077,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T213">
-            <v>618000</v>
+            <v>1104000</v>
           </cell>
           <cell r="U213">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="Y213" t="str">
             <v/>
@@ -4403,7 +4417,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T233">
-            <v>1648000</v>
+            <v>1948000</v>
           </cell>
           <cell r="U233">
             <v>5</v>
@@ -4981,7 +4995,7 @@
       </c>
       <c r="I6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$T:$T)</f>
-        <v>64071500</v>
+        <v>65293900</v>
       </c>
       <c r="J6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$U:$U)</f>
@@ -4997,7 +5011,7 @@
       </c>
       <c r="M6" s="17">
         <f>K6+I6</f>
-        <v>70571500</v>
+        <v>71793900</v>
       </c>
       <c r="N6" s="17">
         <f>L6+J6</f>
@@ -5005,7 +5019,7 @@
       </c>
       <c r="O6" s="19">
         <f t="shared" ref="O6:T11" si="0">I6/C6</f>
-        <v>0.43779504734497454</v>
+        <v>0.44614760138030224</v>
       </c>
       <c r="P6" s="19">
         <f t="shared" si="0"/>
@@ -5021,7 +5035,7 @@
       </c>
       <c r="S6" s="19">
         <f t="shared" si="0"/>
-        <v>0.42633001459658371</v>
+        <v>0.43371466434673589</v>
       </c>
       <c r="T6" s="19">
         <f t="shared" si="0"/>
@@ -5057,7 +5071,7 @@
       </c>
       <c r="I7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$T:$T)</f>
-        <v>32899300</v>
+        <v>33725100</v>
       </c>
       <c r="J7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$U:$U)</f>
@@ -5073,7 +5087,7 @@
       </c>
       <c r="M7" s="17">
         <f t="shared" ref="M7:N11" si="2">K7+I7</f>
-        <v>47719300</v>
+        <v>48545100</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" si="2"/>
@@ -5081,7 +5095,7 @@
       </c>
       <c r="O7" s="19">
         <f t="shared" si="0"/>
-        <v>0.47937976872087251</v>
+        <v>0.49141260264164582</v>
       </c>
       <c r="P7" s="19">
         <f t="shared" si="0"/>
@@ -5097,7 +5111,7 @@
       </c>
       <c r="S7" s="19">
         <f t="shared" si="0"/>
-        <v>0.57638278214532235</v>
+        <v>0.58635729772907164</v>
       </c>
       <c r="T7" s="19">
         <f t="shared" si="0"/>
@@ -5209,11 +5223,11 @@
       </c>
       <c r="I9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$T:$T)</f>
-        <v>97703500</v>
+        <v>105405500</v>
       </c>
       <c r="J9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$U:$U)</f>
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="K9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Y:$Y)</f>
@@ -5225,19 +5239,19 @@
       </c>
       <c r="M9" s="17">
         <f t="shared" si="2"/>
-        <v>97703500</v>
+        <v>105405500</v>
       </c>
       <c r="N9" s="17">
         <f t="shared" si="2"/>
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="O9" s="19">
         <f t="shared" si="0"/>
-        <v>0.31868089101466568</v>
+        <v>0.34380261359978243</v>
       </c>
       <c r="P9" s="19">
         <f t="shared" si="0"/>
-        <v>0.8305555555555556</v>
+        <v>0.85833333333333328</v>
       </c>
       <c r="Q9" s="19">
         <f t="shared" si="0"/>
@@ -5249,11 +5263,11 @@
       </c>
       <c r="S9" s="19">
         <f t="shared" si="0"/>
-        <v>0.30116897803213749</v>
+        <v>0.32491023058505036</v>
       </c>
       <c r="T9" s="19">
         <f t="shared" si="0"/>
-        <v>0.67191011235955056</v>
+        <v>0.69438202247191017</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="14.5">
@@ -5285,7 +5299,7 @@
       </c>
       <c r="I10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$T:$T)</f>
-        <v>40885200</v>
+        <v>42857200</v>
       </c>
       <c r="J10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$U:$U)</f>
@@ -5293,7 +5307,7 @@
       </c>
       <c r="K10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Y:$Y)</f>
-        <v>5400000</v>
+        <v>5650000</v>
       </c>
       <c r="L10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Z:$Z)</f>
@@ -5301,7 +5315,7 @@
       </c>
       <c r="M10" s="17">
         <f t="shared" si="2"/>
-        <v>46285200</v>
+        <v>48507200</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="2"/>
@@ -5309,7 +5323,7 @@
       </c>
       <c r="O10" s="19">
         <f t="shared" si="0"/>
-        <v>0.32948241986275334</v>
+        <v>0.34537421767637166</v>
       </c>
       <c r="P10" s="19">
         <f t="shared" si="0"/>
@@ -5317,7 +5331,7 @@
       </c>
       <c r="Q10" s="19">
         <f t="shared" si="0"/>
-        <v>0.16611598023877169</v>
+        <v>0.17380653487945558</v>
       </c>
       <c r="R10" s="19">
         <f t="shared" si="0"/>
@@ -5325,7 +5339,7 @@
       </c>
       <c r="S10" s="19">
         <f t="shared" si="0"/>
-        <v>0.29556967656936345</v>
+        <v>0.30975900320805411</v>
       </c>
       <c r="T10" s="19">
         <f t="shared" si="0"/>
@@ -5361,7 +5375,7 @@
       </c>
       <c r="I11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$T:$T)</f>
-        <v>47290100</v>
+        <v>50185100</v>
       </c>
       <c r="J11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$U:$U)</f>
@@ -5377,7 +5391,7 @@
       </c>
       <c r="M11" s="17">
         <f t="shared" si="2"/>
-        <v>60920100</v>
+        <v>63815100</v>
       </c>
       <c r="N11" s="17">
         <f t="shared" si="2"/>
@@ -5385,7 +5399,7 @@
       </c>
       <c r="O11" s="19">
         <f t="shared" si="0"/>
-        <v>0.18231156488837208</v>
+        <v>0.19347229367413987</v>
       </c>
       <c r="P11" s="19">
         <f t="shared" si="0"/>
@@ -5401,7 +5415,7 @@
       </c>
       <c r="S11" s="19">
         <f t="shared" si="0"/>
-        <v>0.20512564093239755</v>
+        <v>0.21487347014638916</v>
       </c>
       <c r="T11" s="19">
         <f t="shared" si="0"/>
@@ -5439,15 +5453,15 @@
       </c>
       <c r="I12" s="23">
         <f t="shared" si="3"/>
-        <v>300932400</v>
+        <v>315549600</v>
       </c>
       <c r="J12" s="23">
         <f t="shared" si="3"/>
-        <v>1160</v>
+        <v>1170</v>
       </c>
       <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>42000000</v>
+        <v>42250000</v>
       </c>
       <c r="L12" s="23">
         <f t="shared" si="3"/>
@@ -5455,23 +5469,23 @@
       </c>
       <c r="M12" s="23">
         <f t="shared" si="3"/>
-        <v>342932400</v>
+        <v>357799600</v>
       </c>
       <c r="N12" s="23">
         <f t="shared" si="3"/>
-        <v>1165</v>
+        <v>1175</v>
       </c>
       <c r="O12" s="24">
         <f>AVERAGE(O6:O11)</f>
-        <v>0.32364201563879225</v>
+        <v>0.33573528849555956</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ref="P12:T12" si="4">AVERAGE(P6:P11)</f>
-        <v>0.72325951507133868</v>
+        <v>0.72788914470096833</v>
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="4"/>
-        <v>0.38471963992191788</v>
+        <v>0.38600139902869851</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="4"/>
@@ -5479,11 +5493,11 @@
       </c>
       <c r="S12" s="24">
         <f t="shared" si="4"/>
-        <v>0.33456447465162525</v>
+        <v>0.3454040702748748</v>
       </c>
       <c r="T12" s="24">
         <f t="shared" si="4"/>
-        <v>0.57715629052615569</v>
+        <v>0.58090160887821551</v>
       </c>
     </row>
     <row r="13" spans="1:20">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -533,13 +533,13 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="T4">
-            <v>315549600</v>
+            <v>317849600</v>
           </cell>
           <cell r="U4">
             <v>1170</v>
           </cell>
           <cell r="Y4">
-            <v>42250000</v>
+            <v>43600000</v>
           </cell>
           <cell r="Z4">
             <v>5</v>
@@ -1102,7 +1102,7 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T38">
-            <v>10407400</v>
+            <v>12407400</v>
           </cell>
           <cell r="U38">
             <v>5</v>
@@ -1652,7 +1652,7 @@
             <v>10</v>
           </cell>
           <cell r="Y70">
-            <v>3520000</v>
+            <v>3720000</v>
           </cell>
           <cell r="Z70">
             <v>0</v>
@@ -1663,13 +1663,13 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T71">
-            <v>3202800</v>
+            <v>3352800</v>
           </cell>
           <cell r="U71">
             <v>5</v>
           </cell>
           <cell r="Y71">
-            <v>1350000</v>
+            <v>1500000</v>
           </cell>
           <cell r="Z71">
             <v>0</v>
@@ -3029,7 +3029,7 @@
             <v>10</v>
           </cell>
           <cell r="Y151">
-            <v>2000000</v>
+            <v>3000000</v>
           </cell>
           <cell r="Z151">
             <v>0</v>
@@ -3193,7 +3193,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T161">
-            <v>3714200</v>
+            <v>3864200</v>
           </cell>
           <cell r="U161">
             <v>5</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="K7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Y:$Y)</f>
-        <v>14820000</v>
+        <v>15820000</v>
       </c>
       <c r="L7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Z:$Z)</f>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="M7" s="17">
         <f t="shared" ref="M7:N11" si="2">K7+I7</f>
-        <v>48545100</v>
+        <v>49545100</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" si="2"/>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Q7" s="19">
         <f t="shared" si="0"/>
-        <v>1.0464549044545233</v>
+        <v>1.1170658966579323</v>
       </c>
       <c r="R7" s="19">
         <f t="shared" si="0"/>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="S7" s="19">
         <f t="shared" si="0"/>
-        <v>0.58635729772907164</v>
+        <v>0.5984359070579035</v>
       </c>
       <c r="T7" s="19">
         <f t="shared" si="0"/>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="I8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$T:$T)</f>
-        <v>18082800</v>
+        <v>20232800</v>
       </c>
       <c r="J8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$U:$U)</f>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="K8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Y:$Y)</f>
-        <v>1650000</v>
+        <v>1800000</v>
       </c>
       <c r="L8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Z:$Z)</f>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="M8" s="17">
         <f t="shared" si="2"/>
-        <v>19732800</v>
+        <v>22032800</v>
       </c>
       <c r="N8" s="17">
         <f t="shared" si="2"/>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O8" s="19">
         <f t="shared" si="0"/>
-        <v>0.1942024020011153</v>
+        <v>0.21729258517531386</v>
       </c>
       <c r="P8" s="19">
         <f t="shared" si="0"/>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="Q8" s="19">
         <f t="shared" si="0"/>
-        <v>0.39436594475059694</v>
+        <v>0.43021739427337846</v>
       </c>
       <c r="R8" s="19">
         <f t="shared" si="0"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="S8" s="19">
         <f t="shared" si="0"/>
-        <v>0.2028097556339471</v>
+        <v>0.22644869374501486</v>
       </c>
       <c r="T8" s="19">
         <f t="shared" si="0"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="I10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$T:$T)</f>
-        <v>42857200</v>
+        <v>43007200</v>
       </c>
       <c r="J10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$U:$U)</f>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="M10" s="17">
         <f t="shared" si="2"/>
-        <v>48507200</v>
+        <v>48657200</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="2"/>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="O10" s="19">
         <f t="shared" si="0"/>
-        <v>0.34537421767637166</v>
+        <v>0.34658302582649481</v>
       </c>
       <c r="P10" s="19">
         <f t="shared" si="0"/>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="S10" s="19">
         <f t="shared" si="0"/>
-        <v>0.30975900320805411</v>
+        <v>0.31071687854369928</v>
       </c>
       <c r="T10" s="19">
         <f t="shared" si="0"/>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="K11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Y:$Y)</f>
-        <v>13630000</v>
+        <v>13830000</v>
       </c>
       <c r="L11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Z:$Z)</f>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="M11" s="17">
         <f t="shared" si="2"/>
-        <v>63815100</v>
+        <v>64015100</v>
       </c>
       <c r="N11" s="17">
         <f t="shared" si="2"/>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="Q11" s="19">
         <f t="shared" si="0"/>
-        <v>0.36252374720587627</v>
+        <v>0.36784324459701168</v>
       </c>
       <c r="R11" s="19">
         <f t="shared" si="0"/>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="S11" s="19">
         <f t="shared" si="0"/>
-        <v>0.21487347014638916</v>
+        <v>0.21554689530797752</v>
       </c>
       <c r="T11" s="19">
         <f t="shared" si="0"/>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="I12" s="23">
         <f t="shared" si="3"/>
-        <v>315549600</v>
+        <v>317849600</v>
       </c>
       <c r="J12" s="23">
         <f t="shared" si="3"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>42250000</v>
+        <v>43600000</v>
       </c>
       <c r="L12" s="23">
         <f t="shared" si="3"/>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="M12" s="23">
         <f t="shared" si="3"/>
-        <v>357799600</v>
+        <v>361449600</v>
       </c>
       <c r="N12" s="23">
         <f t="shared" si="3"/>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="O12" s="24">
         <f>AVERAGE(O6:O11)</f>
-        <v>0.33573528849555956</v>
+        <v>0.3397851203829465</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ref="P12:T12" si="4">AVERAGE(P6:P11)</f>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="4"/>
-        <v>0.38600139902869851</v>
+        <v>0.40463172221491944</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="4"/>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="S12" s="24">
         <f t="shared" si="4"/>
-        <v>0.3454040702748748</v>
+        <v>0.35162887826439687</v>
       </c>
       <c r="T12" s="24">
         <f t="shared" si="4"/>

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -533,16 +533,16 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="T4">
-            <v>317849600</v>
+            <v>341814900</v>
           </cell>
           <cell r="U4">
             <v>1170</v>
           </cell>
           <cell r="Y4">
-            <v>43600000</v>
+            <v>44700000</v>
           </cell>
           <cell r="Z4">
-            <v>5</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="5">
@@ -575,7 +575,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T7">
-            <v>3252500</v>
+            <v>3420500</v>
           </cell>
           <cell r="U7">
             <v>31</v>
@@ -779,7 +779,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T19">
-            <v>58000</v>
+            <v>394000</v>
           </cell>
           <cell r="U19">
             <v>10</v>
@@ -847,7 +847,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T23">
-            <v>58000</v>
+            <v>394000</v>
           </cell>
           <cell r="U23">
             <v>10</v>
@@ -864,7 +864,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T24">
-            <v>938000</v>
+            <v>1172000</v>
           </cell>
           <cell r="U24">
             <v>9</v>
@@ -915,7 +915,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T27">
-            <v>876000</v>
+            <v>963000</v>
           </cell>
           <cell r="U27">
             <v>18</v>
@@ -966,7 +966,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T30">
-            <v>597900</v>
+            <v>648300</v>
           </cell>
           <cell r="U30">
             <v>9</v>
@@ -1170,7 +1170,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T42">
-            <v>7500000</v>
+            <v>10500000</v>
           </cell>
           <cell r="U42">
             <v>0</v>
@@ -1187,7 +1187,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T43">
-            <v>126500</v>
+            <v>626500</v>
           </cell>
           <cell r="U43">
             <v>0</v>
@@ -1289,7 +1289,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T49">
-            <v>2253000</v>
+            <v>2421000</v>
           </cell>
           <cell r="U49">
             <v>0</v>
@@ -1323,7 +1323,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T51">
-            <v>2978000</v>
+            <v>3062000</v>
           </cell>
           <cell r="U51">
             <v>10</v>
@@ -1374,7 +1374,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T54">
-            <v>904500</v>
+            <v>1188500</v>
           </cell>
           <cell r="U54">
             <v>7</v>
@@ -1408,7 +1408,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T56">
-            <v>1152000</v>
+            <v>1320000</v>
           </cell>
           <cell r="U56">
             <v>5</v>
@@ -1425,7 +1425,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T57">
-            <v>755200</v>
+            <v>923200</v>
           </cell>
           <cell r="U57">
             <v>0</v>
@@ -1544,7 +1544,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T64">
-            <v>649000</v>
+            <v>817000</v>
           </cell>
           <cell r="U64">
             <v>0</v>
@@ -1663,7 +1663,7 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T71">
-            <v>3352800</v>
+            <v>3502800</v>
           </cell>
           <cell r="U71">
             <v>5</v>
@@ -1680,7 +1680,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T72">
-            <v>1275500</v>
+            <v>1359500</v>
           </cell>
           <cell r="U72">
             <v>7</v>
@@ -1731,7 +1731,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T75">
-            <v>595000</v>
+            <v>735400</v>
           </cell>
           <cell r="U75">
             <v>5</v>
@@ -1884,7 +1884,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T84">
-            <v>486000</v>
+            <v>720000</v>
           </cell>
           <cell r="U84">
             <v>5</v>
@@ -1941,7 +1941,7 @@
             <v/>
           </cell>
           <cell r="Y87">
-            <v>0</v>
+            <v>500000</v>
           </cell>
           <cell r="Z87">
             <v>1</v>
@@ -2190,7 +2190,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T102">
-            <v>889200</v>
+            <v>974200</v>
           </cell>
           <cell r="U102">
             <v>5</v>
@@ -2207,7 +2207,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T103">
-            <v>1331000</v>
+            <v>1499000</v>
           </cell>
           <cell r="U103">
             <v>5</v>
@@ -2258,7 +2258,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T106">
-            <v>562000</v>
+            <v>647000</v>
           </cell>
           <cell r="U106">
             <v>0</v>
@@ -2462,7 +2462,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T118">
-            <v>727600</v>
+            <v>1195600</v>
           </cell>
           <cell r="U118">
             <v>6</v>
@@ -2683,7 +2683,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T131">
-            <v>8618000</v>
+            <v>13618000</v>
           </cell>
           <cell r="U131">
             <v>5</v>
@@ -2947,7 +2947,7 @@
             <v>0</v>
           </cell>
           <cell r="Z146">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="147">
@@ -3040,7 +3040,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T152">
-            <v>3076500</v>
+            <v>3160500</v>
           </cell>
           <cell r="U152">
             <v>15</v>
@@ -3091,7 +3091,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T155">
-            <v>6518300</v>
+            <v>6602300</v>
           </cell>
           <cell r="U155">
             <v>5</v>
@@ -3142,7 +3142,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T158">
-            <v>542400</v>
+            <v>1010400</v>
           </cell>
           <cell r="U158">
             <v>5</v>
@@ -3159,13 +3159,13 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T159">
-            <v>3528000</v>
+            <v>3696000</v>
           </cell>
           <cell r="U159">
             <v>5</v>
           </cell>
           <cell r="Y159">
-            <v>500000</v>
+            <v>1000000</v>
           </cell>
           <cell r="Z159">
             <v>0</v>
@@ -3176,7 +3176,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T160">
-            <v>635000</v>
+            <v>1135000</v>
           </cell>
           <cell r="U160">
             <v>5</v>
@@ -3193,13 +3193,13 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T161">
-            <v>3864200</v>
+            <v>4214200</v>
           </cell>
           <cell r="U161">
             <v>5</v>
           </cell>
           <cell r="Y161">
-            <v>1950000</v>
+            <v>2050000</v>
           </cell>
           <cell r="Z161">
             <v>0</v>
@@ -3244,7 +3244,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T164">
-            <v>796800</v>
+            <v>1264800</v>
           </cell>
           <cell r="U164">
             <v>10</v>
@@ -3363,7 +3363,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T171">
-            <v>462500</v>
+            <v>546500</v>
           </cell>
           <cell r="U171">
             <v>5</v>
@@ -3380,7 +3380,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T172">
-            <v>452400</v>
+            <v>536400</v>
           </cell>
           <cell r="U172">
             <v>5</v>
@@ -3414,7 +3414,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T174">
-            <v>653000</v>
+            <v>737000</v>
           </cell>
           <cell r="U174">
             <v>5</v>
@@ -3499,7 +3499,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T179">
-            <v>1076000</v>
+            <v>1221000</v>
           </cell>
           <cell r="U179">
             <v>5</v>
@@ -3516,7 +3516,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T180">
-            <v>2500000</v>
+            <v>3075000</v>
           </cell>
           <cell r="U180">
             <v>5</v>
@@ -3533,7 +3533,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T181">
-            <v>1320000</v>
+            <v>1465000</v>
           </cell>
           <cell r="U181">
             <v>5</v>
@@ -3550,7 +3550,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T182">
-            <v>921000</v>
+            <v>1066000</v>
           </cell>
           <cell r="U182">
             <v>5</v>
@@ -3567,7 +3567,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T183">
-            <v>776000</v>
+            <v>921000</v>
           </cell>
           <cell r="U183">
             <v>5</v>
@@ -3635,7 +3635,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T187">
-            <v>4402000</v>
+            <v>5402000</v>
           </cell>
           <cell r="U187">
             <v>5</v>
@@ -3771,7 +3771,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T195">
-            <v>16451600</v>
+            <v>18535600</v>
           </cell>
           <cell r="U195">
             <v>13</v>
@@ -4196,7 +4196,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T220">
-            <v>1116000</v>
+            <v>1467000</v>
           </cell>
           <cell r="U220">
             <v>5</v>
@@ -4213,7 +4213,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T221">
-            <v>648000</v>
+            <v>720500</v>
           </cell>
           <cell r="U221">
             <v>5</v>
@@ -4230,7 +4230,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T222">
-            <v>918000</v>
+            <v>1086000</v>
           </cell>
           <cell r="U222">
             <v>5</v>
@@ -4264,7 +4264,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T224">
-            <v>1745000</v>
+            <v>2213000</v>
           </cell>
           <cell r="U224">
             <v>5</v>
@@ -4281,7 +4281,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T225">
-            <v>5976000</v>
+            <v>8521000</v>
           </cell>
           <cell r="U225">
             <v>5</v>
@@ -4298,7 +4298,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T226">
-            <v>2802000</v>
+            <v>3280000</v>
           </cell>
           <cell r="U226">
             <v>5</v>
@@ -4315,7 +4315,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T227">
-            <v>1862000</v>
+            <v>2966000</v>
           </cell>
           <cell r="U227">
             <v>0</v>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="I6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$T:$T)</f>
-        <v>65293900</v>
+        <v>71428300</v>
       </c>
       <c r="J6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$U:$U)</f>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="M6" s="17">
         <f>K6+I6</f>
-        <v>71793900</v>
+        <v>77928300</v>
       </c>
       <c r="N6" s="17">
         <f>L6+J6</f>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="O6" s="19">
         <f t="shared" ref="O6:T11" si="0">I6/C6</f>
-        <v>0.44614760138030224</v>
+        <v>0.48806342882983927</v>
       </c>
       <c r="P6" s="19">
         <f t="shared" si="0"/>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="S6" s="19">
         <f t="shared" si="0"/>
-        <v>0.43371466434673589</v>
+        <v>0.47077323390443671</v>
       </c>
       <c r="T6" s="19">
         <f t="shared" si="0"/>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="I7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$T:$T)</f>
-        <v>33725100</v>
+        <v>34597100</v>
       </c>
       <c r="J7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$U:$U)</f>
@@ -5083,19 +5083,19 @@
       </c>
       <c r="L7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Z:$Z)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" s="17">
         <f t="shared" ref="M7:N11" si="2">K7+I7</f>
-        <v>49545100</v>
+        <v>50417100</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" si="2"/>
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O7" s="19">
         <f t="shared" si="0"/>
-        <v>0.49141260264164582</v>
+        <v>0.50411862247564232</v>
       </c>
       <c r="P7" s="19">
         <f t="shared" si="0"/>
@@ -5107,15 +5107,15 @@
       </c>
       <c r="R7" s="19">
         <f t="shared" si="0"/>
-        <v>4.3478260869565216E-2</v>
+        <v>8.6956521739130432E-2</v>
       </c>
       <c r="S7" s="19">
         <f t="shared" si="0"/>
-        <v>0.5984359070579035</v>
+        <v>0.6089684543926448</v>
       </c>
       <c r="T7" s="19">
         <f t="shared" si="0"/>
-        <v>0.70666666666666667</v>
+        <v>0.71111111111111114</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="14.5">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="I8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$T:$T)</f>
-        <v>20232800</v>
+        <v>20382800</v>
       </c>
       <c r="J8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$U:$U)</f>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="M8" s="17">
         <f t="shared" si="2"/>
-        <v>22032800</v>
+        <v>22182800</v>
       </c>
       <c r="N8" s="17">
         <f t="shared" si="2"/>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O8" s="19">
         <f t="shared" si="0"/>
-        <v>0.21729258517531386</v>
+        <v>0.21890352818746725</v>
       </c>
       <c r="P8" s="19">
         <f t="shared" si="0"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="S8" s="19">
         <f t="shared" si="0"/>
-        <v>0.22644869374501486</v>
+        <v>0.22799036362182365</v>
       </c>
       <c r="T8" s="19">
         <f t="shared" si="0"/>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$T:$T)</f>
-        <v>105405500</v>
+        <v>112376400</v>
       </c>
       <c r="J9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$U:$U)</f>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="M9" s="17">
         <f t="shared" si="2"/>
-        <v>105405500</v>
+        <v>112376400</v>
       </c>
       <c r="N9" s="17">
         <f t="shared" si="2"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O9" s="19">
         <f t="shared" si="0"/>
-        <v>0.34380261359978243</v>
+        <v>0.36653969695067706</v>
       </c>
       <c r="P9" s="19">
         <f t="shared" si="0"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="S9" s="19">
         <f t="shared" si="0"/>
-        <v>0.32491023058505036</v>
+        <v>0.3463978828079925</v>
       </c>
       <c r="T9" s="19">
         <f t="shared" si="0"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="I10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$T:$T)</f>
-        <v>43007200</v>
+        <v>45831200</v>
       </c>
       <c r="J10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$U:$U)</f>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="K10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Y:$Y)</f>
-        <v>5650000</v>
+        <v>6250000</v>
       </c>
       <c r="L10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Z:$Z)</f>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="M10" s="17">
         <f t="shared" si="2"/>
-        <v>48657200</v>
+        <v>52081200</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="2"/>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="O10" s="19">
         <f t="shared" si="0"/>
-        <v>0.34658302582649481</v>
+        <v>0.36934085393281235</v>
       </c>
       <c r="P10" s="19">
         <f t="shared" si="0"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="Q10" s="19">
         <f t="shared" si="0"/>
-        <v>0.17380653487945558</v>
+        <v>0.19226386601709686</v>
       </c>
       <c r="R10" s="19">
         <f t="shared" si="0"/>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="S10" s="19">
         <f t="shared" si="0"/>
-        <v>0.31071687854369928</v>
+        <v>0.3325819795386934</v>
       </c>
       <c r="T10" s="19">
         <f t="shared" si="0"/>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="I11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$T:$T)</f>
-        <v>50185100</v>
+        <v>57199100</v>
       </c>
       <c r="J11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$U:$U)</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="K11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Y:$Y)</f>
-        <v>13830000</v>
+        <v>14330000</v>
       </c>
       <c r="L11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Z:$Z)</f>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="M11" s="17">
         <f t="shared" si="2"/>
-        <v>64015100</v>
+        <v>71529100</v>
       </c>
       <c r="N11" s="17">
         <f t="shared" si="2"/>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="O11" s="19">
         <f t="shared" si="0"/>
-        <v>0.19347229367413987</v>
+        <v>0.22051248424525394</v>
       </c>
       <c r="P11" s="19">
         <f t="shared" si="0"/>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="Q11" s="19">
         <f t="shared" si="0"/>
-        <v>0.36784324459701168</v>
+        <v>0.38114198807485011</v>
       </c>
       <c r="R11" s="19">
         <f t="shared" si="0"/>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="S11" s="19">
         <f t="shared" si="0"/>
-        <v>0.21554689530797752</v>
+        <v>0.2408474786288525</v>
       </c>
       <c r="T11" s="19">
         <f t="shared" si="0"/>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="I12" s="23">
         <f t="shared" si="3"/>
-        <v>317849600</v>
+        <v>341814900</v>
       </c>
       <c r="J12" s="23">
         <f t="shared" si="3"/>
@@ -5461,23 +5461,23 @@
       </c>
       <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>43600000</v>
+        <v>44700000</v>
       </c>
       <c r="L12" s="23">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M12" s="23">
         <f t="shared" si="3"/>
-        <v>361449600</v>
+        <v>386514900</v>
       </c>
       <c r="N12" s="23">
         <f t="shared" si="3"/>
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="O12" s="24">
         <f>AVERAGE(O6:O11)</f>
-        <v>0.3397851203829465</v>
+        <v>0.36124643577028204</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ref="P12:T12" si="4">AVERAGE(P6:P11)</f>
@@ -5485,19 +5485,19 @@
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="4"/>
-        <v>0.40463172221491944</v>
+        <v>0.40992440131749941</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="4"/>
-        <v>1.5001488981536628E-2</v>
+        <v>2.224786579313083E-2</v>
       </c>
       <c r="S12" s="24">
         <f t="shared" si="4"/>
-        <v>0.35162887826439687</v>
+        <v>0.37125989881574056</v>
       </c>
       <c r="T12" s="24">
         <f t="shared" si="4"/>
-        <v>0.58090160887821551</v>
+        <v>0.58164234961895633</v>
       </c>
     </row>
     <row r="13" spans="1:20">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -533,13 +533,13 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="T4">
-            <v>341814900</v>
+            <v>383748300</v>
           </cell>
           <cell r="U4">
-            <v>1170</v>
+            <v>1675</v>
           </cell>
           <cell r="Y4">
-            <v>44700000</v>
+            <v>45450000</v>
           </cell>
           <cell r="Z4">
             <v>6</v>
@@ -813,10 +813,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T21">
-            <v>786000</v>
+            <v>1104000</v>
           </cell>
           <cell r="U21">
-            <v>15</v>
+            <v>20</v>
           </cell>
           <cell r="Y21" t="str">
             <v/>
@@ -898,10 +898,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T26">
-            <v>0</v>
+            <v>631800</v>
           </cell>
           <cell r="U26">
-            <v>6</v>
+            <v>16</v>
           </cell>
           <cell r="Y26" t="str">
             <v/>
@@ -983,10 +983,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T31">
-            <v>469000</v>
+            <v>787000</v>
           </cell>
           <cell r="U31">
-            <v>13</v>
+            <v>18</v>
           </cell>
           <cell r="Y31" t="str">
             <v/>
@@ -1000,7 +1000,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T32">
-            <v>648200</v>
+            <v>1320200</v>
           </cell>
           <cell r="U32">
             <v>14</v>
@@ -1051,10 +1051,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T35">
-            <v>1319100</v>
+            <v>1619100</v>
           </cell>
           <cell r="U35">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y35" t="str">
             <v/>
@@ -1068,10 +1068,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T36">
-            <v>11315000</v>
+            <v>12915000</v>
           </cell>
           <cell r="U36">
-            <v>8</v>
+            <v>28</v>
           </cell>
           <cell r="Y36" t="str">
             <v/>
@@ -1119,10 +1119,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T39">
-            <v>1576000</v>
+            <v>1876000</v>
           </cell>
           <cell r="U39">
-            <v>8</v>
+            <v>18</v>
           </cell>
           <cell r="Y39" t="str">
             <v/>
@@ -1136,10 +1136,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T40">
-            <v>2377000</v>
+            <v>4777000</v>
           </cell>
           <cell r="U40">
-            <v>7</v>
+            <v>37</v>
           </cell>
           <cell r="Y40">
             <v>0</v>
@@ -1153,7 +1153,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T41">
-            <v>2094200</v>
+            <v>2594200</v>
           </cell>
           <cell r="U41">
             <v>6</v>
@@ -1221,7 +1221,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T45">
-            <v>2094000</v>
+            <v>3104000</v>
           </cell>
           <cell r="U45">
             <v>10</v>
@@ -1255,7 +1255,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T47">
-            <v>668000</v>
+            <v>1785600</v>
           </cell>
           <cell r="U47">
             <v>0</v>
@@ -1289,10 +1289,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T49">
-            <v>2421000</v>
+            <v>3021000</v>
           </cell>
           <cell r="U49">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="Y49">
             <v>0</v>
@@ -1323,7 +1323,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T51">
-            <v>3062000</v>
+            <v>3146000</v>
           </cell>
           <cell r="U51">
             <v>10</v>
@@ -1357,7 +1357,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T53">
-            <v>473400</v>
+            <v>977400</v>
           </cell>
           <cell r="U53">
             <v>5</v>
@@ -1425,10 +1425,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T57">
-            <v>923200</v>
+            <v>1523200</v>
           </cell>
           <cell r="U57">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="Y57">
             <v>0</v>
@@ -1442,10 +1442,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T58">
-            <v>530000</v>
+            <v>1064000</v>
           </cell>
           <cell r="U58">
-            <v>10</v>
+            <v>20</v>
           </cell>
           <cell r="Y58">
             <v>0</v>
@@ -1459,10 +1459,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T59">
-            <v>2777000</v>
+            <v>3461000</v>
           </cell>
           <cell r="U59">
-            <v>7</v>
+            <v>12</v>
           </cell>
           <cell r="Y59" t="str">
             <v/>
@@ -1493,7 +1493,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T61">
-            <v>3112300</v>
+            <v>3696300</v>
           </cell>
           <cell r="U61">
             <v>11</v>
@@ -1510,7 +1510,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T62">
-            <v>7655000</v>
+            <v>8823000</v>
           </cell>
           <cell r="U62">
             <v>5</v>
@@ -1646,7 +1646,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T70">
-            <v>5752000</v>
+            <v>6952000</v>
           </cell>
           <cell r="U70">
             <v>10</v>
@@ -1663,13 +1663,13 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T71">
-            <v>3502800</v>
+            <v>4488800</v>
           </cell>
           <cell r="U71">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y71">
-            <v>1500000</v>
+            <v>1650000</v>
           </cell>
           <cell r="Z71">
             <v>0</v>
@@ -1697,10 +1697,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T73">
-            <v>2037600</v>
+            <v>3009600</v>
           </cell>
           <cell r="U73">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y73">
             <v>2000000</v>
@@ -1714,7 +1714,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T74">
-            <v>1354600</v>
+            <v>1858600</v>
           </cell>
           <cell r="U74">
             <v>5</v>
@@ -1782,10 +1782,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T78">
-            <v>753600</v>
+            <v>1053600</v>
           </cell>
           <cell r="U78">
-            <v>10</v>
+            <v>20</v>
           </cell>
           <cell r="Y78" t="str">
             <v/>
@@ -1833,10 +1833,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T81">
-            <v>810000</v>
+            <v>960000</v>
           </cell>
           <cell r="U81">
-            <v>7</v>
+            <v>12</v>
           </cell>
           <cell r="Y81" t="str">
             <v/>
@@ -1867,10 +1867,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T83">
-            <v>2008000</v>
+            <v>2358000</v>
           </cell>
           <cell r="U83">
-            <v>8</v>
+            <v>13</v>
           </cell>
           <cell r="Y83" t="str">
             <v/>
@@ -1952,7 +1952,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T88">
-            <v>1871000</v>
+            <v>1955000</v>
           </cell>
           <cell r="U88">
             <v>10</v>
@@ -1969,7 +1969,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T89">
-            <v>3172400</v>
+            <v>3508400</v>
           </cell>
           <cell r="U89">
             <v>5</v>
@@ -2020,10 +2020,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T92">
-            <v>8225000</v>
+            <v>10665000</v>
           </cell>
           <cell r="U92">
-            <v>8</v>
+            <v>28</v>
           </cell>
           <cell r="Y92" t="str">
             <v/>
@@ -2037,10 +2037,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T93">
-            <v>719500</v>
+            <v>869500</v>
           </cell>
           <cell r="U93">
-            <v>8</v>
+            <v>13</v>
           </cell>
           <cell r="Y93" t="str">
             <v/>
@@ -2122,10 +2122,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T98">
-            <v>435000</v>
+            <v>1131000</v>
           </cell>
           <cell r="U98">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y98" t="str">
             <v/>
@@ -2156,10 +2156,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T100">
-            <v>452500</v>
+            <v>602500</v>
           </cell>
           <cell r="U100">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y100" t="str">
             <v/>
@@ -2173,10 +2173,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T101">
-            <v>952700</v>
+            <v>1252700</v>
           </cell>
           <cell r="U101">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y101" t="str">
             <v/>
@@ -2190,10 +2190,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T102">
-            <v>974200</v>
+            <v>1574200</v>
           </cell>
           <cell r="U102">
-            <v>5</v>
+            <v>25</v>
           </cell>
           <cell r="Y102" t="str">
             <v/>
@@ -2258,10 +2258,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T106">
-            <v>647000</v>
+            <v>1511000</v>
           </cell>
           <cell r="U106">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="Y106" t="str">
             <v/>
@@ -2309,10 +2309,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T109">
-            <v>2195000</v>
+            <v>2545000</v>
           </cell>
           <cell r="U109">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y109" t="str">
             <v/>
@@ -2326,10 +2326,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T110">
-            <v>663000</v>
+            <v>813000</v>
           </cell>
           <cell r="U110">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y110" t="str">
             <v/>
@@ -2343,10 +2343,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T111">
-            <v>1956000</v>
+            <v>2946000</v>
           </cell>
           <cell r="U111">
-            <v>7</v>
+            <v>12</v>
           </cell>
           <cell r="Y111" t="str">
             <v/>
@@ -2360,10 +2360,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T112">
-            <v>871000</v>
+            <v>1021000</v>
           </cell>
           <cell r="U112">
-            <v>7</v>
+            <v>12</v>
           </cell>
           <cell r="Y112" t="str">
             <v/>
@@ -2785,10 +2785,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T137">
-            <v>461400</v>
+            <v>1387400</v>
           </cell>
           <cell r="U137">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y137" t="str">
             <v/>
@@ -2802,10 +2802,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T138">
-            <v>405000</v>
+            <v>1041000</v>
           </cell>
           <cell r="U138">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y138" t="str">
             <v/>
@@ -2870,10 +2870,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T142">
-            <v>597400</v>
+            <v>747400</v>
           </cell>
           <cell r="U142">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y142" t="str">
             <v/>
@@ -2955,10 +2955,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T147">
-            <v>1449600</v>
+            <v>1749600</v>
           </cell>
           <cell r="U147">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y147">
             <v>0</v>
@@ -2989,10 +2989,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T149">
-            <v>603600</v>
+            <v>1167600</v>
           </cell>
           <cell r="U149">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y149" t="str">
             <v/>
@@ -3006,7 +3006,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T150">
-            <v>5358200</v>
+            <v>6366200</v>
           </cell>
           <cell r="U150">
             <v>5</v>
@@ -3023,10 +3023,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T151">
-            <v>4247300</v>
+            <v>4547300</v>
           </cell>
           <cell r="U151">
-            <v>10</v>
+            <v>20</v>
           </cell>
           <cell r="Y151">
             <v>3000000</v>
@@ -3040,10 +3040,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T152">
-            <v>3160500</v>
+            <v>3310500</v>
           </cell>
           <cell r="U152">
-            <v>15</v>
+            <v>20</v>
           </cell>
           <cell r="Y152" t="str">
             <v/>
@@ -3091,10 +3091,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T155">
-            <v>6602300</v>
+            <v>6752300</v>
           </cell>
           <cell r="U155">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y155">
             <v>0</v>
@@ -3108,7 +3108,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T156">
-            <v>531500</v>
+            <v>615500</v>
           </cell>
           <cell r="U156">
             <v>5</v>
@@ -3159,10 +3159,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T159">
-            <v>3696000</v>
+            <v>3906000</v>
           </cell>
           <cell r="U159">
-            <v>5</v>
+            <v>12</v>
           </cell>
           <cell r="Y159">
             <v>1000000</v>
@@ -3193,7 +3193,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T161">
-            <v>4214200</v>
+            <v>4414200</v>
           </cell>
           <cell r="U161">
             <v>5</v>
@@ -3210,7 +3210,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T162">
-            <v>1601900</v>
+            <v>2105900</v>
           </cell>
           <cell r="U162">
             <v>5</v>
@@ -3227,7 +3227,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T163">
-            <v>987200</v>
+            <v>1455200</v>
           </cell>
           <cell r="U163">
             <v>5</v>
@@ -3244,10 +3244,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T164">
-            <v>1264800</v>
+            <v>1654800</v>
           </cell>
           <cell r="U164">
-            <v>10</v>
+            <v>23</v>
           </cell>
           <cell r="Y164" t="str">
             <v/>
@@ -3261,7 +3261,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T165">
-            <v>595200</v>
+            <v>1099200</v>
           </cell>
           <cell r="U165">
             <v>5</v>
@@ -3278,7 +3278,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T166">
-            <v>542400</v>
+            <v>1382400</v>
           </cell>
           <cell r="U166">
             <v>5</v>
@@ -3295,7 +3295,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T167">
-            <v>651400</v>
+            <v>1827400</v>
           </cell>
           <cell r="U167">
             <v>5</v>
@@ -3431,10 +3431,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T175">
-            <v>511700</v>
+            <v>811700</v>
           </cell>
           <cell r="U175">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y175">
             <v>0</v>
@@ -3448,13 +3448,13 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T176">
-            <v>2834700</v>
+            <v>3434700</v>
           </cell>
           <cell r="U176">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y176">
-            <v>1000000</v>
+            <v>1300000</v>
           </cell>
           <cell r="Z176">
             <v>0</v>
@@ -3465,10 +3465,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T177">
-            <v>177500</v>
+            <v>477500</v>
           </cell>
           <cell r="U177">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="Y177" t="str">
             <v/>
@@ -3482,10 +3482,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T178">
-            <v>511700</v>
+            <v>811700</v>
           </cell>
           <cell r="U178">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y178" t="str">
             <v/>
@@ -3703,13 +3703,13 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T191">
-            <v>608400</v>
+            <v>872400</v>
           </cell>
           <cell r="U191">
             <v>3</v>
           </cell>
           <cell r="Y191">
-            <v>2000000</v>
+            <v>2300000</v>
           </cell>
           <cell r="Z191">
             <v>0</v>
@@ -3788,10 +3788,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T196">
-            <v>8656400</v>
+            <v>9256400</v>
           </cell>
           <cell r="U196">
-            <v>10</v>
+            <v>30</v>
           </cell>
           <cell r="Y196" t="str">
             <v/>
@@ -3856,10 +3856,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T200">
-            <v>7428900</v>
+            <v>8728900</v>
           </cell>
           <cell r="U200">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="Y200">
             <v>1500000</v>
@@ -3907,10 +3907,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T203">
-            <v>1446500</v>
+            <v>2478500</v>
           </cell>
           <cell r="U203">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="Y203" t="str">
             <v/>
@@ -4060,10 +4060,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T212">
-            <v>3365000</v>
+            <v>4349000</v>
           </cell>
           <cell r="U212">
-            <v>7</v>
+            <v>17</v>
           </cell>
           <cell r="Y212" t="str">
             <v/>
@@ -4145,10 +4145,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T217">
-            <v>558000</v>
+            <v>708000</v>
           </cell>
           <cell r="U217">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="Y217" t="str">
             <v/>
@@ -4162,7 +4162,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T218">
-            <v>573000</v>
+            <v>741000</v>
           </cell>
           <cell r="U218">
             <v>3</v>
@@ -4179,7 +4179,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T219">
-            <v>703000</v>
+            <v>1069000</v>
           </cell>
           <cell r="U219">
             <v>3</v>
@@ -4247,7 +4247,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T223">
-            <v>1182000</v>
+            <v>1446000</v>
           </cell>
           <cell r="U223">
             <v>7</v>
@@ -4417,10 +4417,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T233">
-            <v>1948000</v>
+            <v>2098000</v>
           </cell>
           <cell r="U233">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y233" t="str">
             <v/>
@@ -4434,10 +4434,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T234">
-            <v>822000</v>
+            <v>1122000</v>
           </cell>
           <cell r="U234">
-            <v>5</v>
+            <v>15</v>
           </cell>
           <cell r="Y234" t="str">
             <v/>
@@ -4451,10 +4451,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T235">
-            <v>1571000</v>
+            <v>1721000</v>
           </cell>
           <cell r="U235">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y235" t="str">
             <v/>
@@ -4502,7 +4502,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T238">
-            <v>2052000</v>
+            <v>2316000</v>
           </cell>
           <cell r="U238">
             <v>10</v>
@@ -4519,7 +4519,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T239">
-            <v>636000</v>
+            <v>870000</v>
           </cell>
           <cell r="U239">
             <v>10</v>
@@ -4995,15 +4995,15 @@
       </c>
       <c r="I6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$T:$T)</f>
-        <v>71428300</v>
+        <v>76925900</v>
       </c>
       <c r="J6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$U:$U)</f>
-        <v>195</v>
+        <v>265</v>
       </c>
       <c r="K6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$Y:$Y)</f>
-        <v>6500000</v>
+        <v>6800000</v>
       </c>
       <c r="L6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$Z:$Z)</f>
@@ -5011,23 +5011,23 @@
       </c>
       <c r="M6" s="17">
         <f>K6+I6</f>
-        <v>77928300</v>
+        <v>83725900</v>
       </c>
       <c r="N6" s="17">
         <f>L6+J6</f>
-        <v>195</v>
+        <v>265</v>
       </c>
       <c r="O6" s="19">
         <f t="shared" ref="O6:T11" si="0">I6/C6</f>
-        <v>0.48806342882983927</v>
+        <v>0.52562805666411394</v>
       </c>
       <c r="P6" s="19">
         <f t="shared" si="0"/>
-        <v>0.91549295774647887</v>
+        <v>1.244131455399061</v>
       </c>
       <c r="Q6" s="19">
         <f t="shared" si="0"/>
-        <v>0.33885726288173884</v>
+        <v>0.35449682886089606</v>
       </c>
       <c r="R6" s="19">
         <f t="shared" si="0"/>
@@ -5035,11 +5035,11 @@
       </c>
       <c r="S6" s="19">
         <f t="shared" si="0"/>
-        <v>0.47077323390443671</v>
+        <v>0.50579715847207596</v>
       </c>
       <c r="T6" s="19">
         <f t="shared" si="0"/>
-        <v>0.76470588235294112</v>
+        <v>1.0392156862745099</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="14.5">
@@ -5071,15 +5071,15 @@
       </c>
       <c r="I7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$T:$T)</f>
-        <v>34597100</v>
+        <v>38109100</v>
       </c>
       <c r="J7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$U:$U)</f>
-        <v>158</v>
+        <v>223</v>
       </c>
       <c r="K7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Y:$Y)</f>
-        <v>15820000</v>
+        <v>16120000</v>
       </c>
       <c r="L7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Z:$Z)</f>
@@ -5087,23 +5087,23 @@
       </c>
       <c r="M7" s="17">
         <f t="shared" ref="M7:N11" si="2">K7+I7</f>
-        <v>50417100</v>
+        <v>54229100</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" si="2"/>
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="O7" s="19">
         <f t="shared" si="0"/>
-        <v>0.50411862247564232</v>
+        <v>0.55529240877953645</v>
       </c>
       <c r="P7" s="19">
         <f t="shared" si="0"/>
-        <v>0.78217821782178221</v>
+        <v>1.1039603960396041</v>
       </c>
       <c r="Q7" s="19">
         <f t="shared" si="0"/>
-        <v>1.1170658966579323</v>
+        <v>1.138249194318955</v>
       </c>
       <c r="R7" s="19">
         <f t="shared" si="0"/>
@@ -5111,11 +5111,11 @@
       </c>
       <c r="S7" s="19">
         <f t="shared" si="0"/>
-        <v>0.6089684543926448</v>
+        <v>0.65501211315415153</v>
       </c>
       <c r="T7" s="19">
         <f t="shared" si="0"/>
-        <v>0.71111111111111114</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="14.5">
@@ -5147,15 +5147,15 @@
       </c>
       <c r="I8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$T:$T)</f>
-        <v>20382800</v>
+        <v>24258600</v>
       </c>
       <c r="J8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$U:$U)</f>
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="K8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Y:$Y)</f>
-        <v>1800000</v>
+        <v>1950000</v>
       </c>
       <c r="L8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Z:$Z)</f>
@@ -5163,23 +5163,23 @@
       </c>
       <c r="M8" s="17">
         <f t="shared" si="2"/>
-        <v>22182800</v>
+        <v>26208600</v>
       </c>
       <c r="N8" s="17">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="O8" s="19">
         <f t="shared" si="0"/>
-        <v>0.21890352818746725</v>
+        <v>0.26052814769749461</v>
       </c>
       <c r="P8" s="19">
         <f t="shared" si="0"/>
-        <v>0.27555555555555555</v>
+        <v>0.49777777777777776</v>
       </c>
       <c r="Q8" s="19">
         <f t="shared" si="0"/>
-        <v>0.43021739427337846</v>
+        <v>0.46606884379616004</v>
       </c>
       <c r="R8" s="19">
         <f t="shared" si="0"/>
@@ -5187,11 +5187,11 @@
       </c>
       <c r="S8" s="19">
         <f t="shared" si="0"/>
-        <v>0.22799036362182365</v>
+        <v>0.26936672755553526</v>
       </c>
       <c r="T8" s="19">
         <f t="shared" si="0"/>
-        <v>0.26956521739130435</v>
+        <v>0.48695652173913045</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="14.5">
@@ -5223,11 +5223,11 @@
       </c>
       <c r="I9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$T:$T)</f>
-        <v>112376400</v>
+        <v>124158400</v>
       </c>
       <c r="J9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$U:$U)</f>
-        <v>309</v>
+        <v>444</v>
       </c>
       <c r="K9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Y:$Y)</f>
@@ -5239,19 +5239,19 @@
       </c>
       <c r="M9" s="17">
         <f t="shared" si="2"/>
-        <v>112376400</v>
+        <v>124158400</v>
       </c>
       <c r="N9" s="17">
         <f t="shared" si="2"/>
-        <v>309</v>
+        <v>444</v>
       </c>
       <c r="O9" s="19">
         <f t="shared" si="0"/>
-        <v>0.36653969695067706</v>
+        <v>0.40496921337470271</v>
       </c>
       <c r="P9" s="19">
         <f t="shared" si="0"/>
-        <v>0.85833333333333328</v>
+        <v>1.2333333333333334</v>
       </c>
       <c r="Q9" s="19">
         <f t="shared" si="0"/>
@@ -5263,11 +5263,11 @@
       </c>
       <c r="S9" s="19">
         <f t="shared" si="0"/>
-        <v>0.3463978828079925</v>
+        <v>0.38271564930739776</v>
       </c>
       <c r="T9" s="19">
         <f t="shared" si="0"/>
-        <v>0.69438202247191017</v>
+        <v>0.99775280898876406</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="14.5">
@@ -5299,11 +5299,11 @@
       </c>
       <c r="I10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$T:$T)</f>
-        <v>45831200</v>
+        <v>55483200</v>
       </c>
       <c r="J10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$U:$U)</f>
-        <v>218</v>
+        <v>268</v>
       </c>
       <c r="K10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Y:$Y)</f>
@@ -5315,19 +5315,19 @@
       </c>
       <c r="M10" s="17">
         <f t="shared" si="2"/>
-        <v>52081200</v>
+        <v>61733200</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="2"/>
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="O10" s="19">
         <f t="shared" si="0"/>
-        <v>0.36934085393281235</v>
+        <v>0.44712362903273351</v>
       </c>
       <c r="P10" s="19">
         <f t="shared" si="0"/>
-        <v>0.89711934156378603</v>
+        <v>1.1028806584362141</v>
       </c>
       <c r="Q10" s="19">
         <f t="shared" si="0"/>
@@ -5339,11 +5339,11 @@
       </c>
       <c r="S10" s="19">
         <f t="shared" si="0"/>
-        <v>0.3325819795386934</v>
+        <v>0.39421806446967556</v>
       </c>
       <c r="T10" s="19">
         <f t="shared" si="0"/>
-        <v>0.51288056206088994</v>
+        <v>0.62997658079625296</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="14.5">
@@ -5375,11 +5375,11 @@
       </c>
       <c r="I11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$T:$T)</f>
-        <v>57199100</v>
+        <v>64813100</v>
       </c>
       <c r="J11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$U:$U)</f>
-        <v>228</v>
+        <v>363</v>
       </c>
       <c r="K11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Y:$Y)</f>
@@ -5391,19 +5391,19 @@
       </c>
       <c r="M11" s="17">
         <f t="shared" si="2"/>
-        <v>71529100</v>
+        <v>79143100</v>
       </c>
       <c r="N11" s="17">
         <f t="shared" si="2"/>
-        <v>231</v>
+        <v>366</v>
       </c>
       <c r="O11" s="19">
         <f t="shared" si="0"/>
-        <v>0.22051248424525394</v>
+        <v>0.2498657792279261</v>
       </c>
       <c r="P11" s="19">
         <f t="shared" si="0"/>
-        <v>0.6386554621848739</v>
+        <v>1.0168067226890756</v>
       </c>
       <c r="Q11" s="19">
         <f t="shared" si="0"/>
@@ -5415,11 +5415,11 @@
       </c>
       <c r="S11" s="19">
         <f t="shared" si="0"/>
-        <v>0.2408474786288525</v>
+        <v>0.26648477453052166</v>
       </c>
       <c r="T11" s="19">
         <f t="shared" si="0"/>
-        <v>0.53720930232558139</v>
+        <v>0.85116279069767442</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="14.5">
@@ -5453,15 +5453,15 @@
       </c>
       <c r="I12" s="23">
         <f t="shared" si="3"/>
-        <v>341814900</v>
+        <v>383748300</v>
       </c>
       <c r="J12" s="23">
         <f t="shared" si="3"/>
-        <v>1170</v>
+        <v>1675</v>
       </c>
       <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>44700000</v>
+        <v>45450000</v>
       </c>
       <c r="L12" s="23">
         <f t="shared" si="3"/>
@@ -5469,23 +5469,23 @@
       </c>
       <c r="M12" s="23">
         <f t="shared" si="3"/>
-        <v>386514900</v>
+        <v>429198300</v>
       </c>
       <c r="N12" s="23">
         <f t="shared" si="3"/>
-        <v>1176</v>
+        <v>1681</v>
       </c>
       <c r="O12" s="24">
         <f>AVERAGE(O6:O11)</f>
-        <v>0.36124643577028204</v>
+        <v>0.40723453912941787</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ref="P12:T12" si="4">AVERAGE(P6:P11)</f>
-        <v>0.72788914470096833</v>
+        <v>1.033148390612511</v>
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="4"/>
-        <v>0.40992440131749941</v>
+        <v>0.42203678684465967</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="4"/>
@@ -5493,11 +5493,11 @@
       </c>
       <c r="S12" s="24">
         <f t="shared" si="4"/>
-        <v>0.37125989881574056</v>
+        <v>0.41226574791489295</v>
       </c>
       <c r="T12" s="24">
         <f t="shared" si="4"/>
-        <v>0.58164234961895633</v>
+        <v>0.83417739808272184</v>
       </c>
     </row>
     <row r="13" spans="1:20">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -533,13 +533,13 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="T4">
-            <v>383748300</v>
+            <v>407812300</v>
           </cell>
           <cell r="U4">
             <v>1675</v>
           </cell>
           <cell r="Y4">
-            <v>45450000</v>
+            <v>46450000</v>
           </cell>
           <cell r="Z4">
             <v>6</v>
@@ -643,7 +643,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T11">
-            <v>983000</v>
+            <v>1115000</v>
           </cell>
           <cell r="U11">
             <v>5</v>
@@ -660,7 +660,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T12">
-            <v>2108000</v>
+            <v>2444000</v>
           </cell>
           <cell r="U12">
             <v>5</v>
@@ -711,7 +711,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T15">
-            <v>434800</v>
+            <v>602800</v>
           </cell>
           <cell r="U15">
             <v>23</v>
@@ -762,7 +762,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T18">
-            <v>954000</v>
+            <v>1122000</v>
           </cell>
           <cell r="U18">
             <v>15</v>
@@ -796,7 +796,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T20">
-            <v>543600</v>
+            <v>1047600</v>
           </cell>
           <cell r="U20">
             <v>7</v>
@@ -1034,7 +1034,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T34">
-            <v>595200</v>
+            <v>1267200</v>
           </cell>
           <cell r="U34">
             <v>5</v>
@@ -1085,7 +1085,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T37">
-            <v>414000</v>
+            <v>546000</v>
           </cell>
           <cell r="U37">
             <v>5</v>
@@ -1153,7 +1153,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T41">
-            <v>2594200</v>
+            <v>3602200</v>
           </cell>
           <cell r="U41">
             <v>6</v>
@@ -1221,7 +1221,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T45">
-            <v>3104000</v>
+            <v>3254000</v>
           </cell>
           <cell r="U45">
             <v>10</v>
@@ -1272,7 +1272,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T48">
-            <v>2048000</v>
+            <v>2384000</v>
           </cell>
           <cell r="U48">
             <v>5</v>
@@ -1340,7 +1340,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T52">
-            <v>1756400</v>
+            <v>2596400</v>
           </cell>
           <cell r="U52">
             <v>5</v>
@@ -1459,7 +1459,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T59">
-            <v>3461000</v>
+            <v>3961000</v>
           </cell>
           <cell r="U59">
             <v>12</v>
@@ -1578,7 +1578,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T66">
-            <v>2822000</v>
+            <v>3086000</v>
           </cell>
           <cell r="U66">
             <v>5</v>
@@ -1595,7 +1595,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T67">
-            <v>20034000</v>
+            <v>26534000</v>
           </cell>
           <cell r="U67">
             <v>5</v>
@@ -1612,7 +1612,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T68">
-            <v>2988000</v>
+            <v>3828000</v>
           </cell>
           <cell r="U68">
             <v>5</v>
@@ -1629,7 +1629,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T69">
-            <v>2945000</v>
+            <v>3077000</v>
           </cell>
           <cell r="U69">
             <v>10</v>
@@ -1646,7 +1646,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T70">
-            <v>6952000</v>
+            <v>7084000</v>
           </cell>
           <cell r="U70">
             <v>10</v>
@@ -1799,7 +1799,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T79">
-            <v>690800</v>
+            <v>756800</v>
           </cell>
           <cell r="U79">
             <v>0</v>
@@ -1816,7 +1816,7 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T80">
-            <v>150000</v>
+            <v>654000</v>
           </cell>
           <cell r="U80">
             <v>5</v>
@@ -1850,7 +1850,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T82">
-            <v>2004000</v>
+            <v>2774000</v>
           </cell>
           <cell r="U82">
             <v>8</v>
@@ -1918,7 +1918,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T86">
-            <v>168000</v>
+            <v>318000</v>
           </cell>
           <cell r="U86">
             <v>0</v>
@@ -2207,7 +2207,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T103">
-            <v>1499000</v>
+            <v>1631000</v>
           </cell>
           <cell r="U103">
             <v>5</v>
@@ -2411,7 +2411,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T115">
-            <v>1418000</v>
+            <v>2290000</v>
           </cell>
           <cell r="U115">
             <v>5</v>
@@ -2428,7 +2428,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T116">
-            <v>809200</v>
+            <v>1337200</v>
           </cell>
           <cell r="U116">
             <v>5</v>
@@ -2513,7 +2513,7 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T121">
-            <v>718400</v>
+            <v>918400</v>
           </cell>
           <cell r="U121">
             <v>5</v>
@@ -2598,7 +2598,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T126">
-            <v>1488000</v>
+            <v>2022000</v>
           </cell>
           <cell r="U126">
             <v>5</v>
@@ -2632,7 +2632,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T128">
-            <v>848000</v>
+            <v>1612000</v>
           </cell>
           <cell r="U128">
             <v>5</v>
@@ -2649,7 +2649,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T129">
-            <v>1188000</v>
+            <v>2582000</v>
           </cell>
           <cell r="U129">
             <v>5</v>
@@ -2666,7 +2666,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T130">
-            <v>618000</v>
+            <v>852000</v>
           </cell>
           <cell r="U130">
             <v>5</v>
@@ -2683,7 +2683,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T131">
-            <v>13618000</v>
+            <v>13786000</v>
           </cell>
           <cell r="U131">
             <v>5</v>
@@ -2700,7 +2700,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T132">
-            <v>3340000</v>
+            <v>3972000</v>
           </cell>
           <cell r="U132">
             <v>5</v>
@@ -2887,7 +2887,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T143">
-            <v>420500</v>
+            <v>570500</v>
           </cell>
           <cell r="U143">
             <v>6</v>
@@ -2955,7 +2955,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T147">
-            <v>1749600</v>
+            <v>2589600</v>
           </cell>
           <cell r="U147">
             <v>15</v>
@@ -3029,7 +3029,7 @@
             <v>20</v>
           </cell>
           <cell r="Y151">
-            <v>3000000</v>
+            <v>4000000</v>
           </cell>
           <cell r="Z151">
             <v>0</v>
@@ -3431,7 +3431,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T175">
-            <v>811700</v>
+            <v>961700</v>
           </cell>
           <cell r="U175">
             <v>15</v>
@@ -3448,7 +3448,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T176">
-            <v>3434700</v>
+            <v>3584700</v>
           </cell>
           <cell r="U176">
             <v>15</v>
@@ -3465,7 +3465,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T177">
-            <v>477500</v>
+            <v>627500</v>
           </cell>
           <cell r="U177">
             <v>10</v>
@@ -3482,7 +3482,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T178">
-            <v>811700</v>
+            <v>961700</v>
           </cell>
           <cell r="U178">
             <v>15</v>
@@ -3771,7 +3771,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T195">
-            <v>18535600</v>
+            <v>18601600</v>
           </cell>
           <cell r="U195">
             <v>13</v>
@@ -3788,7 +3788,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T196">
-            <v>9256400</v>
+            <v>9322400</v>
           </cell>
           <cell r="U196">
             <v>30</v>
@@ -3992,7 +3992,7 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T208">
-            <v>58000</v>
+            <v>562000</v>
           </cell>
           <cell r="U208">
             <v>0</v>
@@ -4009,7 +4009,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T209">
-            <v>883000</v>
+            <v>1245000</v>
           </cell>
           <cell r="U209">
             <v>9</v>
@@ -4026,7 +4026,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T210">
-            <v>865000</v>
+            <v>1033000</v>
           </cell>
           <cell r="U210">
             <v>5</v>
@@ -4077,7 +4077,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T213">
-            <v>1104000</v>
+            <v>1272000</v>
           </cell>
           <cell r="U213">
             <v>8</v>
@@ -4349,7 +4349,7 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T229">
-            <v>190000</v>
+            <v>718000</v>
           </cell>
           <cell r="U229">
             <v>0</v>
@@ -4366,7 +4366,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T230">
-            <v>684000</v>
+            <v>1234000</v>
           </cell>
           <cell r="U230">
             <v>0</v>
@@ -4383,7 +4383,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T231">
-            <v>84000</v>
+            <v>234000</v>
           </cell>
           <cell r="U231">
             <v>0</v>
@@ -4400,7 +4400,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T232">
-            <v>134600</v>
+            <v>284600</v>
           </cell>
           <cell r="U232">
             <v>0</v>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="I6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$T:$T)</f>
-        <v>76925900</v>
+        <v>77123900</v>
       </c>
       <c r="J6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$U:$U)</f>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="M6" s="17">
         <f>K6+I6</f>
-        <v>83725900</v>
+        <v>83923900</v>
       </c>
       <c r="N6" s="17">
         <f>L6+J6</f>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="O6" s="19">
         <f t="shared" ref="O6:T11" si="0">I6/C6</f>
-        <v>0.52562805666411394</v>
+        <v>0.52698097362991481</v>
       </c>
       <c r="P6" s="19">
         <f t="shared" si="0"/>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="S6" s="19">
         <f t="shared" si="0"/>
-        <v>0.50579715847207596</v>
+        <v>0.50699329774770596</v>
       </c>
       <c r="T6" s="19">
         <f t="shared" si="0"/>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="I7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$T:$T)</f>
-        <v>38109100</v>
+        <v>40009100</v>
       </c>
       <c r="J7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$U:$U)</f>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="K7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Y:$Y)</f>
-        <v>16120000</v>
+        <v>17120000</v>
       </c>
       <c r="L7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Z:$Z)</f>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="M7" s="17">
         <f t="shared" ref="M7:N11" si="2">K7+I7</f>
-        <v>54229100</v>
+        <v>57129100</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" si="2"/>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="O7" s="19">
         <f t="shared" si="0"/>
-        <v>0.55529240877953645</v>
+        <v>0.5829775437389324</v>
       </c>
       <c r="P7" s="19">
         <f t="shared" si="0"/>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Q7" s="19">
         <f t="shared" si="0"/>
-        <v>1.138249194318955</v>
+        <v>1.2088601865223643</v>
       </c>
       <c r="R7" s="19">
         <f t="shared" si="0"/>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="S7" s="19">
         <f t="shared" si="0"/>
-        <v>0.65501211315415153</v>
+        <v>0.69004008020776364</v>
       </c>
       <c r="T7" s="19">
         <f t="shared" si="0"/>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="I8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$T:$T)</f>
-        <v>24258600</v>
+        <v>25994600</v>
       </c>
       <c r="J8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$U:$U)</f>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="M8" s="17">
         <f t="shared" si="2"/>
-        <v>26208600</v>
+        <v>27944600</v>
       </c>
       <c r="N8" s="17">
         <f t="shared" si="2"/>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O8" s="19">
         <f t="shared" si="0"/>
-        <v>0.26052814769749461</v>
+        <v>0.27917212815814979</v>
       </c>
       <c r="P8" s="19">
         <f t="shared" si="0"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="S8" s="19">
         <f t="shared" si="0"/>
-        <v>0.26936672755553526</v>
+        <v>0.28720898692980207</v>
       </c>
       <c r="T8" s="19">
         <f t="shared" si="0"/>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$T:$T)</f>
-        <v>124158400</v>
+        <v>137628400</v>
       </c>
       <c r="J9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$U:$U)</f>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="M9" s="17">
         <f t="shared" si="2"/>
-        <v>124158400</v>
+        <v>137628400</v>
       </c>
       <c r="N9" s="17">
         <f t="shared" si="2"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O9" s="19">
         <f t="shared" si="0"/>
-        <v>0.40496921337470271</v>
+        <v>0.44890450332815929</v>
       </c>
       <c r="P9" s="19">
         <f t="shared" si="0"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="S9" s="19">
         <f t="shared" si="0"/>
-        <v>0.38271564930739776</v>
+        <v>0.42423664020427343</v>
       </c>
       <c r="T9" s="19">
         <f t="shared" si="0"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="I10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$T:$T)</f>
-        <v>55483200</v>
+        <v>60915200</v>
       </c>
       <c r="J10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$U:$U)</f>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="M10" s="17">
         <f t="shared" si="2"/>
-        <v>61733200</v>
+        <v>67165200</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="2"/>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="O10" s="19">
         <f t="shared" si="0"/>
-        <v>0.44712362903273351</v>
+        <v>0.49089860150919135</v>
       </c>
       <c r="P10" s="19">
         <f t="shared" si="0"/>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="S10" s="19">
         <f t="shared" si="0"/>
-        <v>0.39421806446967556</v>
+        <v>0.42890592329117316</v>
       </c>
       <c r="T10" s="19">
         <f t="shared" si="0"/>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="I11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$T:$T)</f>
-        <v>64813100</v>
+        <v>66141100</v>
       </c>
       <c r="J11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$U:$U)</f>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="M11" s="17">
         <f t="shared" si="2"/>
-        <v>79143100</v>
+        <v>80471100</v>
       </c>
       <c r="N11" s="17">
         <f t="shared" si="2"/>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="O11" s="19">
         <f t="shared" si="0"/>
-        <v>0.2498657792279261</v>
+        <v>0.25498545032550801</v>
       </c>
       <c r="P11" s="19">
         <f t="shared" si="0"/>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="S11" s="19">
         <f t="shared" si="0"/>
-        <v>0.26648477453052166</v>
+        <v>0.27095631760346839</v>
       </c>
       <c r="T11" s="19">
         <f t="shared" si="0"/>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="I12" s="23">
         <f t="shared" si="3"/>
-        <v>383748300</v>
+        <v>407812300</v>
       </c>
       <c r="J12" s="23">
         <f t="shared" si="3"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>45450000</v>
+        <v>46450000</v>
       </c>
       <c r="L12" s="23">
         <f t="shared" si="3"/>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="M12" s="23">
         <f t="shared" si="3"/>
-        <v>429198300</v>
+        <v>454262300</v>
       </c>
       <c r="N12" s="23">
         <f t="shared" si="3"/>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="O12" s="24">
         <f>AVERAGE(O6:O11)</f>
-        <v>0.40723453912941787</v>
+        <v>0.43065320011497593</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ref="P12:T12" si="4">AVERAGE(P6:P11)</f>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="4"/>
-        <v>0.42203678684465967</v>
+        <v>0.4338052855452279</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="4"/>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="S12" s="24">
         <f t="shared" si="4"/>
-        <v>0.41226574791489295</v>
+        <v>0.43472354099736443</v>
       </c>
       <c r="T12" s="24">
         <f t="shared" si="4"/>

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -533,16 +533,16 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="T4">
-            <v>407812300</v>
+            <v>441167300</v>
           </cell>
           <cell r="U4">
-            <v>1675</v>
+            <v>1720</v>
           </cell>
           <cell r="Y4">
-            <v>46450000</v>
+            <v>76950000</v>
           </cell>
           <cell r="Z4">
-            <v>6</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="5">
@@ -575,7 +575,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T7">
-            <v>3420500</v>
+            <v>4410500</v>
           </cell>
           <cell r="U7">
             <v>31</v>
@@ -864,7 +864,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T24">
-            <v>1172000</v>
+            <v>1832000</v>
           </cell>
           <cell r="U24">
             <v>9</v>
@@ -1221,7 +1221,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T45">
-            <v>3254000</v>
+            <v>3488000</v>
           </cell>
           <cell r="U45">
             <v>10</v>
@@ -1238,13 +1238,13 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T46">
-            <v>695600</v>
+            <v>1029600</v>
           </cell>
           <cell r="U46">
             <v>7</v>
           </cell>
           <cell r="Y46">
-            <v>200000</v>
+            <v>300000</v>
           </cell>
           <cell r="Z46">
             <v>1</v>
@@ -1289,7 +1289,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T49">
-            <v>3021000</v>
+            <v>3153000</v>
           </cell>
           <cell r="U49">
             <v>20</v>
@@ -1374,7 +1374,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T54">
-            <v>1188500</v>
+            <v>1590500</v>
           </cell>
           <cell r="U54">
             <v>7</v>
@@ -1408,7 +1408,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T56">
-            <v>1320000</v>
+            <v>1742000</v>
           </cell>
           <cell r="U56">
             <v>5</v>
@@ -1425,7 +1425,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T57">
-            <v>1523200</v>
+            <v>1655200</v>
           </cell>
           <cell r="U57">
             <v>20</v>
@@ -1510,7 +1510,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T62">
-            <v>8823000</v>
+            <v>9823000</v>
           </cell>
           <cell r="U62">
             <v>5</v>
@@ -1544,7 +1544,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T64">
-            <v>817000</v>
+            <v>949000</v>
           </cell>
           <cell r="U64">
             <v>0</v>
@@ -1652,7 +1652,7 @@
             <v>10</v>
           </cell>
           <cell r="Y70">
-            <v>3720000</v>
+            <v>4120000</v>
           </cell>
           <cell r="Z70">
             <v>0</v>
@@ -1680,7 +1680,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T72">
-            <v>1359500</v>
+            <v>1664300</v>
           </cell>
           <cell r="U72">
             <v>7</v>
@@ -1731,7 +1731,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T75">
-            <v>735400</v>
+            <v>867400</v>
           </cell>
           <cell r="U75">
             <v>5</v>
@@ -1748,7 +1748,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T76">
-            <v>234000</v>
+            <v>366000</v>
           </cell>
           <cell r="U76">
             <v>5</v>
@@ -1771,7 +1771,7 @@
             <v/>
           </cell>
           <cell r="Y77">
-            <v>0</v>
+            <v>5000000</v>
           </cell>
           <cell r="Z77">
             <v>0</v>
@@ -1884,7 +1884,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T84">
-            <v>720000</v>
+            <v>852000</v>
           </cell>
           <cell r="U84">
             <v>5</v>
@@ -2173,7 +2173,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T101">
-            <v>1252700</v>
+            <v>1912700</v>
           </cell>
           <cell r="U101">
             <v>15</v>
@@ -2190,7 +2190,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T102">
-            <v>1574200</v>
+            <v>1706200</v>
           </cell>
           <cell r="U102">
             <v>25</v>
@@ -2207,7 +2207,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T103">
-            <v>1631000</v>
+            <v>1763000</v>
           </cell>
           <cell r="U103">
             <v>5</v>
@@ -2297,11 +2297,11 @@
           <cell r="U108" t="str">
             <v/>
           </cell>
-          <cell r="Y108">
-            <v>2000000</v>
-          </cell>
-          <cell r="Z108">
-            <v>0</v>
+          <cell r="Y108" t="str">
+            <v/>
+          </cell>
+          <cell r="Z108" t="str">
+            <v/>
           </cell>
         </row>
         <row r="109">
@@ -2376,11 +2376,11 @@
           <cell r="A113" t="str">
             <v>DARIANUS</v>
           </cell>
-          <cell r="T113" t="str">
-            <v/>
-          </cell>
-          <cell r="U113" t="str">
-            <v/>
+          <cell r="T113">
+            <v>865000</v>
+          </cell>
+          <cell r="U113">
+            <v>10</v>
           </cell>
           <cell r="Y113" t="str">
             <v/>
@@ -2479,7 +2479,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T119">
-            <v>898200</v>
+            <v>1690200</v>
           </cell>
           <cell r="U119">
             <v>7</v>
@@ -2529,11 +2529,11 @@
           <cell r="A122" t="str">
             <v>APRIANUS</v>
           </cell>
-          <cell r="T122" t="str">
-            <v/>
-          </cell>
-          <cell r="U122" t="str">
-            <v/>
+          <cell r="T122">
+            <v>0</v>
+          </cell>
+          <cell r="U122">
+            <v>0</v>
           </cell>
           <cell r="Y122" t="str">
             <v/>
@@ -2563,11 +2563,11 @@
           <cell r="A124" t="str">
             <v>APRIANUS</v>
           </cell>
-          <cell r="T124" t="str">
-            <v/>
-          </cell>
-          <cell r="U124" t="str">
-            <v/>
+          <cell r="T124">
+            <v>0</v>
+          </cell>
+          <cell r="U124">
+            <v>10</v>
           </cell>
           <cell r="Y124" t="str">
             <v/>
@@ -2580,11 +2580,11 @@
           <cell r="A125" t="str">
             <v>APRIANUS</v>
           </cell>
-          <cell r="T125" t="str">
-            <v/>
-          </cell>
-          <cell r="U125" t="str">
-            <v/>
+          <cell r="T125">
+            <v>0</v>
+          </cell>
+          <cell r="U125">
+            <v>0</v>
           </cell>
           <cell r="Y125" t="str">
             <v/>
@@ -2620,11 +2620,11 @@
           <cell r="U127" t="str">
             <v/>
           </cell>
-          <cell r="Y127">
-            <v>0</v>
-          </cell>
-          <cell r="Z127">
-            <v>0</v>
+          <cell r="Y127" t="str">
+            <v/>
+          </cell>
+          <cell r="Z127" t="str">
+            <v/>
           </cell>
         </row>
         <row r="128">
@@ -2683,7 +2683,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T131">
-            <v>13786000</v>
+            <v>18786000</v>
           </cell>
           <cell r="U131">
             <v>5</v>
@@ -2706,7 +2706,7 @@
             <v>5</v>
           </cell>
           <cell r="Y132">
-            <v>0</v>
+            <v>3000000</v>
           </cell>
           <cell r="Z132">
             <v>0</v>
@@ -2836,7 +2836,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T140">
-            <v>1594400</v>
+            <v>1828400</v>
           </cell>
           <cell r="U140">
             <v>5</v>
@@ -2858,11 +2858,11 @@
           <cell r="U141" t="str">
             <v/>
           </cell>
-          <cell r="Y141">
-            <v>100000</v>
-          </cell>
-          <cell r="Z141">
-            <v>0</v>
+          <cell r="Y141" t="str">
+            <v/>
+          </cell>
+          <cell r="Z141" t="str">
+            <v/>
           </cell>
         </row>
         <row r="142">
@@ -2870,7 +2870,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T142">
-            <v>747400</v>
+            <v>981400</v>
           </cell>
           <cell r="U142">
             <v>10</v>
@@ -2887,7 +2887,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T143">
-            <v>570500</v>
+            <v>804500</v>
           </cell>
           <cell r="U143">
             <v>6</v>
@@ -2926,11 +2926,11 @@
           <cell r="U145" t="str">
             <v/>
           </cell>
-          <cell r="Y145">
-            <v>0</v>
-          </cell>
-          <cell r="Z145">
-            <v>0</v>
+          <cell r="Y145" t="str">
+            <v/>
+          </cell>
+          <cell r="Z145" t="str">
+            <v/>
           </cell>
         </row>
         <row r="146">
@@ -2943,11 +2943,11 @@
           <cell r="U146" t="str">
             <v/>
           </cell>
-          <cell r="Y146">
-            <v>0</v>
-          </cell>
-          <cell r="Z146">
-            <v>1</v>
+          <cell r="Y146" t="str">
+            <v/>
+          </cell>
+          <cell r="Z146" t="str">
+            <v/>
           </cell>
         </row>
         <row r="147">
@@ -2961,7 +2961,7 @@
             <v>15</v>
           </cell>
           <cell r="Y147">
-            <v>0</v>
+            <v>7000000</v>
           </cell>
           <cell r="Z147">
             <v>0</v>
@@ -3023,7 +3023,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T151">
-            <v>4547300</v>
+            <v>5557300</v>
           </cell>
           <cell r="U151">
             <v>20</v>
@@ -3079,11 +3079,11 @@
           <cell r="U154" t="str">
             <v/>
           </cell>
-          <cell r="Y154">
-            <v>2000000</v>
-          </cell>
-          <cell r="Z154">
-            <v>0</v>
+          <cell r="Y154" t="str">
+            <v/>
+          </cell>
+          <cell r="Z154" t="str">
+            <v/>
           </cell>
         </row>
         <row r="155">
@@ -3091,7 +3091,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T155">
-            <v>6752300</v>
+            <v>6986300</v>
           </cell>
           <cell r="U155">
             <v>10</v>
@@ -3142,7 +3142,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T158">
-            <v>1010400</v>
+            <v>2000400</v>
           </cell>
           <cell r="U158">
             <v>5</v>
@@ -3159,7 +3159,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T159">
-            <v>3906000</v>
+            <v>5896000</v>
           </cell>
           <cell r="U159">
             <v>12</v>
@@ -3176,7 +3176,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T160">
-            <v>1135000</v>
+            <v>2125000</v>
           </cell>
           <cell r="U160">
             <v>5</v>
@@ -3193,13 +3193,13 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T161">
-            <v>4414200</v>
+            <v>5042200</v>
           </cell>
           <cell r="U161">
             <v>5</v>
           </cell>
           <cell r="Y161">
-            <v>2050000</v>
+            <v>2150000</v>
           </cell>
           <cell r="Z161">
             <v>0</v>
@@ -3244,7 +3244,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T164">
-            <v>1654800</v>
+            <v>2314800</v>
           </cell>
           <cell r="U164">
             <v>23</v>
@@ -3396,11 +3396,11 @@
           <cell r="A173" t="str">
             <v>JULAIHA</v>
           </cell>
-          <cell r="T173" t="str">
-            <v/>
-          </cell>
-          <cell r="U173" t="str">
-            <v/>
+          <cell r="T173">
+            <v>0</v>
+          </cell>
+          <cell r="U173">
+            <v>0</v>
           </cell>
           <cell r="Y173" t="str">
             <v/>
@@ -3414,7 +3414,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T174">
-            <v>737000</v>
+            <v>971000</v>
           </cell>
           <cell r="U174">
             <v>5</v>
@@ -3499,7 +3499,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T179">
-            <v>1221000</v>
+            <v>1353000</v>
           </cell>
           <cell r="U179">
             <v>5</v>
@@ -3516,7 +3516,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T180">
-            <v>3075000</v>
+            <v>3150000</v>
           </cell>
           <cell r="U180">
             <v>5</v>
@@ -3533,7 +3533,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T181">
-            <v>1465000</v>
+            <v>1597000</v>
           </cell>
           <cell r="U181">
             <v>5</v>
@@ -3550,7 +3550,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T182">
-            <v>1066000</v>
+            <v>1300000</v>
           </cell>
           <cell r="U182">
             <v>5</v>
@@ -3590,7 +3590,7 @@
             <v/>
           </cell>
           <cell r="Y184">
-            <v>0</v>
+            <v>7000000</v>
           </cell>
           <cell r="Z184">
             <v>0</v>
@@ -3635,7 +3635,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T187">
-            <v>5402000</v>
+            <v>6534000</v>
           </cell>
           <cell r="U187">
             <v>5</v>
@@ -3686,7 +3686,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T190">
-            <v>2134000</v>
+            <v>2266000</v>
           </cell>
           <cell r="U190">
             <v>5</v>
@@ -3736,11 +3736,11 @@
           <cell r="A193" t="str">
             <v>SLAMET HOIRI</v>
           </cell>
-          <cell r="T193" t="str">
-            <v/>
-          </cell>
-          <cell r="U193" t="str">
-            <v/>
+          <cell r="T193">
+            <v>462000</v>
+          </cell>
+          <cell r="U193">
+            <v>7</v>
           </cell>
           <cell r="Y193" t="str">
             <v/>
@@ -3760,7 +3760,7 @@
             <v/>
           </cell>
           <cell r="Y194">
-            <v>0</v>
+            <v>5000000</v>
           </cell>
           <cell r="Z194">
             <v>0</v>
@@ -3804,11 +3804,11 @@
           <cell r="A197" t="str">
             <v>SLAMET HOIRI</v>
           </cell>
-          <cell r="T197" t="str">
-            <v/>
-          </cell>
-          <cell r="U197" t="str">
-            <v/>
+          <cell r="T197">
+            <v>841200</v>
+          </cell>
+          <cell r="U197">
+            <v>8</v>
           </cell>
           <cell r="Y197" t="str">
             <v/>
@@ -3862,7 +3862,7 @@
             <v>10</v>
           </cell>
           <cell r="Y200">
-            <v>1500000</v>
+            <v>2500000</v>
           </cell>
           <cell r="Z200">
             <v>0</v>
@@ -3930,7 +3930,7 @@
             <v/>
           </cell>
           <cell r="Y204">
-            <v>3000000</v>
+            <v>9000000</v>
           </cell>
           <cell r="Z204">
             <v>0</v>
@@ -4042,11 +4042,11 @@
           <cell r="A211" t="str">
             <v>DARIANUS</v>
           </cell>
-          <cell r="T211" t="str">
-            <v/>
-          </cell>
-          <cell r="U211" t="str">
-            <v/>
+          <cell r="T211">
+            <v>720000</v>
+          </cell>
+          <cell r="U211">
+            <v>5</v>
           </cell>
           <cell r="Y211" t="str">
             <v/>
@@ -4196,7 +4196,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T220">
-            <v>1467000</v>
+            <v>1731000</v>
           </cell>
           <cell r="U220">
             <v>5</v>
@@ -4213,7 +4213,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T221">
-            <v>720500</v>
+            <v>852500</v>
           </cell>
           <cell r="U221">
             <v>5</v>
@@ -4230,7 +4230,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T222">
-            <v>1086000</v>
+            <v>1218000</v>
           </cell>
           <cell r="U222">
             <v>5</v>
@@ -4264,7 +4264,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T224">
-            <v>2213000</v>
+            <v>2945000</v>
           </cell>
           <cell r="U224">
             <v>5</v>
@@ -4281,7 +4281,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T225">
-            <v>8521000</v>
+            <v>10351000</v>
           </cell>
           <cell r="U225">
             <v>5</v>
@@ -4298,7 +4298,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T226">
-            <v>3280000</v>
+            <v>3778000</v>
           </cell>
           <cell r="U226">
             <v>5</v>
@@ -4315,7 +4315,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T227">
-            <v>2966000</v>
+            <v>3230000</v>
           </cell>
           <cell r="U227">
             <v>0</v>
@@ -4467,11 +4467,11 @@
           <cell r="A236" t="str">
             <v>EFENDI</v>
           </cell>
-          <cell r="T236" t="str">
-            <v/>
-          </cell>
-          <cell r="U236" t="str">
-            <v/>
+          <cell r="T236">
+            <v>5485000</v>
+          </cell>
+          <cell r="U236">
+            <v>5</v>
           </cell>
           <cell r="Y236" t="str">
             <v/>
@@ -4995,15 +4995,15 @@
       </c>
       <c r="I6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$T:$T)</f>
-        <v>77123900</v>
+        <v>79823100</v>
       </c>
       <c r="J6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$U:$U)</f>
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="K6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$Y:$Y)</f>
-        <v>6800000</v>
+        <v>23800000</v>
       </c>
       <c r="L6" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A6,[1]Sheet1!$Z:$Z)</f>
@@ -5011,23 +5011,23 @@
       </c>
       <c r="M6" s="17">
         <f>K6+I6</f>
-        <v>83923900</v>
+        <v>103623100</v>
       </c>
       <c r="N6" s="17">
         <f>L6+J6</f>
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="O6" s="19">
         <f t="shared" ref="O6:T11" si="0">I6/C6</f>
-        <v>0.52698097362991481</v>
+        <v>0.54542437501420504</v>
       </c>
       <c r="P6" s="19">
         <f t="shared" si="0"/>
-        <v>1.244131455399061</v>
+        <v>1.3145539906103287</v>
       </c>
       <c r="Q6" s="19">
         <f t="shared" si="0"/>
-        <v>0.35449682886089606</v>
+        <v>1.2407389010131362</v>
       </c>
       <c r="R6" s="19">
         <f t="shared" si="0"/>
@@ -5035,11 +5035,11 @@
       </c>
       <c r="S6" s="19">
         <f t="shared" si="0"/>
-        <v>0.50699329774770596</v>
+        <v>0.62599828167947758</v>
       </c>
       <c r="T6" s="19">
         <f t="shared" si="0"/>
-        <v>1.0392156862745099</v>
+        <v>1.0980392156862746</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="14.5">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="I7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$T:$T)</f>
-        <v>40009100</v>
+        <v>43463900</v>
       </c>
       <c r="J7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$U:$U)</f>
@@ -5079,23 +5079,23 @@
       </c>
       <c r="K7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Y:$Y)</f>
-        <v>17120000</v>
+        <v>15120000</v>
       </c>
       <c r="L7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Z:$Z)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" s="17">
         <f t="shared" ref="M7:N11" si="2">K7+I7</f>
-        <v>57129100</v>
+        <v>58583900</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" si="2"/>
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O7" s="19">
         <f t="shared" si="0"/>
-        <v>0.5829775437389324</v>
+        <v>0.63331786176931215</v>
       </c>
       <c r="P7" s="19">
         <f t="shared" si="0"/>
@@ -5103,19 +5103,19 @@
       </c>
       <c r="Q7" s="19">
         <f t="shared" si="0"/>
-        <v>1.2088601865223643</v>
+        <v>1.0676382021155459</v>
       </c>
       <c r="R7" s="19">
         <f t="shared" si="0"/>
-        <v>8.6956521739130432E-2</v>
+        <v>4.3478260869565216E-2</v>
       </c>
       <c r="S7" s="19">
         <f t="shared" si="0"/>
-        <v>0.69004008020776364</v>
+        <v>0.70761204105934816</v>
       </c>
       <c r="T7" s="19">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.99555555555555553</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="14.5">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="J8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$U:$U)</f>
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="K8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Y:$Y)</f>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="N8" s="17">
         <f t="shared" si="2"/>
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="O8" s="19">
         <f t="shared" si="0"/>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="P8" s="19">
         <f t="shared" si="0"/>
-        <v>0.49777777777777776</v>
+        <v>0.54222222222222227</v>
       </c>
       <c r="Q8" s="19">
         <f t="shared" si="0"/>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="T8" s="19">
         <f t="shared" si="0"/>
-        <v>0.48695652173913045</v>
+        <v>0.5304347826086957</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="14.5">
@@ -5223,15 +5223,15 @@
       </c>
       <c r="I9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$T:$T)</f>
-        <v>137628400</v>
+        <v>144324400</v>
       </c>
       <c r="J9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$U:$U)</f>
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="K9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Y:$Y)</f>
-        <v>0</v>
+        <v>7000000</v>
       </c>
       <c r="L9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Z:$Z)</f>
@@ -5239,23 +5239,23 @@
       </c>
       <c r="M9" s="17">
         <f t="shared" si="2"/>
-        <v>137628400</v>
+        <v>151324400</v>
       </c>
       <c r="N9" s="17">
         <f t="shared" si="2"/>
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="O9" s="19">
         <f t="shared" si="0"/>
-        <v>0.44890450332815929</v>
+        <v>0.47074494145201567</v>
       </c>
       <c r="P9" s="19">
         <f t="shared" si="0"/>
-        <v>1.2333333333333334</v>
+        <v>1.2749999999999999</v>
       </c>
       <c r="Q9" s="19">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.39266354751881349</v>
       </c>
       <c r="R9" s="19">
         <f t="shared" si="0"/>
@@ -5263,11 +5263,11 @@
       </c>
       <c r="S9" s="19">
         <f t="shared" si="0"/>
-        <v>0.42423664020427343</v>
+        <v>0.46645427133445971</v>
       </c>
       <c r="T9" s="19">
         <f t="shared" si="0"/>
-        <v>0.99775280898876406</v>
+        <v>1.0314606741573034</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="14.5">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="I10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$T:$T)</f>
-        <v>60915200</v>
+        <v>68615200</v>
       </c>
       <c r="J10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$U:$U)</f>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="K10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Y:$Y)</f>
-        <v>6250000</v>
+        <v>13350000</v>
       </c>
       <c r="L10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Z:$Z)</f>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="M10" s="17">
         <f t="shared" si="2"/>
-        <v>67165200</v>
+        <v>81965200</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="2"/>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="O10" s="19">
         <f t="shared" si="0"/>
-        <v>0.49089860150919135</v>
+        <v>0.55295075321551057</v>
       </c>
       <c r="P10" s="19">
         <f t="shared" si="0"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="Q10" s="19">
         <f t="shared" si="0"/>
-        <v>0.19226386601709686</v>
+        <v>0.41067561781251888</v>
       </c>
       <c r="R10" s="19">
         <f t="shared" si="0"/>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="S10" s="19">
         <f t="shared" si="0"/>
-        <v>0.42890592329117316</v>
+        <v>0.52341628974149812</v>
       </c>
       <c r="T10" s="19">
         <f t="shared" si="0"/>
@@ -5375,15 +5375,15 @@
       </c>
       <c r="I11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$T:$T)</f>
-        <v>66141100</v>
+        <v>78946100</v>
       </c>
       <c r="J11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$U:$U)</f>
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="K11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Y:$Y)</f>
-        <v>14330000</v>
+        <v>15730000</v>
       </c>
       <c r="L11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Z:$Z)</f>
@@ -5391,23 +5391,23 @@
       </c>
       <c r="M11" s="17">
         <f t="shared" si="2"/>
-        <v>80471100</v>
+        <v>94676100</v>
       </c>
       <c r="N11" s="17">
         <f t="shared" si="2"/>
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="O11" s="19">
         <f t="shared" si="0"/>
-        <v>0.25498545032550801</v>
+        <v>0.3043509536421769</v>
       </c>
       <c r="P11" s="19">
         <f t="shared" si="0"/>
-        <v>1.0168067226890756</v>
+        <v>1.0308123249299719</v>
       </c>
       <c r="Q11" s="19">
         <f t="shared" si="0"/>
-        <v>0.38114198807485011</v>
+        <v>0.4183784698127978</v>
       </c>
       <c r="R11" s="19">
         <f t="shared" si="0"/>
@@ -5415,11 +5415,11 @@
       </c>
       <c r="S11" s="19">
         <f t="shared" si="0"/>
-        <v>0.27095631760346839</v>
+        <v>0.3187863397052822</v>
       </c>
       <c r="T11" s="19">
         <f t="shared" si="0"/>
-        <v>0.85116279069767442</v>
+        <v>0.86279069767441863</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="14.5">
@@ -5453,51 +5453,51 @@
       </c>
       <c r="I12" s="23">
         <f t="shared" si="3"/>
-        <v>407812300</v>
+        <v>441167300</v>
       </c>
       <c r="J12" s="23">
         <f t="shared" si="3"/>
-        <v>1675</v>
+        <v>1720</v>
       </c>
       <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>46450000</v>
+        <v>76950000</v>
       </c>
       <c r="L12" s="23">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M12" s="23">
         <f t="shared" si="3"/>
-        <v>454262300</v>
+        <v>518117300</v>
       </c>
       <c r="N12" s="23">
         <f t="shared" si="3"/>
-        <v>1681</v>
+        <v>1725</v>
       </c>
       <c r="O12" s="24">
         <f>AVERAGE(O6:O11)</f>
-        <v>0.43065320011497593</v>
+        <v>0.46432683554189502</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ref="P12:T12" si="4">AVERAGE(P6:P11)</f>
-        <v>1.033148390612511</v>
+        <v>1.0615715987063901</v>
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="4"/>
-        <v>0.4338052855452279</v>
+        <v>0.66602726367816201</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="4"/>
-        <v>2.224786579313083E-2</v>
+        <v>1.5001488981536628E-2</v>
       </c>
       <c r="S12" s="24">
         <f t="shared" si="4"/>
-        <v>0.43472354099736443</v>
+        <v>0.48824603507497794</v>
       </c>
       <c r="T12" s="24">
         <f t="shared" si="4"/>
-        <v>0.83417739808272184</v>
+        <v>0.85804291774641683</v>
       </c>
     </row>
     <row r="13" spans="1:20">

--- a/GAP DAILY KPI DSE.xlsx
+++ b/GAP DAILY KPI DSE.xlsx
@@ -533,13 +533,13 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="T4">
-            <v>441167300</v>
+            <v>444353300</v>
           </cell>
           <cell r="U4">
-            <v>1720</v>
+            <v>1740</v>
           </cell>
           <cell r="Y4">
-            <v>76950000</v>
+            <v>88050000</v>
           </cell>
           <cell r="Z4">
             <v>5</v>
@@ -1073,11 +1073,11 @@
           <cell r="U36">
             <v>28</v>
           </cell>
-          <cell r="Y36" t="str">
-            <v/>
-          </cell>
-          <cell r="Z36" t="str">
-            <v/>
+          <cell r="Y36">
+            <v>400000</v>
+          </cell>
+          <cell r="Z36">
+            <v>0</v>
           </cell>
         </row>
         <row r="37">
@@ -1227,7 +1227,7 @@
             <v>10</v>
           </cell>
           <cell r="Y45">
-            <v>9020000</v>
+            <v>19170000</v>
           </cell>
           <cell r="Z45">
             <v>0</v>
@@ -1669,7 +1669,7 @@
             <v>15</v>
           </cell>
           <cell r="Y71">
-            <v>1650000</v>
+            <v>1800000</v>
           </cell>
           <cell r="Z71">
             <v>0</v>
@@ -1872,11 +1872,11 @@
           <cell r="U83">
             <v>13</v>
           </cell>
-          <cell r="Y83" t="str">
-            <v/>
-          </cell>
-          <cell r="Z83" t="str">
-            <v/>
+          <cell r="Y83">
+            <v>300000</v>
+          </cell>
+          <cell r="Z83">
+            <v>0</v>
           </cell>
         </row>
         <row r="84">
@@ -2382,22 +2382,22 @@
           <cell r="U113">
             <v>10</v>
           </cell>
-          <cell r="Y113" t="str">
-            <v/>
-          </cell>
-          <cell r="Z113" t="str">
-            <v/>
+          <cell r="Y113">
+            <v>0</v>
+          </cell>
+          <cell r="Z113">
+            <v>0</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114" t="str">
-            <v>DARIANUS</v>
-          </cell>
-          <cell r="T114" t="str">
-            <v/>
-          </cell>
-          <cell r="U114" t="str">
-            <v/>
+            <v>URAY ILHAM</v>
+          </cell>
+          <cell r="T114">
+            <v>2290000</v>
+          </cell>
+          <cell r="U114">
+            <v>5</v>
           </cell>
           <cell r="Y114" t="str">
             <v/>
@@ -2411,7 +2411,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T115">
-            <v>2290000</v>
+            <v>1337200</v>
           </cell>
           <cell r="U115">
             <v>5</v>
@@ -2427,34 +2427,34 @@
           <cell r="A116" t="str">
             <v>URAY ILHAM</v>
           </cell>
-          <cell r="T116">
-            <v>1337200</v>
-          </cell>
-          <cell r="U116">
-            <v>5</v>
-          </cell>
-          <cell r="Y116" t="str">
-            <v/>
-          </cell>
-          <cell r="Z116" t="str">
-            <v/>
+          <cell r="T116" t="str">
+            <v/>
+          </cell>
+          <cell r="U116" t="str">
+            <v/>
+          </cell>
+          <cell r="Y116">
+            <v>0</v>
+          </cell>
+          <cell r="Z116">
+            <v>0</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117" t="str">
             <v>URAY ILHAM</v>
           </cell>
-          <cell r="T117" t="str">
-            <v/>
-          </cell>
-          <cell r="U117" t="str">
-            <v/>
-          </cell>
-          <cell r="Y117">
-            <v>0</v>
-          </cell>
-          <cell r="Z117">
-            <v>0</v>
+          <cell r="T117">
+            <v>1195600</v>
+          </cell>
+          <cell r="U117">
+            <v>6</v>
+          </cell>
+          <cell r="Y117" t="str">
+            <v/>
+          </cell>
+          <cell r="Z117" t="str">
+            <v/>
           </cell>
         </row>
         <row r="118">
@@ -2462,10 +2462,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T118">
-            <v>1195600</v>
+            <v>1690200</v>
           </cell>
           <cell r="U118">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="Y118" t="str">
             <v/>
@@ -2476,13 +2476,13 @@
         </row>
         <row r="119">
           <cell r="A119" t="str">
-            <v>URAY ILHAM</v>
+            <v>APRIANUS</v>
           </cell>
           <cell r="T119">
-            <v>1690200</v>
+            <v>84000</v>
           </cell>
           <cell r="U119">
-            <v>7</v>
+            <v>0</v>
           </cell>
           <cell r="Y119" t="str">
             <v/>
@@ -2496,10 +2496,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T120">
-            <v>84000</v>
+            <v>918400</v>
           </cell>
           <cell r="U120">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y120" t="str">
             <v/>
@@ -2513,10 +2513,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T121">
-            <v>918400</v>
+            <v>0</v>
           </cell>
           <cell r="U121">
-            <v>5</v>
+            <v>0</v>
           </cell>
           <cell r="Y121" t="str">
             <v/>
@@ -2550,7 +2550,7 @@
             <v>0</v>
           </cell>
           <cell r="U123">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="Y123" t="str">
             <v/>
@@ -2567,7 +2567,7 @@
             <v>0</v>
           </cell>
           <cell r="U124">
-            <v>10</v>
+            <v>0</v>
           </cell>
           <cell r="Y124" t="str">
             <v/>
@@ -2578,13 +2578,13 @@
         </row>
         <row r="125">
           <cell r="A125" t="str">
-            <v>APRIANUS</v>
+            <v>DARIANUS</v>
           </cell>
           <cell r="T125">
-            <v>0</v>
+            <v>2022000</v>
           </cell>
           <cell r="U125">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y125" t="str">
             <v/>
@@ -2597,11 +2597,11 @@
           <cell r="A126" t="str">
             <v>DARIANUS</v>
           </cell>
-          <cell r="T126">
-            <v>2022000</v>
-          </cell>
-          <cell r="U126">
-            <v>5</v>
+          <cell r="T126" t="str">
+            <v/>
+          </cell>
+          <cell r="U126" t="str">
+            <v/>
           </cell>
           <cell r="Y126" t="str">
             <v/>
@@ -2614,11 +2614,11 @@
           <cell r="A127" t="str">
             <v>DARIANUS</v>
           </cell>
-          <cell r="T127" t="str">
-            <v/>
-          </cell>
-          <cell r="U127" t="str">
-            <v/>
+          <cell r="T127">
+            <v>1612000</v>
+          </cell>
+          <cell r="U127">
+            <v>5</v>
           </cell>
           <cell r="Y127" t="str">
             <v/>
@@ -2632,7 +2632,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T128">
-            <v>1612000</v>
+            <v>2582000</v>
           </cell>
           <cell r="U128">
             <v>5</v>
@@ -2649,7 +2649,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T129">
-            <v>2582000</v>
+            <v>852000</v>
           </cell>
           <cell r="U129">
             <v>5</v>
@@ -2663,19 +2663,19 @@
         </row>
         <row r="130">
           <cell r="A130" t="str">
-            <v>DARIANUS</v>
+            <v>EFENDI</v>
           </cell>
           <cell r="T130">
-            <v>852000</v>
+            <v>18786000</v>
           </cell>
           <cell r="U130">
             <v>5</v>
           </cell>
-          <cell r="Y130" t="str">
-            <v/>
-          </cell>
-          <cell r="Z130" t="str">
-            <v/>
+          <cell r="Y130">
+            <v>7000000</v>
+          </cell>
+          <cell r="Z130">
+            <v>0</v>
           </cell>
         </row>
         <row r="131">
@@ -2683,13 +2683,13 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T131">
-            <v>18786000</v>
+            <v>3972000</v>
           </cell>
           <cell r="U131">
             <v>5</v>
           </cell>
           <cell r="Y131">
-            <v>7000000</v>
+            <v>3000000</v>
           </cell>
           <cell r="Z131">
             <v>0</v>
@@ -2700,13 +2700,13 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T132">
-            <v>3972000</v>
+            <v>450000</v>
           </cell>
           <cell r="U132">
             <v>5</v>
           </cell>
           <cell r="Y132">
-            <v>3000000</v>
+            <v>100000</v>
           </cell>
           <cell r="Z132">
             <v>0</v>
@@ -2716,28 +2716,28 @@
           <cell r="A133" t="str">
             <v>EFENDI</v>
           </cell>
-          <cell r="T133">
-            <v>450000</v>
-          </cell>
-          <cell r="U133">
-            <v>5</v>
-          </cell>
-          <cell r="Y133">
-            <v>100000</v>
-          </cell>
-          <cell r="Z133">
-            <v>0</v>
+          <cell r="T133" t="str">
+            <v/>
+          </cell>
+          <cell r="U133" t="str">
+            <v/>
+          </cell>
+          <cell r="Y133" t="str">
+            <v/>
+          </cell>
+          <cell r="Z133" t="str">
+            <v/>
           </cell>
         </row>
         <row r="134">
           <cell r="A134" t="str">
-            <v>EFENDI</v>
-          </cell>
-          <cell r="T134" t="str">
-            <v/>
-          </cell>
-          <cell r="U134" t="str">
-            <v/>
+            <v>APRIANUS</v>
+          </cell>
+          <cell r="T134">
+            <v>0</v>
+          </cell>
+          <cell r="U134">
+            <v>0</v>
           </cell>
           <cell r="Y134" t="str">
             <v/>
@@ -2751,7 +2751,7 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T135">
-            <v>0</v>
+            <v>1000000</v>
           </cell>
           <cell r="U135">
             <v>0</v>
@@ -2768,10 +2768,10 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T136">
-            <v>1000000</v>
+            <v>1387400</v>
           </cell>
           <cell r="U136">
-            <v>0</v>
+            <v>15</v>
           </cell>
           <cell r="Y136" t="str">
             <v/>
@@ -2785,7 +2785,7 @@
             <v>APRIANUS</v>
           </cell>
           <cell r="T137">
-            <v>1387400</v>
+            <v>1041000</v>
           </cell>
           <cell r="U137">
             <v>15</v>
@@ -2801,45 +2801,45 @@
           <cell r="A138" t="str">
             <v>APRIANUS</v>
           </cell>
-          <cell r="T138">
-            <v>1041000</v>
-          </cell>
-          <cell r="U138">
-            <v>15</v>
-          </cell>
-          <cell r="Y138" t="str">
-            <v/>
-          </cell>
-          <cell r="Z138" t="str">
-            <v/>
+          <cell r="T138" t="str">
+            <v/>
+          </cell>
+          <cell r="U138" t="str">
+            <v/>
+          </cell>
+          <cell r="Y138">
+            <v>0</v>
+          </cell>
+          <cell r="Z138">
+            <v>0</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139" t="str">
-            <v>APRIANUS</v>
-          </cell>
-          <cell r="T139" t="str">
-            <v/>
-          </cell>
-          <cell r="U139" t="str">
-            <v/>
-          </cell>
-          <cell r="Y139">
-            <v>0</v>
-          </cell>
-          <cell r="Z139">
-            <v>0</v>
+            <v>JULAIHA</v>
+          </cell>
+          <cell r="T139">
+            <v>1828400</v>
+          </cell>
+          <cell r="U139">
+            <v>5</v>
+          </cell>
+          <cell r="Y139" t="str">
+            <v/>
+          </cell>
+          <cell r="Z139" t="str">
+            <v/>
           </cell>
         </row>
         <row r="140">
           <cell r="A140" t="str">
             <v>JULAIHA</v>
           </cell>
-          <cell r="T140">
-            <v>1828400</v>
-          </cell>
-          <cell r="U140">
-            <v>5</v>
+          <cell r="T140" t="str">
+            <v/>
+          </cell>
+          <cell r="U140" t="str">
+            <v/>
           </cell>
           <cell r="Y140" t="str">
             <v/>
@@ -2852,11 +2852,11 @@
           <cell r="A141" t="str">
             <v>JULAIHA</v>
           </cell>
-          <cell r="T141" t="str">
-            <v/>
-          </cell>
-          <cell r="U141" t="str">
-            <v/>
+          <cell r="T141">
+            <v>981400</v>
+          </cell>
+          <cell r="U141">
+            <v>10</v>
           </cell>
           <cell r="Y141" t="str">
             <v/>
@@ -2870,10 +2870,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T142">
-            <v>981400</v>
+            <v>804500</v>
           </cell>
           <cell r="U142">
-            <v>10</v>
+            <v>6</v>
           </cell>
           <cell r="Y142" t="str">
             <v/>
@@ -2886,17 +2886,17 @@
           <cell r="A143" t="str">
             <v>JULAIHA</v>
           </cell>
-          <cell r="T143">
-            <v>804500</v>
-          </cell>
-          <cell r="U143">
-            <v>6</v>
-          </cell>
-          <cell r="Y143" t="str">
-            <v/>
-          </cell>
-          <cell r="Z143" t="str">
-            <v/>
+          <cell r="T143" t="str">
+            <v/>
+          </cell>
+          <cell r="U143" t="str">
+            <v/>
+          </cell>
+          <cell r="Y143">
+            <v>0</v>
+          </cell>
+          <cell r="Z143">
+            <v>0</v>
           </cell>
         </row>
         <row r="144">
@@ -2909,11 +2909,11 @@
           <cell r="U144" t="str">
             <v/>
           </cell>
-          <cell r="Y144">
-            <v>0</v>
-          </cell>
-          <cell r="Z144">
-            <v>0</v>
+          <cell r="Y144" t="str">
+            <v/>
+          </cell>
+          <cell r="Z144" t="str">
+            <v/>
           </cell>
         </row>
         <row r="145">
@@ -2935,19 +2935,19 @@
         </row>
         <row r="146">
           <cell r="A146" t="str">
-            <v>JULAIHA</v>
-          </cell>
-          <cell r="T146" t="str">
-            <v/>
-          </cell>
-          <cell r="U146" t="str">
-            <v/>
-          </cell>
-          <cell r="Y146" t="str">
-            <v/>
-          </cell>
-          <cell r="Z146" t="str">
-            <v/>
+            <v>URAY ILHAM</v>
+          </cell>
+          <cell r="T146">
+            <v>2589600</v>
+          </cell>
+          <cell r="U146">
+            <v>15</v>
+          </cell>
+          <cell r="Y146">
+            <v>7000000</v>
+          </cell>
+          <cell r="Z146">
+            <v>0</v>
           </cell>
         </row>
         <row r="147">
@@ -2955,13 +2955,13 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T147">
-            <v>2589600</v>
+            <v>697400</v>
           </cell>
           <cell r="U147">
-            <v>15</v>
+            <v>5</v>
           </cell>
           <cell r="Y147">
-            <v>7000000</v>
+            <v>0</v>
           </cell>
           <cell r="Z147">
             <v>0</v>
@@ -2972,16 +2972,16 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T148">
-            <v>697400</v>
+            <v>1167600</v>
           </cell>
           <cell r="U148">
-            <v>5</v>
-          </cell>
-          <cell r="Y148">
-            <v>0</v>
-          </cell>
-          <cell r="Z148">
-            <v>0</v>
+            <v>15</v>
+          </cell>
+          <cell r="Y148" t="str">
+            <v/>
+          </cell>
+          <cell r="Z148" t="str">
+            <v/>
           </cell>
         </row>
         <row r="149">
@@ -2989,10 +2989,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T149">
-            <v>1167600</v>
+            <v>6366200</v>
           </cell>
           <cell r="U149">
-            <v>15</v>
+            <v>5</v>
           </cell>
           <cell r="Y149" t="str">
             <v/>
@@ -3003,19 +3003,19 @@
         </row>
         <row r="150">
           <cell r="A150" t="str">
-            <v>URAY ILHAM</v>
+            <v>JULAIHA</v>
           </cell>
           <cell r="T150">
-            <v>6366200</v>
+            <v>5557300</v>
           </cell>
           <cell r="U150">
-            <v>5</v>
-          </cell>
-          <cell r="Y150" t="str">
-            <v/>
-          </cell>
-          <cell r="Z150" t="str">
-            <v/>
+            <v>20</v>
+          </cell>
+          <cell r="Y150">
+            <v>4000000</v>
+          </cell>
+          <cell r="Z150">
+            <v>0</v>
           </cell>
         </row>
         <row r="151">
@@ -3023,27 +3023,27 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T151">
-            <v>5557300</v>
+            <v>3310500</v>
           </cell>
           <cell r="U151">
             <v>20</v>
           </cell>
-          <cell r="Y151">
-            <v>4000000</v>
-          </cell>
-          <cell r="Z151">
-            <v>0</v>
+          <cell r="Y151" t="str">
+            <v/>
+          </cell>
+          <cell r="Z151" t="str">
+            <v/>
           </cell>
         </row>
         <row r="152">
           <cell r="A152" t="str">
             <v>JULAIHA</v>
           </cell>
-          <cell r="T152">
-            <v>3310500</v>
-          </cell>
-          <cell r="U152">
-            <v>20</v>
+          <cell r="T152" t="str">
+            <v/>
+          </cell>
+          <cell r="U152" t="str">
+            <v/>
           </cell>
           <cell r="Y152" t="str">
             <v/>
@@ -3073,17 +3073,17 @@
           <cell r="A154" t="str">
             <v>JULAIHA</v>
           </cell>
-          <cell r="T154" t="str">
-            <v/>
-          </cell>
-          <cell r="U154" t="str">
-            <v/>
-          </cell>
-          <cell r="Y154" t="str">
-            <v/>
-          </cell>
-          <cell r="Z154" t="str">
-            <v/>
+          <cell r="T154">
+            <v>6986300</v>
+          </cell>
+          <cell r="U154">
+            <v>10</v>
+          </cell>
+          <cell r="Y154">
+            <v>0</v>
+          </cell>
+          <cell r="Z154">
+            <v>0</v>
           </cell>
         </row>
         <row r="155">
@@ -3091,16 +3091,16 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T155">
-            <v>6986300</v>
+            <v>615500</v>
           </cell>
           <cell r="U155">
-            <v>10</v>
-          </cell>
-          <cell r="Y155">
-            <v>0</v>
-          </cell>
-          <cell r="Z155">
-            <v>0</v>
+            <v>5</v>
+          </cell>
+          <cell r="Y155" t="str">
+            <v/>
+          </cell>
+          <cell r="Z155" t="str">
+            <v/>
           </cell>
         </row>
         <row r="156">
@@ -3108,10 +3108,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T156">
-            <v>615500</v>
+            <v>246500</v>
           </cell>
           <cell r="U156">
-            <v>5</v>
+            <v>4</v>
           </cell>
           <cell r="Y156" t="str">
             <v/>
@@ -3122,13 +3122,13 @@
         </row>
         <row r="157">
           <cell r="A157" t="str">
-            <v>JULAIHA</v>
+            <v>URAY ILHAM</v>
           </cell>
           <cell r="T157">
-            <v>246500</v>
+            <v>2000400</v>
           </cell>
           <cell r="U157">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="Y157" t="str">
             <v/>
@@ -3142,16 +3142,16 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T158">
-            <v>2000400</v>
+            <v>5896000</v>
           </cell>
           <cell r="U158">
-            <v>5</v>
-          </cell>
-          <cell r="Y158" t="str">
-            <v/>
-          </cell>
-          <cell r="Z158" t="str">
-            <v/>
+            <v>12</v>
+          </cell>
+          <cell r="Y158">
+            <v>1000000</v>
+          </cell>
+          <cell r="Z158">
+            <v>0</v>
           </cell>
         </row>
         <row r="159">
@@ -3159,13 +3159,13 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T159">
-            <v>5896000</v>
+            <v>2125000</v>
           </cell>
           <cell r="U159">
-            <v>12</v>
+            <v>5</v>
           </cell>
           <cell r="Y159">
-            <v>1000000</v>
+            <v>0</v>
           </cell>
           <cell r="Z159">
             <v>0</v>
@@ -3176,13 +3176,13 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T160">
-            <v>2125000</v>
+            <v>5042200</v>
           </cell>
           <cell r="U160">
             <v>5</v>
           </cell>
           <cell r="Y160">
-            <v>0</v>
+            <v>2250000</v>
           </cell>
           <cell r="Z160">
             <v>0</v>
@@ -3193,13 +3193,13 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T161">
-            <v>5042200</v>
+            <v>2105900</v>
           </cell>
           <cell r="U161">
             <v>5</v>
           </cell>
           <cell r="Y161">
-            <v>2150000</v>
+            <v>0</v>
           </cell>
           <cell r="Z161">
             <v>0</v>
@@ -3210,13 +3210,13 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T162">
-            <v>2105900</v>
+            <v>1455200</v>
           </cell>
           <cell r="U162">
             <v>5</v>
           </cell>
           <cell r="Y162">
-            <v>0</v>
+            <v>300000</v>
           </cell>
           <cell r="Z162">
             <v>0</v>
@@ -3227,16 +3227,16 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T163">
-            <v>1455200</v>
+            <v>2314800</v>
           </cell>
           <cell r="U163">
-            <v>5</v>
-          </cell>
-          <cell r="Y163">
-            <v>300000</v>
-          </cell>
-          <cell r="Z163">
-            <v>0</v>
+            <v>23</v>
+          </cell>
+          <cell r="Y163" t="str">
+            <v/>
+          </cell>
+          <cell r="Z163" t="str">
+            <v/>
           </cell>
         </row>
         <row r="164">
@@ -3244,10 +3244,10 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T164">
-            <v>2314800</v>
+            <v>1099200</v>
           </cell>
           <cell r="U164">
-            <v>23</v>
+            <v>5</v>
           </cell>
           <cell r="Y164" t="str">
             <v/>
@@ -3261,7 +3261,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T165">
-            <v>1099200</v>
+            <v>1382400</v>
           </cell>
           <cell r="U165">
             <v>5</v>
@@ -3278,7 +3278,7 @@
             <v>URAY ILHAM</v>
           </cell>
           <cell r="T166">
-            <v>1382400</v>
+            <v>1827400</v>
           </cell>
           <cell r="U166">
             <v>5</v>
@@ -3294,11 +3294,11 @@
           <cell r="A167" t="str">
             <v>URAY ILHAM</v>
           </cell>
-          <cell r="T167">
-            <v>1827400</v>
-          </cell>
-          <cell r="U167">
-            <v>5</v>
+          <cell r="T167" t="str">
+            <v/>
+          </cell>
+          <cell r="U167" t="str">
+            <v/>
           </cell>
           <cell r="Y167" t="str">
             <v/>
@@ -3317,11 +3317,11 @@
           <cell r="U168" t="str">
             <v/>
           </cell>
-          <cell r="Y168" t="str">
-            <v/>
-          </cell>
-          <cell r="Z168" t="str">
-            <v/>
+          <cell r="Y168">
+            <v>0</v>
+          </cell>
+          <cell r="Z168">
+            <v>0</v>
           </cell>
         </row>
         <row r="169">
@@ -3343,19 +3343,19 @@
         </row>
         <row r="170">
           <cell r="A170" t="str">
-            <v>URAY ILHAM</v>
-          </cell>
-          <cell r="T170" t="str">
-            <v/>
-          </cell>
-          <cell r="U170" t="str">
-            <v/>
-          </cell>
-          <cell r="Y170">
-            <v>0</v>
-          </cell>
-          <cell r="Z170">
-            <v>0</v>
+            <v>JULAIHA</v>
+          </cell>
+          <cell r="T170">
+            <v>546500</v>
+          </cell>
+          <cell r="U170">
+            <v>5</v>
+          </cell>
+          <cell r="Y170" t="str">
+            <v/>
+          </cell>
+          <cell r="Z170" t="str">
+            <v/>
           </cell>
         </row>
         <row r="171">
@@ -3363,7 +3363,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T171">
-            <v>546500</v>
+            <v>536400</v>
           </cell>
           <cell r="U171">
             <v>5</v>
@@ -3380,10 +3380,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T172">
-            <v>536400</v>
+            <v>0</v>
           </cell>
           <cell r="U172">
-            <v>5</v>
+            <v>0</v>
           </cell>
           <cell r="Y172" t="str">
             <v/>
@@ -3397,10 +3397,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T173">
-            <v>0</v>
+            <v>971000</v>
           </cell>
           <cell r="U173">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y173" t="str">
             <v/>
@@ -3414,16 +3414,16 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T174">
-            <v>971000</v>
+            <v>961700</v>
           </cell>
           <cell r="U174">
-            <v>5</v>
-          </cell>
-          <cell r="Y174" t="str">
-            <v/>
-          </cell>
-          <cell r="Z174" t="str">
-            <v/>
+            <v>15</v>
+          </cell>
+          <cell r="Y174">
+            <v>0</v>
+          </cell>
+          <cell r="Z174">
+            <v>0</v>
           </cell>
         </row>
         <row r="175">
@@ -3431,13 +3431,13 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T175">
-            <v>961700</v>
+            <v>3584700</v>
           </cell>
           <cell r="U175">
             <v>15</v>
           </cell>
           <cell r="Y175">
-            <v>0</v>
+            <v>1300000</v>
           </cell>
           <cell r="Z175">
             <v>0</v>
@@ -3448,16 +3448,16 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T176">
-            <v>3584700</v>
+            <v>627500</v>
           </cell>
           <cell r="U176">
-            <v>15</v>
-          </cell>
-          <cell r="Y176">
-            <v>1300000</v>
-          </cell>
-          <cell r="Z176">
-            <v>0</v>
+            <v>10</v>
+          </cell>
+          <cell r="Y176" t="str">
+            <v/>
+          </cell>
+          <cell r="Z176" t="str">
+            <v/>
           </cell>
         </row>
         <row r="177">
@@ -3465,10 +3465,10 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T177">
-            <v>627500</v>
+            <v>961700</v>
           </cell>
           <cell r="U177">
-            <v>10</v>
+            <v>15</v>
           </cell>
           <cell r="Y177" t="str">
             <v/>
@@ -3479,13 +3479,13 @@
         </row>
         <row r="178">
           <cell r="A178" t="str">
-            <v>JULAIHA</v>
+            <v>DARIANUS</v>
           </cell>
           <cell r="T178">
-            <v>961700</v>
+            <v>1353000</v>
           </cell>
           <cell r="U178">
-            <v>15</v>
+            <v>5</v>
           </cell>
           <cell r="Y178" t="str">
             <v/>
@@ -3499,7 +3499,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T179">
-            <v>1353000</v>
+            <v>3150000</v>
           </cell>
           <cell r="U179">
             <v>5</v>
@@ -3516,7 +3516,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T180">
-            <v>3150000</v>
+            <v>1597000</v>
           </cell>
           <cell r="U180">
             <v>5</v>
@@ -3533,7 +3533,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T181">
-            <v>1597000</v>
+            <v>1300000</v>
           </cell>
           <cell r="U181">
             <v>5</v>
@@ -3550,7 +3550,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T182">
-            <v>1300000</v>
+            <v>921000</v>
           </cell>
           <cell r="U182">
             <v>5</v>
@@ -3566,34 +3566,34 @@
           <cell r="A183" t="str">
             <v>DARIANUS</v>
           </cell>
-          <cell r="T183">
-            <v>921000</v>
-          </cell>
-          <cell r="U183">
-            <v>5</v>
-          </cell>
-          <cell r="Y183" t="str">
-            <v/>
-          </cell>
-          <cell r="Z183" t="str">
-            <v/>
+          <cell r="T183" t="str">
+            <v/>
+          </cell>
+          <cell r="U183" t="str">
+            <v/>
+          </cell>
+          <cell r="Y183">
+            <v>7000000</v>
+          </cell>
+          <cell r="Z183">
+            <v>0</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184" t="str">
-            <v>DARIANUS</v>
-          </cell>
-          <cell r="T184" t="str">
-            <v/>
-          </cell>
-          <cell r="U184" t="str">
-            <v/>
-          </cell>
-          <cell r="Y184">
-            <v>7000000</v>
-          </cell>
-          <cell r="Z184">
-            <v>0</v>
+            <v>SLAMET HOIRI</v>
+          </cell>
+          <cell r="T184">
+            <v>1000000</v>
+          </cell>
+          <cell r="U184">
+            <v>0</v>
+          </cell>
+          <cell r="Y184" t="str">
+            <v/>
+          </cell>
+          <cell r="Z184" t="str">
+            <v/>
           </cell>
         </row>
         <row r="185">
@@ -3601,10 +3601,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T185">
-            <v>1000000</v>
+            <v>2419000</v>
           </cell>
           <cell r="U185">
-            <v>0</v>
+            <v>8</v>
           </cell>
           <cell r="Y185" t="str">
             <v/>
@@ -3618,10 +3618,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T186">
-            <v>2419000</v>
+            <v>6534000</v>
           </cell>
           <cell r="U186">
-            <v>8</v>
+            <v>5</v>
           </cell>
           <cell r="Y186" t="str">
             <v/>
@@ -3635,7 +3635,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T187">
-            <v>6534000</v>
+            <v>403000</v>
           </cell>
           <cell r="U187">
             <v>5</v>
@@ -3652,10 +3652,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T188">
-            <v>403000</v>
+            <v>218400</v>
           </cell>
           <cell r="U188">
-            <v>5</v>
+            <v>0</v>
           </cell>
           <cell r="Y188" t="str">
             <v/>
@@ -3669,10 +3669,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T189">
-            <v>218400</v>
+            <v>2266000</v>
           </cell>
           <cell r="U189">
-            <v>0</v>
+            <v>5</v>
           </cell>
           <cell r="Y189" t="str">
             <v/>
@@ -3686,16 +3686,16 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T190">
-            <v>2266000</v>
+            <v>872400</v>
           </cell>
           <cell r="U190">
-            <v>5</v>
-          </cell>
-          <cell r="Y190" t="str">
-            <v/>
-          </cell>
-          <cell r="Z190" t="str">
-            <v/>
+            <v>3</v>
+          </cell>
+          <cell r="Y190">
+            <v>2300000</v>
+          </cell>
+          <cell r="Z190">
+            <v>0</v>
           </cell>
         </row>
         <row r="191">
@@ -3703,16 +3703,16 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T191">
-            <v>872400</v>
+            <v>0</v>
           </cell>
           <cell r="U191">
-            <v>3</v>
-          </cell>
-          <cell r="Y191">
-            <v>2300000</v>
-          </cell>
-          <cell r="Z191">
-            <v>0</v>
+            <v>0</v>
+          </cell>
+          <cell r="Y191" t="str">
+            <v/>
+          </cell>
+          <cell r="Z191" t="str">
+            <v/>
           </cell>
         </row>
         <row r="192">
@@ -3720,10 +3720,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T192">
-            <v>0</v>
+            <v>462000</v>
           </cell>
           <cell r="U192">
-            <v>0</v>
+            <v>7</v>
           </cell>
           <cell r="Y192" t="str">
             <v/>
@@ -3736,31 +3736,31 @@
           <cell r="A193" t="str">
             <v>SLAMET HOIRI</v>
           </cell>
-          <cell r="T193">
-            <v>462000</v>
-          </cell>
-          <cell r="U193">
-            <v>7</v>
-          </cell>
-          <cell r="Y193" t="str">
-            <v/>
-          </cell>
-          <cell r="Z193" t="str">
-            <v/>
+          <cell r="T193" t="str">
+            <v/>
+          </cell>
+          <cell r="U193" t="str">
+            <v/>
+          </cell>
+          <cell r="Y193">
+            <v>5000000</v>
+          </cell>
+          <cell r="Z193">
+            <v>0</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194" t="str">
             <v>SLAMET HOIRI</v>
           </cell>
-          <cell r="T194" t="str">
-            <v/>
-          </cell>
-          <cell r="U194" t="str">
-            <v/>
+          <cell r="T194">
+            <v>18601600</v>
+          </cell>
+          <cell r="U194">
+            <v>13</v>
           </cell>
           <cell r="Y194">
-            <v>5000000</v>
+            <v>0</v>
           </cell>
           <cell r="Z194">
             <v>0</v>
@@ -3771,16 +3771,16 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T195">
-            <v>18601600</v>
+            <v>9322400</v>
           </cell>
           <cell r="U195">
-            <v>13</v>
-          </cell>
-          <cell r="Y195">
-            <v>0</v>
-          </cell>
-          <cell r="Z195">
-            <v>0</v>
+            <v>30</v>
+          </cell>
+          <cell r="Y195" t="str">
+            <v/>
+          </cell>
+          <cell r="Z195" t="str">
+            <v/>
           </cell>
         </row>
         <row r="196">
@@ -3788,10 +3788,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T196">
-            <v>9322400</v>
+            <v>841200</v>
           </cell>
           <cell r="U196">
-            <v>30</v>
+            <v>8</v>
           </cell>
           <cell r="Y196" t="str">
             <v/>
@@ -3804,11 +3804,11 @@
           <cell r="A197" t="str">
             <v>SLAMET HOIRI</v>
           </cell>
-          <cell r="T197">
-            <v>841200</v>
-          </cell>
-          <cell r="U197">
-            <v>8</v>
+          <cell r="T197" t="str">
+            <v/>
+          </cell>
+          <cell r="U197" t="str">
+            <v/>
           </cell>
           <cell r="Y197" t="str">
             <v/>
@@ -3827,25 +3827,25 @@
           <cell r="U198" t="str">
             <v/>
           </cell>
-          <cell r="Y198" t="str">
-            <v/>
-          </cell>
-          <cell r="Z198" t="str">
-            <v/>
+          <cell r="Y198">
+            <v>0</v>
+          </cell>
+          <cell r="Z198">
+            <v>0</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199" t="str">
             <v>SLAMET HOIRI</v>
           </cell>
-          <cell r="T199" t="str">
-            <v/>
-          </cell>
-          <cell r="U199" t="str">
-            <v/>
+          <cell r="T199">
+            <v>8728900</v>
+          </cell>
+          <cell r="U199">
+            <v>10</v>
           </cell>
           <cell r="Y199">
-            <v>0</v>
+            <v>2500000</v>
           </cell>
           <cell r="Z199">
             <v>0</v>
@@ -3856,16 +3856,16 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T200">
-            <v>8728900</v>
+            <v>428900</v>
           </cell>
           <cell r="U200">
-            <v>10</v>
-          </cell>
-          <cell r="Y200">
-            <v>2500000</v>
-          </cell>
-          <cell r="Z200">
-            <v>0</v>
+            <v>0</v>
+          </cell>
+          <cell r="Y200" t="str">
+            <v/>
+          </cell>
+          <cell r="Z200" t="str">
+            <v/>
           </cell>
         </row>
         <row r="201">
@@ -3873,7 +3873,7 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T201">
-            <v>428900</v>
+            <v>386400</v>
           </cell>
           <cell r="U201">
             <v>0</v>
@@ -3890,10 +3890,10 @@
             <v>SLAMET HOIRI</v>
           </cell>
           <cell r="T202">
-            <v>386400</v>
+            <v>2478500</v>
           </cell>
           <cell r="U202">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="Y202" t="str">
             <v/>
@@ -3906,17 +3906,17 @@
           <cell r="A203" t="str">
             <v>SLAMET HOIRI</v>
           </cell>
-          <cell r="T203">
-            <v>2478500</v>
-          </cell>
-          <cell r="U203">
-            <v>20</v>
-          </cell>
-          <cell r="Y203" t="str">
-            <v/>
-          </cell>
-          <cell r="Z203" t="str">
-            <v/>
+          <cell r="T203" t="str">
+            <v/>
+          </cell>
+          <cell r="U203" t="str">
+            <v/>
+          </cell>
+          <cell r="Y203">
+            <v>9000000</v>
+          </cell>
+          <cell r="Z203">
+            <v>0</v>
           </cell>
         </row>
         <row r="204">
@@ -3930,7 +3930,7 @@
             <v/>
           </cell>
           <cell r="Y204">
-            <v>9000000</v>
+            <v>0</v>
           </cell>
           <cell r="Z204">
             <v>0</v>
@@ -3957,25 +3957,25 @@
           <cell r="A206" t="str">
             <v>SLAMET HOIRI</v>
           </cell>
-          <cell r="T206" t="str">
-            <v/>
-          </cell>
-          <cell r="U206" t="str">
-            <v/>
-          </cell>
-          <cell r="Y206">
-            <v>0</v>
-          </cell>
-          <cell r="Z206">
-            <v>0</v>
+          <cell r="T206">
+            <v>0</v>
+          </cell>
+          <cell r="U206">
+            <v>0</v>
+          </cell>
+          <cell r="Y206" t="str">
+            <v/>
+          </cell>
+          <cell r="Z206" t="str">
+            <v/>
           </cell>
         </row>
         <row r="207">
           <cell r="A207" t="str">
-            <v>SLAMET HOIRI</v>
+            <v>APRIANUS</v>
           </cell>
           <cell r="T207">
-            <v>0</v>
+            <v>562000</v>
           </cell>
           <cell r="U207">
             <v>0</v>
@@ -3989,13 +3989,13 @@
         </row>
         <row r="208">
           <cell r="A208" t="str">
-            <v>APRIANUS</v>
+            <v>DARIANUS</v>
           </cell>
           <cell r="T208">
-            <v>562000</v>
+            <v>1245000</v>
           </cell>
           <cell r="U208">
-            <v>0</v>
+            <v>9</v>
           </cell>
           <cell r="Y208" t="str">
             <v/>
@@ -4009,10 +4009,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T209">
-            <v>1245000</v>
+            <v>1033000</v>
           </cell>
           <cell r="U209">
-            <v>9</v>
+            <v>5</v>
           </cell>
           <cell r="Y209" t="str">
             <v/>
@@ -4026,7 +4026,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T210">
-            <v>1033000</v>
+            <v>720000</v>
           </cell>
           <cell r="U210">
             <v>5</v>
@@ -4043,10 +4043,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T211">
-            <v>720000</v>
+            <v>4349000</v>
           </cell>
           <cell r="U211">
-            <v>5</v>
+            <v>17</v>
           </cell>
           <cell r="Y211" t="str">
             <v/>
@@ -4060,10 +4060,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T212">
-            <v>4349000</v>
+            <v>1272000</v>
           </cell>
           <cell r="U212">
-            <v>17</v>
+            <v>8</v>
           </cell>
           <cell r="Y212" t="str">
             <v/>
@@ -4076,17 +4076,17 @@
           <cell r="A213" t="str">
             <v>DARIANUS</v>
           </cell>
-          <cell r="T213">
-            <v>1272000</v>
-          </cell>
-          <cell r="U213">
-            <v>8</v>
-          </cell>
-          <cell r="Y213" t="str">
-            <v/>
-          </cell>
-          <cell r="Z213" t="str">
-            <v/>
+          <cell r="T213" t="str">
+            <v/>
+          </cell>
+          <cell r="U213" t="str">
+            <v/>
+          </cell>
+          <cell r="Y213">
+            <v>0</v>
+          </cell>
+          <cell r="Z213">
+            <v>0</v>
           </cell>
         </row>
         <row r="214">
@@ -4099,45 +4099,45 @@
           <cell r="U214" t="str">
             <v/>
           </cell>
-          <cell r="Y214" t="str">
-            <v/>
-          </cell>
-          <cell r="Z214" t="str">
-            <v/>
+          <cell r="Y214">
+            <v>0</v>
+          </cell>
+          <cell r="Z214">
+            <v>0</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215" t="str">
             <v>DARIANUS</v>
           </cell>
-          <cell r="T215" t="str">
-            <v/>
-          </cell>
-          <cell r="U215" t="str">
-            <v/>
-          </cell>
-          <cell r="Y215">
-            <v>0</v>
-          </cell>
-          <cell r="Z215">
-            <v>0</v>
+          <cell r="T215">
+            <v>708000</v>
+          </cell>
+          <cell r="U215">
+            <v>8</v>
+          </cell>
+          <cell r="Y215" t="str">
+            <v/>
+          </cell>
+          <cell r="Z215" t="str">
+            <v/>
           </cell>
         </row>
         <row r="216">
           <cell r="A216" t="str">
             <v>DARIANUS</v>
           </cell>
-          <cell r="T216" t="str">
-            <v/>
-          </cell>
-          <cell r="U216" t="str">
-            <v/>
-          </cell>
-          <cell r="Y216">
-            <v>0</v>
-          </cell>
-          <cell r="Z216">
-            <v>0</v>
+          <cell r="T216">
+            <v>741000</v>
+          </cell>
+          <cell r="U216">
+            <v>3</v>
+          </cell>
+          <cell r="Y216" t="str">
+            <v/>
+          </cell>
+          <cell r="Z216" t="str">
+            <v/>
           </cell>
         </row>
         <row r="217">
@@ -4145,10 +4145,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T217">
-            <v>708000</v>
+            <v>1069000</v>
           </cell>
           <cell r="U217">
-            <v>8</v>
+            <v>3</v>
           </cell>
           <cell r="Y217" t="str">
             <v/>
@@ -4162,10 +4162,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T218">
-            <v>741000</v>
+            <v>1731000</v>
           </cell>
           <cell r="U218">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y218" t="str">
             <v/>
@@ -4179,10 +4179,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T219">
-            <v>1069000</v>
+            <v>852500</v>
           </cell>
           <cell r="U219">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="Y219" t="str">
             <v/>
@@ -4196,7 +4196,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T220">
-            <v>1731000</v>
+            <v>1218000</v>
           </cell>
           <cell r="U220">
             <v>5</v>
@@ -4213,10 +4213,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T221">
-            <v>852500</v>
+            <v>1446000</v>
           </cell>
           <cell r="U221">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="Y221" t="str">
             <v/>
@@ -4230,7 +4230,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T222">
-            <v>1218000</v>
+            <v>2945000</v>
           </cell>
           <cell r="U222">
             <v>5</v>
@@ -4247,10 +4247,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T223">
-            <v>1446000</v>
+            <v>10351000</v>
           </cell>
           <cell r="U223">
-            <v>7</v>
+            <v>5</v>
           </cell>
           <cell r="Y223" t="str">
             <v/>
@@ -4264,7 +4264,7 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T224">
-            <v>2945000</v>
+            <v>3778000</v>
           </cell>
           <cell r="U224">
             <v>5</v>
@@ -4281,10 +4281,10 @@
             <v>DARIANUS</v>
           </cell>
           <cell r="T225">
-            <v>10351000</v>
+            <v>3230000</v>
           </cell>
           <cell r="U225">
-            <v>5</v>
+            <v>0</v>
           </cell>
           <cell r="Y225" t="str">
             <v/>
@@ -4295,27 +4295,27 @@
         </row>
         <row r="226">
           <cell r="A226" t="str">
-            <v>DARIANUS</v>
-          </cell>
-          <cell r="T226">
-            <v>3778000</v>
-          </cell>
-          <cell r="U226">
-            <v>5</v>
-          </cell>
-          <cell r="Y226" t="str">
-            <v/>
-          </cell>
-          <cell r="Z226" t="str">
-            <v/>
+            <v>URAY ILHAM</v>
+          </cell>
+          <cell r="T226" t="str">
+            <v/>
+          </cell>
+          <cell r="U226" t="str">
+            <v/>
+          </cell>
+          <cell r="Y226">
+            <v>0</v>
+          </cell>
+          <cell r="Z226">
+            <v>0</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227" t="str">
-            <v>DARIANUS</v>
+            <v>APRIANUS</v>
           </cell>
           <cell r="T227">
-            <v>3230000</v>
+            <v>718000</v>
           </cell>
           <cell r="U227">
             <v>0</v>
@@ -4329,27 +4329,27 @@
         </row>
         <row r="228">
           <cell r="A228" t="str">
-            <v>URAY ILHAM</v>
-          </cell>
-          <cell r="T228" t="str">
-            <v/>
-          </cell>
-          <cell r="U228" t="str">
-            <v/>
-          </cell>
-          <cell r="Y228">
-            <v>0</v>
-          </cell>
-          <cell r="Z228">
-            <v>0</v>
+            <v>JULAIHA</v>
+          </cell>
+          <cell r="T228">
+            <v>1234000</v>
+          </cell>
+          <cell r="U228">
+            <v>0</v>
+          </cell>
+          <cell r="Y228" t="str">
+            <v/>
+          </cell>
+          <cell r="Z228" t="str">
+            <v/>
           </cell>
         </row>
         <row r="229">
           <cell r="A229" t="str">
-            <v>APRIANUS</v>
+            <v>JULAIHA</v>
           </cell>
           <cell r="T229">
-            <v>718000</v>
+            <v>234000</v>
           </cell>
           <cell r="U229">
             <v>0</v>
@@ -4366,7 +4366,7 @@
             <v>JULAIHA</v>
           </cell>
           <cell r="T230">
-            <v>1234000</v>
+            <v>284600</v>
           </cell>
           <cell r="U230">
             <v>0</v>
@@ -4380,13 +4380,13 @@
         </row>
         <row r="231">
           <cell r="A231" t="str">
-            <v>JULAIHA</v>
+            <v>EFENDI</v>
           </cell>
           <cell r="T231">
-            <v>234000</v>
+            <v>2098000</v>
           </cell>
           <cell r="U231">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="Y231" t="str">
             <v/>
@@ -4397,13 +4397,13 @@
         </row>
         <row r="232">
           <cell r="A232" t="str">
-            <v>JULAIHA</v>
+            <v>EFENDI</v>
           </cell>
           <cell r="T232">
-            <v>284600</v>
+            <v>1122000</v>
           </cell>
           <cell r="U232">
-            <v>0</v>
+            <v>15</v>
           </cell>
           <cell r="Y232" t="str">
             <v/>
@@ -4417,7 +4417,7 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T233">
-            <v>2098000</v>
+            <v>1721000</v>
           </cell>
           <cell r="U233">
             <v>10</v>
@@ -4434,10 +4434,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T234">
-            <v>1122000</v>
+            <v>5485000</v>
           </cell>
           <cell r="U234">
-            <v>15</v>
+            <v>5</v>
           </cell>
           <cell r="Y234" t="str">
             <v/>
@@ -4450,17 +4450,17 @@
           <cell r="A235" t="str">
             <v>EFENDI</v>
           </cell>
-          <cell r="T235">
-            <v>1721000</v>
-          </cell>
-          <cell r="U235">
-            <v>10</v>
-          </cell>
-          <cell r="Y235" t="str">
-            <v/>
-          </cell>
-          <cell r="Z235" t="str">
-            <v/>
+          <cell r="T235" t="str">
+            <v/>
+          </cell>
+          <cell r="U235" t="str">
+            <v/>
+          </cell>
+          <cell r="Y235">
+            <v>0</v>
+          </cell>
+          <cell r="Z235">
+            <v>0</v>
           </cell>
         </row>
         <row r="236">
@@ -4468,10 +4468,10 @@
             <v>EFENDI</v>
           </cell>
           <cell r="T236">
-            <v>5485000</v>
+            <v>2316000</v>
           </cell>
           <cell r="U236">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="Y236" t="str">
             <v/>
@@ -4484,11 +4484,11 @@
           <cell r="A237" t="str">
             <v>EFENDI</v>
           </cell>
-          <cell r="T237" t="str">
-            <v/>
-          </cell>
-          <cell r="U237" t="str">
-            <v/>
+          <cell r="T237">
+            <v>870000</v>
+          </cell>
+          <cell r="U237">
+            <v>10</v>
           </cell>
           <cell r="Y237" t="str">
             <v/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="K7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Y:$Y)</f>
-        <v>15120000</v>
+        <v>25270000</v>
       </c>
       <c r="L7" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A7,[1]Sheet1!$Z:$Z)</f>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="M7" s="17">
         <f t="shared" ref="M7:N11" si="2">K7+I7</f>
-        <v>58583900</v>
+        <v>68733900</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" si="2"/>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Q7" s="19">
         <f t="shared" si="0"/>
-        <v>1.0676382021155459</v>
+        <v>1.7843397729801485</v>
       </c>
       <c r="R7" s="19">
         <f t="shared" si="0"/>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="S7" s="19">
         <f t="shared" si="0"/>
-        <v>0.70761204105934816</v>
+        <v>0.83020992574699071</v>
       </c>
       <c r="T7" s="19">
         <f t="shared" si="0"/>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="K8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Y:$Y)</f>
-        <v>1950000</v>
+        <v>2100000</v>
       </c>
       <c r="L8" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A8,[1]Sheet1!$Z:$Z)</f>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="M8" s="17">
         <f t="shared" si="2"/>
-        <v>27944600</v>
+        <v>28094600</v>
       </c>
       <c r="N8" s="17">
         <f t="shared" si="2"/>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="Q8" s="19">
         <f t="shared" si="0"/>
-        <v>0.46606884379616004</v>
+        <v>0.50192029331894161</v>
       </c>
       <c r="R8" s="19">
         <f t="shared" si="0"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="S8" s="19">
         <f t="shared" si="0"/>
-        <v>0.28720898692980207</v>
+        <v>0.28875065680661083</v>
       </c>
       <c r="T8" s="19">
         <f t="shared" si="0"/>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="K9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Y:$Y)</f>
-        <v>7000000</v>
+        <v>7700000</v>
       </c>
       <c r="L9" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A9,[1]Sheet1!$Z:$Z)</f>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="M9" s="17">
         <f t="shared" si="2"/>
-        <v>151324400</v>
+        <v>152024400</v>
       </c>
       <c r="N9" s="17">
         <f t="shared" si="2"/>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Q9" s="19">
         <f t="shared" si="0"/>
-        <v>0.39266354751881349</v>
+        <v>0.43192990227069483</v>
       </c>
       <c r="R9" s="19">
         <f t="shared" si="0"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="S9" s="19">
         <f t="shared" si="0"/>
-        <v>0.46645427133445971</v>
+        <v>0.46861200657037749</v>
       </c>
       <c r="T9" s="19">
         <f t="shared" si="0"/>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="K10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Y:$Y)</f>
-        <v>13350000</v>
+        <v>13450000</v>
       </c>
       <c r="L10" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A10,[1]Sheet1!$Z:$Z)</f>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="M10" s="17">
         <f t="shared" si="2"/>
-        <v>81965200</v>
+        <v>82065200</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="2"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="Q10" s="19">
         <f t="shared" si="0"/>
-        <v>0.41067561781251888</v>
+        <v>0.41375183966879248</v>
       </c>
       <c r="R10" s="19">
         <f t="shared" si="0"/>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="S10" s="19">
         <f t="shared" si="0"/>
-        <v>0.52341628974149812</v>
+        <v>0.5240548732985949</v>
       </c>
       <c r="T10" s="19">
         <f t="shared" si="0"/>
@@ -5375,11 +5375,11 @@
       </c>
       <c r="I11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$T:$T)</f>
-        <v>78946100</v>
+        <v>82132100</v>
       </c>
       <c r="J11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$U:$U)</f>
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="K11" s="18">
         <f>SUMIF([1]Sheet1!$A:$A,A11,[1]Sheet1!$Y:$Y)</f>
@@ -5391,19 +5391,19 @@
       </c>
       <c r="M11" s="17">
         <f t="shared" si="2"/>
-        <v>94676100</v>
+        <v>97862100</v>
       </c>
       <c r="N11" s="17">
         <f t="shared" si="2"/>
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="O11" s="19">
         <f t="shared" si="0"/>
-        <v>0.3043509536421769</v>
+        <v>0.3166335380675504</v>
       </c>
       <c r="P11" s="19">
         <f t="shared" si="0"/>
-        <v>1.0308123249299719</v>
+        <v>1.0868347338935573</v>
       </c>
       <c r="Q11" s="19">
         <f t="shared" si="0"/>
@@ -5415,11 +5415,11 @@
       </c>
       <c r="S11" s="19">
         <f t="shared" si="0"/>
-        <v>0.3187863397052822</v>
+        <v>0.3295140025293849</v>
       </c>
       <c r="T11" s="19">
         <f t="shared" si="0"/>
-        <v>0.86279069767441863</v>
+        <v>0.90930232558139534</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="14.5">
@@ -5453,15 +5453,15 @@
       </c>
       <c r="I12" s="23">
         <f t="shared" si="3"/>
-        <v>441167300</v>
+        <v>444353300</v>
       </c>
       <c r="J12" s="23">
         <f t="shared" si="3"/>
-        <v>1720</v>
+        <v>1740</v>
       </c>
       <c r="K12" s="23">
         <f t="shared" si="3"/>
-        <v>76950000</v>
+        <v>88050000</v>
       </c>
       <c r="L12" s="23">
         <f t="shared" si="3"/>
@@ -5469,23 +5469,23 @@
       </c>
       <c r="M12" s="23">
         <f t="shared" si="3"/>
-        <v>518117300</v>
+        <v>532403300</v>
       </c>
       <c r="N12" s="23">
         <f t="shared" si="3"/>
-        <v>1725</v>
+        <v>1745</v>
       </c>
       <c r="O12" s="24">
         <f>AVERAGE(O6:O11)</f>
-        <v>0.46432683554189502</v>
+        <v>0.466373932946124</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ref="P12:T12" si="4">AVERAGE(P6:P11)</f>
-        <v>1.0615715987063901</v>
+        <v>1.0709086668669876</v>
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="4"/>
-        <v>0.66602726367816201</v>
+        <v>0.79850986317741868</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="4"/>
@@ -5493,11 +5493,11 @@
       </c>
       <c r="S12" s="24">
         <f t="shared" si="4"/>
-        <v>0.48824603507497794</v>
+        <v>0.51118995777190601</v>
       </c>
       <c r="T12" s="24">
         <f t="shared" si="4"/>
-        <v>0.85804291774641683</v>
+        <v>0.86579485573091286</v>
       </c>
     </row>
     <row r="13" spans="1:20">
